--- a/KWI-RoboChallenge_Rangliste.xlsx
+++ b/KWI-RoboChallenge_Rangliste.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8839809D-6D8E-1C45-95ED-1C0E306B47DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A544003A-9FEC-864B-A1ED-E713D30EE779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Linienfolger-Resultate" sheetId="15" r:id="rId1"/>
     <sheet name="Move-it-over-Spielplan" sheetId="11" r:id="rId2"/>
-    <sheet name="Tabelle1" sheetId="17" r:id="rId3"/>
-    <sheet name="Move-it-over-Rangliste" sheetId="14" r:id="rId4"/>
-    <sheet name="RoboBall-Spielplan" sheetId="12" r:id="rId5"/>
-    <sheet name="RoboBall-Rangliste" sheetId="16" r:id="rId6"/>
-    <sheet name="Teams" sheetId="13" r:id="rId7"/>
+    <sheet name="Move-it-over-Rangliste" sheetId="14" r:id="rId3"/>
+    <sheet name="RoboBall-Spielplan" sheetId="12" r:id="rId4"/>
+    <sheet name="RoboBall-Rangliste" sheetId="16" r:id="rId5"/>
+    <sheet name="Teams" sheetId="13" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -64,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="137">
   <si>
     <t>Gruppennummer</t>
   </si>
@@ -481,7 +480,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -563,59 +562,8 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="17">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -634,86 +582,8 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF7273"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF7273"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7C7BFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF83F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF71FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7C7BFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF71FF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF83F"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="32">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -830,269 +700,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thick">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thick">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thick">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="200">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1168,6 +780,7 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1195,482 +808,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="14" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="14" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1679,10 +816,10 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF7273"/>
+      <color rgb="FFFF71FF"/>
       <color rgb="FFFFF83F"/>
       <color rgb="FF7C7BFF"/>
-      <color rgb="FFFF71FF"/>
-      <color rgb="FFFF7273"/>
       <color rgb="FF4142FF"/>
       <color rgb="FF302CFF"/>
       <color rgb="FF3F34FF"/>
@@ -3114,49 +2251,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="27" x14ac:dyDescent="0.35">
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="38"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="29"/>
       <c r="S1" s="5"/>
     </row>
     <row r="2" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
       <c r="I2" s="8"/>
       <c r="J2" s="9"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
+      <c r="O2" s="31"/>
+      <c r="P2" s="31"/>
+      <c r="Q2" s="31"/>
       <c r="R2" s="10"/>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
@@ -3222,10 +2359,10 @@
     </row>
     <row r="4" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="str">
-        <f>IF(E4 &gt; F4, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B4" s="31" t="s">
+        <f t="shared" ref="A4:A13" si="0">IF(E4 &gt; F4, 1, "")</f>
+        <v/>
+      </c>
+      <c r="B4" s="32" t="s">
         <v>125</v>
       </c>
       <c r="C4" s="22" t="s">
@@ -3243,14 +2380,14 @@
         <v>5</v>
       </c>
       <c r="I4" s="7" t="str">
-        <f>IF(F4 &gt; E4, 1, "")</f>
+        <f t="shared" ref="I4:I13" si="1">IF(F4 &gt; E4, 1, "")</f>
         <v/>
       </c>
       <c r="J4" s="18" t="str">
         <f>IF(N4 &gt; O4, 1, "")</f>
         <v/>
       </c>
-      <c r="K4" s="31" t="s">
+      <c r="K4" s="32" t="s">
         <v>125</v>
       </c>
       <c r="L4" s="22" t="s">
@@ -3278,20 +2415,20 @@
         <v>1</v>
       </c>
       <c r="V4">
-        <f>SUMIF(D$4:D$88,U4,E$4:E$88)+SUMIF(G$4:G$88,U4,F$4:F$88)+SUMIF(M$4:M$88,U4,N$4:N$88)+SUMIF(P$4:P$88,U4,O$4:O$88)</f>
+        <f t="shared" ref="V4:V43" si="2">SUMIF(D$4:D$88,U4,E$4:E$88)+SUMIF(G$4:G$88,U4,F$4:F$88)+SUMIF(M$4:M$88,U4,N$4:N$88)+SUMIF(P$4:P$88,U4,O$4:O$88)</f>
         <v>0</v>
       </c>
       <c r="W4">
-        <f>SUMIF(D$4:D$88,U4,A$4:A$88)+SUMIF(G$4:G$88,U4,I$4:I$88)+SUMIF(M$4:M$88,U4,J$4:J$88)+SUMIF(P$4:P$88,U4,R$4:R$88)</f>
+        <f t="shared" ref="W4:W43" si="3">SUMIF(D$4:D$88,U4,A$4:A$88)+SUMIF(G$4:G$88,U4,I$4:I$88)+SUMIF(M$4:M$88,U4,J$4:J$88)+SUMIF(P$4:P$88,U4,R$4:R$88)</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="str">
-        <f>IF(E5 &gt; F5, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B5" s="31"/>
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B5" s="32"/>
       <c r="C5" s="22" t="s">
         <v>14</v>
       </c>
@@ -3307,14 +2444,14 @@
         <v>20</v>
       </c>
       <c r="I5" s="7" t="str">
-        <f>IF(F5 &gt; E5, 1, "")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J5" s="18" t="str">
-        <f t="shared" ref="J5:J13" si="0">IF(N5 &gt; O5, 1, "")</f>
-        <v/>
-      </c>
-      <c r="K5" s="31"/>
+        <f t="shared" ref="J5:J13" si="4">IF(N5 &gt; O5, 1, "")</f>
+        <v/>
+      </c>
+      <c r="K5" s="32"/>
       <c r="L5" s="22" t="s">
         <v>15</v>
       </c>
@@ -3330,7 +2467,7 @@
         <v>13</v>
       </c>
       <c r="R5" t="str">
-        <f t="shared" ref="R5:R13" si="1">IF(O5 &gt; N5, 1, "")</f>
+        <f t="shared" ref="R5:R13" si="5">IF(O5 &gt; N5, 1, "")</f>
         <v/>
       </c>
       <c r="T5" t="s">
@@ -3340,20 +2477,20 @@
         <v>2</v>
       </c>
       <c r="V5">
-        <f>SUMIF(D$4:D$88,U5,E$4:E$88)+SUMIF(G$4:G$88,U5,F$4:F$88)+SUMIF(M$4:M$88,U5,N$4:N$88)+SUMIF(P$4:P$88,U5,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W5">
-        <f>SUMIF(D$4:D$88,U5,A$4:A$88)+SUMIF(G$4:G$88,U5,I$4:I$88)+SUMIF(M$4:M$88,U5,J$4:J$88)+SUMIF(P$4:P$88,U5,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="str">
-        <f>IF(E6 &gt; F6, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B6" s="31"/>
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B6" s="32"/>
       <c r="C6" s="22" t="s">
         <v>15</v>
       </c>
@@ -3369,14 +2506,14 @@
         <v>13</v>
       </c>
       <c r="I6" s="7" t="str">
-        <f>IF(F6 &gt; E6, 1, "")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J6" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K6" s="31"/>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="K6" s="32"/>
       <c r="L6" s="22" t="s">
         <v>17</v>
       </c>
@@ -3392,7 +2529,7 @@
         <v>5</v>
       </c>
       <c r="R6" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T6" t="s">
@@ -3402,20 +2539,20 @@
         <v>3</v>
       </c>
       <c r="V6">
-        <f>SUMIF(D$4:D$88,U6,E$4:E$88)+SUMIF(G$4:G$88,U6,F$4:F$88)+SUMIF(M$4:M$88,U6,N$4:N$88)+SUMIF(P$4:P$88,U6,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W6">
-        <f>SUMIF(D$4:D$88,U6,A$4:A$88)+SUMIF(G$4:G$88,U6,I$4:I$88)+SUMIF(M$4:M$88,U6,J$4:J$88)+SUMIF(P$4:P$88,U6,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="str">
-        <f>IF(E7 &gt; F7, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B7" s="31"/>
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B7" s="32"/>
       <c r="C7" s="22" t="s">
         <v>17</v>
       </c>
@@ -3431,14 +2568,14 @@
         <v>5</v>
       </c>
       <c r="I7" s="7" t="str">
-        <f>IF(F7 &gt; E7, 1, "")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J7" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K7" s="31"/>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="K7" s="32"/>
       <c r="L7" s="22" t="s">
         <v>14</v>
       </c>
@@ -3454,7 +2591,7 @@
         <v>20</v>
       </c>
       <c r="R7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T7" t="s">
@@ -3464,20 +2601,20 @@
         <v>4</v>
       </c>
       <c r="V7">
-        <f>SUMIF(D$4:D$88,U7,E$4:E$88)+SUMIF(G$4:G$88,U7,F$4:F$88)+SUMIF(M$4:M$88,U7,N$4:N$88)+SUMIF(P$4:P$88,U7,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W7">
-        <f>SUMIF(D$4:D$88,U7,A$4:A$88)+SUMIF(G$4:G$88,U7,I$4:I$88)+SUMIF(M$4:M$88,U7,J$4:J$88)+SUMIF(P$4:P$88,U7,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="24" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="str">
-        <f>IF(E8 &gt; F8, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B8" s="32"/>
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B8" s="33"/>
       <c r="C8" s="26" t="s">
         <v>14</v>
       </c>
@@ -3493,14 +2630,14 @@
         <v>4</v>
       </c>
       <c r="I8" s="7" t="str">
-        <f>IF(F8 &gt; E8, 1, "")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J8" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K8" s="32"/>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="K8" s="33"/>
       <c r="L8" s="26" t="s">
         <v>15</v>
       </c>
@@ -3516,7 +2653,7 @@
         <v>4</v>
       </c>
       <c r="R8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T8" t="s">
@@ -3526,20 +2663,20 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <f>SUMIF(D$4:D$88,U8,E$4:E$88)+SUMIF(G$4:G$88,U8,F$4:F$88)+SUMIF(M$4:M$88,U8,N$4:N$88)+SUMIF(P$4:P$88,U8,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W8">
-        <f>SUMIF(D$4:D$88,U8,A$4:A$88)+SUMIF(G$4:G$88,U8,I$4:I$88)+SUMIF(M$4:M$88,U8,J$4:J$88)+SUMIF(P$4:P$88,U8,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="str">
-        <f>IF(E9 &gt; F9, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B9" s="33" t="s">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B9" s="34" t="s">
         <v>126</v>
       </c>
       <c r="C9" s="24" t="s">
@@ -3557,14 +2694,14 @@
         <v>13</v>
       </c>
       <c r="I9" s="7" t="str">
-        <f>IF(F9 &gt; E9, 1, "")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J9" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K9" s="33" t="s">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="K9" s="34" t="s">
         <v>126</v>
       </c>
       <c r="L9" s="24" t="s">
@@ -3582,7 +2719,7 @@
         <v>20</v>
       </c>
       <c r="R9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T9" t="s">
@@ -3592,20 +2729,20 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <f>SUMIF(D$4:D$88,U9,E$4:E$88)+SUMIF(G$4:G$88,U9,F$4:F$88)+SUMIF(M$4:M$88,U9,N$4:N$88)+SUMIF(P$4:P$88,U9,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W9">
-        <f>SUMIF(D$4:D$88,U9,A$4:A$88)+SUMIF(G$4:G$88,U9,I$4:I$88)+SUMIF(M$4:M$88,U9,J$4:J$88)+SUMIF(P$4:P$88,U9,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="str">
-        <f>IF(E10 &gt; F10, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B10" s="34"/>
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B10" s="35"/>
       <c r="C10" s="22" t="s">
         <v>17</v>
       </c>
@@ -3621,14 +2758,14 @@
         <v>5</v>
       </c>
       <c r="I10" s="7" t="str">
-        <f>IF(F10 &gt; E10, 1, "")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J10" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K10" s="34"/>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="K10" s="35"/>
       <c r="L10" s="22" t="s">
         <v>15</v>
       </c>
@@ -3644,7 +2781,7 @@
         <v>13</v>
       </c>
       <c r="R10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T10" t="s">
@@ -3654,20 +2791,20 @@
         <v>14</v>
       </c>
       <c r="V10">
-        <f>SUMIF(D$4:D$88,U10,E$4:E$88)+SUMIF(G$4:G$88,U10,F$4:F$88)+SUMIF(M$4:M$88,U10,N$4:N$88)+SUMIF(P$4:P$88,U10,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W10">
-        <f>SUMIF(D$4:D$88,U10,A$4:A$88)+SUMIF(G$4:G$88,U10,I$4:I$88)+SUMIF(M$4:M$88,U10,J$4:J$88)+SUMIF(P$4:P$88,U10,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="str">
-        <f>IF(E11 &gt; F11, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B11" s="34"/>
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B11" s="35"/>
       <c r="C11" s="22" t="s">
         <v>14</v>
       </c>
@@ -3683,14 +2820,14 @@
         <v>20</v>
       </c>
       <c r="I11" s="7" t="str">
-        <f>IF(F11 &gt; E11, 1, "")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J11" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K11" s="34"/>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="K11" s="35"/>
       <c r="L11" s="22" t="s">
         <v>20</v>
       </c>
@@ -3706,7 +2843,7 @@
         <v>13</v>
       </c>
       <c r="R11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T11" t="s">
@@ -3716,20 +2853,20 @@
         <v>16</v>
       </c>
       <c r="V11">
-        <f>SUMIF(D$4:D$88,U11,E$4:E$88)+SUMIF(G$4:G$88,U11,F$4:F$88)+SUMIF(M$4:M$88,U11,N$4:N$88)+SUMIF(P$4:P$88,U11,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W11">
-        <f>SUMIF(D$4:D$88,U11,A$4:A$88)+SUMIF(G$4:G$88,U11,I$4:I$88)+SUMIF(M$4:M$88,U11,J$4:J$88)+SUMIF(P$4:P$88,U11,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="str">
-        <f>IF(E12 &gt; F12, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B12" s="34"/>
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B12" s="35"/>
       <c r="C12" s="22" t="s">
         <v>15</v>
       </c>
@@ -3745,14 +2882,14 @@
         <v>4</v>
       </c>
       <c r="I12" s="7" t="str">
-        <f>IF(F12 &gt; E12, 1, "")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J12" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K12" s="34"/>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="K12" s="35"/>
       <c r="L12" s="22" t="s">
         <v>13</v>
       </c>
@@ -3768,7 +2905,7 @@
         <v>4</v>
       </c>
       <c r="R12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T12" t="s">
@@ -3778,20 +2915,20 @@
         <v>19</v>
       </c>
       <c r="V12">
-        <f>SUMIF(D$4:D$88,U12,E$4:E$88)+SUMIF(G$4:G$88,U12,F$4:F$88)+SUMIF(M$4:M$88,U12,N$4:N$88)+SUMIF(P$4:P$88,U12,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W12">
-        <f>SUMIF(D$4:D$88,U12,A$4:A$88)+SUMIF(G$4:G$88,U12,I$4:I$88)+SUMIF(M$4:M$88,U12,J$4:J$88)+SUMIF(P$4:P$88,U12,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A13" s="7" t="str">
-        <f>IF(E13 &gt; F13, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B13" s="34"/>
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="B13" s="35"/>
       <c r="C13" s="22" t="s">
         <v>17</v>
       </c>
@@ -3807,14 +2944,14 @@
         <v>5</v>
       </c>
       <c r="I13" s="7" t="str">
-        <f>IF(F13 &gt; E13, 1, "")</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="J13" s="18" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="K13" s="34"/>
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="K13" s="35"/>
       <c r="L13" s="22" t="s">
         <v>4</v>
       </c>
@@ -3830,7 +2967,7 @@
         <v>20</v>
       </c>
       <c r="R13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="T13" t="s">
@@ -3840,11 +2977,11 @@
         <v>21</v>
       </c>
       <c r="V13">
-        <f>SUMIF(D$4:D$88,U13,E$4:E$88)+SUMIF(G$4:G$88,U13,F$4:F$88)+SUMIF(M$4:M$88,U13,N$4:N$88)+SUMIF(P$4:P$88,U13,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W13">
-        <f>SUMIF(D$4:D$88,U13,A$4:A$88)+SUMIF(G$4:G$88,U13,I$4:I$88)+SUMIF(M$4:M$88,U13,J$4:J$88)+SUMIF(P$4:P$88,U13,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3874,11 +3011,11 @@
         <v>26</v>
       </c>
       <c r="V14">
-        <f>SUMIF(D$4:D$88,U14,E$4:E$88)+SUMIF(G$4:G$88,U14,F$4:F$88)+SUMIF(M$4:M$88,U14,N$4:N$88)+SUMIF(P$4:P$88,U14,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W14">
-        <f>SUMIF(D$4:D$88,U14,A$4:A$88)+SUMIF(G$4:G$88,U14,I$4:I$88)+SUMIF(M$4:M$88,U14,J$4:J$88)+SUMIF(P$4:P$88,U14,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -3908,34 +3045,34 @@
         <v>28</v>
       </c>
       <c r="V15">
-        <f>SUMIF(D$4:D$88,U15,E$4:E$88)+SUMIF(G$4:G$88,U15,F$4:F$88)+SUMIF(M$4:M$88,U15,N$4:N$88)+SUMIF(P$4:P$88,U15,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W15">
-        <f>SUMIF(D$4:D$88,U15,A$4:A$88)+SUMIF(G$4:G$88,U15,I$4:I$88)+SUMIF(M$4:M$88,U15,J$4:J$88)+SUMIF(P$4:P$88,U15,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="27" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29"/>
-      <c r="F16" s="29"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="29"/>
-      <c r="J16" s="29"/>
-      <c r="K16" s="29"/>
-      <c r="L16" s="29"/>
-      <c r="M16" s="29"/>
-      <c r="N16" s="29"/>
-      <c r="O16" s="29"/>
-      <c r="P16" s="29"/>
-      <c r="Q16" s="29"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="30"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="30"/>
+      <c r="O16" s="30"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="30"/>
       <c r="R16" s="5"/>
       <c r="T16" t="s">
         <v>20</v>
@@ -3944,36 +3081,36 @@
         <v>31</v>
       </c>
       <c r="V16">
-        <f>SUMIF(D$4:D$88,U16,E$4:E$88)+SUMIF(G$4:G$88,U16,F$4:F$88)+SUMIF(M$4:M$88,U16,N$4:N$88)+SUMIF(P$4:P$88,U16,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W16">
-        <f>SUMIF(D$4:D$88,U16,A$4:A$88)+SUMIF(G$4:G$88,U16,I$4:I$88)+SUMIF(M$4:M$88,U16,J$4:J$88)+SUMIF(P$4:P$88,U16,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
       <c r="I17" s="8"/>
       <c r="J17" s="9"/>
-      <c r="K17" s="30" t="s">
+      <c r="K17" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="30"/>
-      <c r="M17" s="30"/>
-      <c r="N17" s="30"/>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="31"/>
+      <c r="Q17" s="31"/>
       <c r="R17" s="10"/>
       <c r="T17" t="s">
         <v>20</v>
@@ -3982,11 +3119,11 @@
         <v>33</v>
       </c>
       <c r="V17">
-        <f>SUMIF(D$4:D$88,U17,E$4:E$88)+SUMIF(G$4:G$88,U17,F$4:F$88)+SUMIF(M$4:M$88,U17,N$4:N$88)+SUMIF(P$4:P$88,U17,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W17">
-        <f>SUMIF(D$4:D$88,U17,A$4:A$88)+SUMIF(G$4:G$88,U17,I$4:I$88)+SUMIF(M$4:M$88,U17,J$4:J$88)+SUMIF(P$4:P$88,U17,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4044,20 +3181,20 @@
         <v>34</v>
       </c>
       <c r="V18">
-        <f>SUMIF(D$4:D$88,U18,E$4:E$88)+SUMIF(G$4:G$88,U18,F$4:F$88)+SUMIF(M$4:M$88,U18,N$4:N$88)+SUMIF(P$4:P$88,U18,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W18">
-        <f>SUMIF(D$4:D$88,U18,A$4:A$88)+SUMIF(G$4:G$88,U18,I$4:I$88)+SUMIF(M$4:M$88,U18,J$4:J$88)+SUMIF(P$4:P$88,U18,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="23" x14ac:dyDescent="0.2">
       <c r="A19" s="7" t="str">
-        <f>IF(E19 &gt; F19, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B19" s="31" t="s">
+        <f t="shared" ref="A19:A28" si="6">IF(E19 &gt; F19, 1, "")</f>
+        <v/>
+      </c>
+      <c r="B19" s="32" t="s">
         <v>127</v>
       </c>
       <c r="C19" s="22" t="s">
@@ -4075,14 +3212,14 @@
         <v>14</v>
       </c>
       <c r="I19" s="7" t="str">
-        <f>IF(F19 &gt; E19, 1, "")</f>
+        <f t="shared" ref="I19:I28" si="7">IF(F19 &gt; E19, 1, "")</f>
         <v/>
       </c>
       <c r="J19" s="18" t="str">
-        <f t="shared" ref="J19:J28" si="2">IF(N19 &gt; O19, 1, "")</f>
-        <v/>
-      </c>
-      <c r="K19" s="31" t="s">
+        <f t="shared" ref="J19:J28" si="8">IF(N19 &gt; O19, 1, "")</f>
+        <v/>
+      </c>
+      <c r="K19" s="32" t="s">
         <v>127</v>
       </c>
       <c r="L19" s="22" t="s">
@@ -4100,7 +3237,7 @@
         <v>15</v>
       </c>
       <c r="R19" t="str">
-        <f t="shared" ref="R19:R28" si="3">IF(O19 &gt; N19, 1, "")</f>
+        <f t="shared" ref="R19:R28" si="9">IF(O19 &gt; N19, 1, "")</f>
         <v/>
       </c>
       <c r="T19" t="s">
@@ -4110,20 +3247,20 @@
         <v>37</v>
       </c>
       <c r="V19">
-        <f>SUMIF(D$4:D$88,U19,E$4:E$88)+SUMIF(G$4:G$88,U19,F$4:F$88)+SUMIF(M$4:M$88,U19,N$4:N$88)+SUMIF(P$4:P$88,U19,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W19">
-        <f>SUMIF(D$4:D$88,U19,A$4:A$88)+SUMIF(G$4:G$88,U19,I$4:I$88)+SUMIF(M$4:M$88,U19,J$4:J$88)+SUMIF(P$4:P$88,U19,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A20" s="7" t="str">
-        <f>IF(E20 &gt; F20, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B20" s="31"/>
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B20" s="32"/>
       <c r="C20" s="22" t="s">
         <v>5</v>
       </c>
@@ -4139,14 +3276,14 @@
         <v>20</v>
       </c>
       <c r="I20" s="7" t="str">
-        <f>IF(F20 &gt; E20, 1, "")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J20" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K20" s="31"/>
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K20" s="32"/>
       <c r="L20" s="22" t="s">
         <v>17</v>
       </c>
@@ -4162,7 +3299,7 @@
         <v>14</v>
       </c>
       <c r="R20" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T20" t="s">
@@ -4172,20 +3309,20 @@
         <v>38</v>
       </c>
       <c r="V20">
-        <f>SUMIF(D$4:D$88,U20,E$4:E$88)+SUMIF(G$4:G$88,U20,F$4:F$88)+SUMIF(M$4:M$88,U20,N$4:N$88)+SUMIF(P$4:P$88,U20,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W20">
-        <f>SUMIF(D$4:D$88,U20,A$4:A$88)+SUMIF(G$4:G$88,U20,I$4:I$88)+SUMIF(M$4:M$88,U20,J$4:J$88)+SUMIF(P$4:P$88,U20,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7" t="str">
-        <f>IF(E21 &gt; F21, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B21" s="31"/>
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B21" s="32"/>
       <c r="C21" s="22" t="s">
         <v>15</v>
       </c>
@@ -4201,14 +3338,14 @@
         <v>4</v>
       </c>
       <c r="I21" s="7" t="str">
-        <f>IF(F21 &gt; E21, 1, "")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J21" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K21" s="31"/>
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K21" s="32"/>
       <c r="L21" s="22" t="s">
         <v>5</v>
       </c>
@@ -4224,7 +3361,7 @@
         <v>20</v>
       </c>
       <c r="R21" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T21" t="s">
@@ -4234,20 +3371,20 @@
         <v>40</v>
       </c>
       <c r="V21">
-        <f>SUMIF(D$4:D$88,U21,E$4:E$88)+SUMIF(G$4:G$88,U21,F$4:F$88)+SUMIF(M$4:M$88,U21,N$4:N$88)+SUMIF(P$4:P$88,U21,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W21">
-        <f>SUMIF(D$4:D$88,U21,A$4:A$88)+SUMIF(G$4:G$88,U21,I$4:I$88)+SUMIF(M$4:M$88,U21,J$4:J$88)+SUMIF(P$4:P$88,U21,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="7" t="str">
-        <f>IF(E22 &gt; F22, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B22" s="31"/>
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B22" s="32"/>
       <c r="C22" s="22" t="s">
         <v>13</v>
       </c>
@@ -4263,14 +3400,14 @@
         <v>14</v>
       </c>
       <c r="I22" s="7" t="str">
-        <f>IF(F22 &gt; E22, 1, "")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J22" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K22" s="31"/>
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K22" s="32"/>
       <c r="L22" s="22" t="s">
         <v>15</v>
       </c>
@@ -4286,7 +3423,7 @@
         <v>4</v>
       </c>
       <c r="R22" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T22" t="s">
@@ -4296,20 +3433,20 @@
         <v>43</v>
       </c>
       <c r="V22">
-        <f>SUMIF(D$4:D$88,U22,E$4:E$88)+SUMIF(G$4:G$88,U22,F$4:F$88)+SUMIF(M$4:M$88,U22,N$4:N$88)+SUMIF(P$4:P$88,U22,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W22">
-        <f>SUMIF(D$4:D$88,U22,A$4:A$88)+SUMIF(G$4:G$88,U22,I$4:I$88)+SUMIF(M$4:M$88,U22,J$4:J$88)+SUMIF(P$4:P$88,U22,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="str">
-        <f>IF(E23 &gt; F23, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B23" s="32"/>
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B23" s="33"/>
       <c r="C23" s="26" t="s">
         <v>17</v>
       </c>
@@ -4325,14 +3462,14 @@
         <v>14</v>
       </c>
       <c r="I23" s="7" t="str">
-        <f>IF(F23 &gt; E23, 1, "")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J23" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K23" s="32"/>
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K23" s="33"/>
       <c r="L23" s="26" t="s">
         <v>13</v>
       </c>
@@ -4348,7 +3485,7 @@
         <v>4</v>
       </c>
       <c r="R23" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T23" t="s">
@@ -4358,20 +3495,20 @@
         <v>45</v>
       </c>
       <c r="V23">
-        <f>SUMIF(D$4:D$88,U23,E$4:E$88)+SUMIF(G$4:G$88,U23,F$4:F$88)+SUMIF(M$4:M$88,U23,N$4:N$88)+SUMIF(P$4:P$88,U23,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W23">
-        <f>SUMIF(D$4:D$88,U23,A$4:A$88)+SUMIF(G$4:G$88,U23,I$4:I$88)+SUMIF(M$4:M$88,U23,J$4:J$88)+SUMIF(P$4:P$88,U23,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A24" s="7" t="str">
-        <f>IF(E24 &gt; F24, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B24" s="33" t="s">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B24" s="34" t="s">
         <v>128</v>
       </c>
       <c r="C24" s="24" t="s">
@@ -4389,14 +3526,14 @@
         <v>20</v>
       </c>
       <c r="I24" s="7" t="str">
-        <f>IF(F24 &gt; E24, 1, "")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J24" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K24" s="33" t="s">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K24" s="34" t="s">
         <v>128</v>
       </c>
       <c r="L24" s="24" t="s">
@@ -4414,7 +3551,7 @@
         <v>14</v>
       </c>
       <c r="R24" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T24" t="s">
@@ -4424,20 +3561,20 @@
         <v>47</v>
       </c>
       <c r="V24">
-        <f>SUMIF(D$4:D$88,U24,E$4:E$88)+SUMIF(G$4:G$88,U24,F$4:F$88)+SUMIF(M$4:M$88,U24,N$4:N$88)+SUMIF(P$4:P$88,U24,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W24">
-        <f>SUMIF(D$4:D$88,U24,A$4:A$88)+SUMIF(G$4:G$88,U24,I$4:I$88)+SUMIF(M$4:M$88,U24,J$4:J$88)+SUMIF(P$4:P$88,U24,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A25" s="7" t="str">
-        <f>IF(E25 &gt; F25, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B25" s="34"/>
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B25" s="35"/>
       <c r="C25" s="22" t="s">
         <v>15</v>
       </c>
@@ -4453,14 +3590,14 @@
         <v>4</v>
       </c>
       <c r="I25" s="7" t="str">
-        <f>IF(F25 &gt; E25, 1, "")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J25" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K25" s="34"/>
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K25" s="35"/>
       <c r="L25" s="22" t="s">
         <v>5</v>
       </c>
@@ -4476,7 +3613,7 @@
         <v>20</v>
       </c>
       <c r="R25" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T25" t="s">
@@ -4486,20 +3623,20 @@
         <v>49</v>
       </c>
       <c r="V25">
-        <f>SUMIF(D$4:D$88,U25,E$4:E$88)+SUMIF(G$4:G$88,U25,F$4:F$88)+SUMIF(M$4:M$88,U25,N$4:N$88)+SUMIF(P$4:P$88,U25,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W25">
-        <f>SUMIF(D$4:D$88,U25,A$4:A$88)+SUMIF(G$4:G$88,U25,I$4:I$88)+SUMIF(M$4:M$88,U25,J$4:J$88)+SUMIF(P$4:P$88,U25,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A26" s="7" t="str">
-        <f>IF(E26 &gt; F26, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B26" s="34"/>
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B26" s="35"/>
       <c r="C26" s="22" t="s">
         <v>13</v>
       </c>
@@ -4515,14 +3652,14 @@
         <v>20</v>
       </c>
       <c r="I26" s="7" t="str">
-        <f>IF(F26 &gt; E26, 1, "")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J26" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K26" s="34"/>
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K26" s="35"/>
       <c r="L26" s="22" t="s">
         <v>15</v>
       </c>
@@ -4538,7 +3675,7 @@
         <v>4</v>
       </c>
       <c r="R26" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T26" t="s">
@@ -4548,20 +3685,20 @@
         <v>51</v>
       </c>
       <c r="V26">
-        <f>SUMIF(D$4:D$88,U26,E$4:E$88)+SUMIF(G$4:G$88,U26,F$4:F$88)+SUMIF(M$4:M$88,U26,N$4:N$88)+SUMIF(P$4:P$88,U26,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W26">
-        <f>SUMIF(D$4:D$88,U26,A$4:A$88)+SUMIF(G$4:G$88,U26,I$4:I$88)+SUMIF(M$4:M$88,U26,J$4:J$88)+SUMIF(P$4:P$88,U26,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A27" s="7" t="str">
-        <f>IF(E27 &gt; F27, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B27" s="34"/>
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B27" s="35"/>
       <c r="C27" s="22" t="s">
         <v>17</v>
       </c>
@@ -4577,14 +3714,14 @@
         <v>14</v>
       </c>
       <c r="I27" s="7" t="str">
-        <f>IF(F27 &gt; E27, 1, "")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J27" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K27" s="34"/>
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K27" s="35"/>
       <c r="L27" s="22" t="s">
         <v>15</v>
       </c>
@@ -4600,7 +3737,7 @@
         <v>13</v>
       </c>
       <c r="R27" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T27" t="s">
@@ -4610,20 +3747,20 @@
         <v>52</v>
       </c>
       <c r="V27">
-        <f>SUMIF(D$4:D$88,U27,E$4:E$88)+SUMIF(G$4:G$88,U27,F$4:F$88)+SUMIF(M$4:M$88,U27,N$4:N$88)+SUMIF(P$4:P$88,U27,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W27">
-        <f>SUMIF(D$4:D$88,U27,A$4:A$88)+SUMIF(G$4:G$88,U27,I$4:I$88)+SUMIF(M$4:M$88,U27,J$4:J$88)+SUMIF(P$4:P$88,U27,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A28" s="7" t="str">
-        <f>IF(E28 &gt; F28, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B28" s="34"/>
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="B28" s="35"/>
       <c r="C28" s="22" t="s">
         <v>5</v>
       </c>
@@ -4639,14 +3776,14 @@
         <v>20</v>
       </c>
       <c r="I28" s="7" t="str">
-        <f>IF(F28 &gt; E28, 1, "")</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="J28" s="18" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K28" s="34"/>
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+      <c r="K28" s="35"/>
       <c r="L28" s="22" t="s">
         <v>4</v>
       </c>
@@ -4662,7 +3799,7 @@
         <v>13</v>
       </c>
       <c r="R28" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="T28" t="s">
@@ -4672,11 +3809,11 @@
         <v>55</v>
       </c>
       <c r="V28">
-        <f>SUMIF(D$4:D$88,U28,E$4:E$88)+SUMIF(G$4:G$88,U28,F$4:F$88)+SUMIF(M$4:M$88,U28,N$4:N$88)+SUMIF(P$4:P$88,U28,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W28">
-        <f>SUMIF(D$4:D$88,U28,A$4:A$88)+SUMIF(G$4:G$88,U28,I$4:I$88)+SUMIF(M$4:M$88,U28,J$4:J$88)+SUMIF(P$4:P$88,U28,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4706,11 +3843,11 @@
         <v>59</v>
       </c>
       <c r="V29">
-        <f>SUMIF(D$4:D$88,U29,E$4:E$88)+SUMIF(G$4:G$88,U29,F$4:F$88)+SUMIF(M$4:M$88,U29,N$4:N$88)+SUMIF(P$4:P$88,U29,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W29">
-        <f>SUMIF(D$4:D$88,U29,A$4:A$88)+SUMIF(G$4:G$88,U29,I$4:I$88)+SUMIF(M$4:M$88,U29,J$4:J$88)+SUMIF(P$4:P$88,U29,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4740,34 +3877,34 @@
         <v>65</v>
       </c>
       <c r="V30">
-        <f>SUMIF(D$4:D$88,U30,E$4:E$88)+SUMIF(G$4:G$88,U30,F$4:F$88)+SUMIF(M$4:M$88,U30,N$4:N$88)+SUMIF(P$4:P$88,U30,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W30">
-        <f>SUMIF(D$4:D$88,U30,A$4:A$88)+SUMIF(G$4:G$88,U30,I$4:I$88)+SUMIF(M$4:M$88,U30,J$4:J$88)+SUMIF(P$4:P$88,U30,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:23" ht="27" x14ac:dyDescent="0.35">
       <c r="A31" s="6"/>
-      <c r="B31" s="29" t="s">
+      <c r="B31" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="29"/>
-      <c r="M31" s="29"/>
-      <c r="N31" s="29"/>
-      <c r="O31" s="29"/>
-      <c r="P31" s="29"/>
-      <c r="Q31" s="29"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="30"/>
+      <c r="L31" s="30"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
       <c r="R31" s="5"/>
       <c r="T31" t="s">
         <v>4</v>
@@ -4776,36 +3913,36 @@
         <v>63</v>
       </c>
       <c r="V31">
-        <f>SUMIF(D$4:D$88,U31,E$4:E$88)+SUMIF(G$4:G$88,U31,F$4:F$88)+SUMIF(M$4:M$88,U31,N$4:N$88)+SUMIF(P$4:P$88,U31,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W31">
-        <f>SUMIF(D$4:D$88,U31,A$4:A$88)+SUMIF(G$4:G$88,U31,I$4:I$88)+SUMIF(M$4:M$88,U31,J$4:J$88)+SUMIF(P$4:P$88,U31,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A32" s="7"/>
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
       <c r="I32" s="8"/>
       <c r="J32" s="9"/>
-      <c r="K32" s="30" t="s">
+      <c r="K32" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
       <c r="R32" s="10"/>
       <c r="T32" t="s">
         <v>4</v>
@@ -4814,11 +3951,11 @@
         <v>67</v>
       </c>
       <c r="V32">
-        <f>SUMIF(D$4:D$88,U32,E$4:E$88)+SUMIF(G$4:G$88,U32,F$4:F$88)+SUMIF(M$4:M$88,U32,N$4:N$88)+SUMIF(P$4:P$88,U32,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W32">
-        <f>SUMIF(D$4:D$88,U32,A$4:A$88)+SUMIF(G$4:G$88,U32,I$4:I$88)+SUMIF(M$4:M$88,U32,J$4:J$88)+SUMIF(P$4:P$88,U32,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -4876,20 +4013,20 @@
         <v>69</v>
       </c>
       <c r="V33">
-        <f>SUMIF(D$4:D$88,U33,E$4:E$88)+SUMIF(G$4:G$88,U33,F$4:F$88)+SUMIF(M$4:M$88,U33,N$4:N$88)+SUMIF(P$4:P$88,U33,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W33">
-        <f>SUMIF(D$4:D$88,U33,A$4:A$88)+SUMIF(G$4:G$88,U33,I$4:I$88)+SUMIF(M$4:M$88,U33,J$4:J$88)+SUMIF(P$4:P$88,U33,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A34" s="7" t="str">
-        <f>IF(E34 &gt; F34, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B34" s="31" t="s">
+        <f t="shared" ref="A34:A43" si="10">IF(E34 &gt; F34, 1, "")</f>
+        <v/>
+      </c>
+      <c r="B34" s="32" t="s">
         <v>132</v>
       </c>
       <c r="C34" s="22" t="s">
@@ -4907,14 +4044,14 @@
         <v>20</v>
       </c>
       <c r="I34" s="7" t="str">
-        <f>IF(F34 &gt; E34, 1, "")</f>
+        <f t="shared" ref="I34:I43" si="11">IF(F34 &gt; E34, 1, "")</f>
         <v/>
       </c>
       <c r="J34" s="18" t="str">
-        <f t="shared" ref="J34:J43" si="4">IF(N34 &gt; O34, 1, "")</f>
-        <v/>
-      </c>
-      <c r="K34" s="31" t="s">
+        <f t="shared" ref="J34:J43" si="12">IF(N34 &gt; O34, 1, "")</f>
+        <v/>
+      </c>
+      <c r="K34" s="32" t="s">
         <v>132</v>
       </c>
       <c r="L34" s="22" t="s">
@@ -4932,7 +4069,7 @@
         <v>13</v>
       </c>
       <c r="R34" t="str">
-        <f t="shared" ref="R34:R43" si="5">IF(O34 &gt; N34, 1, "")</f>
+        <f t="shared" ref="R34:R43" si="13">IF(O34 &gt; N34, 1, "")</f>
         <v/>
       </c>
       <c r="T34" t="s">
@@ -4942,20 +4079,20 @@
         <v>72</v>
       </c>
       <c r="V34">
-        <f>SUMIF(D$4:D$88,U34,E$4:E$88)+SUMIF(G$4:G$88,U34,F$4:F$88)+SUMIF(M$4:M$88,U34,N$4:N$88)+SUMIF(P$4:P$88,U34,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W34">
-        <f>SUMIF(D$4:D$88,U34,A$4:A$88)+SUMIF(G$4:G$88,U34,I$4:I$88)+SUMIF(M$4:M$88,U34,J$4:J$88)+SUMIF(P$4:P$88,U34,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A35" s="7" t="str">
-        <f>IF(E35 &gt; F35, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B35" s="31"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B35" s="32"/>
       <c r="C35" s="22" t="s">
         <v>5</v>
       </c>
@@ -4971,14 +4108,14 @@
         <v>15</v>
       </c>
       <c r="I35" s="7" t="str">
-        <f>IF(F35 &gt; E35, 1, "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J35" s="18" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K35" s="31"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K35" s="32"/>
       <c r="L35" s="22" t="s">
         <v>4</v>
       </c>
@@ -4994,7 +4131,7 @@
         <v>15</v>
       </c>
       <c r="R35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T35" t="s">
@@ -5004,20 +4141,20 @@
         <v>73</v>
       </c>
       <c r="V35">
-        <f>SUMIF(D$4:D$88,U35,E$4:E$88)+SUMIF(G$4:G$88,U35,F$4:F$88)+SUMIF(M$4:M$88,U35,N$4:N$88)+SUMIF(P$4:P$88,U35,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W35">
-        <f>SUMIF(D$4:D$88,U35,A$4:A$88)+SUMIF(G$4:G$88,U35,I$4:I$88)+SUMIF(M$4:M$88,U35,J$4:J$88)+SUMIF(P$4:P$88,U35,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:23" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7" t="str">
-        <f>IF(E36 &gt; F36, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B36" s="31"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B36" s="32"/>
       <c r="C36" s="22" t="s">
         <v>14</v>
       </c>
@@ -5033,14 +4170,14 @@
         <v>13</v>
       </c>
       <c r="I36" s="7" t="str">
-        <f>IF(F36 &gt; E36, 1, "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J36" s="18" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K36" s="31"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K36" s="32"/>
       <c r="L36" s="22" t="s">
         <v>17</v>
       </c>
@@ -5056,7 +4193,7 @@
         <v>20</v>
       </c>
       <c r="R36" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T36" t="s">
@@ -5066,20 +4203,20 @@
         <v>75</v>
       </c>
       <c r="V36">
-        <f>SUMIF(D$4:D$88,U36,E$4:E$88)+SUMIF(G$4:G$88,U36,F$4:F$88)+SUMIF(M$4:M$88,U36,N$4:N$88)+SUMIF(P$4:P$88,U36,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W36">
-        <f>SUMIF(D$4:D$88,U36,A$4:A$88)+SUMIF(G$4:G$88,U36,I$4:I$88)+SUMIF(M$4:M$88,U36,J$4:J$88)+SUMIF(P$4:P$88,U36,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A37" s="7" t="str">
-        <f>IF(E37 &gt; F37, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B37" s="31"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B37" s="32"/>
       <c r="C37" s="22" t="s">
         <v>4</v>
       </c>
@@ -5095,14 +4232,14 @@
         <v>14</v>
       </c>
       <c r="I37" s="7" t="str">
-        <f>IF(F37 &gt; E37, 1, "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J37" s="18" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K37" s="31"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K37" s="32"/>
       <c r="L37" s="22" t="s">
         <v>5</v>
       </c>
@@ -5118,7 +4255,7 @@
         <v>15</v>
       </c>
       <c r="R37" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T37" t="s">
@@ -5128,20 +4265,20 @@
         <v>78</v>
       </c>
       <c r="V37">
-        <f>SUMIF(D$4:D$88,U37,E$4:E$88)+SUMIF(G$4:G$88,U37,F$4:F$88)+SUMIF(M$4:M$88,U37,N$4:N$88)+SUMIF(P$4:P$88,U37,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W37">
-        <f>SUMIF(D$4:D$88,U37,A$4:A$88)+SUMIF(G$4:G$88,U37,I$4:I$88)+SUMIF(M$4:M$88,U37,J$4:J$88)+SUMIF(P$4:P$88,U37,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:23" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7" t="str">
-        <f>IF(E38 &gt; F38, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B38" s="32"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B38" s="33"/>
       <c r="C38" s="26" t="s">
         <v>17</v>
       </c>
@@ -5157,14 +4294,14 @@
         <v>20</v>
       </c>
       <c r="I38" s="7" t="str">
-        <f>IF(F38 &gt; E38, 1, "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J38" s="18" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K38" s="32"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K38" s="33"/>
       <c r="L38" s="26" t="s">
         <v>14</v>
       </c>
@@ -5180,7 +4317,7 @@
         <v>13</v>
       </c>
       <c r="R38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T38" t="s">
@@ -5190,20 +4327,20 @@
         <v>79</v>
       </c>
       <c r="V38">
-        <f>SUMIF(D$4:D$88,U38,E$4:E$88)+SUMIF(G$4:G$88,U38,F$4:F$88)+SUMIF(M$4:M$88,U38,N$4:N$88)+SUMIF(P$4:P$88,U38,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W38">
-        <f>SUMIF(D$4:D$88,U38,A$4:A$88)+SUMIF(G$4:G$88,U38,I$4:I$88)+SUMIF(M$4:M$88,U38,J$4:J$88)+SUMIF(P$4:P$88,U38,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A39" s="7" t="str">
-        <f>IF(E39 &gt; F39, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B39" s="33" t="s">
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B39" s="34" t="s">
         <v>133</v>
       </c>
       <c r="C39" s="24" t="s">
@@ -5221,14 +4358,14 @@
         <v>15</v>
       </c>
       <c r="I39" s="7" t="str">
-        <f>IF(F39 &gt; E39, 1, "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J39" s="18" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K39" s="33" t="s">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K39" s="34" t="s">
         <v>133</v>
       </c>
       <c r="L39" s="24" t="s">
@@ -5246,7 +4383,7 @@
         <v>13</v>
       </c>
       <c r="R39" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T39" t="s">
@@ -5256,20 +4393,20 @@
         <v>82</v>
       </c>
       <c r="V39">
-        <f>SUMIF(D$4:D$88,U39,E$4:E$88)+SUMIF(G$4:G$88,U39,F$4:F$88)+SUMIF(M$4:M$88,U39,N$4:N$88)+SUMIF(P$4:P$88,U39,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W39">
-        <f>SUMIF(D$4:D$88,U39,A$4:A$88)+SUMIF(G$4:G$88,U39,I$4:I$88)+SUMIF(M$4:M$88,U39,J$4:J$88)+SUMIF(P$4:P$88,U39,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A40" s="7" t="str">
-        <f>IF(E40 &gt; F40, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B40" s="34"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B40" s="35"/>
       <c r="C40" s="22" t="s">
         <v>14</v>
       </c>
@@ -5285,14 +4422,14 @@
         <v>13</v>
       </c>
       <c r="I40" s="7" t="str">
-        <f>IF(F40 &gt; E40, 1, "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J40" s="18" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K40" s="34"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K40" s="35"/>
       <c r="L40" s="22" t="s">
         <v>17</v>
       </c>
@@ -5308,7 +4445,7 @@
         <v>20</v>
       </c>
       <c r="R40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T40" t="s">
@@ -5318,20 +4455,20 @@
         <v>83</v>
       </c>
       <c r="V40">
-        <f>SUMIF(D$4:D$88,U40,E$4:E$88)+SUMIF(G$4:G$88,U40,F$4:F$88)+SUMIF(M$4:M$88,U40,N$4:N$88)+SUMIF(P$4:P$88,U40,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W40">
-        <f>SUMIF(D$4:D$88,U40,A$4:A$88)+SUMIF(G$4:G$88,U40,I$4:I$88)+SUMIF(M$4:M$88,U40,J$4:J$88)+SUMIF(P$4:P$88,U40,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A41" s="7" t="str">
-        <f>IF(E41 &gt; F41, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B41" s="34"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B41" s="35"/>
       <c r="C41" s="22" t="s">
         <v>4</v>
       </c>
@@ -5347,14 +4484,14 @@
         <v>20</v>
       </c>
       <c r="I41" s="7" t="str">
-        <f>IF(F41 &gt; E41, 1, "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J41" s="18" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K41" s="34"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K41" s="35"/>
       <c r="L41" s="22" t="s">
         <v>5</v>
       </c>
@@ -5370,7 +4507,7 @@
         <v>15</v>
       </c>
       <c r="R41" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T41" t="s">
@@ -5380,20 +4517,20 @@
         <v>85</v>
       </c>
       <c r="V41">
-        <f>SUMIF(D$4:D$88,U41,E$4:E$88)+SUMIF(G$4:G$88,U41,F$4:F$88)+SUMIF(M$4:M$88,U41,N$4:N$88)+SUMIF(P$4:P$88,U41,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W41">
-        <f>SUMIF(D$4:D$88,U41,A$4:A$88)+SUMIF(G$4:G$88,U41,I$4:I$88)+SUMIF(M$4:M$88,U41,J$4:J$88)+SUMIF(P$4:P$88,U41,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A42" s="7" t="str">
-        <f>IF(E42 &gt; F42, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B42" s="34"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B42" s="35"/>
       <c r="C42" s="22" t="s">
         <v>17</v>
       </c>
@@ -5409,14 +4546,14 @@
         <v>20</v>
       </c>
       <c r="I42" s="7" t="str">
-        <f>IF(F42 &gt; E42, 1, "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J42" s="18" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K42" s="34"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K42" s="35"/>
       <c r="L42" s="22" t="s">
         <v>14</v>
       </c>
@@ -5432,7 +4569,7 @@
         <v>4</v>
       </c>
       <c r="R42" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T42" t="s">
@@ -5442,20 +4579,20 @@
         <v>88</v>
       </c>
       <c r="V42">
-        <f>SUMIF(D$4:D$88,U42,E$4:E$88)+SUMIF(G$4:G$88,U42,F$4:F$88)+SUMIF(M$4:M$88,U42,N$4:N$88)+SUMIF(P$4:P$88,U42,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W42">
-        <f>SUMIF(D$4:D$88,U42,A$4:A$88)+SUMIF(G$4:G$88,U42,I$4:I$88)+SUMIF(M$4:M$88,U42,J$4:J$88)+SUMIF(P$4:P$88,U42,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A43" s="7" t="str">
-        <f>IF(E43 &gt; F43, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B43" s="34"/>
+        <f t="shared" si="10"/>
+        <v/>
+      </c>
+      <c r="B43" s="35"/>
       <c r="C43" s="22" t="s">
         <v>5</v>
       </c>
@@ -5471,14 +4608,14 @@
         <v>15</v>
       </c>
       <c r="I43" s="7" t="str">
-        <f>IF(F43 &gt; E43, 1, "")</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="J43" s="18" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="K43" s="34"/>
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="K43" s="35"/>
       <c r="L43" s="22" t="s">
         <v>13</v>
       </c>
@@ -5494,7 +4631,7 @@
         <v>4</v>
       </c>
       <c r="R43" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="T43" t="s">
@@ -5504,11 +4641,11 @@
         <v>89</v>
       </c>
       <c r="V43">
-        <f>SUMIF(D$4:D$88,U43,E$4:E$88)+SUMIF(G$4:G$88,U43,F$4:F$88)+SUMIF(M$4:M$88,U43,N$4:N$88)+SUMIF(P$4:P$88,U43,O$4:O$88)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="W43">
-        <f>SUMIF(D$4:D$88,U43,A$4:A$88)+SUMIF(G$4:G$88,U43,I$4:I$88)+SUMIF(M$4:M$88,U43,J$4:J$88)+SUMIF(P$4:P$88,U43,R$4:R$88)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -5554,48 +4691,48 @@
     </row>
     <row r="46" spans="1:23" ht="27" x14ac:dyDescent="0.35">
       <c r="A46" s="6"/>
-      <c r="B46" s="29" t="s">
+      <c r="B46" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
       <c r="R46" s="5"/>
     </row>
     <row r="47" spans="1:23" ht="22" x14ac:dyDescent="0.2">
       <c r="A47" s="7"/>
-      <c r="B47" s="30" t="s">
+      <c r="B47" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C47" s="30"/>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="30"/>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
       <c r="I47" s="8"/>
       <c r="J47" s="9"/>
-      <c r="K47" s="30" t="s">
+      <c r="K47" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="30"/>
-      <c r="Q47" s="30"/>
+      <c r="L47" s="31"/>
+      <c r="M47" s="31"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
       <c r="R47" s="10"/>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.2">
@@ -5648,10 +4785,10 @@
     </row>
     <row r="49" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A49" s="7" t="str">
-        <f>IF(E49 &gt; F49, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B49" s="31" t="s">
+        <f t="shared" ref="A49:A58" si="14">IF(E49 &gt; F49, 1, "")</f>
+        <v/>
+      </c>
+      <c r="B49" s="32" t="s">
         <v>134</v>
       </c>
       <c r="C49" s="22" t="s">
@@ -5669,14 +4806,14 @@
         <v>15</v>
       </c>
       <c r="I49" s="7" t="str">
-        <f>IF(F49 &gt; E49, 1, "")</f>
+        <f t="shared" ref="I49:I58" si="15">IF(F49 &gt; E49, 1, "")</f>
         <v/>
       </c>
       <c r="J49" s="18" t="str">
-        <f t="shared" ref="J49:J58" si="6">IF(N49 &gt; O49, 1, "")</f>
-        <v/>
-      </c>
-      <c r="K49" s="31" t="s">
+        <f t="shared" ref="J49:J58" si="16">IF(N49 &gt; O49, 1, "")</f>
+        <v/>
+      </c>
+      <c r="K49" s="32" t="s">
         <v>134</v>
       </c>
       <c r="L49" s="22" t="s">
@@ -5694,16 +4831,16 @@
         <v>20</v>
       </c>
       <c r="R49" t="str">
-        <f t="shared" ref="R49:R58" si="7">IF(O49 &gt; N49, 1, "")</f>
+        <f t="shared" ref="R49:R58" si="17">IF(O49 &gt; N49, 1, "")</f>
         <v/>
       </c>
     </row>
     <row r="50" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A50" s="7" t="str">
-        <f>IF(E50 &gt; F50, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B50" s="31"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="B50" s="32"/>
       <c r="C50" s="22" t="s">
         <v>5</v>
       </c>
@@ -5719,14 +4856,14 @@
         <v>13</v>
       </c>
       <c r="I50" s="7" t="str">
-        <f>IF(F50 &gt; E50, 1, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J50" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K50" s="31"/>
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="K50" s="32"/>
       <c r="L50" s="22" t="s">
         <v>13</v>
       </c>
@@ -5742,16 +4879,16 @@
         <v>4</v>
       </c>
       <c r="R50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:18" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7" t="str">
-        <f>IF(E51 &gt; F51, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B51" s="31"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="B51" s="32"/>
       <c r="C51" s="22" t="s">
         <v>14</v>
       </c>
@@ -5767,14 +4904,14 @@
         <v>4</v>
       </c>
       <c r="I51" s="7" t="str">
-        <f>IF(F51 &gt; E51, 1, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J51" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K51" s="31"/>
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="K51" s="32"/>
       <c r="L51" s="22" t="s">
         <v>17</v>
       </c>
@@ -5790,16 +4927,16 @@
         <v>15</v>
       </c>
       <c r="R51" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="52" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A52" s="7" t="str">
-        <f>IF(E52 &gt; F52, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B52" s="31"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="B52" s="32"/>
       <c r="C52" s="22" t="s">
         <v>20</v>
       </c>
@@ -5815,14 +4952,14 @@
         <v>14</v>
       </c>
       <c r="I52" s="7" t="str">
-        <f>IF(F52 &gt; E52, 1, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J52" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K52" s="31"/>
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="K52" s="32"/>
       <c r="L52" s="22" t="s">
         <v>5</v>
       </c>
@@ -5838,16 +4975,16 @@
         <v>13</v>
       </c>
       <c r="R52" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:18" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="str">
-        <f>IF(E53 &gt; F53, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B53" s="32"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="B53" s="33"/>
       <c r="C53" s="26" t="s">
         <v>17</v>
       </c>
@@ -5863,14 +5000,14 @@
         <v>15</v>
       </c>
       <c r="I53" s="7" t="str">
-        <f>IF(F53 &gt; E53, 1, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J53" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K53" s="32"/>
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="K53" s="33"/>
       <c r="L53" s="26" t="s">
         <v>14</v>
       </c>
@@ -5886,16 +5023,16 @@
         <v>4</v>
       </c>
       <c r="R53" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="54" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A54" s="7" t="str">
-        <f>IF(E54 &gt; F54, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B54" s="33" t="s">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="B54" s="34" t="s">
         <v>135</v>
       </c>
       <c r="C54" s="24" t="s">
@@ -5913,14 +5050,14 @@
         <v>13</v>
       </c>
       <c r="I54" s="7" t="str">
-        <f>IF(F54 &gt; E54, 1, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J54" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K54" s="33" t="s">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="K54" s="34" t="s">
         <v>135</v>
       </c>
       <c r="L54" s="24" t="s">
@@ -5938,16 +5075,16 @@
         <v>4</v>
       </c>
       <c r="R54" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="55" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A55" s="7" t="str">
-        <f>IF(E55 &gt; F55, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B55" s="34"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="B55" s="35"/>
       <c r="C55" s="22" t="s">
         <v>14</v>
       </c>
@@ -5963,14 +5100,14 @@
         <v>4</v>
       </c>
       <c r="I55" s="7" t="str">
-        <f>IF(F55 &gt; E55, 1, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J55" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K55" s="34"/>
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="K55" s="35"/>
       <c r="L55" s="22" t="s">
         <v>17</v>
       </c>
@@ -5986,16 +5123,16 @@
         <v>15</v>
       </c>
       <c r="R55" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="56" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A56" s="7" t="str">
-        <f>IF(E56 &gt; F56, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B56" s="34"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="B56" s="35"/>
       <c r="C56" s="22" t="s">
         <v>20</v>
       </c>
@@ -6011,14 +5148,14 @@
         <v>15</v>
       </c>
       <c r="I56" s="7" t="str">
-        <f>IF(F56 &gt; E56, 1, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J56" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K56" s="34"/>
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="K56" s="35"/>
       <c r="L56" s="22" t="s">
         <v>5</v>
       </c>
@@ -6034,16 +5171,16 @@
         <v>13</v>
       </c>
       <c r="R56" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="57" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A57" s="7" t="str">
-        <f>IF(E57 &gt; F57, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B57" s="34"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="B57" s="35"/>
       <c r="C57" s="22" t="s">
         <v>17</v>
       </c>
@@ -6059,14 +5196,14 @@
         <v>15</v>
       </c>
       <c r="I57" s="7" t="str">
-        <f>IF(F57 &gt; E57, 1, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J57" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K57" s="34"/>
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="K57" s="35"/>
       <c r="L57" s="22" t="s">
         <v>14</v>
       </c>
@@ -6082,16 +5219,16 @@
         <v>20</v>
       </c>
       <c r="R57" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
     <row r="58" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A58" s="7" t="str">
-        <f>IF(E58 &gt; F58, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B58" s="34"/>
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="B58" s="35"/>
       <c r="C58" s="22" t="s">
         <v>5</v>
       </c>
@@ -6107,14 +5244,14 @@
         <v>13</v>
       </c>
       <c r="I58" s="7" t="str">
-        <f>IF(F58 &gt; E58, 1, "")</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="J58" s="18" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="K58" s="34"/>
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="K58" s="35"/>
       <c r="L58" s="22" t="s">
         <v>20</v>
       </c>
@@ -6130,7 +5267,7 @@
         <v>4</v>
       </c>
       <c r="R58" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
     </row>
@@ -6176,48 +5313,48 @@
     </row>
     <row r="61" spans="1:18" ht="27" x14ac:dyDescent="0.35">
       <c r="A61" s="6"/>
-      <c r="B61" s="29" t="s">
+      <c r="B61" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
       <c r="R61" s="5"/>
     </row>
     <row r="62" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A62" s="7"/>
-      <c r="B62" s="30" t="s">
+      <c r="B62" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C62" s="30"/>
-      <c r="D62" s="30"/>
-      <c r="E62" s="30"/>
-      <c r="F62" s="30"/>
-      <c r="G62" s="30"/>
-      <c r="H62" s="30"/>
+      <c r="C62" s="31"/>
+      <c r="D62" s="31"/>
+      <c r="E62" s="31"/>
+      <c r="F62" s="31"/>
+      <c r="G62" s="31"/>
+      <c r="H62" s="31"/>
       <c r="I62" s="8"/>
       <c r="J62" s="9"/>
-      <c r="K62" s="30" t="s">
+      <c r="K62" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="L62" s="30"/>
-      <c r="M62" s="30"/>
-      <c r="N62" s="30"/>
-      <c r="O62" s="30"/>
-      <c r="P62" s="30"/>
-      <c r="Q62" s="30"/>
+      <c r="L62" s="31"/>
+      <c r="M62" s="31"/>
+      <c r="N62" s="31"/>
+      <c r="O62" s="31"/>
+      <c r="P62" s="31"/>
+      <c r="Q62" s="31"/>
       <c r="R62" s="10"/>
     </row>
     <row r="63" spans="1:18" x14ac:dyDescent="0.2">
@@ -6270,10 +5407,10 @@
     </row>
     <row r="64" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A64" s="7" t="str">
-        <f>IF(E64 &gt; F64, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B64" s="31" t="s">
+        <f t="shared" ref="A64:A73" si="18">IF(E64 &gt; F64, 1, "")</f>
+        <v/>
+      </c>
+      <c r="B64" s="32" t="s">
         <v>129</v>
       </c>
       <c r="C64" s="22" t="s">
@@ -6291,14 +5428,14 @@
         <v>4</v>
       </c>
       <c r="I64" s="7" t="str">
-        <f>IF(F64 &gt; E64, 1, "")</f>
+        <f t="shared" ref="I64:I73" si="19">IF(F64 &gt; E64, 1, "")</f>
         <v/>
       </c>
       <c r="J64" s="18" t="str">
-        <f t="shared" ref="J64:J73" si="8">IF(N64 &gt; O64, 1, "")</f>
-        <v/>
-      </c>
-      <c r="K64" s="31" t="s">
+        <f t="shared" ref="J64:J73" si="20">IF(N64 &gt; O64, 1, "")</f>
+        <v/>
+      </c>
+      <c r="K64" s="32" t="s">
         <v>129</v>
       </c>
       <c r="L64" s="22" t="s">
@@ -6316,16 +5453,16 @@
         <v>15</v>
       </c>
       <c r="R64" t="str">
-        <f t="shared" ref="R64:R73" si="9">IF(O64 &gt; N64, 1, "")</f>
+        <f t="shared" ref="R64:R73" si="21">IF(O64 &gt; N64, 1, "")</f>
         <v/>
       </c>
     </row>
     <row r="65" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A65" s="7" t="str">
-        <f>IF(E65 &gt; F65, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B65" s="31"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="B65" s="32"/>
       <c r="C65" s="22" t="s">
         <v>5</v>
       </c>
@@ -6341,14 +5478,14 @@
         <v>14</v>
       </c>
       <c r="I65" s="7" t="str">
-        <f>IF(F65 &gt; E65, 1, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J65" s="18" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K65" s="31"/>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="K65" s="32"/>
       <c r="L65" s="22" t="s">
         <v>13</v>
       </c>
@@ -6364,16 +5501,16 @@
         <v>15</v>
       </c>
       <c r="R65" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="66" spans="1:18" ht="23" x14ac:dyDescent="0.2">
       <c r="A66" s="7" t="str">
-        <f>IF(E66 &gt; F66, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B66" s="31"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="B66" s="32"/>
       <c r="C66" s="22" t="s">
         <v>20</v>
       </c>
@@ -6389,14 +5526,14 @@
         <v>15</v>
       </c>
       <c r="I66" s="7" t="str">
-        <f>IF(F66 &gt; E66, 1, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J66" s="18" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K66" s="31"/>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="K66" s="32"/>
       <c r="L66" s="22" t="s">
         <v>17</v>
       </c>
@@ -6412,16 +5549,16 @@
         <v>4</v>
       </c>
       <c r="R66" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="67" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A67" s="7" t="str">
-        <f>IF(E67 &gt; F67, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B67" s="31"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="B67" s="32"/>
       <c r="C67" s="22" t="s">
         <v>13</v>
       </c>
@@ -6437,14 +5574,14 @@
         <v>14</v>
       </c>
       <c r="I67" s="7" t="str">
-        <f>IF(F67 &gt; E67, 1, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J67" s="18" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K67" s="31"/>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="K67" s="32"/>
       <c r="L67" s="22" t="s">
         <v>5</v>
       </c>
@@ -6460,16 +5597,16 @@
         <v>14</v>
       </c>
       <c r="R67" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="68" spans="1:18" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="str">
-        <f>IF(E68 &gt; F68, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B68" s="32"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="B68" s="33"/>
       <c r="C68" s="26" t="s">
         <v>17</v>
       </c>
@@ -6485,14 +5622,14 @@
         <v>4</v>
       </c>
       <c r="I68" s="7" t="str">
-        <f>IF(F68 &gt; E68, 1, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J68" s="18" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K68" s="32"/>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="K68" s="33"/>
       <c r="L68" s="26" t="s">
         <v>20</v>
       </c>
@@ -6508,16 +5645,16 @@
         <v>15</v>
       </c>
       <c r="R68" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="69" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A69" s="7" t="str">
-        <f>IF(E69 &gt; F69, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B69" s="33" t="s">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="B69" s="34" t="s">
         <v>136</v>
       </c>
       <c r="C69" s="24" t="s">
@@ -6535,14 +5672,14 @@
         <v>14</v>
       </c>
       <c r="I69" s="7" t="str">
-        <f>IF(F69 &gt; E69, 1, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J69" s="18" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K69" s="33" t="s">
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="K69" s="34" t="s">
         <v>136</v>
       </c>
       <c r="L69" s="24" t="s">
@@ -6560,16 +5697,16 @@
         <v>4</v>
       </c>
       <c r="R69" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="70" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A70" s="7" t="str">
-        <f>IF(E70 &gt; F70, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B70" s="34"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="B70" s="35"/>
       <c r="C70" s="22" t="s">
         <v>20</v>
       </c>
@@ -6585,14 +5722,14 @@
         <v>15</v>
       </c>
       <c r="I70" s="7" t="str">
-        <f>IF(F70 &gt; E70, 1, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J70" s="18" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K70" s="34"/>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="K70" s="35"/>
       <c r="L70" s="22" t="s">
         <v>17</v>
       </c>
@@ -6608,16 +5745,16 @@
         <v>4</v>
       </c>
       <c r="R70" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="71" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A71" s="7" t="str">
-        <f>IF(E71 &gt; F71, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B71" s="34"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="B71" s="35"/>
       <c r="C71" s="22" t="s">
         <v>13</v>
       </c>
@@ -6633,14 +5770,14 @@
         <v>20</v>
       </c>
       <c r="I71" s="7" t="str">
-        <f>IF(F71 &gt; E71, 1, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J71" s="18" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K71" s="34"/>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="K71" s="35"/>
       <c r="L71" s="22" t="s">
         <v>5</v>
       </c>
@@ -6656,16 +5793,16 @@
         <v>14</v>
       </c>
       <c r="R71" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="72" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A72" s="7" t="str">
-        <f>IF(E72 &gt; F72, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B72" s="34"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="B72" s="35"/>
       <c r="C72" s="22" t="s">
         <v>17</v>
       </c>
@@ -6681,14 +5818,14 @@
         <v>4</v>
       </c>
       <c r="I72" s="7" t="str">
-        <f>IF(F72 &gt; E72, 1, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J72" s="18" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K72" s="34"/>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="K72" s="35"/>
       <c r="L72" s="22" t="s">
         <v>20</v>
       </c>
@@ -6704,16 +5841,16 @@
         <v>13</v>
       </c>
       <c r="R72" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
     <row r="73" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A73" s="7" t="str">
-        <f>IF(E73 &gt; F73, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B73" s="34"/>
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+      <c r="B73" s="35"/>
       <c r="C73" s="22" t="s">
         <v>5</v>
       </c>
@@ -6729,14 +5866,14 @@
         <v>14</v>
       </c>
       <c r="I73" s="7" t="str">
-        <f>IF(F73 &gt; E73, 1, "")</f>
+        <f t="shared" si="19"/>
         <v/>
       </c>
       <c r="J73" s="18" t="str">
-        <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="K73" s="34"/>
+        <f t="shared" si="20"/>
+        <v/>
+      </c>
+      <c r="K73" s="35"/>
       <c r="L73" s="22" t="s">
         <v>13</v>
       </c>
@@ -6752,7 +5889,7 @@
         <v>15</v>
       </c>
       <c r="R73" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
     </row>
@@ -6798,48 +5935,48 @@
     </row>
     <row r="76" spans="1:18" ht="27" x14ac:dyDescent="0.35">
       <c r="A76" s="6"/>
-      <c r="B76" s="29" t="s">
+      <c r="B76" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="29"/>
-      <c r="H76" s="29"/>
-      <c r="I76" s="29"/>
-      <c r="J76" s="29"/>
-      <c r="K76" s="29"/>
-      <c r="L76" s="29"/>
-      <c r="M76" s="29"/>
-      <c r="N76" s="29"/>
-      <c r="O76" s="29"/>
-      <c r="P76" s="29"/>
-      <c r="Q76" s="29"/>
+      <c r="C76" s="30"/>
+      <c r="D76" s="30"/>
+      <c r="E76" s="30"/>
+      <c r="F76" s="30"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="30"/>
+      <c r="I76" s="30"/>
+      <c r="J76" s="30"/>
+      <c r="K76" s="30"/>
+      <c r="L76" s="30"/>
+      <c r="M76" s="30"/>
+      <c r="N76" s="30"/>
+      <c r="O76" s="30"/>
+      <c r="P76" s="30"/>
+      <c r="Q76" s="30"/>
       <c r="R76" s="5"/>
     </row>
     <row r="77" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A77" s="7"/>
-      <c r="B77" s="30" t="s">
+      <c r="B77" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C77" s="30"/>
-      <c r="D77" s="30"/>
-      <c r="E77" s="30"/>
-      <c r="F77" s="30"/>
-      <c r="G77" s="30"/>
-      <c r="H77" s="30"/>
+      <c r="C77" s="31"/>
+      <c r="D77" s="31"/>
+      <c r="E77" s="31"/>
+      <c r="F77" s="31"/>
+      <c r="G77" s="31"/>
+      <c r="H77" s="31"/>
       <c r="I77" s="8"/>
       <c r="J77" s="9"/>
-      <c r="K77" s="30" t="s">
+      <c r="K77" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="L77" s="30"/>
-      <c r="M77" s="30"/>
-      <c r="N77" s="30"/>
-      <c r="O77" s="30"/>
-      <c r="P77" s="30"/>
-      <c r="Q77" s="30"/>
+      <c r="L77" s="31"/>
+      <c r="M77" s="31"/>
+      <c r="N77" s="31"/>
+      <c r="O77" s="31"/>
+      <c r="P77" s="31"/>
+      <c r="Q77" s="31"/>
       <c r="R77" s="10"/>
     </row>
     <row r="78" spans="1:18" x14ac:dyDescent="0.2">
@@ -6892,10 +6029,10 @@
     </row>
     <row r="79" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A79" s="7" t="str">
-        <f>IF(E79 &gt; F79, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B79" s="31" t="s">
+        <f t="shared" ref="A79:A88" si="22">IF(E79 &gt; F79, 1, "")</f>
+        <v/>
+      </c>
+      <c r="B79" s="32" t="s">
         <v>131</v>
       </c>
       <c r="C79" s="22" t="s">
@@ -6913,14 +6050,14 @@
         <v>13</v>
       </c>
       <c r="I79" s="7" t="str">
-        <f>IF(F79 &gt; E79, 1, "")</f>
+        <f t="shared" ref="I79:I88" si="23">IF(F79 &gt; E79, 1, "")</f>
         <v/>
       </c>
       <c r="J79" s="18" t="str">
-        <f t="shared" ref="J79:J88" si="10">IF(N79 &gt; O79, 1, "")</f>
-        <v/>
-      </c>
-      <c r="K79" s="31" t="s">
+        <f t="shared" ref="J79:J88" si="24">IF(N79 &gt; O79, 1, "")</f>
+        <v/>
+      </c>
+      <c r="K79" s="32" t="s">
         <v>131</v>
       </c>
       <c r="L79" s="22" t="s">
@@ -6938,16 +6075,16 @@
         <v>15</v>
       </c>
       <c r="R79" t="str">
-        <f t="shared" ref="R79:R88" si="11">IF(O79 &gt; N79, 1, "")</f>
+        <f t="shared" ref="R79:R88" si="25">IF(O79 &gt; N79, 1, "")</f>
         <v/>
       </c>
     </row>
     <row r="80" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A80" s="7" t="str">
-        <f>IF(E80 &gt; F80, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B80" s="31"/>
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="B80" s="32"/>
       <c r="C80" s="22" t="s">
         <v>5</v>
       </c>
@@ -6963,14 +6100,14 @@
         <v>4</v>
       </c>
       <c r="I80" s="7" t="str">
-        <f>IF(F80 &gt; E80, 1, "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J80" s="18" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K80" s="31"/>
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="K80" s="32"/>
       <c r="L80" s="22" t="s">
         <v>20</v>
       </c>
@@ -6986,16 +6123,16 @@
         <v>13</v>
       </c>
       <c r="R80" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="81" spans="1:18" ht="23" x14ac:dyDescent="0.2">
       <c r="A81" s="7" t="str">
-        <f>IF(E81 &gt; F81, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B81" s="31"/>
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="B81" s="32"/>
       <c r="C81" s="22" t="s">
         <v>14</v>
       </c>
@@ -7011,14 +6148,14 @@
         <v>15</v>
       </c>
       <c r="I81" s="7" t="str">
-        <f>IF(F81 &gt; E81, 1, "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J81" s="18" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K81" s="31"/>
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="K81" s="32"/>
       <c r="L81" s="22" t="s">
         <v>17</v>
       </c>
@@ -7034,16 +6171,16 @@
         <v>13</v>
       </c>
       <c r="R81" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="82" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A82" s="7" t="str">
-        <f>IF(E82 &gt; F82, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B82" s="31"/>
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="B82" s="32"/>
       <c r="C82" s="22" t="s">
         <v>20</v>
       </c>
@@ -7059,14 +6196,14 @@
         <v>14</v>
       </c>
       <c r="I82" s="7" t="str">
-        <f>IF(F82 &gt; E82, 1, "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J82" s="18" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K82" s="31"/>
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="K82" s="32"/>
       <c r="L82" s="22" t="s">
         <v>5</v>
       </c>
@@ -7082,16 +6219,16 @@
         <v>4</v>
       </c>
       <c r="R82" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="83" spans="1:18" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="str">
-        <f>IF(E83 &gt; F83, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B83" s="32"/>
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="B83" s="33"/>
       <c r="C83" s="26" t="s">
         <v>17</v>
       </c>
@@ -7107,14 +6244,14 @@
         <v>13</v>
       </c>
       <c r="I83" s="7" t="str">
-        <f>IF(F83 &gt; E83, 1, "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J83" s="18" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K83" s="32"/>
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="K83" s="33"/>
       <c r="L83" s="26" t="s">
         <v>14</v>
       </c>
@@ -7130,16 +6267,16 @@
         <v>15</v>
       </c>
       <c r="R83" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="84" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A84" s="7" t="str">
-        <f>IF(E84 &gt; F84, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B84" s="33" t="s">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="B84" s="34" t="s">
         <v>130</v>
       </c>
       <c r="C84" s="24" t="s">
@@ -7157,14 +6294,14 @@
         <v>4</v>
       </c>
       <c r="I84" s="7" t="str">
-        <f>IF(F84 &gt; E84, 1, "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J84" s="18" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K84" s="33" t="s">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="K84" s="34" t="s">
         <v>130</v>
       </c>
       <c r="L84" s="24" t="s">
@@ -7182,16 +6319,16 @@
         <v>4</v>
       </c>
       <c r="R84" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="85" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A85" s="7" t="str">
-        <f>IF(E85 &gt; F85, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B85" s="34"/>
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="B85" s="35"/>
       <c r="C85" s="22" t="s">
         <v>14</v>
       </c>
@@ -7207,14 +6344,14 @@
         <v>15</v>
       </c>
       <c r="I85" s="7" t="str">
-        <f>IF(F85 &gt; E85, 1, "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J85" s="18" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K85" s="34"/>
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="K85" s="35"/>
       <c r="L85" s="22" t="s">
         <v>17</v>
       </c>
@@ -7230,16 +6367,16 @@
         <v>13</v>
       </c>
       <c r="R85" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="86" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A86" s="7" t="str">
-        <f>IF(E86 &gt; F86, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B86" s="34"/>
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="B86" s="35"/>
       <c r="C86" s="22" t="s">
         <v>20</v>
       </c>
@@ -7255,14 +6392,14 @@
         <v>15</v>
       </c>
       <c r="I86" s="7" t="str">
-        <f>IF(F86 &gt; E86, 1, "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J86" s="18" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K86" s="34"/>
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="K86" s="35"/>
       <c r="L86" s="22" t="s">
         <v>5</v>
       </c>
@@ -7278,16 +6415,16 @@
         <v>4</v>
       </c>
       <c r="R86" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="87" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A87" s="7" t="str">
-        <f>IF(E87 &gt; F87, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B87" s="34"/>
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="B87" s="35"/>
       <c r="C87" s="22" t="s">
         <v>17</v>
       </c>
@@ -7303,14 +6440,14 @@
         <v>13</v>
       </c>
       <c r="I87" s="7" t="str">
-        <f>IF(F87 &gt; E87, 1, "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J87" s="18" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K87" s="34"/>
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="K87" s="35"/>
       <c r="L87" s="22" t="s">
         <v>14</v>
       </c>
@@ -7326,16 +6463,16 @@
         <v>20</v>
       </c>
       <c r="R87" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
     <row r="88" spans="1:18" ht="22" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="str">
-        <f>IF(E88 &gt; F88, 1, "")</f>
-        <v/>
-      </c>
-      <c r="B88" s="34"/>
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="B88" s="35"/>
       <c r="C88" s="22" t="s">
         <v>5</v>
       </c>
@@ -7351,14 +6488,14 @@
         <v>4</v>
       </c>
       <c r="I88" s="7" t="str">
-        <f>IF(F88 &gt; E88, 1, "")</f>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="J88" s="18" t="str">
-        <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="K88" s="34"/>
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="K88" s="35"/>
       <c r="L88" s="22" t="s">
         <v>20</v>
       </c>
@@ -7374,7 +6511,7 @@
         <v>15</v>
       </c>
       <c r="R88" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
     </row>
@@ -7600,6 +6737,41 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B1:Q1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="K2:Q2"/>
+    <mergeCell ref="B4:B8"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="K4:K8"/>
+    <mergeCell ref="K9:K13"/>
+    <mergeCell ref="B16:Q16"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="K17:Q17"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="K19:K23"/>
+    <mergeCell ref="K24:K28"/>
+    <mergeCell ref="B31:Q31"/>
+    <mergeCell ref="B32:H32"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="K34:K38"/>
+    <mergeCell ref="K39:K43"/>
+    <mergeCell ref="B46:Q46"/>
+    <mergeCell ref="B47:H47"/>
+    <mergeCell ref="K47:Q47"/>
+    <mergeCell ref="B49:B53"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="K49:K53"/>
+    <mergeCell ref="K54:K58"/>
+    <mergeCell ref="B61:Q61"/>
+    <mergeCell ref="B62:H62"/>
+    <mergeCell ref="K62:Q62"/>
+    <mergeCell ref="B64:B68"/>
+    <mergeCell ref="B69:B73"/>
+    <mergeCell ref="K64:K68"/>
+    <mergeCell ref="K69:K73"/>
     <mergeCell ref="B76:Q76"/>
     <mergeCell ref="B77:H77"/>
     <mergeCell ref="K77:Q77"/>
@@ -7607,41 +6779,6 @@
     <mergeCell ref="B84:B88"/>
     <mergeCell ref="K79:K83"/>
     <mergeCell ref="K84:K88"/>
-    <mergeCell ref="B61:Q61"/>
-    <mergeCell ref="B62:H62"/>
-    <mergeCell ref="K62:Q62"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="B69:B73"/>
-    <mergeCell ref="K64:K68"/>
-    <mergeCell ref="K69:K73"/>
-    <mergeCell ref="B46:Q46"/>
-    <mergeCell ref="B47:H47"/>
-    <mergeCell ref="K47:Q47"/>
-    <mergeCell ref="B49:B53"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="K49:K53"/>
-    <mergeCell ref="K54:K58"/>
-    <mergeCell ref="B31:Q31"/>
-    <mergeCell ref="B32:H32"/>
-    <mergeCell ref="K32:Q32"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="B39:B43"/>
-    <mergeCell ref="K34:K38"/>
-    <mergeCell ref="K39:K43"/>
-    <mergeCell ref="B16:Q16"/>
-    <mergeCell ref="B17:H17"/>
-    <mergeCell ref="K17:Q17"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="K19:K23"/>
-    <mergeCell ref="K24:K28"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="K2:Q2"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="B9:B13"/>
-    <mergeCell ref="K4:K8"/>
-    <mergeCell ref="K9:K13"/>
-    <mergeCell ref="B1:Q1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7649,2462 +6786,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{990AFEB4-A92B-1849-96F5-AAADB6DDF155}">
-  <dimension ref="A1:L88"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" style="40" customWidth="1"/>
-    <col min="2" max="7" width="10.83203125" style="40"/>
-    <col min="8" max="8" width="18.83203125" style="40" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="40"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A1" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-    </row>
-    <row r="2" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A2" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-    </row>
-    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.15">
-      <c r="A3" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="44"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="I3" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="K3" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="L3" s="70" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A4" s="67" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="185" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="180" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="44"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="67" t="s">
-        <v>125</v>
-      </c>
-      <c r="I4" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="186" t="s">
-        <v>66</v>
-      </c>
-      <c r="K4" s="184" t="s">
-        <v>75</v>
-      </c>
-      <c r="L4" s="53" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A5" s="67"/>
-      <c r="B5" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="186" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="181" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" s="187" t="s">
-        <v>69</v>
-      </c>
-      <c r="K5" s="182" t="s">
-        <v>78</v>
-      </c>
-      <c r="L5" s="58" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A6" s="67"/>
-      <c r="B6" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="187" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="182" t="s">
-        <v>81</v>
-      </c>
-      <c r="E6" s="58" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="44"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="185" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="180" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6" s="48" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A7" s="67"/>
-      <c r="B7" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="185" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="180" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7" s="186" t="s">
-        <v>67</v>
-      </c>
-      <c r="K7" s="181" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" s="55" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="22" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="148"/>
-      <c r="B8" s="189" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="190" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="191" t="s">
-        <v>74</v>
-      </c>
-      <c r="E8" s="192" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="44"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="148"/>
-      <c r="I8" s="193" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="195" t="s">
-        <v>72</v>
-      </c>
-      <c r="K8" s="191" t="s">
-        <v>124</v>
-      </c>
-      <c r="L8" s="192" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="188" t="s">
-        <v>71</v>
-      </c>
-      <c r="D9" s="183" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="61" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="44"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" s="62" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="196" t="s">
-        <v>61</v>
-      </c>
-      <c r="K9" s="194" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="63" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A10" s="64"/>
-      <c r="B10" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="185" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="180" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="44"/>
-      <c r="G10" s="49"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="J10" s="187" t="s">
-        <v>70</v>
-      </c>
-      <c r="K10" s="182" t="s">
-        <v>79</v>
-      </c>
-      <c r="L10" s="58" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A11" s="64"/>
-      <c r="B11" s="50" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="186" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" s="181" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="44"/>
-      <c r="G11" s="49"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="197" t="s">
-        <v>21</v>
-      </c>
-      <c r="K11" s="182" t="s">
-        <v>77</v>
-      </c>
-      <c r="L11" s="58" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A12" s="64"/>
-      <c r="B12" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="187" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="184" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="F12" s="44"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="J12" s="198" t="s">
-        <v>82</v>
-      </c>
-      <c r="K12" s="184" t="s">
-        <v>76</v>
-      </c>
-      <c r="L12" s="53" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A13" s="64"/>
-      <c r="B13" s="46" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="185" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="180" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="48" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" s="44"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="64"/>
-      <c r="I13" s="52" t="s">
-        <v>4</v>
-      </c>
-      <c r="J13" s="199" t="s">
-        <v>6</v>
-      </c>
-      <c r="K13" s="181" t="s">
-        <v>26</v>
-      </c>
-      <c r="L13" s="55" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A14" s="65"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="65"/>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="66"/>
-      <c r="L14" s="66"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A15" s="65"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-    </row>
-    <row r="16" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A16" s="39" t="s">
-        <v>37</v>
-      </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
-      <c r="K16" s="39"/>
-      <c r="L16" s="39"/>
-    </row>
-    <row r="17" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A17" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="41"/>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="43"/>
-      <c r="H17" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="41"/>
-    </row>
-    <row r="18" spans="1:12" s="72" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="C18" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="F18" s="71"/>
-      <c r="G18" s="71"/>
-      <c r="H18" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="I18" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="J18" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="K18" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" s="70" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A19" s="67" t="s">
-        <v>127</v>
-      </c>
-      <c r="B19" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C19" s="138" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="158" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="51" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="44"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="67" t="s">
-        <v>127</v>
-      </c>
-      <c r="I19" s="89" t="s">
-        <v>13</v>
-      </c>
-      <c r="J19" s="172" t="s">
-        <v>77</v>
-      </c>
-      <c r="K19" s="171" t="s">
-        <v>72</v>
-      </c>
-      <c r="L19" s="83" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A20" s="67"/>
-      <c r="B20" s="47" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="159" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="113" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="55" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="44"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="134" t="s">
-        <v>60</v>
-      </c>
-      <c r="K20" s="158" t="s">
-        <v>64</v>
-      </c>
-      <c r="L20" s="76" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A21" s="67"/>
-      <c r="B21" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="179" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="117" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="53" t="s">
-        <v>4</v>
-      </c>
-      <c r="F21" s="44"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="67"/>
-      <c r="I21" s="78" t="s">
-        <v>5</v>
-      </c>
-      <c r="J21" s="159" t="s">
-        <v>8</v>
-      </c>
-      <c r="K21" s="113" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" s="81" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A22" s="67"/>
-      <c r="B22" s="57" t="s">
-        <v>13</v>
-      </c>
-      <c r="C22" s="172" t="s">
-        <v>81</v>
-      </c>
-      <c r="D22" s="158" t="s">
-        <v>63</v>
-      </c>
-      <c r="E22" s="76" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" s="44"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="67"/>
-      <c r="I22" s="82" t="s">
-        <v>15</v>
-      </c>
-      <c r="J22" s="173" t="s">
-        <v>70</v>
-      </c>
-      <c r="K22" s="117" t="s">
-        <v>74</v>
-      </c>
-      <c r="L22" s="86" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="148"/>
-      <c r="B23" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C23" s="155" t="s">
-        <v>73</v>
-      </c>
-      <c r="D23" s="178" t="s">
-        <v>61</v>
-      </c>
-      <c r="E23" s="177" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="44"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="148"/>
-      <c r="I23" s="175" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="176" t="s">
-        <v>78</v>
-      </c>
-      <c r="K23" s="156" t="s">
-        <v>7</v>
-      </c>
-      <c r="L23" s="157" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="B24" s="90" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="141" t="s">
-        <v>12</v>
-      </c>
-      <c r="D24" s="122" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="44"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="I24" s="93" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="174" t="s">
-        <v>18</v>
-      </c>
-      <c r="K24" s="123" t="s">
-        <v>67</v>
-      </c>
-      <c r="L24" s="94" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A25" s="64"/>
-      <c r="B25" s="82" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="173" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="117" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="86" t="s">
-        <v>4</v>
-      </c>
-      <c r="F25" s="44"/>
-      <c r="G25" s="49"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="78" t="s">
-        <v>5</v>
-      </c>
-      <c r="J25" s="159" t="s">
-        <v>11</v>
-      </c>
-      <c r="K25" s="113" t="s">
-        <v>23</v>
-      </c>
-      <c r="L25" s="81" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A26" s="64"/>
-      <c r="B26" s="89" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="172" t="s">
-        <v>79</v>
-      </c>
-      <c r="D26" s="113" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" s="44"/>
-      <c r="G26" s="49"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="82" t="s">
-        <v>15</v>
-      </c>
-      <c r="J26" s="173" t="s">
-        <v>69</v>
-      </c>
-      <c r="K26" s="117" t="s">
-        <v>76</v>
-      </c>
-      <c r="L26" s="86" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A27" s="64"/>
-      <c r="B27" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C27" s="134" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="158" t="s">
-        <v>66</v>
-      </c>
-      <c r="E27" s="76" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" s="44"/>
-      <c r="G27" s="49"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="82" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="173" t="s">
-        <v>68</v>
-      </c>
-      <c r="K27" s="114" t="s">
-        <v>82</v>
-      </c>
-      <c r="L27" s="88" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A28" s="64"/>
-      <c r="B28" s="78" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="159" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="113" t="s">
-        <v>25</v>
-      </c>
-      <c r="E28" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="F28" s="44"/>
-      <c r="G28" s="49"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="85" t="s">
-        <v>4</v>
-      </c>
-      <c r="J28" s="161" t="s">
-        <v>124</v>
-      </c>
-      <c r="K28" s="114" t="s">
-        <v>80</v>
-      </c>
-      <c r="L28" s="88" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A29" s="65"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="66"/>
-      <c r="D29" s="66"/>
-      <c r="E29" s="66"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="66"/>
-      <c r="H29" s="66"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="66"/>
-      <c r="K29" s="66"/>
-      <c r="L29" s="66"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A30" s="65"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="66"/>
-      <c r="D30" s="66"/>
-      <c r="E30" s="66"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="66"/>
-      <c r="H30" s="66"/>
-      <c r="I30" s="66"/>
-      <c r="J30" s="66"/>
-      <c r="K30" s="66"/>
-      <c r="L30" s="66"/>
-    </row>
-    <row r="31" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A31" s="39" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="39"/>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
-      <c r="F31" s="39"/>
-      <c r="G31" s="39"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="39"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="39"/>
-    </row>
-    <row r="32" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A32" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="41"/>
-      <c r="C32" s="41"/>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="43"/>
-      <c r="H32" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="I32" s="41"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="41"/>
-      <c r="L32" s="41"/>
-    </row>
-    <row r="33" spans="1:12" s="72" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="B33" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="D33" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="F33" s="71"/>
-      <c r="G33" s="71"/>
-      <c r="H33" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="I33" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="J33" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="K33" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="L33" s="70" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A34" s="67" t="s">
-        <v>132</v>
-      </c>
-      <c r="B34" s="77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="138" t="s">
-        <v>19</v>
-      </c>
-      <c r="D34" s="121" t="s">
-        <v>22</v>
-      </c>
-      <c r="E34" s="107" t="s">
-        <v>20</v>
-      </c>
-      <c r="F34" s="44"/>
-      <c r="G34" s="49"/>
-      <c r="H34" s="67" t="s">
-        <v>132</v>
-      </c>
-      <c r="I34" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34" s="140" t="s">
-        <v>65</v>
-      </c>
-      <c r="K34" s="114" t="s">
-        <v>80</v>
-      </c>
-      <c r="L34" s="88" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A35" s="67"/>
-      <c r="B35" s="47" t="s">
-        <v>5</v>
-      </c>
-      <c r="C35" s="159" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="116" t="s">
-        <v>72</v>
-      </c>
-      <c r="E35" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F35" s="44"/>
-      <c r="G35" s="49"/>
-      <c r="H35" s="67"/>
-      <c r="I35" s="101" t="s">
-        <v>4</v>
-      </c>
-      <c r="J35" s="166" t="s">
-        <v>75</v>
-      </c>
-      <c r="K35" s="96" t="s">
-        <v>70</v>
-      </c>
-      <c r="L35" s="105" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A36" s="67"/>
-      <c r="B36" s="108" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="160" t="s">
-        <v>61</v>
-      </c>
-      <c r="D36" s="87" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36" s="109" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="44"/>
-      <c r="G36" s="49"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="142" t="s">
-        <v>59</v>
-      </c>
-      <c r="K36" s="113" t="s">
-        <v>25</v>
-      </c>
-      <c r="L36" s="81" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A37" s="67"/>
-      <c r="B37" s="85" t="s">
-        <v>4</v>
-      </c>
-      <c r="C37" s="161" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="158" t="s">
-        <v>67</v>
-      </c>
-      <c r="E37" s="76" t="s">
-        <v>14</v>
-      </c>
-      <c r="F37" s="44"/>
-      <c r="G37" s="49"/>
-      <c r="H37" s="67"/>
-      <c r="I37" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="J37" s="135" t="s">
-        <v>9</v>
-      </c>
-      <c r="K37" s="96" t="s">
-        <v>71</v>
-      </c>
-      <c r="L37" s="105" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="148"/>
-      <c r="B38" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C38" s="155" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" s="164" t="s">
-        <v>26</v>
-      </c>
-      <c r="E38" s="165" t="s">
-        <v>20</v>
-      </c>
-      <c r="F38" s="44"/>
-      <c r="G38" s="49"/>
-      <c r="H38" s="148"/>
-      <c r="I38" s="144" t="s">
-        <v>14</v>
-      </c>
-      <c r="J38" s="145" t="s">
-        <v>64</v>
-      </c>
-      <c r="K38" s="169" t="s">
-        <v>79</v>
-      </c>
-      <c r="L38" s="170" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="59" t="s">
-        <v>133</v>
-      </c>
-      <c r="B39" s="90" t="s">
-        <v>5</v>
-      </c>
-      <c r="C39" s="141" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="125" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39" s="106" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="44"/>
-      <c r="G39" s="49"/>
-      <c r="H39" s="59" t="s">
-        <v>133</v>
-      </c>
-      <c r="I39" s="167" t="s">
-        <v>4</v>
-      </c>
-      <c r="J39" s="168" t="s">
-        <v>6</v>
-      </c>
-      <c r="K39" s="120" t="s">
-        <v>81</v>
-      </c>
-      <c r="L39" s="119" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A40" s="64"/>
-      <c r="B40" s="99" t="s">
-        <v>14</v>
-      </c>
-      <c r="C40" s="163" t="s">
-        <v>66</v>
-      </c>
-      <c r="D40" s="87" t="s">
-        <v>82</v>
-      </c>
-      <c r="E40" s="109" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="44"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="64"/>
-      <c r="I40" s="110" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="162" t="s">
-        <v>73</v>
-      </c>
-      <c r="K40" s="79" t="s">
-        <v>23</v>
-      </c>
-      <c r="L40" s="104" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A41" s="64"/>
-      <c r="B41" s="85" t="s">
-        <v>4</v>
-      </c>
-      <c r="C41" s="161" t="s">
-        <v>124</v>
-      </c>
-      <c r="D41" s="113" t="s">
-        <v>21</v>
-      </c>
-      <c r="E41" s="81" t="s">
-        <v>20</v>
-      </c>
-      <c r="F41" s="44"/>
-      <c r="G41" s="49"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="78" t="s">
-        <v>5</v>
-      </c>
-      <c r="J41" s="159" t="s">
-        <v>12</v>
-      </c>
-      <c r="K41" s="116" t="s">
-        <v>16</v>
-      </c>
-      <c r="L41" s="83" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A42" s="64"/>
-      <c r="B42" s="110" t="s">
-        <v>17</v>
-      </c>
-      <c r="C42" s="162" t="s">
-        <v>60</v>
-      </c>
-      <c r="D42" s="79" t="s">
-        <v>24</v>
-      </c>
-      <c r="E42" s="104" t="s">
-        <v>20</v>
-      </c>
-      <c r="F42" s="44"/>
-      <c r="G42" s="49"/>
-      <c r="H42" s="64"/>
-      <c r="I42" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="J42" s="140" t="s">
-        <v>63</v>
-      </c>
-      <c r="K42" s="117" t="s">
-        <v>76</v>
-      </c>
-      <c r="L42" s="86" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A43" s="64"/>
-      <c r="B43" s="78" t="s">
-        <v>5</v>
-      </c>
-      <c r="C43" s="159" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="116" t="s">
-        <v>68</v>
-      </c>
-      <c r="E43" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F43" s="44"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="64"/>
-      <c r="I43" s="118" t="s">
-        <v>13</v>
-      </c>
-      <c r="J43" s="151" t="s">
-        <v>77</v>
-      </c>
-      <c r="K43" s="111" t="s">
-        <v>74</v>
-      </c>
-      <c r="L43" s="112" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A44" s="65"/>
-      <c r="B44" s="65"/>
-      <c r="C44" s="66"/>
-      <c r="D44" s="66"/>
-      <c r="E44" s="66"/>
-      <c r="F44" s="65"/>
-      <c r="G44" s="66"/>
-      <c r="H44" s="66"/>
-      <c r="I44" s="66"/>
-      <c r="J44" s="66"/>
-      <c r="K44" s="66"/>
-      <c r="L44" s="66"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A45" s="65"/>
-      <c r="B45" s="65"/>
-      <c r="C45" s="66"/>
-      <c r="D45" s="66"/>
-      <c r="E45" s="66"/>
-      <c r="F45" s="65"/>
-      <c r="G45" s="66"/>
-      <c r="H45" s="66"/>
-      <c r="I45" s="66"/>
-      <c r="J45" s="66"/>
-      <c r="K45" s="66"/>
-      <c r="L45" s="66"/>
-    </row>
-    <row r="46" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A46" s="39" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="39"/>
-      <c r="C46" s="39"/>
-      <c r="D46" s="39"/>
-      <c r="E46" s="39"/>
-      <c r="F46" s="39"/>
-      <c r="G46" s="39"/>
-      <c r="H46" s="39"/>
-      <c r="I46" s="39"/>
-      <c r="J46" s="39"/>
-      <c r="K46" s="39"/>
-      <c r="L46" s="39"/>
-    </row>
-    <row r="47" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A47" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="B47" s="41"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="42"/>
-      <c r="G47" s="43"/>
-      <c r="H47" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="I47" s="41"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="41"/>
-    </row>
-    <row r="48" spans="1:12" s="72" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="B48" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="C48" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="D48" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="E48" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="F48" s="71"/>
-      <c r="G48" s="71"/>
-      <c r="H48" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="I48" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="J48" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="K48" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="L48" s="70" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A49" s="67" t="s">
-        <v>134</v>
-      </c>
-      <c r="B49" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C49" s="134" t="s">
-        <v>59</v>
-      </c>
-      <c r="D49" s="116" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" s="44"/>
-      <c r="G49" s="49"/>
-      <c r="H49" s="67" t="s">
-        <v>134</v>
-      </c>
-      <c r="I49" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="J49" s="140" t="s">
-        <v>63</v>
-      </c>
-      <c r="K49" s="113" t="s">
-        <v>26</v>
-      </c>
-      <c r="L49" s="81" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A50" s="67"/>
-      <c r="B50" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="C50" s="135" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="87" t="s">
-        <v>82</v>
-      </c>
-      <c r="E50" s="115" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="44"/>
-      <c r="G50" s="49"/>
-      <c r="H50" s="67"/>
-      <c r="I50" s="102" t="s">
-        <v>13</v>
-      </c>
-      <c r="J50" s="150" t="s">
-        <v>80</v>
-      </c>
-      <c r="K50" s="84" t="s">
-        <v>75</v>
-      </c>
-      <c r="L50" s="97" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A51" s="67"/>
-      <c r="B51" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="C51" s="136" t="s">
-        <v>67</v>
-      </c>
-      <c r="D51" s="117" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" s="86" t="s">
-        <v>4</v>
-      </c>
-      <c r="F51" s="44"/>
-      <c r="G51" s="49"/>
-      <c r="H51" s="67"/>
-      <c r="I51" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="142" t="s">
-        <v>18</v>
-      </c>
-      <c r="K51" s="116" t="s">
-        <v>69</v>
-      </c>
-      <c r="L51" s="83" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A52" s="67"/>
-      <c r="B52" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="C52" s="137" t="s">
-        <v>21</v>
-      </c>
-      <c r="D52" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="E52" s="100" t="s">
-        <v>14</v>
-      </c>
-      <c r="F52" s="44"/>
-      <c r="G52" s="49"/>
-      <c r="H52" s="67"/>
-      <c r="I52" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="J52" s="135" t="s">
-        <v>11</v>
-      </c>
-      <c r="K52" s="87" t="s">
-        <v>79</v>
-      </c>
-      <c r="L52" s="115" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="148"/>
-      <c r="B53" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C53" s="155" t="s">
-        <v>60</v>
-      </c>
-      <c r="D53" s="146" t="s">
-        <v>70</v>
-      </c>
-      <c r="E53" s="147" t="s">
-        <v>15</v>
-      </c>
-      <c r="F53" s="44"/>
-      <c r="G53" s="49"/>
-      <c r="H53" s="148"/>
-      <c r="I53" s="144" t="s">
-        <v>14</v>
-      </c>
-      <c r="J53" s="145" t="s">
-        <v>64</v>
-      </c>
-      <c r="K53" s="156" t="s">
-        <v>76</v>
-      </c>
-      <c r="L53" s="157" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="59" t="s">
-        <v>135</v>
-      </c>
-      <c r="B54" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="C54" s="135" t="s">
-        <v>10</v>
-      </c>
-      <c r="D54" s="87" t="s">
-        <v>78</v>
-      </c>
-      <c r="E54" s="115" t="s">
-        <v>13</v>
-      </c>
-      <c r="F54" s="44"/>
-      <c r="G54" s="49"/>
-      <c r="H54" s="59" t="s">
-        <v>135</v>
-      </c>
-      <c r="I54" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="J54" s="137" t="s">
-        <v>23</v>
-      </c>
-      <c r="K54" s="84" t="s">
-        <v>74</v>
-      </c>
-      <c r="L54" s="97" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A55" s="64"/>
-      <c r="B55" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="C55" s="140" t="s">
-        <v>61</v>
-      </c>
-      <c r="D55" s="117" t="s">
-        <v>124</v>
-      </c>
-      <c r="E55" s="86" t="s">
-        <v>4</v>
-      </c>
-      <c r="F55" s="44"/>
-      <c r="G55" s="49"/>
-      <c r="H55" s="64"/>
-      <c r="I55" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="134" t="s">
-        <v>73</v>
-      </c>
-      <c r="K55" s="116" t="s">
-        <v>72</v>
-      </c>
-      <c r="L55" s="83" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A56" s="64"/>
-      <c r="B56" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="C56" s="137" t="s">
-        <v>22</v>
-      </c>
-      <c r="D56" s="96" t="s">
-        <v>71</v>
-      </c>
-      <c r="E56" s="105" t="s">
-        <v>15</v>
-      </c>
-      <c r="F56" s="44"/>
-      <c r="G56" s="49"/>
-      <c r="H56" s="64"/>
-      <c r="I56" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="J56" s="135" t="s">
-        <v>12</v>
-      </c>
-      <c r="K56" s="87" t="s">
-        <v>81</v>
-      </c>
-      <c r="L56" s="115" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A57" s="64"/>
-      <c r="B57" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" s="134" t="s">
-        <v>19</v>
-      </c>
-      <c r="D57" s="116" t="s">
-        <v>16</v>
-      </c>
-      <c r="E57" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" s="44"/>
-      <c r="G57" s="49"/>
-      <c r="H57" s="64"/>
-      <c r="I57" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="J57" s="140" t="s">
-        <v>66</v>
-      </c>
-      <c r="K57" s="113" t="s">
-        <v>24</v>
-      </c>
-      <c r="L57" s="81" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A58" s="64"/>
-      <c r="B58" s="90" t="s">
-        <v>5</v>
-      </c>
-      <c r="C58" s="141" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="120" t="s">
-        <v>77</v>
-      </c>
-      <c r="E58" s="119" t="s">
-        <v>13</v>
-      </c>
-      <c r="F58" s="44"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="64"/>
-      <c r="I58" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="J58" s="143" t="s">
-        <v>25</v>
-      </c>
-      <c r="K58" s="111" t="s">
-        <v>7</v>
-      </c>
-      <c r="L58" s="112" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A59" s="65"/>
-      <c r="B59" s="65"/>
-      <c r="C59" s="66"/>
-      <c r="D59" s="66"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="65"/>
-      <c r="G59" s="66"/>
-      <c r="H59" s="66"/>
-      <c r="I59" s="95"/>
-      <c r="J59" s="95"/>
-      <c r="K59" s="95"/>
-      <c r="L59" s="95"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A60" s="65"/>
-      <c r="B60" s="65"/>
-      <c r="C60" s="66"/>
-      <c r="D60" s="66"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="65"/>
-      <c r="G60" s="66"/>
-      <c r="H60" s="66"/>
-      <c r="I60" s="66"/>
-      <c r="J60" s="66"/>
-      <c r="K60" s="66"/>
-      <c r="L60" s="66"/>
-    </row>
-    <row r="61" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A61" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="B61" s="39"/>
-      <c r="C61" s="39"/>
-      <c r="D61" s="39"/>
-      <c r="E61" s="39"/>
-      <c r="F61" s="39"/>
-      <c r="G61" s="39"/>
-      <c r="H61" s="39"/>
-      <c r="I61" s="39"/>
-      <c r="J61" s="39"/>
-      <c r="K61" s="39"/>
-      <c r="L61" s="39"/>
-    </row>
-    <row r="62" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A62" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="B62" s="41"/>
-      <c r="C62" s="41"/>
-      <c r="D62" s="41"/>
-      <c r="E62" s="41"/>
-      <c r="F62" s="42"/>
-      <c r="G62" s="43"/>
-      <c r="H62" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="I62" s="41"/>
-      <c r="J62" s="41"/>
-      <c r="K62" s="41"/>
-      <c r="L62" s="41"/>
-    </row>
-    <row r="63" spans="1:12" s="72" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="B63" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="C63" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="D63" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="E63" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="F63" s="71"/>
-      <c r="G63" s="71"/>
-      <c r="H63" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="I63" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="J63" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="K63" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="L63" s="70" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A64" s="67" t="s">
-        <v>129</v>
-      </c>
-      <c r="B64" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="134" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" s="117" t="s">
-        <v>75</v>
-      </c>
-      <c r="E64" s="86" t="s">
-        <v>4</v>
-      </c>
-      <c r="F64" s="44"/>
-      <c r="G64" s="49"/>
-      <c r="H64" s="67" t="s">
-        <v>129</v>
-      </c>
-      <c r="I64" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="J64" s="149" t="s">
-        <v>25</v>
-      </c>
-      <c r="K64" s="116" t="s">
-        <v>72</v>
-      </c>
-      <c r="L64" s="83" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A65" s="67"/>
-      <c r="B65" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="C65" s="135" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="74" t="s">
-        <v>64</v>
-      </c>
-      <c r="E65" s="100" t="s">
-        <v>14</v>
-      </c>
-      <c r="F65" s="44"/>
-      <c r="G65" s="49"/>
-      <c r="H65" s="67"/>
-      <c r="I65" s="102" t="s">
-        <v>13</v>
-      </c>
-      <c r="J65" s="150" t="s">
-        <v>77</v>
-      </c>
-      <c r="K65" s="96" t="s">
-        <v>68</v>
-      </c>
-      <c r="L65" s="105" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A66" s="67"/>
-      <c r="B66" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="C66" s="154" t="s">
-        <v>21</v>
-      </c>
-      <c r="D66" s="116" t="s">
-        <v>70</v>
-      </c>
-      <c r="E66" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" s="44"/>
-      <c r="G66" s="49"/>
-      <c r="H66" s="67"/>
-      <c r="I66" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="142" t="s">
-        <v>73</v>
-      </c>
-      <c r="K66" s="117" t="s">
-        <v>124</v>
-      </c>
-      <c r="L66" s="86" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A67" s="67"/>
-      <c r="B67" s="102" t="s">
-        <v>13</v>
-      </c>
-      <c r="C67" s="150" t="s">
-        <v>80</v>
-      </c>
-      <c r="D67" s="74" t="s">
-        <v>66</v>
-      </c>
-      <c r="E67" s="100" t="s">
-        <v>14</v>
-      </c>
-      <c r="F67" s="44"/>
-      <c r="G67" s="49"/>
-      <c r="H67" s="67"/>
-      <c r="I67" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="J67" s="135" t="s">
-        <v>10</v>
-      </c>
-      <c r="K67" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="L67" s="100" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="148"/>
-      <c r="B68" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C68" s="155" t="s">
-        <v>60</v>
-      </c>
-      <c r="D68" s="156" t="s">
-        <v>76</v>
-      </c>
-      <c r="E68" s="157" t="s">
-        <v>4</v>
-      </c>
-      <c r="F68" s="44"/>
-      <c r="G68" s="49"/>
-      <c r="H68" s="148"/>
-      <c r="I68" s="152" t="s">
-        <v>20</v>
-      </c>
-      <c r="J68" s="153" t="s">
-        <v>26</v>
-      </c>
-      <c r="K68" s="146" t="s">
-        <v>69</v>
-      </c>
-      <c r="L68" s="147" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="B69" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="C69" s="135" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="E69" s="100" t="s">
-        <v>14</v>
-      </c>
-      <c r="F69" s="44"/>
-      <c r="G69" s="49"/>
-      <c r="H69" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="I69" s="102" t="s">
-        <v>13</v>
-      </c>
-      <c r="J69" s="150" t="s">
-        <v>79</v>
-      </c>
-      <c r="K69" s="84" t="s">
-        <v>6</v>
-      </c>
-      <c r="L69" s="97" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A70" s="64"/>
-      <c r="B70" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="C70" s="149" t="s">
-        <v>24</v>
-      </c>
-      <c r="D70" s="116" t="s">
-        <v>71</v>
-      </c>
-      <c r="E70" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F70" s="44"/>
-      <c r="G70" s="49"/>
-      <c r="H70" s="64"/>
-      <c r="I70" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="134" t="s">
-        <v>18</v>
-      </c>
-      <c r="K70" s="117" t="s">
-        <v>74</v>
-      </c>
-      <c r="L70" s="86" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A71" s="64"/>
-      <c r="B71" s="102" t="s">
-        <v>13</v>
-      </c>
-      <c r="C71" s="150" t="s">
-        <v>78</v>
-      </c>
-      <c r="D71" s="79" t="s">
-        <v>23</v>
-      </c>
-      <c r="E71" s="104" t="s">
-        <v>20</v>
-      </c>
-      <c r="F71" s="44"/>
-      <c r="G71" s="49"/>
-      <c r="H71" s="64"/>
-      <c r="I71" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="J71" s="135" t="s">
-        <v>12</v>
-      </c>
-      <c r="K71" s="74" t="s">
-        <v>63</v>
-      </c>
-      <c r="L71" s="100" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A72" s="64"/>
-      <c r="B72" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C72" s="134" t="s">
-        <v>59</v>
-      </c>
-      <c r="D72" s="117" t="s">
-        <v>7</v>
-      </c>
-      <c r="E72" s="86" t="s">
-        <v>4</v>
-      </c>
-      <c r="F72" s="44"/>
-      <c r="G72" s="49"/>
-      <c r="H72" s="64"/>
-      <c r="I72" s="80" t="s">
-        <v>20</v>
-      </c>
-      <c r="J72" s="149" t="s">
-        <v>22</v>
-      </c>
-      <c r="K72" s="114" t="s">
-        <v>82</v>
-      </c>
-      <c r="L72" s="88" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A73" s="64"/>
-      <c r="B73" s="90" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="141" t="s">
-        <v>11</v>
-      </c>
-      <c r="D73" s="123" t="s">
-        <v>65</v>
-      </c>
-      <c r="E73" s="94" t="s">
-        <v>14</v>
-      </c>
-      <c r="F73" s="44"/>
-      <c r="G73" s="49"/>
-      <c r="H73" s="64"/>
-      <c r="I73" s="118" t="s">
-        <v>13</v>
-      </c>
-      <c r="J73" s="151" t="s">
-        <v>81</v>
-      </c>
-      <c r="K73" s="125" t="s">
-        <v>16</v>
-      </c>
-      <c r="L73" s="106" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A74" s="65"/>
-      <c r="B74" s="65"/>
-      <c r="C74" s="66"/>
-      <c r="D74" s="66"/>
-      <c r="E74" s="66"/>
-      <c r="F74" s="65"/>
-      <c r="G74" s="66"/>
-      <c r="H74" s="66"/>
-      <c r="I74" s="66"/>
-      <c r="J74" s="66"/>
-      <c r="K74" s="66"/>
-      <c r="L74" s="66"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.15">
-      <c r="A75" s="65"/>
-      <c r="B75" s="65"/>
-      <c r="C75" s="66"/>
-      <c r="D75" s="66"/>
-      <c r="E75" s="66"/>
-      <c r="F75" s="65"/>
-      <c r="G75" s="66"/>
-      <c r="H75" s="66"/>
-      <c r="I75" s="66"/>
-      <c r="J75" s="66"/>
-      <c r="K75" s="66"/>
-      <c r="L75" s="66"/>
-    </row>
-    <row r="76" spans="1:12" ht="25" x14ac:dyDescent="0.25">
-      <c r="A76" s="39" t="s">
-        <v>41</v>
-      </c>
-      <c r="B76" s="39"/>
-      <c r="C76" s="39"/>
-      <c r="D76" s="39"/>
-      <c r="E76" s="39"/>
-      <c r="F76" s="39"/>
-      <c r="G76" s="39"/>
-      <c r="H76" s="39"/>
-      <c r="I76" s="39"/>
-      <c r="J76" s="39"/>
-      <c r="K76" s="39"/>
-      <c r="L76" s="39"/>
-    </row>
-    <row r="77" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A77" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="B77" s="41"/>
-      <c r="C77" s="41"/>
-      <c r="D77" s="41"/>
-      <c r="E77" s="41"/>
-      <c r="F77" s="42"/>
-      <c r="G77" s="43"/>
-      <c r="H77" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I77" s="41"/>
-      <c r="J77" s="41"/>
-      <c r="K77" s="41"/>
-      <c r="L77" s="41"/>
-    </row>
-    <row r="78" spans="1:12" s="72" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A78" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="B78" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="C78" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="D78" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="E78" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="F78" s="71"/>
-      <c r="G78" s="71"/>
-      <c r="H78" s="69" t="s">
-        <v>28</v>
-      </c>
-      <c r="I78" s="70" t="s">
-        <v>2</v>
-      </c>
-      <c r="J78" s="133" t="s">
-        <v>33</v>
-      </c>
-      <c r="K78" s="124" t="s">
-        <v>36</v>
-      </c>
-      <c r="L78" s="70" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A79" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="B79" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C79" s="134" t="s">
-        <v>19</v>
-      </c>
-      <c r="D79" s="114" t="s">
-        <v>80</v>
-      </c>
-      <c r="E79" s="88" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" s="44"/>
-      <c r="G79" s="49"/>
-      <c r="H79" s="67" t="s">
-        <v>131</v>
-      </c>
-      <c r="I79" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="J79" s="140" t="s">
-        <v>63</v>
-      </c>
-      <c r="K79" s="116" t="s">
-        <v>69</v>
-      </c>
-      <c r="L79" s="83" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A80" s="45"/>
-      <c r="B80" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="C80" s="135" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="84" t="s">
-        <v>7</v>
-      </c>
-      <c r="E80" s="97" t="s">
-        <v>4</v>
-      </c>
-      <c r="F80" s="44"/>
-      <c r="G80" s="49"/>
-      <c r="H80" s="67"/>
-      <c r="I80" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="J80" s="137" t="s">
-        <v>25</v>
-      </c>
-      <c r="K80" s="87" t="s">
-        <v>81</v>
-      </c>
-      <c r="L80" s="115" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" ht="21" x14ac:dyDescent="0.15">
-      <c r="A81" s="45"/>
-      <c r="B81" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="C81" s="136" t="s">
-        <v>66</v>
-      </c>
-      <c r="D81" s="116" t="s">
-        <v>72</v>
-      </c>
-      <c r="E81" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" s="44"/>
-      <c r="G81" s="49"/>
-      <c r="H81" s="67"/>
-      <c r="I81" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="142" t="s">
-        <v>18</v>
-      </c>
-      <c r="K81" s="114" t="s">
-        <v>82</v>
-      </c>
-      <c r="L81" s="88" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A82" s="45"/>
-      <c r="B82" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="C82" s="137" t="s">
-        <v>22</v>
-      </c>
-      <c r="D82" s="74" t="s">
-        <v>64</v>
-      </c>
-      <c r="E82" s="100" t="s">
-        <v>14</v>
-      </c>
-      <c r="F82" s="44"/>
-      <c r="G82" s="49"/>
-      <c r="H82" s="67"/>
-      <c r="I82" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="J82" s="135" t="s">
-        <v>11</v>
-      </c>
-      <c r="K82" s="84" t="s">
-        <v>74</v>
-      </c>
-      <c r="L82" s="97" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" ht="21" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="128"/>
-      <c r="B83" s="130" t="s">
-        <v>17</v>
-      </c>
-      <c r="C83" s="138" t="s">
-        <v>60</v>
-      </c>
-      <c r="D83" s="126" t="s">
-        <v>79</v>
-      </c>
-      <c r="E83" s="127" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="44"/>
-      <c r="G83" s="49"/>
-      <c r="H83" s="148"/>
-      <c r="I83" s="144" t="s">
-        <v>14</v>
-      </c>
-      <c r="J83" s="145" t="s">
-        <v>61</v>
-      </c>
-      <c r="K83" s="146" t="s">
-        <v>70</v>
-      </c>
-      <c r="L83" s="147" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" ht="21" thickTop="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="129" t="s">
-        <v>130</v>
-      </c>
-      <c r="B84" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="C84" s="139" t="s">
-        <v>9</v>
-      </c>
-      <c r="D84" s="132" t="s">
-        <v>6</v>
-      </c>
-      <c r="E84" s="131" t="s">
-        <v>4</v>
-      </c>
-      <c r="F84" s="44"/>
-      <c r="G84" s="49"/>
-      <c r="H84" s="59" t="s">
-        <v>130</v>
-      </c>
-      <c r="I84" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="J84" s="137" t="s">
-        <v>24</v>
-      </c>
-      <c r="K84" s="84" t="s">
-        <v>75</v>
-      </c>
-      <c r="L84" s="97" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A85" s="68"/>
-      <c r="B85" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="C85" s="140" t="s">
-        <v>67</v>
-      </c>
-      <c r="D85" s="116" t="s">
-        <v>71</v>
-      </c>
-      <c r="E85" s="83" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" s="44"/>
-      <c r="G85" s="49"/>
-      <c r="H85" s="64"/>
-      <c r="I85" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="J85" s="134" t="s">
-        <v>73</v>
-      </c>
-      <c r="K85" s="114" t="s">
-        <v>77</v>
-      </c>
-      <c r="L85" s="88" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A86" s="68"/>
-      <c r="B86" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="C86" s="137" t="s">
-        <v>23</v>
-      </c>
-      <c r="D86" s="96" t="s">
-        <v>16</v>
-      </c>
-      <c r="E86" s="105" t="s">
-        <v>15</v>
-      </c>
-      <c r="F86" s="44"/>
-      <c r="G86" s="49"/>
-      <c r="H86" s="64"/>
-      <c r="I86" s="98" t="s">
-        <v>5</v>
-      </c>
-      <c r="J86" s="135" t="s">
-        <v>10</v>
-      </c>
-      <c r="K86" s="84" t="s">
-        <v>124</v>
-      </c>
-      <c r="L86" s="97" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A87" s="68"/>
-      <c r="B87" s="73" t="s">
-        <v>17</v>
-      </c>
-      <c r="C87" s="134" t="s">
-        <v>59</v>
-      </c>
-      <c r="D87" s="114" t="s">
-        <v>78</v>
-      </c>
-      <c r="E87" s="88" t="s">
-        <v>13</v>
-      </c>
-      <c r="F87" s="44"/>
-      <c r="G87" s="49"/>
-      <c r="H87" s="64"/>
-      <c r="I87" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="J87" s="140" t="s">
-        <v>65</v>
-      </c>
-      <c r="K87" s="113" t="s">
-        <v>26</v>
-      </c>
-      <c r="L87" s="81" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" ht="20" x14ac:dyDescent="0.15">
-      <c r="A88" s="68"/>
-      <c r="B88" s="90" t="s">
-        <v>5</v>
-      </c>
-      <c r="C88" s="141" t="s">
-        <v>12</v>
-      </c>
-      <c r="D88" s="111" t="s">
-        <v>76</v>
-      </c>
-      <c r="E88" s="112" t="s">
-        <v>4</v>
-      </c>
-      <c r="F88" s="44"/>
-      <c r="G88" s="49"/>
-      <c r="H88" s="64"/>
-      <c r="I88" s="91" t="s">
-        <v>20</v>
-      </c>
-      <c r="J88" s="143" t="s">
-        <v>21</v>
-      </c>
-      <c r="K88" s="125" t="s">
-        <v>68</v>
-      </c>
-      <c r="L88" s="106" t="s">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="42">
-    <mergeCell ref="A76:L76"/>
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="H77:L77"/>
-    <mergeCell ref="A79:A83"/>
-    <mergeCell ref="H79:H83"/>
-    <mergeCell ref="A84:A88"/>
-    <mergeCell ref="H84:H88"/>
-    <mergeCell ref="A61:L61"/>
-    <mergeCell ref="A62:E62"/>
-    <mergeCell ref="H62:L62"/>
-    <mergeCell ref="A64:A68"/>
-    <mergeCell ref="H64:H68"/>
-    <mergeCell ref="A69:A73"/>
-    <mergeCell ref="H69:H73"/>
-    <mergeCell ref="A46:L46"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="H47:L47"/>
-    <mergeCell ref="A49:A53"/>
-    <mergeCell ref="H49:H53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="H54:H58"/>
-    <mergeCell ref="A31:L31"/>
-    <mergeCell ref="A32:E32"/>
-    <mergeCell ref="H32:L32"/>
-    <mergeCell ref="A34:A38"/>
-    <mergeCell ref="H34:H38"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="H39:H43"/>
-    <mergeCell ref="A16:L16"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="H17:L17"/>
-    <mergeCell ref="A19:A23"/>
-    <mergeCell ref="H19:H23"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="H24:H28"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="H2:L2"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="H4:H8"/>
-    <mergeCell ref="A9:A13"/>
-    <mergeCell ref="H9:H13"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5341441-BD61-1349-832E-175BFD75E11B}">
   <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -10690,7 +7371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B8B5130-A9A4-3D41-9E23-ABC295084148}">
   <dimension ref="A1:O134"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -10703,36 +7384,36 @@
   <sheetData>
     <row r="1" spans="1:15" ht="27" x14ac:dyDescent="0.35">
       <c r="A1" s="6"/>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
       <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
       <c r="F2" s="8"/>
       <c r="G2" s="9"/>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="31"/>
       <c r="L2" s="10"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.2">
@@ -10768,7 +7449,7 @@
     </row>
     <row r="4" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A4" s="7"/>
-      <c r="B4" s="35" t="s">
+      <c r="B4" s="36" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="14" t="s">
@@ -10782,7 +7463,7 @@
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>44</v>
       </c>
       <c r="I4" s="14" t="s">
@@ -10798,7 +7479,7 @@
     </row>
     <row r="5" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
-      <c r="B5" s="36"/>
+      <c r="B5" s="37"/>
       <c r="C5" s="14" t="s">
         <v>5</v>
       </c>
@@ -10810,7 +7491,7 @@
       </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="36"/>
+      <c r="H5" s="37"/>
       <c r="I5" s="14" t="s">
         <v>5</v>
       </c>
@@ -10824,7 +7505,7 @@
     </row>
     <row r="6" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
-      <c r="B6" s="36"/>
+      <c r="B6" s="37"/>
       <c r="C6" s="14" t="s">
         <v>14</v>
       </c>
@@ -10836,7 +7517,7 @@
       </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="36"/>
+      <c r="H6" s="37"/>
       <c r="I6" s="14" t="s">
         <v>14</v>
       </c>
@@ -10850,7 +7531,7 @@
     </row>
     <row r="7" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
-      <c r="B7" s="36"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="14" t="s">
         <v>20</v>
       </c>
@@ -10862,7 +7543,7 @@
       </c>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="36"/>
+      <c r="H7" s="37"/>
       <c r="I7" s="14" t="s">
         <v>20</v>
       </c>
@@ -10876,7 +7557,7 @@
     </row>
     <row r="8" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A8" s="7"/>
-      <c r="B8" s="36"/>
+      <c r="B8" s="37"/>
       <c r="C8" s="14" t="s">
         <v>15</v>
       </c>
@@ -10888,7 +7569,7 @@
       </c>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="36"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="14" t="s">
         <v>15</v>
       </c>
@@ -10902,7 +7583,7 @@
     </row>
     <row r="9" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
-      <c r="B9" s="36"/>
+      <c r="B9" s="37"/>
       <c r="C9" s="14" t="s">
         <v>13</v>
       </c>
@@ -10914,7 +7595,7 @@
       </c>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="36"/>
+      <c r="H9" s="37"/>
       <c r="I9" s="14" t="s">
         <v>13</v>
       </c>
@@ -10928,7 +7609,7 @@
     </row>
     <row r="10" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
-      <c r="B10" s="36"/>
+      <c r="B10" s="37"/>
       <c r="C10" s="14" t="s">
         <v>4</v>
       </c>
@@ -10940,7 +7621,7 @@
       </c>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
-      <c r="H10" s="36"/>
+      <c r="H10" s="37"/>
       <c r="I10" s="14" t="s">
         <v>4</v>
       </c>
@@ -10954,7 +7635,7 @@
     </row>
     <row r="11" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
-      <c r="B11" s="37"/>
+      <c r="B11" s="38"/>
       <c r="C11" s="14" t="s">
         <v>27</v>
       </c>
@@ -10966,7 +7647,7 @@
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="37"/>
+      <c r="H11" s="38"/>
       <c r="I11" s="14" t="s">
         <v>27</v>
       </c>
@@ -10980,7 +7661,7 @@
     </row>
     <row r="12" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
-      <c r="B12" s="35" t="s">
+      <c r="B12" s="36" t="s">
         <v>45</v>
       </c>
       <c r="C12" s="14" t="s">
@@ -10994,7 +7675,7 @@
       </c>
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
-      <c r="H12" s="35" t="s">
+      <c r="H12" s="36" t="s">
         <v>45</v>
       </c>
       <c r="I12" s="14" t="s">
@@ -11010,7 +7691,7 @@
     </row>
     <row r="13" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
-      <c r="B13" s="36"/>
+      <c r="B13" s="37"/>
       <c r="C13" s="14" t="s">
         <v>5</v>
       </c>
@@ -11022,7 +7703,7 @@
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="36"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="14" t="s">
         <v>5</v>
       </c>
@@ -11036,7 +7717,7 @@
     </row>
     <row r="14" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A14" s="7"/>
-      <c r="B14" s="36"/>
+      <c r="B14" s="37"/>
       <c r="C14" s="14" t="s">
         <v>14</v>
       </c>
@@ -11048,7 +7729,7 @@
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
-      <c r="H14" s="36"/>
+      <c r="H14" s="37"/>
       <c r="I14" s="14" t="s">
         <v>14</v>
       </c>
@@ -11062,7 +7743,7 @@
     </row>
     <row r="15" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A15" s="7"/>
-      <c r="B15" s="36"/>
+      <c r="B15" s="37"/>
       <c r="C15" s="14" t="s">
         <v>20</v>
       </c>
@@ -11074,7 +7755,7 @@
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="36"/>
+      <c r="H15" s="37"/>
       <c r="I15" s="14" t="s">
         <v>20</v>
       </c>
@@ -11088,7 +7769,7 @@
     </row>
     <row r="16" spans="1:15" ht="22" x14ac:dyDescent="0.2">
       <c r="A16" s="7"/>
-      <c r="B16" s="36"/>
+      <c r="B16" s="37"/>
       <c r="C16" s="14" t="s">
         <v>15</v>
       </c>
@@ -11100,7 +7781,7 @@
       </c>
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
-      <c r="H16" s="36"/>
+      <c r="H16" s="37"/>
       <c r="I16" s="14" t="s">
         <v>15</v>
       </c>
@@ -11114,7 +7795,7 @@
     </row>
     <row r="17" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
-      <c r="B17" s="36"/>
+      <c r="B17" s="37"/>
       <c r="C17" s="14" t="s">
         <v>13</v>
       </c>
@@ -11126,7 +7807,7 @@
       </c>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="36"/>
+      <c r="H17" s="37"/>
       <c r="I17" s="14" t="s">
         <v>13</v>
       </c>
@@ -11140,7 +7821,7 @@
     </row>
     <row r="18" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A18" s="7"/>
-      <c r="B18" s="36"/>
+      <c r="B18" s="37"/>
       <c r="C18" s="14" t="s">
         <v>4</v>
       </c>
@@ -11152,7 +7833,7 @@
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
-      <c r="H18" s="36"/>
+      <c r="H18" s="37"/>
       <c r="I18" s="14" t="s">
         <v>4</v>
       </c>
@@ -11166,7 +7847,7 @@
     </row>
     <row r="19" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
-      <c r="B19" s="37"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="14" t="s">
         <v>27</v>
       </c>
@@ -11178,7 +7859,7 @@
       </c>
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="37"/>
+      <c r="H19" s="38"/>
       <c r="I19" s="14" t="s">
         <v>27</v>
       </c>
@@ -11192,7 +7873,7 @@
     </row>
     <row r="20" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="36" t="s">
         <v>46</v>
       </c>
       <c r="C20" s="14" t="s">
@@ -11206,7 +7887,7 @@
       </c>
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
-      <c r="H20" s="35" t="s">
+      <c r="H20" s="36" t="s">
         <v>46</v>
       </c>
       <c r="I20" s="14" t="s">
@@ -11222,7 +7903,7 @@
     </row>
     <row r="21" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
-      <c r="B21" s="36"/>
+      <c r="B21" s="37"/>
       <c r="C21" s="14" t="s">
         <v>5</v>
       </c>
@@ -11234,7 +7915,7 @@
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
-      <c r="H21" s="36"/>
+      <c r="H21" s="37"/>
       <c r="I21" s="14" t="s">
         <v>5</v>
       </c>
@@ -11248,7 +7929,7 @@
     </row>
     <row r="22" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
-      <c r="B22" s="36"/>
+      <c r="B22" s="37"/>
       <c r="C22" s="14" t="s">
         <v>14</v>
       </c>
@@ -11260,7 +7941,7 @@
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
-      <c r="H22" s="36"/>
+      <c r="H22" s="37"/>
       <c r="I22" s="14" t="s">
         <v>14</v>
       </c>
@@ -11274,7 +7955,7 @@
     </row>
     <row r="23" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A23" s="7"/>
-      <c r="B23" s="36"/>
+      <c r="B23" s="37"/>
       <c r="C23" s="14" t="s">
         <v>20</v>
       </c>
@@ -11286,7 +7967,7 @@
       </c>
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
-      <c r="H23" s="36"/>
+      <c r="H23" s="37"/>
       <c r="I23" s="14" t="s">
         <v>20</v>
       </c>
@@ -11300,7 +7981,7 @@
     </row>
     <row r="24" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
-      <c r="B24" s="36"/>
+      <c r="B24" s="37"/>
       <c r="C24" s="14" t="s">
         <v>15</v>
       </c>
@@ -11312,7 +7993,7 @@
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
-      <c r="H24" s="36"/>
+      <c r="H24" s="37"/>
       <c r="I24" s="14" t="s">
         <v>15</v>
       </c>
@@ -11326,7 +8007,7 @@
     </row>
     <row r="25" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
-      <c r="B25" s="36"/>
+      <c r="B25" s="37"/>
       <c r="C25" s="14" t="s">
         <v>13</v>
       </c>
@@ -11338,7 +8019,7 @@
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="36"/>
+      <c r="H25" s="37"/>
       <c r="I25" s="14" t="s">
         <v>27</v>
       </c>
@@ -11352,7 +8033,7 @@
     </row>
     <row r="26" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A26" s="7"/>
-      <c r="B26" s="36"/>
+      <c r="B26" s="37"/>
       <c r="C26" s="14" t="s">
         <v>4</v>
       </c>
@@ -11364,7 +8045,7 @@
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
-      <c r="H26" s="36"/>
+      <c r="H26" s="37"/>
       <c r="I26" s="14"/>
       <c r="J26" s="14"/>
       <c r="K26" s="15"/>
@@ -11372,7 +8053,7 @@
     </row>
     <row r="27" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A27" s="7"/>
-      <c r="B27" s="37"/>
+      <c r="B27" s="38"/>
       <c r="C27" s="14" t="s">
         <v>27</v>
       </c>
@@ -11384,7 +8065,7 @@
       </c>
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
-      <c r="H27" s="37"/>
+      <c r="H27" s="38"/>
       <c r="I27" s="14"/>
       <c r="J27" s="14"/>
       <c r="K27" s="15"/>
@@ -11420,36 +8101,36 @@
     </row>
     <row r="30" spans="1:12" ht="27" x14ac:dyDescent="0.35">
       <c r="A30" s="6"/>
-      <c r="B30" s="29" t="s">
+      <c r="B30" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
+      <c r="C30" s="30"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="30"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="30"/>
+      <c r="I30" s="30"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="30"/>
       <c r="L30" s="5"/>
     </row>
     <row r="31" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A31" s="7"/>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
+      <c r="E31" s="31"/>
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
-      <c r="H31" s="30" t="s">
+      <c r="H31" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
       <c r="L31" s="10"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -11484,7 +8165,7 @@
     </row>
     <row r="33" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A33" s="7"/>
-      <c r="B33" s="35" t="s">
+      <c r="B33" s="36" t="s">
         <v>50</v>
       </c>
       <c r="C33" s="14" t="s">
@@ -11498,7 +8179,7 @@
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
-      <c r="H33" s="35" t="s">
+      <c r="H33" s="36" t="s">
         <v>50</v>
       </c>
       <c r="I33" s="14" t="s">
@@ -11514,7 +8195,7 @@
     </row>
     <row r="34" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A34" s="7"/>
-      <c r="B34" s="36"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="14" t="s">
         <v>5</v>
       </c>
@@ -11526,7 +8207,7 @@
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
-      <c r="H34" s="36"/>
+      <c r="H34" s="37"/>
       <c r="I34" s="14" t="s">
         <v>5</v>
       </c>
@@ -11540,7 +8221,7 @@
     </row>
     <row r="35" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A35" s="7"/>
-      <c r="B35" s="36"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="14" t="s">
         <v>14</v>
       </c>
@@ -11552,7 +8233,7 @@
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
-      <c r="H35" s="36"/>
+      <c r="H35" s="37"/>
       <c r="I35" s="14" t="s">
         <v>14</v>
       </c>
@@ -11566,7 +8247,7 @@
     </row>
     <row r="36" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A36" s="7"/>
-      <c r="B36" s="36"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="14" t="s">
         <v>20</v>
       </c>
@@ -11578,7 +8259,7 @@
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
-      <c r="H36" s="36"/>
+      <c r="H36" s="37"/>
       <c r="I36" s="14" t="s">
         <v>20</v>
       </c>
@@ -11592,7 +8273,7 @@
     </row>
     <row r="37" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A37" s="7"/>
-      <c r="B37" s="36"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="14" t="s">
         <v>15</v>
       </c>
@@ -11604,7 +8285,7 @@
       </c>
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
-      <c r="H37" s="36"/>
+      <c r="H37" s="37"/>
       <c r="I37" s="14" t="s">
         <v>15</v>
       </c>
@@ -11618,7 +8299,7 @@
     </row>
     <row r="38" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A38" s="7"/>
-      <c r="B38" s="36"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="14" t="s">
         <v>13</v>
       </c>
@@ -11630,7 +8311,7 @@
       </c>
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
-      <c r="H38" s="36"/>
+      <c r="H38" s="37"/>
       <c r="I38" s="14" t="s">
         <v>13</v>
       </c>
@@ -11644,7 +8325,7 @@
     </row>
     <row r="39" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A39" s="7"/>
-      <c r="B39" s="36"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="14" t="s">
         <v>4</v>
       </c>
@@ -11656,7 +8337,7 @@
       </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
-      <c r="H39" s="36"/>
+      <c r="H39" s="37"/>
       <c r="I39" s="14" t="s">
         <v>4</v>
       </c>
@@ -11670,7 +8351,7 @@
     </row>
     <row r="40" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
-      <c r="B40" s="37"/>
+      <c r="B40" s="38"/>
       <c r="C40" s="14" t="s">
         <v>27</v>
       </c>
@@ -11682,7 +8363,7 @@
       </c>
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
-      <c r="H40" s="37"/>
+      <c r="H40" s="38"/>
       <c r="I40" s="14" t="s">
         <v>27</v>
       </c>
@@ -11696,7 +8377,7 @@
     </row>
     <row r="41" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A41" s="7"/>
-      <c r="B41" s="35" t="s">
+      <c r="B41" s="36" t="s">
         <v>51</v>
       </c>
       <c r="C41" s="14" t="s">
@@ -11710,7 +8391,7 @@
       </c>
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
-      <c r="H41" s="35" t="s">
+      <c r="H41" s="36" t="s">
         <v>51</v>
       </c>
       <c r="I41" s="14" t="s">
@@ -11726,7 +8407,7 @@
     </row>
     <row r="42" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A42" s="7"/>
-      <c r="B42" s="36"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="14" t="s">
         <v>5</v>
       </c>
@@ -11738,7 +8419,7 @@
       </c>
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
-      <c r="H42" s="36"/>
+      <c r="H42" s="37"/>
       <c r="I42" s="14" t="s">
         <v>5</v>
       </c>
@@ -11752,7 +8433,7 @@
     </row>
     <row r="43" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A43" s="7"/>
-      <c r="B43" s="36"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="14" t="s">
         <v>14</v>
       </c>
@@ -11764,7 +8445,7 @@
       </c>
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
-      <c r="H43" s="36"/>
+      <c r="H43" s="37"/>
       <c r="I43" s="14" t="s">
         <v>14</v>
       </c>
@@ -11778,7 +8459,7 @@
     </row>
     <row r="44" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A44" s="7"/>
-      <c r="B44" s="36"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="14" t="s">
         <v>20</v>
       </c>
@@ -11790,7 +8471,7 @@
       </c>
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
-      <c r="H44" s="36"/>
+      <c r="H44" s="37"/>
       <c r="I44" s="14" t="s">
         <v>20</v>
       </c>
@@ -11804,7 +8485,7 @@
     </row>
     <row r="45" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A45" s="7"/>
-      <c r="B45" s="36"/>
+      <c r="B45" s="37"/>
       <c r="C45" s="14" t="s">
         <v>15</v>
       </c>
@@ -11816,7 +8497,7 @@
       </c>
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
-      <c r="H45" s="36"/>
+      <c r="H45" s="37"/>
       <c r="I45" s="14" t="s">
         <v>15</v>
       </c>
@@ -11830,7 +8511,7 @@
     </row>
     <row r="46" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A46" s="7"/>
-      <c r="B46" s="36"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="14" t="s">
         <v>13</v>
       </c>
@@ -11842,7 +8523,7 @@
       </c>
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
-      <c r="H46" s="36"/>
+      <c r="H46" s="37"/>
       <c r="I46" s="14" t="s">
         <v>13</v>
       </c>
@@ -11856,7 +8537,7 @@
     </row>
     <row r="47" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A47" s="7"/>
-      <c r="B47" s="36"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="14" t="s">
         <v>4</v>
       </c>
@@ -11868,7 +8549,7 @@
       </c>
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
-      <c r="H47" s="36"/>
+      <c r="H47" s="37"/>
       <c r="I47" s="14" t="s">
         <v>4</v>
       </c>
@@ -11882,7 +8563,7 @@
     </row>
     <row r="48" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A48" s="7"/>
-      <c r="B48" s="37"/>
+      <c r="B48" s="38"/>
       <c r="C48" s="14" t="s">
         <v>27</v>
       </c>
@@ -11894,7 +8575,7 @@
       </c>
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
-      <c r="H48" s="37"/>
+      <c r="H48" s="38"/>
       <c r="I48" s="14" t="s">
         <v>27</v>
       </c>
@@ -11908,7 +8589,7 @@
     </row>
     <row r="49" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A49" s="7"/>
-      <c r="B49" s="35" t="s">
+      <c r="B49" s="36" t="s">
         <v>52</v>
       </c>
       <c r="C49" s="14" t="s">
@@ -11922,7 +8603,7 @@
       </c>
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
-      <c r="H49" s="35" t="s">
+      <c r="H49" s="36" t="s">
         <v>52</v>
       </c>
       <c r="I49" s="14" t="s">
@@ -11938,7 +8619,7 @@
     </row>
     <row r="50" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
-      <c r="B50" s="36"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="14" t="s">
         <v>5</v>
       </c>
@@ -11950,7 +8631,7 @@
       </c>
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
-      <c r="H50" s="36"/>
+      <c r="H50" s="37"/>
       <c r="I50" s="14" t="s">
         <v>5</v>
       </c>
@@ -11964,7 +8645,7 @@
     </row>
     <row r="51" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A51" s="7"/>
-      <c r="B51" s="36"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="14" t="s">
         <v>14</v>
       </c>
@@ -11976,7 +8657,7 @@
       </c>
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
-      <c r="H51" s="36"/>
+      <c r="H51" s="37"/>
       <c r="I51" s="14" t="s">
         <v>14</v>
       </c>
@@ -11990,7 +8671,7 @@
     </row>
     <row r="52" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A52" s="7"/>
-      <c r="B52" s="36"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="14" t="s">
         <v>20</v>
       </c>
@@ -12002,7 +8683,7 @@
       </c>
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
-      <c r="H52" s="36"/>
+      <c r="H52" s="37"/>
       <c r="I52" s="14" t="s">
         <v>20</v>
       </c>
@@ -12016,7 +8697,7 @@
     </row>
     <row r="53" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A53" s="7"/>
-      <c r="B53" s="36"/>
+      <c r="B53" s="37"/>
       <c r="C53" s="14" t="s">
         <v>15</v>
       </c>
@@ -12028,7 +8709,7 @@
       </c>
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
-      <c r="H53" s="36"/>
+      <c r="H53" s="37"/>
       <c r="I53" s="14" t="s">
         <v>15</v>
       </c>
@@ -12042,7 +8723,7 @@
     </row>
     <row r="54" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A54" s="7"/>
-      <c r="B54" s="36"/>
+      <c r="B54" s="37"/>
       <c r="C54" s="14" t="s">
         <v>13</v>
       </c>
@@ -12054,7 +8735,7 @@
       </c>
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
-      <c r="H54" s="36"/>
+      <c r="H54" s="37"/>
       <c r="I54" s="14" t="s">
         <v>27</v>
       </c>
@@ -12068,7 +8749,7 @@
     </row>
     <row r="55" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A55" s="7"/>
-      <c r="B55" s="36"/>
+      <c r="B55" s="37"/>
       <c r="C55" s="14" t="s">
         <v>4</v>
       </c>
@@ -12080,7 +8761,7 @@
       </c>
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
-      <c r="H55" s="36"/>
+      <c r="H55" s="37"/>
       <c r="I55" s="14"/>
       <c r="J55" s="14"/>
       <c r="K55" s="15"/>
@@ -12088,7 +8769,7 @@
     </row>
     <row r="56" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A56" s="7"/>
-      <c r="B56" s="37"/>
+      <c r="B56" s="38"/>
       <c r="C56" s="14" t="s">
         <v>27</v>
       </c>
@@ -12100,7 +8781,7 @@
       </c>
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
-      <c r="H56" s="37"/>
+      <c r="H56" s="38"/>
       <c r="I56" s="14"/>
       <c r="J56" s="14"/>
       <c r="K56" s="15"/>
@@ -12136,36 +8817,36 @@
     </row>
     <row r="59" spans="1:12" ht="27" x14ac:dyDescent="0.35">
       <c r="A59" s="6"/>
-      <c r="B59" s="29" t="s">
+      <c r="B59" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
-      <c r="F59" s="29"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="29"/>
-      <c r="I59" s="29"/>
-      <c r="J59" s="29"/>
-      <c r="K59" s="29"/>
+      <c r="C59" s="30"/>
+      <c r="D59" s="30"/>
+      <c r="E59" s="30"/>
+      <c r="F59" s="30"/>
+      <c r="G59" s="30"/>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30"/>
+      <c r="J59" s="30"/>
+      <c r="K59" s="30"/>
       <c r="L59" s="5"/>
     </row>
     <row r="60" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
-      <c r="B60" s="30" t="s">
+      <c r="B60" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="31"/>
       <c r="F60" s="8"/>
       <c r="G60" s="9"/>
-      <c r="H60" s="30" t="s">
+      <c r="H60" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="I60" s="30"/>
-      <c r="J60" s="30"/>
-      <c r="K60" s="30"/>
+      <c r="I60" s="31"/>
+      <c r="J60" s="31"/>
+      <c r="K60" s="31"/>
       <c r="L60" s="10"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
@@ -12200,7 +8881,7 @@
     </row>
     <row r="62" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A62" s="7"/>
-      <c r="B62" s="35" t="s">
+      <c r="B62" s="36" t="s">
         <v>53</v>
       </c>
       <c r="C62" s="14" t="s">
@@ -12214,7 +8895,7 @@
       </c>
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
-      <c r="H62" s="35" t="s">
+      <c r="H62" s="36" t="s">
         <v>53</v>
       </c>
       <c r="I62" s="14" t="s">
@@ -12230,7 +8911,7 @@
     </row>
     <row r="63" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A63" s="7"/>
-      <c r="B63" s="36"/>
+      <c r="B63" s="37"/>
       <c r="C63" s="14" t="s">
         <v>5</v>
       </c>
@@ -12242,7 +8923,7 @@
       </c>
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
-      <c r="H63" s="36"/>
+      <c r="H63" s="37"/>
       <c r="I63" s="14" t="s">
         <v>5</v>
       </c>
@@ -12256,7 +8937,7 @@
     </row>
     <row r="64" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A64" s="7"/>
-      <c r="B64" s="36"/>
+      <c r="B64" s="37"/>
       <c r="C64" s="14" t="s">
         <v>14</v>
       </c>
@@ -12268,7 +8949,7 @@
       </c>
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
-      <c r="H64" s="36"/>
+      <c r="H64" s="37"/>
       <c r="I64" s="14" t="s">
         <v>14</v>
       </c>
@@ -12282,7 +8963,7 @@
     </row>
     <row r="65" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A65" s="7"/>
-      <c r="B65" s="36"/>
+      <c r="B65" s="37"/>
       <c r="C65" s="14" t="s">
         <v>20</v>
       </c>
@@ -12294,7 +8975,7 @@
       </c>
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
-      <c r="H65" s="36"/>
+      <c r="H65" s="37"/>
       <c r="I65" s="14" t="s">
         <v>20</v>
       </c>
@@ -12308,7 +8989,7 @@
     </row>
     <row r="66" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A66" s="7"/>
-      <c r="B66" s="36"/>
+      <c r="B66" s="37"/>
       <c r="C66" s="14" t="s">
         <v>15</v>
       </c>
@@ -12320,7 +9001,7 @@
       </c>
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
-      <c r="H66" s="36"/>
+      <c r="H66" s="37"/>
       <c r="I66" s="14" t="s">
         <v>15</v>
       </c>
@@ -12334,7 +9015,7 @@
     </row>
     <row r="67" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A67" s="7"/>
-      <c r="B67" s="36"/>
+      <c r="B67" s="37"/>
       <c r="C67" s="14" t="s">
         <v>13</v>
       </c>
@@ -12346,7 +9027,7 @@
       </c>
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
-      <c r="H67" s="36"/>
+      <c r="H67" s="37"/>
       <c r="I67" s="14" t="s">
         <v>13</v>
       </c>
@@ -12360,7 +9041,7 @@
     </row>
     <row r="68" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A68" s="7"/>
-      <c r="B68" s="36"/>
+      <c r="B68" s="37"/>
       <c r="C68" s="14" t="s">
         <v>4</v>
       </c>
@@ -12372,7 +9053,7 @@
       </c>
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
-      <c r="H68" s="36"/>
+      <c r="H68" s="37"/>
       <c r="I68" s="14" t="s">
         <v>4</v>
       </c>
@@ -12386,7 +9067,7 @@
     </row>
     <row r="69" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A69" s="7"/>
-      <c r="B69" s="37"/>
+      <c r="B69" s="38"/>
       <c r="C69" s="14" t="s">
         <v>27</v>
       </c>
@@ -12398,7 +9079,7 @@
       </c>
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
-      <c r="H69" s="37"/>
+      <c r="H69" s="38"/>
       <c r="I69" s="14" t="s">
         <v>27</v>
       </c>
@@ -12412,7 +9093,7 @@
     </row>
     <row r="70" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
-      <c r="B70" s="35" t="s">
+      <c r="B70" s="36" t="s">
         <v>54</v>
       </c>
       <c r="C70" s="14" t="s">
@@ -12426,7 +9107,7 @@
       </c>
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
-      <c r="H70" s="35" t="s">
+      <c r="H70" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I70" s="14" t="s">
@@ -12442,7 +9123,7 @@
     </row>
     <row r="71" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A71" s="7"/>
-      <c r="B71" s="36"/>
+      <c r="B71" s="37"/>
       <c r="C71" s="14" t="s">
         <v>5</v>
       </c>
@@ -12454,7 +9135,7 @@
       </c>
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
-      <c r="H71" s="36"/>
+      <c r="H71" s="37"/>
       <c r="I71" s="14" t="s">
         <v>5</v>
       </c>
@@ -12468,7 +9149,7 @@
     </row>
     <row r="72" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A72" s="7"/>
-      <c r="B72" s="36"/>
+      <c r="B72" s="37"/>
       <c r="C72" s="14" t="s">
         <v>14</v>
       </c>
@@ -12480,7 +9161,7 @@
       </c>
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
-      <c r="H72" s="36"/>
+      <c r="H72" s="37"/>
       <c r="I72" s="14" t="s">
         <v>14</v>
       </c>
@@ -12494,7 +9175,7 @@
     </row>
     <row r="73" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A73" s="7"/>
-      <c r="B73" s="36"/>
+      <c r="B73" s="37"/>
       <c r="C73" s="14" t="s">
         <v>20</v>
       </c>
@@ -12506,7 +9187,7 @@
       </c>
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
-      <c r="H73" s="36"/>
+      <c r="H73" s="37"/>
       <c r="I73" s="14" t="s">
         <v>20</v>
       </c>
@@ -12520,7 +9201,7 @@
     </row>
     <row r="74" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A74" s="7"/>
-      <c r="B74" s="36"/>
+      <c r="B74" s="37"/>
       <c r="C74" s="14" t="s">
         <v>15</v>
       </c>
@@ -12532,7 +9213,7 @@
       </c>
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
-      <c r="H74" s="36"/>
+      <c r="H74" s="37"/>
       <c r="I74" s="14" t="s">
         <v>15</v>
       </c>
@@ -12546,7 +9227,7 @@
     </row>
     <row r="75" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A75" s="7"/>
-      <c r="B75" s="36"/>
+      <c r="B75" s="37"/>
       <c r="C75" s="14" t="s">
         <v>13</v>
       </c>
@@ -12558,7 +9239,7 @@
       </c>
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
-      <c r="H75" s="36"/>
+      <c r="H75" s="37"/>
       <c r="I75" s="14" t="s">
         <v>13</v>
       </c>
@@ -12572,7 +9253,7 @@
     </row>
     <row r="76" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A76" s="7"/>
-      <c r="B76" s="36"/>
+      <c r="B76" s="37"/>
       <c r="C76" s="14" t="s">
         <v>4</v>
       </c>
@@ -12584,7 +9265,7 @@
       </c>
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
-      <c r="H76" s="36"/>
+      <c r="H76" s="37"/>
       <c r="I76" s="14" t="s">
         <v>4</v>
       </c>
@@ -12598,7 +9279,7 @@
     </row>
     <row r="77" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A77" s="7"/>
-      <c r="B77" s="37"/>
+      <c r="B77" s="38"/>
       <c r="C77" s="14" t="s">
         <v>27</v>
       </c>
@@ -12610,7 +9291,7 @@
       </c>
       <c r="F77" s="7"/>
       <c r="G77" s="7"/>
-      <c r="H77" s="37"/>
+      <c r="H77" s="38"/>
       <c r="I77" s="14" t="s">
         <v>27</v>
       </c>
@@ -12624,7 +9305,7 @@
     </row>
     <row r="78" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A78" s="7"/>
-      <c r="B78" s="35" t="s">
+      <c r="B78" s="36" t="s">
         <v>55</v>
       </c>
       <c r="C78" s="14" t="s">
@@ -12638,7 +9319,7 @@
       </c>
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
-      <c r="H78" s="35" t="s">
+      <c r="H78" s="36" t="s">
         <v>55</v>
       </c>
       <c r="I78" s="14" t="s">
@@ -12654,7 +9335,7 @@
     </row>
     <row r="79" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A79" s="7"/>
-      <c r="B79" s="36"/>
+      <c r="B79" s="37"/>
       <c r="C79" s="14" t="s">
         <v>5</v>
       </c>
@@ -12666,7 +9347,7 @@
       </c>
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
-      <c r="H79" s="36"/>
+      <c r="H79" s="37"/>
       <c r="I79" s="14" t="s">
         <v>5</v>
       </c>
@@ -12680,7 +9361,7 @@
     </row>
     <row r="80" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
-      <c r="B80" s="36"/>
+      <c r="B80" s="37"/>
       <c r="C80" s="14" t="s">
         <v>14</v>
       </c>
@@ -12692,7 +9373,7 @@
       </c>
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
-      <c r="H80" s="36"/>
+      <c r="H80" s="37"/>
       <c r="I80" s="14" t="s">
         <v>14</v>
       </c>
@@ -12706,7 +9387,7 @@
     </row>
     <row r="81" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A81" s="7"/>
-      <c r="B81" s="36"/>
+      <c r="B81" s="37"/>
       <c r="C81" s="14" t="s">
         <v>20</v>
       </c>
@@ -12718,7 +9399,7 @@
       </c>
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
-      <c r="H81" s="36"/>
+      <c r="H81" s="37"/>
       <c r="I81" s="14" t="s">
         <v>20</v>
       </c>
@@ -12732,7 +9413,7 @@
     </row>
     <row r="82" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A82" s="7"/>
-      <c r="B82" s="36"/>
+      <c r="B82" s="37"/>
       <c r="C82" s="14" t="s">
         <v>15</v>
       </c>
@@ -12744,7 +9425,7 @@
       </c>
       <c r="F82" s="7"/>
       <c r="G82" s="7"/>
-      <c r="H82" s="36"/>
+      <c r="H82" s="37"/>
       <c r="I82" s="14" t="s">
         <v>15</v>
       </c>
@@ -12758,7 +9439,7 @@
     </row>
     <row r="83" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A83" s="7"/>
-      <c r="B83" s="36"/>
+      <c r="B83" s="37"/>
       <c r="C83" s="14" t="s">
         <v>13</v>
       </c>
@@ -12770,7 +9451,7 @@
       </c>
       <c r="F83" s="7"/>
       <c r="G83" s="7"/>
-      <c r="H83" s="36"/>
+      <c r="H83" s="37"/>
       <c r="I83" s="14" t="s">
         <v>27</v>
       </c>
@@ -12784,7 +9465,7 @@
     </row>
     <row r="84" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A84" s="7"/>
-      <c r="B84" s="36"/>
+      <c r="B84" s="37"/>
       <c r="C84" s="14" t="s">
         <v>4</v>
       </c>
@@ -12796,7 +9477,7 @@
       </c>
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
-      <c r="H84" s="36"/>
+      <c r="H84" s="37"/>
       <c r="I84" s="14"/>
       <c r="J84" s="14"/>
       <c r="K84" s="15"/>
@@ -12804,7 +9485,7 @@
     </row>
     <row r="85" spans="1:12" ht="22" x14ac:dyDescent="0.2">
       <c r="A85" s="7"/>
-      <c r="B85" s="37"/>
+      <c r="B85" s="38"/>
       <c r="C85" s="14" t="s">
         <v>27</v>
       </c>
@@ -12816,7 +9497,7 @@
       </c>
       <c r="F85" s="7"/>
       <c r="G85" s="7"/>
-      <c r="H85" s="37"/>
+      <c r="H85" s="38"/>
       <c r="I85" s="14"/>
       <c r="J85" s="14"/>
       <c r="K85" s="15"/>
@@ -14318,6 +10999,18 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B30:K30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="H31:K31"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="H2:K2"/>
+    <mergeCell ref="B4:B11"/>
+    <mergeCell ref="H4:H11"/>
+    <mergeCell ref="B12:B19"/>
+    <mergeCell ref="H12:H19"/>
+    <mergeCell ref="B20:B27"/>
+    <mergeCell ref="H20:H27"/>
     <mergeCell ref="B33:B40"/>
     <mergeCell ref="H33:H40"/>
     <mergeCell ref="B78:B85"/>
@@ -14333,24 +11026,12 @@
     <mergeCell ref="H49:H56"/>
     <mergeCell ref="B62:B69"/>
     <mergeCell ref="H62:H69"/>
-    <mergeCell ref="B30:K30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="H31:K31"/>
-    <mergeCell ref="B1:K1"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="H2:K2"/>
-    <mergeCell ref="B4:B11"/>
-    <mergeCell ref="H4:H11"/>
-    <mergeCell ref="B12:B19"/>
-    <mergeCell ref="H12:H19"/>
-    <mergeCell ref="B20:B27"/>
-    <mergeCell ref="H20:H27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00503793-7682-CB44-ADC3-931E59EDC6C9}">
   <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -15171,7 +11852,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5009128B-BC04-AE43-96E7-DEE798181085}">
   <dimension ref="A1:C41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -15634,6 +12315,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
+    <f8e6109263404e4da1831cd151bd9fd5 xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </f8e6109263404e4da1831cd151bd9fd5>
+    <kd8ebdb17ae1461db4d8c38e130fcffb xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </kd8ebdb17ae1461db4d8c38e130fcffb>
+    <AnzeigeStartseite xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001FDB85367C20A4499C08F4CA4D5990E0" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="3dd10242c9d5248a8f685c250a5fc978">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4af33632-ae06-419a-9cde-c132ea01998a" xmlns:ns3="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c3e60e7f399f82dd53caaf2d567bcde1" ns2:_="" ns3:_="">
     <xsd:import namespace="4af33632-ae06-419a-9cde-c132ea01998a"/>
@@ -15880,29 +12584,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
-    <f8e6109263404e4da1831cd151bd9fd5 xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </f8e6109263404e4da1831cd151bd9fd5>
-    <kd8ebdb17ae1461db4d8c38e130fcffb xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </kd8ebdb17ae1461db4d8c38e130fcffb>
-    <AnzeigeStartseite xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -15913,6 +12594,31 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33E82EA-34B8-478E-90E7-7586E722C072}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4af33632-ae06-419a-9cde-c132ea01998a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{067E30AD-6895-4D50-B36C-27DC78AA4545}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15931,31 +12637,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33E82EA-34B8-478E-90E7-7586E722C072}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4af33632-ae06-419a-9cde-c132ea01998a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
   <ds:schemaRefs>

--- a/KWI-RoboChallenge_Rangliste.xlsx
+++ b/KWI-RoboChallenge_Rangliste.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C05664A8-F825-D046-B22E-B81C5E377990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB1E81F-7047-0446-9593-7144F1390565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Linienfolger-Resultate" sheetId="15" r:id="rId1"/>
@@ -641,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -706,6 +706,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -718,10 +724,13 @@
     <xf numFmtId="20" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2168,57 +2177,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="27" x14ac:dyDescent="0.35">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
       <c r="V1" s="24"/>
       <c r="W1" s="5"/>
     </row>
     <row r="2" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A2" s="7"/>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
       <c r="K2" s="8"/>
       <c r="L2" s="9"/>
-      <c r="M2" s="31" t="s">
+      <c r="M2" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-      <c r="U2" s="31"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
       <c r="V2" s="10"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -2296,7 +2305,7 @@
     </row>
     <row r="4" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A4" s="7"/>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="28" t="s">
         <v>109</v>
       </c>
       <c r="C4" s="17" t="s">
@@ -2305,12 +2314,16 @@
       <c r="D4" s="17">
         <v>57</v>
       </c>
-      <c r="E4" s="16" t="str">
+      <c r="E4" s="16">
         <f>IF(F4 &gt; G4, 1, "")</f>
-        <v/>
-      </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F4" s="16">
+        <v>6</v>
+      </c>
+      <c r="G4" s="16">
+        <v>4</v>
+      </c>
       <c r="H4" s="16" t="str">
         <f>IF(G4 &gt; F4, 1, "")</f>
         <v/>
@@ -2323,7 +2336,7 @@
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="13"/>
-      <c r="M4" s="26" t="s">
+      <c r="M4" s="28" t="s">
         <v>109</v>
       </c>
       <c r="N4" s="17" t="s">
@@ -2336,11 +2349,15 @@
         <f>IF(Q4 &gt; R4, 1, "")</f>
         <v/>
       </c>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16" t="str">
+      <c r="Q4" s="16">
+        <v>3</v>
+      </c>
+      <c r="R4" s="16">
+        <v>7</v>
+      </c>
+      <c r="S4" s="16">
         <f>IF(R4 &gt; Q4, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T4" s="17">
         <v>63</v>
@@ -2356,7 +2373,7 @@
       </c>
       <c r="Z4">
         <f t="shared" ref="Z4:Z43" si="0">SUMIF(D$4:D$88,Y4,F$4:F$88)+SUMIF(I$4:I$88,Y4,G$4:G$88)+SUMIF(O$4:O$88,Y4,Q$4:Q$88)+SUMIF(T$4:T$88,Y4,R$4:R$88)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA4">
         <f>SUMIF(D$4:D$88,Y4,E$4:E$88)+SUMIF(I$4:I$88,Y4,H$4:H$88)+SUMIF(O$4:O$88,Y4,P$4:P$88)+SUMIF(T$4:T$88,Y4,S$4:S$88)</f>
@@ -2365,7 +2382,7 @@
     </row>
     <row r="5" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A5" s="7"/>
-      <c r="B5" s="26"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="17" t="s">
         <v>14</v>
       </c>
@@ -2376,11 +2393,15 @@
         <f t="shared" ref="E5:E13" si="1">IF(F5 &gt; G5, 1, "")</f>
         <v/>
       </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16" t="str">
+      <c r="F5" s="16">
+        <v>0</v>
+      </c>
+      <c r="G5" s="16">
+        <v>10</v>
+      </c>
+      <c r="H5" s="16">
         <f t="shared" ref="H5:H13" si="2">IF(G5 &gt; F5, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I5" s="17">
         <v>32</v>
@@ -2390,7 +2411,7 @@
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="13"/>
-      <c r="M5" s="26"/>
+      <c r="M5" s="28"/>
       <c r="N5" s="17" t="s">
         <v>15</v>
       </c>
@@ -2401,11 +2422,15 @@
         <f t="shared" ref="P5:P13" si="3">IF(Q5 &gt; R5, 1, "")</f>
         <v/>
       </c>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16" t="str">
+      <c r="Q5" s="16">
+        <v>2</v>
+      </c>
+      <c r="R5" s="16">
+        <v>8</v>
+      </c>
+      <c r="S5" s="16">
         <f t="shared" ref="S5:S13" si="4">IF(R5 &gt; Q5, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T5" s="17">
         <v>84</v>
@@ -2421,7 +2446,7 @@
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA5">
         <f t="shared" ref="AA5:AA43" si="5">SUMIF(D$4:D$88,Y5,E$4:E$88)+SUMIF(I$4:I$88,Y5,H$4:H$88)+SUMIF(O$4:O$88,Y5,P$4:P$88)+SUMIF(T$4:T$88,Y5,S$4:S$88)</f>
@@ -2430,7 +2455,7 @@
     </row>
     <row r="6" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="7"/>
-      <c r="B6" s="26"/>
+      <c r="B6" s="28"/>
       <c r="C6" s="17" t="s">
         <v>15</v>
       </c>
@@ -2441,11 +2466,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16" t="str">
+      <c r="F6" s="16">
+        <v>3</v>
+      </c>
+      <c r="G6" s="16">
+        <v>7</v>
+      </c>
+      <c r="H6" s="16">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I6" s="17">
         <v>93</v>
@@ -2455,19 +2484,23 @@
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="13"/>
-      <c r="M6" s="26"/>
+      <c r="M6" s="28"/>
       <c r="N6" s="17" t="s">
         <v>17</v>
       </c>
       <c r="O6" s="17">
         <v>51</v>
       </c>
-      <c r="P6" s="16" t="str">
+      <c r="P6" s="16">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>7</v>
+      </c>
+      <c r="R6" s="16">
+        <v>3</v>
+      </c>
       <c r="S6" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2495,7 +2528,7 @@
     </row>
     <row r="7" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A7" s="7"/>
-      <c r="B7" s="26"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="17" t="s">
         <v>17</v>
       </c>
@@ -2506,11 +2539,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16" t="str">
+      <c r="F7" s="16">
+        <v>3</v>
+      </c>
+      <c r="G7" s="16">
+        <v>7</v>
+      </c>
+      <c r="H7" s="16">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I7" s="17">
         <v>74</v>
@@ -2520,7 +2557,7 @@
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="13"/>
-      <c r="M7" s="26"/>
+      <c r="M7" s="28"/>
       <c r="N7" s="17" t="s">
         <v>14</v>
       </c>
@@ -2531,8 +2568,12 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
+      <c r="Q7" s="16">
+        <v>5</v>
+      </c>
+      <c r="R7" s="16">
+        <v>5</v>
+      </c>
       <c r="S7" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2551,7 +2592,7 @@
       </c>
       <c r="Z7">
         <f>SUMIF(D$4:D$88,Y7,F$4:F$88)+SUMIF(I$4:I$88,Y7,G$4:G$88)+SUMIF(O$4:O$88,Y7,Q$4:Q$88)+SUMIF(T$4:T$88,Y7,R$4:R$88)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7">
         <f t="shared" si="5"/>
@@ -2560,7 +2601,7 @@
     </row>
     <row r="8" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7"/>
-      <c r="B8" s="27"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="21" t="s">
         <v>14</v>
       </c>
@@ -2571,11 +2612,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20" t="str">
+      <c r="F8" s="20">
+        <v>3</v>
+      </c>
+      <c r="G8" s="20">
+        <v>7</v>
+      </c>
+      <c r="H8" s="20">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I8" s="21">
         <v>62</v>
@@ -2585,7 +2630,7 @@
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="13"/>
-      <c r="M8" s="27"/>
+      <c r="M8" s="29"/>
       <c r="N8" s="21" t="s">
         <v>15</v>
       </c>
@@ -2596,11 +2641,15 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
-      <c r="S8" s="20" t="str">
+      <c r="Q8" s="20">
+        <v>4</v>
+      </c>
+      <c r="R8" s="20">
+        <v>6</v>
+      </c>
+      <c r="S8" s="20">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T8" s="21">
         <v>71</v>
@@ -2616,7 +2665,7 @@
       </c>
       <c r="Z8">
         <f>SUMIF(D$4:D$88,Y8,F$4:F$88)+SUMIF(I$4:I$88,Y8,G$4:G$88)+SUMIF(O$4:O$88,Y8,Q$4:Q$88)+SUMIF(T$4:T$88,Y8,R$4:R$88)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA8">
         <f t="shared" si="5"/>
@@ -2625,7 +2674,7 @@
     </row>
     <row r="9" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A9" s="7"/>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="30" t="s">
         <v>110</v>
       </c>
       <c r="C9" s="19" t="s">
@@ -2634,12 +2683,16 @@
       <c r="D9" s="19">
         <v>22</v>
       </c>
-      <c r="E9" s="15" t="str">
+      <c r="E9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="F9" s="15">
+        <v>6</v>
+      </c>
+      <c r="G9" s="15">
+        <v>4</v>
+      </c>
       <c r="H9" s="15" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2652,7 +2705,7 @@
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="13"/>
-      <c r="M9" s="28" t="s">
+      <c r="M9" s="30" t="s">
         <v>110</v>
       </c>
       <c r="N9" s="19" t="s">
@@ -2665,8 +2718,12 @@
         <f>IF(Q9 &gt; R9, 1, "")</f>
         <v/>
       </c>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
+      <c r="Q9" s="15">
+        <v>5</v>
+      </c>
+      <c r="R9" s="15">
+        <v>5</v>
+      </c>
       <c r="S9" s="15" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2685,7 +2742,7 @@
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA9">
         <f t="shared" si="5"/>
@@ -2694,7 +2751,7 @@
     </row>
     <row r="10" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
-      <c r="B10" s="29"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="17" t="s">
         <v>17</v>
       </c>
@@ -2705,11 +2762,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="16" t="str">
+      <c r="F10" s="16">
+        <v>3</v>
+      </c>
+      <c r="G10" s="16">
+        <v>7</v>
+      </c>
+      <c r="H10" s="16">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I10" s="17">
         <v>77</v>
@@ -2719,7 +2780,7 @@
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="13"/>
-      <c r="M10" s="29"/>
+      <c r="M10" s="31"/>
       <c r="N10" s="17" t="s">
         <v>15</v>
       </c>
@@ -2730,11 +2791,15 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16" t="str">
+      <c r="Q10" s="16">
+        <v>3</v>
+      </c>
+      <c r="R10" s="16">
+        <v>7</v>
+      </c>
+      <c r="S10" s="16">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T10" s="17">
         <v>86</v>
@@ -2750,16 +2815,16 @@
       </c>
       <c r="Z10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
-      <c r="B11" s="29"/>
+      <c r="B11" s="31"/>
       <c r="C11" s="17" t="s">
         <v>14</v>
       </c>
@@ -2770,11 +2835,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16" t="str">
+      <c r="F11" s="16">
+        <v>4</v>
+      </c>
+      <c r="G11" s="16">
+        <v>6</v>
+      </c>
+      <c r="H11" s="16">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I11" s="17">
         <v>31</v>
@@ -2784,7 +2853,7 @@
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="13"/>
-      <c r="M11" s="29"/>
+      <c r="M11" s="31"/>
       <c r="N11" s="17" t="s">
         <v>20</v>
       </c>
@@ -2795,11 +2864,15 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16" t="str">
+      <c r="Q11" s="16">
+        <v>2</v>
+      </c>
+      <c r="R11" s="16">
+        <v>8</v>
+      </c>
+      <c r="S11" s="16">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T11" s="17">
         <v>83</v>
@@ -2815,7 +2888,7 @@
       </c>
       <c r="Z11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA11">
         <f t="shared" si="5"/>
@@ -2824,19 +2897,23 @@
     </row>
     <row r="12" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A12" s="7"/>
-      <c r="B12" s="29"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="17" t="s">
         <v>15</v>
       </c>
       <c r="D12" s="17">
         <v>20</v>
       </c>
-      <c r="E12" s="16" t="str">
+      <c r="E12" s="16">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F12" s="16">
+        <v>7</v>
+      </c>
+      <c r="G12" s="16">
+        <v>3</v>
+      </c>
       <c r="H12" s="16" t="str">
         <f t="shared" si="2"/>
         <v/>
@@ -2849,19 +2926,23 @@
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="13"/>
-      <c r="M12" s="29"/>
+      <c r="M12" s="31"/>
       <c r="N12" s="17" t="s">
         <v>13</v>
       </c>
       <c r="O12" s="17">
         <v>94</v>
       </c>
-      <c r="P12" s="16" t="str">
+      <c r="P12" s="16">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>7</v>
+      </c>
+      <c r="R12" s="16">
+        <v>3</v>
+      </c>
       <c r="S12" s="16" t="str">
         <f t="shared" si="4"/>
         <v/>
@@ -2880,7 +2961,7 @@
       </c>
       <c r="Z12">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA12">
         <f t="shared" si="5"/>
@@ -2889,7 +2970,7 @@
     </row>
     <row r="13" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A13" s="7"/>
-      <c r="B13" s="29"/>
+      <c r="B13" s="31"/>
       <c r="C13" s="17" t="s">
         <v>17</v>
       </c>
@@ -2900,11 +2981,15 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="16" t="str">
+      <c r="F13" s="16">
+        <v>2</v>
+      </c>
+      <c r="G13" s="16">
+        <v>8</v>
+      </c>
+      <c r="H13" s="16">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I13" s="17">
         <v>75</v>
@@ -2914,7 +2999,7 @@
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="13"/>
-      <c r="M13" s="29"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="17" t="s">
         <v>4</v>
       </c>
@@ -2925,11 +3010,15 @@
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16" t="str">
+      <c r="Q13" s="16">
+        <v>2</v>
+      </c>
+      <c r="R13" s="16">
+        <v>8</v>
+      </c>
+      <c r="S13" s="16">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T13" s="17">
         <v>36</v>
@@ -2945,7 +3034,7 @@
       </c>
       <c r="Z13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA13">
         <f t="shared" si="5"/>
@@ -2983,11 +3072,11 @@
       </c>
       <c r="Z14">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA14">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -3021,7 +3110,7 @@
       </c>
       <c r="Z15">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA15">
         <f t="shared" si="5"/>
@@ -3030,28 +3119,28 @@
     </row>
     <row r="16" spans="1:27" ht="27" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
       <c r="V16" s="5"/>
       <c r="X16" t="s">
         <v>20</v>
@@ -3061,7 +3150,7 @@
       </c>
       <c r="Z16">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA16">
         <f t="shared" si="5"/>
@@ -3070,30 +3159,30 @@
     </row>
     <row r="17" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
       <c r="K17" s="8"/>
       <c r="L17" s="9"/>
-      <c r="M17" s="31" t="s">
+      <c r="M17" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="27"/>
+      <c r="U17" s="27"/>
       <c r="V17" s="10"/>
       <c r="X17" t="s">
         <v>20</v>
@@ -3103,7 +3192,7 @@
       </c>
       <c r="Z17">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA17">
         <f t="shared" si="5"/>
@@ -3177,16 +3266,16 @@
       </c>
       <c r="Z18">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA18">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A19" s="7"/>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="28" t="s">
         <v>111</v>
       </c>
       <c r="C19" s="17" t="s">
@@ -3213,7 +3302,7 @@
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="13"/>
-      <c r="M19" s="26" t="s">
+      <c r="M19" s="28" t="s">
         <v>111</v>
       </c>
       <c r="N19" s="17" t="s">
@@ -3246,16 +3335,16 @@
       </c>
       <c r="Z19">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA19">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
-      <c r="B20" s="26"/>
+      <c r="B20" s="28"/>
       <c r="C20" s="17" t="s">
         <v>5</v>
       </c>
@@ -3280,7 +3369,7 @@
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="13"/>
-      <c r="M20" s="26"/>
+      <c r="M20" s="28"/>
       <c r="N20" s="17" t="s">
         <v>17</v>
       </c>
@@ -3311,7 +3400,7 @@
       </c>
       <c r="Z20">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA20">
         <f t="shared" si="5"/>
@@ -3320,7 +3409,7 @@
     </row>
     <row r="21" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7"/>
-      <c r="B21" s="26"/>
+      <c r="B21" s="28"/>
       <c r="C21" s="17" t="s">
         <v>15</v>
       </c>
@@ -3345,7 +3434,7 @@
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="13"/>
-      <c r="M21" s="26"/>
+      <c r="M21" s="28"/>
       <c r="N21" s="17" t="s">
         <v>5</v>
       </c>
@@ -3376,16 +3465,16 @@
       </c>
       <c r="Z21">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA21">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="7"/>
-      <c r="B22" s="26"/>
+      <c r="B22" s="28"/>
       <c r="C22" s="17" t="s">
         <v>13</v>
       </c>
@@ -3410,7 +3499,7 @@
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="26"/>
+      <c r="M22" s="28"/>
       <c r="N22" s="17" t="s">
         <v>15</v>
       </c>
@@ -3441,16 +3530,16 @@
       </c>
       <c r="Z22">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA22">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7"/>
-      <c r="B23" s="27"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="21" t="s">
         <v>17</v>
       </c>
@@ -3475,7 +3564,7 @@
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="13"/>
-      <c r="M23" s="27"/>
+      <c r="M23" s="29"/>
       <c r="N23" s="21" t="s">
         <v>13</v>
       </c>
@@ -3506,7 +3595,7 @@
       </c>
       <c r="Z23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA23">
         <f t="shared" si="5"/>
@@ -3515,7 +3604,7 @@
     </row>
     <row r="24" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A24" s="7"/>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="30" t="s">
         <v>112</v>
       </c>
       <c r="C24" s="19" t="s">
@@ -3542,7 +3631,7 @@
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="13"/>
-      <c r="M24" s="28" t="s">
+      <c r="M24" s="30" t="s">
         <v>112</v>
       </c>
       <c r="N24" s="19" t="s">
@@ -3575,7 +3664,7 @@
       </c>
       <c r="Z24">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA24">
         <f t="shared" si="5"/>
@@ -3584,7 +3673,7 @@
     </row>
     <row r="25" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A25" s="7"/>
-      <c r="B25" s="29"/>
+      <c r="B25" s="31"/>
       <c r="C25" s="17" t="s">
         <v>15</v>
       </c>
@@ -3609,7 +3698,7 @@
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="13"/>
-      <c r="M25" s="29"/>
+      <c r="M25" s="31"/>
       <c r="N25" s="17" t="s">
         <v>5</v>
       </c>
@@ -3640,16 +3729,16 @@
       </c>
       <c r="Z25">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A26" s="7"/>
-      <c r="B26" s="29"/>
+      <c r="B26" s="31"/>
       <c r="C26" s="17" t="s">
         <v>13</v>
       </c>
@@ -3674,7 +3763,7 @@
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="13"/>
-      <c r="M26" s="29"/>
+      <c r="M26" s="31"/>
       <c r="N26" s="17" t="s">
         <v>15</v>
       </c>
@@ -3705,7 +3794,7 @@
       </c>
       <c r="Z26">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA26">
         <f t="shared" si="5"/>
@@ -3714,7 +3803,7 @@
     </row>
     <row r="27" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A27" s="7"/>
-      <c r="B27" s="29"/>
+      <c r="B27" s="31"/>
       <c r="C27" s="17" t="s">
         <v>17</v>
       </c>
@@ -3739,7 +3828,7 @@
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="13"/>
-      <c r="M27" s="29"/>
+      <c r="M27" s="31"/>
       <c r="N27" s="17" t="s">
         <v>15</v>
       </c>
@@ -3770,16 +3859,16 @@
       </c>
       <c r="Z27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A28" s="7"/>
-      <c r="B28" s="29"/>
+      <c r="B28" s="31"/>
       <c r="C28" s="17" t="s">
         <v>5</v>
       </c>
@@ -3804,7 +3893,7 @@
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="13"/>
-      <c r="M28" s="29"/>
+      <c r="M28" s="31"/>
       <c r="N28" s="17" t="s">
         <v>4</v>
       </c>
@@ -3835,11 +3924,11 @@
       </c>
       <c r="Z28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -3873,7 +3962,7 @@
       </c>
       <c r="Z29">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA29">
         <f t="shared" si="5"/>
@@ -3911,7 +4000,7 @@
       </c>
       <c r="Z30">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA30">
         <f t="shared" si="5"/>
@@ -3920,28 +4009,28 @@
     </row>
     <row r="31" spans="1:27" ht="27" x14ac:dyDescent="0.35">
       <c r="A31" s="6"/>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="26"/>
+      <c r="S31" s="26"/>
+      <c r="T31" s="26"/>
+      <c r="U31" s="26"/>
       <c r="V31" s="5"/>
       <c r="X31" t="s">
         <v>4</v>
@@ -3951,7 +4040,7 @@
       </c>
       <c r="Z31">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA31">
         <f t="shared" si="5"/>
@@ -3960,30 +4049,30 @@
     </row>
     <row r="32" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A32" s="7"/>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
       <c r="K32" s="8"/>
       <c r="L32" s="9"/>
-      <c r="M32" s="31" t="s">
+      <c r="M32" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="27"/>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
+      <c r="U32" s="27"/>
       <c r="V32" s="10"/>
       <c r="X32" t="s">
         <v>4</v>
@@ -3993,11 +4082,11 @@
       </c>
       <c r="Z32">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.2">
@@ -4067,16 +4156,16 @@
       </c>
       <c r="Z33">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA33">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A34" s="7"/>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="28" t="s">
         <v>116</v>
       </c>
       <c r="C34" s="17" t="s">
@@ -4103,7 +4192,7 @@
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="13"/>
-      <c r="M34" s="26" t="s">
+      <c r="M34" s="28" t="s">
         <v>116</v>
       </c>
       <c r="N34" s="17" t="s">
@@ -4136,16 +4225,16 @@
       </c>
       <c r="Z34">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA34">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A35" s="7"/>
-      <c r="B35" s="26"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="17" t="s">
         <v>5</v>
       </c>
@@ -4170,7 +4259,7 @@
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="13"/>
-      <c r="M35" s="26"/>
+      <c r="M35" s="28"/>
       <c r="N35" s="17" t="s">
         <v>4</v>
       </c>
@@ -4201,16 +4290,16 @@
       </c>
       <c r="Z35">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA35">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="7"/>
-      <c r="B36" s="26"/>
+      <c r="B36" s="28"/>
       <c r="C36" s="17" t="s">
         <v>14</v>
       </c>
@@ -4235,7 +4324,7 @@
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="13"/>
-      <c r="M36" s="26"/>
+      <c r="M36" s="28"/>
       <c r="N36" s="17" t="s">
         <v>17</v>
       </c>
@@ -4266,7 +4355,7 @@
       </c>
       <c r="Z36">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA36">
         <f t="shared" si="5"/>
@@ -4275,7 +4364,7 @@
     </row>
     <row r="37" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A37" s="7"/>
-      <c r="B37" s="26"/>
+      <c r="B37" s="28"/>
       <c r="C37" s="17" t="s">
         <v>4</v>
       </c>
@@ -4300,7 +4389,7 @@
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="13"/>
-      <c r="M37" s="26"/>
+      <c r="M37" s="28"/>
       <c r="N37" s="17" t="s">
         <v>5</v>
       </c>
@@ -4331,7 +4420,7 @@
       </c>
       <c r="Z37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA37">
         <f t="shared" si="5"/>
@@ -4340,7 +4429,7 @@
     </row>
     <row r="38" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="7"/>
-      <c r="B38" s="27"/>
+      <c r="B38" s="29"/>
       <c r="C38" s="21" t="s">
         <v>17</v>
       </c>
@@ -4365,7 +4454,7 @@
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="13"/>
-      <c r="M38" s="27"/>
+      <c r="M38" s="29"/>
       <c r="N38" s="21" t="s">
         <v>14</v>
       </c>
@@ -4396,16 +4485,16 @@
       </c>
       <c r="Z38">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A39" s="7"/>
-      <c r="B39" s="28" t="s">
+      <c r="B39" s="30" t="s">
         <v>117</v>
       </c>
       <c r="C39" s="19" t="s">
@@ -4432,7 +4521,7 @@
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="13"/>
-      <c r="M39" s="28" t="s">
+      <c r="M39" s="30" t="s">
         <v>117</v>
       </c>
       <c r="N39" s="19" t="s">
@@ -4465,16 +4554,16 @@
       </c>
       <c r="Z39">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA39">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
-      <c r="B40" s="29"/>
+      <c r="B40" s="31"/>
       <c r="C40" s="17" t="s">
         <v>14</v>
       </c>
@@ -4499,7 +4588,7 @@
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="13"/>
-      <c r="M40" s="29"/>
+      <c r="M40" s="31"/>
       <c r="N40" s="17" t="s">
         <v>17</v>
       </c>
@@ -4530,16 +4619,16 @@
       </c>
       <c r="Z40">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA40">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A41" s="7"/>
-      <c r="B41" s="29"/>
+      <c r="B41" s="31"/>
       <c r="C41" s="17" t="s">
         <v>4</v>
       </c>
@@ -4564,7 +4653,7 @@
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="13"/>
-      <c r="M41" s="29"/>
+      <c r="M41" s="31"/>
       <c r="N41" s="17" t="s">
         <v>5</v>
       </c>
@@ -4595,7 +4684,7 @@
       </c>
       <c r="Z41">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA41">
         <f t="shared" si="5"/>
@@ -4604,7 +4693,7 @@
     </row>
     <row r="42" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A42" s="7"/>
-      <c r="B42" s="29"/>
+      <c r="B42" s="31"/>
       <c r="C42" s="17" t="s">
         <v>17</v>
       </c>
@@ -4629,7 +4718,7 @@
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="13"/>
-      <c r="M42" s="29"/>
+      <c r="M42" s="31"/>
       <c r="N42" s="17" t="s">
         <v>14</v>
       </c>
@@ -4660,16 +4749,16 @@
       </c>
       <c r="Z42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A43" s="7"/>
-      <c r="B43" s="29"/>
+      <c r="B43" s="31"/>
       <c r="C43" s="17" t="s">
         <v>5</v>
       </c>
@@ -4694,7 +4783,7 @@
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="13"/>
-      <c r="M43" s="29"/>
+      <c r="M43" s="31"/>
       <c r="N43" s="17" t="s">
         <v>13</v>
       </c>
@@ -4725,11 +4814,11 @@
       </c>
       <c r="Z43">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA43">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
@@ -4782,56 +4871,56 @@
     </row>
     <row r="46" spans="1:27" ht="27" x14ac:dyDescent="0.35">
       <c r="A46" s="6"/>
-      <c r="B46" s="30" t="s">
+      <c r="B46" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="26"/>
+      <c r="O46" s="26"/>
+      <c r="P46" s="26"/>
+      <c r="Q46" s="26"/>
+      <c r="R46" s="26"/>
+      <c r="S46" s="26"/>
+      <c r="T46" s="26"/>
+      <c r="U46" s="26"/>
       <c r="V46" s="5"/>
     </row>
     <row r="47" spans="1:27" ht="22" x14ac:dyDescent="0.2">
       <c r="A47" s="7"/>
-      <c r="B47" s="31" t="s">
+      <c r="B47" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="27"/>
       <c r="K47" s="8"/>
       <c r="L47" s="9"/>
-      <c r="M47" s="31" t="s">
+      <c r="M47" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="31"/>
-      <c r="T47" s="31"/>
-      <c r="U47" s="31"/>
+      <c r="N47" s="27"/>
+      <c r="O47" s="27"/>
+      <c r="P47" s="27"/>
+      <c r="Q47" s="27"/>
+      <c r="R47" s="27"/>
+      <c r="S47" s="27"/>
+      <c r="T47" s="27"/>
+      <c r="U47" s="27"/>
       <c r="V47" s="10"/>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.2">
@@ -4896,7 +4985,7 @@
     </row>
     <row r="49" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A49" s="7"/>
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="28" t="s">
         <v>118</v>
       </c>
       <c r="C49" s="17" t="s">
@@ -4923,7 +5012,7 @@
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="13"/>
-      <c r="M49" s="26" t="s">
+      <c r="M49" s="28" t="s">
         <v>118</v>
       </c>
       <c r="N49" s="17" t="s">
@@ -4951,7 +5040,7 @@
     </row>
     <row r="50" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
-      <c r="B50" s="26"/>
+      <c r="B50" s="28"/>
       <c r="C50" s="17" t="s">
         <v>5</v>
       </c>
@@ -4976,7 +5065,7 @@
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="13"/>
-      <c r="M50" s="26"/>
+      <c r="M50" s="28"/>
       <c r="N50" s="17" t="s">
         <v>13</v>
       </c>
@@ -5002,7 +5091,7 @@
     </row>
     <row r="51" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="7"/>
-      <c r="B51" s="26"/>
+      <c r="B51" s="28"/>
       <c r="C51" s="17" t="s">
         <v>14</v>
       </c>
@@ -5027,7 +5116,7 @@
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="13"/>
-      <c r="M51" s="26"/>
+      <c r="M51" s="28"/>
       <c r="N51" s="17" t="s">
         <v>17</v>
       </c>
@@ -5053,7 +5142,7 @@
     </row>
     <row r="52" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A52" s="7"/>
-      <c r="B52" s="26"/>
+      <c r="B52" s="28"/>
       <c r="C52" s="17" t="s">
         <v>20</v>
       </c>
@@ -5078,7 +5167,7 @@
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="13"/>
-      <c r="M52" s="26"/>
+      <c r="M52" s="28"/>
       <c r="N52" s="17" t="s">
         <v>5</v>
       </c>
@@ -5104,7 +5193,7 @@
     </row>
     <row r="53" spans="1:22" ht="24" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="7"/>
-      <c r="B53" s="27"/>
+      <c r="B53" s="29"/>
       <c r="C53" s="21" t="s">
         <v>17</v>
       </c>
@@ -5129,7 +5218,7 @@
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="13"/>
-      <c r="M53" s="27"/>
+      <c r="M53" s="29"/>
       <c r="N53" s="21" t="s">
         <v>14</v>
       </c>
@@ -5155,7 +5244,7 @@
     </row>
     <row r="54" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A54" s="7"/>
-      <c r="B54" s="28" t="s">
+      <c r="B54" s="30" t="s">
         <v>119</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -5182,7 +5271,7 @@
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="13"/>
-      <c r="M54" s="28" t="s">
+      <c r="M54" s="30" t="s">
         <v>119</v>
       </c>
       <c r="N54" s="19" t="s">
@@ -5210,7 +5299,7 @@
     </row>
     <row r="55" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A55" s="7"/>
-      <c r="B55" s="29"/>
+      <c r="B55" s="31"/>
       <c r="C55" s="17" t="s">
         <v>14</v>
       </c>
@@ -5235,7 +5324,7 @@
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="13"/>
-      <c r="M55" s="29"/>
+      <c r="M55" s="31"/>
       <c r="N55" s="17" t="s">
         <v>17</v>
       </c>
@@ -5261,7 +5350,7 @@
     </row>
     <row r="56" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A56" s="7"/>
-      <c r="B56" s="29"/>
+      <c r="B56" s="31"/>
       <c r="C56" s="17" t="s">
         <v>20</v>
       </c>
@@ -5286,7 +5375,7 @@
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="13"/>
-      <c r="M56" s="29"/>
+      <c r="M56" s="31"/>
       <c r="N56" s="17" t="s">
         <v>5</v>
       </c>
@@ -5312,7 +5401,7 @@
     </row>
     <row r="57" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A57" s="7"/>
-      <c r="B57" s="29"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="17" t="s">
         <v>17</v>
       </c>
@@ -5337,7 +5426,7 @@
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="13"/>
-      <c r="M57" s="29"/>
+      <c r="M57" s="31"/>
       <c r="N57" s="17" t="s">
         <v>14</v>
       </c>
@@ -5363,7 +5452,7 @@
     </row>
     <row r="58" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A58" s="7"/>
-      <c r="B58" s="29"/>
+      <c r="B58" s="31"/>
       <c r="C58" s="17" t="s">
         <v>5</v>
       </c>
@@ -5388,7 +5477,7 @@
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="13"/>
-      <c r="M58" s="29"/>
+      <c r="M58" s="31"/>
       <c r="N58" s="17" t="s">
         <v>20</v>
       </c>
@@ -5462,56 +5551,56 @@
     </row>
     <row r="61" spans="1:22" ht="27" x14ac:dyDescent="0.35">
       <c r="A61" s="6"/>
-      <c r="B61" s="30" t="s">
+      <c r="B61" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="30"/>
-      <c r="P61" s="30"/>
-      <c r="Q61" s="30"/>
-      <c r="R61" s="30"/>
-      <c r="S61" s="30"/>
-      <c r="T61" s="30"/>
-      <c r="U61" s="30"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
+      <c r="R61" s="26"/>
+      <c r="S61" s="26"/>
+      <c r="T61" s="26"/>
+      <c r="U61" s="26"/>
       <c r="V61" s="5"/>
     </row>
     <row r="62" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A62" s="7"/>
-      <c r="B62" s="31" t="s">
+      <c r="B62" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C62" s="31"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="31"/>
-      <c r="F62" s="31"/>
-      <c r="G62" s="31"/>
-      <c r="H62" s="31"/>
-      <c r="I62" s="31"/>
-      <c r="J62" s="31"/>
+      <c r="C62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="27"/>
+      <c r="I62" s="27"/>
+      <c r="J62" s="27"/>
       <c r="K62" s="8"/>
       <c r="L62" s="9"/>
-      <c r="M62" s="31" t="s">
+      <c r="M62" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="N62" s="31"/>
-      <c r="O62" s="31"/>
-      <c r="P62" s="31"/>
-      <c r="Q62" s="31"/>
-      <c r="R62" s="31"/>
-      <c r="S62" s="31"/>
-      <c r="T62" s="31"/>
-      <c r="U62" s="31"/>
+      <c r="N62" s="27"/>
+      <c r="O62" s="27"/>
+      <c r="P62" s="27"/>
+      <c r="Q62" s="27"/>
+      <c r="R62" s="27"/>
+      <c r="S62" s="27"/>
+      <c r="T62" s="27"/>
+      <c r="U62" s="27"/>
       <c r="V62" s="10"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.2">
@@ -5576,7 +5665,7 @@
     </row>
     <row r="64" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A64" s="7"/>
-      <c r="B64" s="26" t="s">
+      <c r="B64" s="28" t="s">
         <v>113</v>
       </c>
       <c r="C64" s="17" t="s">
@@ -5603,7 +5692,7 @@
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="13"/>
-      <c r="M64" s="26" t="s">
+      <c r="M64" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N64" s="17" t="s">
@@ -5631,7 +5720,7 @@
     </row>
     <row r="65" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A65" s="7"/>
-      <c r="B65" s="26"/>
+      <c r="B65" s="28"/>
       <c r="C65" s="17" t="s">
         <v>5</v>
       </c>
@@ -5656,7 +5745,7 @@
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="13"/>
-      <c r="M65" s="26"/>
+      <c r="M65" s="28"/>
       <c r="N65" s="17" t="s">
         <v>13</v>
       </c>
@@ -5682,7 +5771,7 @@
     </row>
     <row r="66" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A66" s="7"/>
-      <c r="B66" s="26"/>
+      <c r="B66" s="28"/>
       <c r="C66" s="17" t="s">
         <v>20</v>
       </c>
@@ -5707,7 +5796,7 @@
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="13"/>
-      <c r="M66" s="26"/>
+      <c r="M66" s="28"/>
       <c r="N66" s="17" t="s">
         <v>17</v>
       </c>
@@ -5733,7 +5822,7 @@
     </row>
     <row r="67" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A67" s="7"/>
-      <c r="B67" s="26"/>
+      <c r="B67" s="28"/>
       <c r="C67" s="17" t="s">
         <v>13</v>
       </c>
@@ -5758,7 +5847,7 @@
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="13"/>
-      <c r="M67" s="26"/>
+      <c r="M67" s="28"/>
       <c r="N67" s="17" t="s">
         <v>5</v>
       </c>
@@ -5784,7 +5873,7 @@
     </row>
     <row r="68" spans="1:22" ht="24" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="7"/>
-      <c r="B68" s="27"/>
+      <c r="B68" s="29"/>
       <c r="C68" s="21" t="s">
         <v>17</v>
       </c>
@@ -5809,7 +5898,7 @@
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="13"/>
-      <c r="M68" s="27"/>
+      <c r="M68" s="29"/>
       <c r="N68" s="21" t="s">
         <v>20</v>
       </c>
@@ -5835,7 +5924,7 @@
     </row>
     <row r="69" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A69" s="7"/>
-      <c r="B69" s="28" t="s">
+      <c r="B69" s="30" t="s">
         <v>120</v>
       </c>
       <c r="C69" s="19" t="s">
@@ -5862,7 +5951,7 @@
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="13"/>
-      <c r="M69" s="28" t="s">
+      <c r="M69" s="30" t="s">
         <v>120</v>
       </c>
       <c r="N69" s="19" t="s">
@@ -5890,7 +5979,7 @@
     </row>
     <row r="70" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
-      <c r="B70" s="29"/>
+      <c r="B70" s="31"/>
       <c r="C70" s="17" t="s">
         <v>20</v>
       </c>
@@ -5915,7 +6004,7 @@
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="13"/>
-      <c r="M70" s="29"/>
+      <c r="M70" s="31"/>
       <c r="N70" s="17" t="s">
         <v>17</v>
       </c>
@@ -5941,7 +6030,7 @@
     </row>
     <row r="71" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A71" s="7"/>
-      <c r="B71" s="29"/>
+      <c r="B71" s="31"/>
       <c r="C71" s="17" t="s">
         <v>13</v>
       </c>
@@ -5966,7 +6055,7 @@
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="13"/>
-      <c r="M71" s="29"/>
+      <c r="M71" s="31"/>
       <c r="N71" s="17" t="s">
         <v>5</v>
       </c>
@@ -5992,7 +6081,7 @@
     </row>
     <row r="72" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A72" s="7"/>
-      <c r="B72" s="29"/>
+      <c r="B72" s="31"/>
       <c r="C72" s="17" t="s">
         <v>17</v>
       </c>
@@ -6017,7 +6106,7 @@
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="13"/>
-      <c r="M72" s="29"/>
+      <c r="M72" s="31"/>
       <c r="N72" s="17" t="s">
         <v>20</v>
       </c>
@@ -6043,7 +6132,7 @@
     </row>
     <row r="73" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A73" s="7"/>
-      <c r="B73" s="29"/>
+      <c r="B73" s="31"/>
       <c r="C73" s="17" t="s">
         <v>5</v>
       </c>
@@ -6068,7 +6157,7 @@
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="13"/>
-      <c r="M73" s="29"/>
+      <c r="M73" s="31"/>
       <c r="N73" s="17" t="s">
         <v>13</v>
       </c>
@@ -6142,56 +6231,56 @@
     </row>
     <row r="76" spans="1:22" ht="27" x14ac:dyDescent="0.35">
       <c r="A76" s="6"/>
-      <c r="B76" s="30" t="s">
+      <c r="B76" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C76" s="30"/>
-      <c r="D76" s="30"/>
-      <c r="E76" s="30"/>
-      <c r="F76" s="30"/>
-      <c r="G76" s="30"/>
-      <c r="H76" s="30"/>
-      <c r="I76" s="30"/>
-      <c r="J76" s="30"/>
-      <c r="K76" s="30"/>
-      <c r="L76" s="30"/>
-      <c r="M76" s="30"/>
-      <c r="N76" s="30"/>
-      <c r="O76" s="30"/>
-      <c r="P76" s="30"/>
-      <c r="Q76" s="30"/>
-      <c r="R76" s="30"/>
-      <c r="S76" s="30"/>
-      <c r="T76" s="30"/>
-      <c r="U76" s="30"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="26"/>
+      <c r="N76" s="26"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="26"/>
+      <c r="Q76" s="26"/>
+      <c r="R76" s="26"/>
+      <c r="S76" s="26"/>
+      <c r="T76" s="26"/>
+      <c r="U76" s="26"/>
       <c r="V76" s="5"/>
     </row>
     <row r="77" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A77" s="7"/>
-      <c r="B77" s="31" t="s">
+      <c r="B77" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C77" s="31"/>
-      <c r="D77" s="31"/>
-      <c r="E77" s="31"/>
-      <c r="F77" s="31"/>
-      <c r="G77" s="31"/>
-      <c r="H77" s="31"/>
-      <c r="I77" s="31"/>
-      <c r="J77" s="31"/>
+      <c r="C77" s="27"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="27"/>
+      <c r="F77" s="27"/>
+      <c r="G77" s="27"/>
+      <c r="H77" s="27"/>
+      <c r="I77" s="27"/>
+      <c r="J77" s="27"/>
       <c r="K77" s="8"/>
       <c r="L77" s="9"/>
-      <c r="M77" s="31" t="s">
+      <c r="M77" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="N77" s="31"/>
-      <c r="O77" s="31"/>
-      <c r="P77" s="31"/>
-      <c r="Q77" s="31"/>
-      <c r="R77" s="31"/>
-      <c r="S77" s="31"/>
-      <c r="T77" s="31"/>
-      <c r="U77" s="31"/>
+      <c r="N77" s="27"/>
+      <c r="O77" s="27"/>
+      <c r="P77" s="27"/>
+      <c r="Q77" s="27"/>
+      <c r="R77" s="27"/>
+      <c r="S77" s="27"/>
+      <c r="T77" s="27"/>
+      <c r="U77" s="27"/>
       <c r="V77" s="10"/>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.2">
@@ -6256,7 +6345,7 @@
     </row>
     <row r="79" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A79" s="7"/>
-      <c r="B79" s="26" t="s">
+      <c r="B79" s="28" t="s">
         <v>115</v>
       </c>
       <c r="C79" s="17" t="s">
@@ -6283,7 +6372,7 @@
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="13"/>
-      <c r="M79" s="26" t="s">
+      <c r="M79" s="28" t="s">
         <v>115</v>
       </c>
       <c r="N79" s="17" t="s">
@@ -6311,7 +6400,7 @@
     </row>
     <row r="80" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
-      <c r="B80" s="26"/>
+      <c r="B80" s="28"/>
       <c r="C80" s="17" t="s">
         <v>5</v>
       </c>
@@ -6336,7 +6425,7 @@
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="13"/>
-      <c r="M80" s="26"/>
+      <c r="M80" s="28"/>
       <c r="N80" s="17" t="s">
         <v>20</v>
       </c>
@@ -6362,7 +6451,7 @@
     </row>
     <row r="81" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A81" s="7"/>
-      <c r="B81" s="26"/>
+      <c r="B81" s="28"/>
       <c r="C81" s="17" t="s">
         <v>14</v>
       </c>
@@ -6387,7 +6476,7 @@
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="13"/>
-      <c r="M81" s="26"/>
+      <c r="M81" s="28"/>
       <c r="N81" s="17" t="s">
         <v>17</v>
       </c>
@@ -6413,7 +6502,7 @@
     </row>
     <row r="82" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A82" s="7"/>
-      <c r="B82" s="26"/>
+      <c r="B82" s="28"/>
       <c r="C82" s="17" t="s">
         <v>20</v>
       </c>
@@ -6438,7 +6527,7 @@
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="13"/>
-      <c r="M82" s="26"/>
+      <c r="M82" s="28"/>
       <c r="N82" s="17" t="s">
         <v>5</v>
       </c>
@@ -6464,7 +6553,7 @@
     </row>
     <row r="83" spans="1:22" ht="24" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="7"/>
-      <c r="B83" s="27"/>
+      <c r="B83" s="29"/>
       <c r="C83" s="21" t="s">
         <v>17</v>
       </c>
@@ -6489,7 +6578,7 @@
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="13"/>
-      <c r="M83" s="27"/>
+      <c r="M83" s="29"/>
       <c r="N83" s="21" t="s">
         <v>14</v>
       </c>
@@ -6515,7 +6604,7 @@
     </row>
     <row r="84" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A84" s="7"/>
-      <c r="B84" s="28" t="s">
+      <c r="B84" s="30" t="s">
         <v>114</v>
       </c>
       <c r="C84" s="19" t="s">
@@ -6542,7 +6631,7 @@
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="13"/>
-      <c r="M84" s="28" t="s">
+      <c r="M84" s="30" t="s">
         <v>114</v>
       </c>
       <c r="N84" s="19" t="s">
@@ -6570,7 +6659,7 @@
     </row>
     <row r="85" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A85" s="7"/>
-      <c r="B85" s="29"/>
+      <c r="B85" s="31"/>
       <c r="C85" s="17" t="s">
         <v>14</v>
       </c>
@@ -6595,7 +6684,7 @@
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="13"/>
-      <c r="M85" s="29"/>
+      <c r="M85" s="31"/>
       <c r="N85" s="17" t="s">
         <v>17</v>
       </c>
@@ -6621,7 +6710,7 @@
     </row>
     <row r="86" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A86" s="7"/>
-      <c r="B86" s="29"/>
+      <c r="B86" s="31"/>
       <c r="C86" s="17" t="s">
         <v>20</v>
       </c>
@@ -6646,7 +6735,7 @@
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="13"/>
-      <c r="M86" s="29"/>
+      <c r="M86" s="31"/>
       <c r="N86" s="17" t="s">
         <v>5</v>
       </c>
@@ -6672,7 +6761,7 @@
     </row>
     <row r="87" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A87" s="7"/>
-      <c r="B87" s="29"/>
+      <c r="B87" s="31"/>
       <c r="C87" s="17" t="s">
         <v>17</v>
       </c>
@@ -6697,7 +6786,7 @@
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="13"/>
-      <c r="M87" s="29"/>
+      <c r="M87" s="31"/>
       <c r="N87" s="17" t="s">
         <v>14</v>
       </c>
@@ -6723,7 +6812,7 @@
     </row>
     <row r="88" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A88" s="7"/>
-      <c r="B88" s="29"/>
+      <c r="B88" s="31"/>
       <c r="C88" s="17" t="s">
         <v>5</v>
       </c>
@@ -6748,7 +6837,7 @@
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="13"/>
-      <c r="M88" s="29"/>
+      <c r="M88" s="31"/>
       <c r="N88" s="17" t="s">
         <v>20</v>
       </c>
@@ -7038,6 +7127,41 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B76:U76"/>
+    <mergeCell ref="B77:J77"/>
+    <mergeCell ref="M77:U77"/>
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="B84:B88"/>
+    <mergeCell ref="M79:M83"/>
+    <mergeCell ref="M84:M88"/>
+    <mergeCell ref="B61:U61"/>
+    <mergeCell ref="B62:J62"/>
+    <mergeCell ref="M62:U62"/>
+    <mergeCell ref="B64:B68"/>
+    <mergeCell ref="B69:B73"/>
+    <mergeCell ref="M64:M68"/>
+    <mergeCell ref="M69:M73"/>
+    <mergeCell ref="B46:U46"/>
+    <mergeCell ref="B47:J47"/>
+    <mergeCell ref="M47:U47"/>
+    <mergeCell ref="B49:B53"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="M49:M53"/>
+    <mergeCell ref="M54:M58"/>
+    <mergeCell ref="B31:U31"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="M32:U32"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="M34:M38"/>
+    <mergeCell ref="M39:M43"/>
+    <mergeCell ref="B16:U16"/>
+    <mergeCell ref="B17:J17"/>
+    <mergeCell ref="M17:U17"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="M19:M23"/>
+    <mergeCell ref="M24:M28"/>
     <mergeCell ref="B1:U1"/>
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="M2:U2"/>
@@ -7045,41 +7169,6 @@
     <mergeCell ref="B9:B13"/>
     <mergeCell ref="M4:M8"/>
     <mergeCell ref="M9:M13"/>
-    <mergeCell ref="B16:U16"/>
-    <mergeCell ref="B17:J17"/>
-    <mergeCell ref="M17:U17"/>
-    <mergeCell ref="B19:B23"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="M19:M23"/>
-    <mergeCell ref="M24:M28"/>
-    <mergeCell ref="B31:U31"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="M32:U32"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="B39:B43"/>
-    <mergeCell ref="M34:M38"/>
-    <mergeCell ref="M39:M43"/>
-    <mergeCell ref="B46:U46"/>
-    <mergeCell ref="B47:J47"/>
-    <mergeCell ref="M47:U47"/>
-    <mergeCell ref="B49:B53"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="M49:M53"/>
-    <mergeCell ref="M54:M58"/>
-    <mergeCell ref="B61:U61"/>
-    <mergeCell ref="B62:J62"/>
-    <mergeCell ref="M62:U62"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="B69:B73"/>
-    <mergeCell ref="M64:M68"/>
-    <mergeCell ref="M69:M73"/>
-    <mergeCell ref="B76:U76"/>
-    <mergeCell ref="B77:J77"/>
-    <mergeCell ref="M77:U77"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="B84:B88"/>
-    <mergeCell ref="M79:M83"/>
-    <mergeCell ref="M84:M88"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -7108,212 +7197,212 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
-        <v>2c</v>
+        <v>2d</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
-        <v>2c</v>
+        <v>2d</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
-        <v>2c</v>
+        <v>2b</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
-        <v>2c</v>
+        <v>2f</v>
       </c>
       <c r="B5">
+        <v>83</v>
+      </c>
+      <c r="C5">
         <v>8</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
-        <v>2c</v>
+        <v>2f</v>
       </c>
       <c r="B6">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
-        <v>2c</v>
+        <v>2e</v>
       </c>
       <c r="B7">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
-        <v>2e</v>
+        <v>2a</v>
       </c>
       <c r="B8">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
-        <v>2e</v>
+        <v>2g</v>
       </c>
       <c r="B9">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <v>2e</v>
+        <v>2g</v>
       </c>
       <c r="B10">
-        <v>17</v>
+        <v>63</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
-        <v>2e</v>
+        <v>2b</v>
       </c>
       <c r="B11">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <v>2e</v>
+        <v>2b</v>
       </c>
       <c r="B12">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <v>2e</v>
+        <v>2f</v>
       </c>
       <c r="B13">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <v>2d</v>
+        <v>2f</v>
       </c>
       <c r="B14">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
-        <v>2d</v>
+        <v>2f</v>
       </c>
       <c r="B15">
-        <v>29</v>
+        <v>94</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <v>2d</v>
+        <v>2e</v>
       </c>
       <c r="B16">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
@@ -7321,52 +7410,52 @@
         <v>2d</v>
       </c>
       <c r="B17">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
-        <v>2d</v>
+        <v>2a</v>
       </c>
       <c r="B18">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
-        <v>2d</v>
+        <v>2g</v>
       </c>
       <c r="B19">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
-        <v>2a</v>
+        <v>2c</v>
       </c>
       <c r="B20">
-        <v>51</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -7374,13 +7463,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
-        <v>2a</v>
+        <v>2c</v>
       </c>
       <c r="B21">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -7388,13 +7477,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <v>2a</v>
+        <v>2d</v>
       </c>
       <c r="B22">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -7402,13 +7491,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <v>2a</v>
+        <v>2d</v>
       </c>
       <c r="B23">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -7416,13 +7505,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <v>2a</v>
+        <v>2c</v>
       </c>
       <c r="B24">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -7430,13 +7519,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
-        <v>2g</v>
+        <v>2e</v>
       </c>
       <c r="B25">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7444,13 +7533,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <v>2g</v>
+        <v>2b</v>
       </c>
       <c r="B26">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -7458,13 +7547,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <v>2g</v>
+        <v>2f</v>
       </c>
       <c r="B27">
-        <v>66</v>
+        <v>92</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -7472,13 +7561,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <v>2g</v>
+        <v>2c</v>
       </c>
       <c r="B28">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -7486,13 +7575,13 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <v>2g</v>
+        <v>2c</v>
       </c>
       <c r="B29">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -7500,13 +7589,13 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <v>2g</v>
+        <v>2e</v>
       </c>
       <c r="B30">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -7514,13 +7603,13 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
-        <v>2b</v>
+        <v>2e</v>
       </c>
       <c r="B31">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -7528,13 +7617,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <v>2b</v>
+        <v>2a</v>
       </c>
       <c r="B32">
-        <v>75</v>
+        <v>53</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -7542,13 +7631,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <v>2b</v>
+        <v>2a</v>
       </c>
       <c r="B33">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -7556,13 +7645,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <v>2b</v>
+        <v>2g</v>
       </c>
       <c r="B34">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -7570,13 +7659,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
-        <v>2b</v>
+        <v>2g</v>
       </c>
       <c r="B35">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -7584,13 +7673,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <v>2f</v>
+        <v>2b</v>
       </c>
       <c r="B36">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -7598,13 +7687,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <v>2f</v>
+        <v>2e</v>
       </c>
       <c r="B37">
-        <v>84</v>
+        <v>15</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7612,13 +7701,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <v>2f</v>
+        <v>2d</v>
       </c>
       <c r="B38">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -7626,13 +7715,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
-        <v>2f</v>
+        <v>2a</v>
       </c>
       <c r="B39">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -7640,13 +7729,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
-        <v>2f</v>
+        <v>2g</v>
       </c>
       <c r="B40">
-        <v>93</v>
+        <v>68</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -7654,10 +7743,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
-        <v>2f</v>
+        <v>2c</v>
       </c>
       <c r="B41">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -7685,55 +7774,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27" x14ac:dyDescent="0.35">
-      <c r="B1" s="30" t="s">
+      <c r="B1" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="30"/>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
+      <c r="S1" s="26"/>
+      <c r="T1" s="26"/>
+      <c r="U1" s="26"/>
       <c r="V1" s="24"/>
     </row>
     <row r="2" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
       <c r="K2" s="8"/>
       <c r="L2" s="9"/>
-      <c r="M2" s="31" t="s">
+      <c r="M2" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="31"/>
-      <c r="O2" s="31"/>
-      <c r="P2" s="31"/>
-      <c r="Q2" s="31"/>
-      <c r="R2" s="31"/>
-      <c r="S2" s="31"/>
-      <c r="T2" s="31"/>
-      <c r="U2" s="31"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="27"/>
       <c r="V2" s="10"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.2">
@@ -7810,7 +7899,7 @@
     </row>
     <row r="4" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="28" t="s">
         <v>109</v>
       </c>
       <c r="C4" s="17" t="s">
@@ -7823,8 +7912,12 @@
         <f>IF(F4&gt;G4,3,IF(F4=G4,1,0))</f>
         <v>1</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
+      <c r="F4" s="16">
+        <v>10</v>
+      </c>
+      <c r="G4" s="16">
+        <v>10</v>
+      </c>
       <c r="H4" s="16">
         <f>IF(G4&gt;F4,3,IF(F4=G4,1,0))</f>
         <v>1</v>
@@ -7837,7 +7930,7 @@
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="13"/>
-      <c r="M4" s="26" t="s">
+      <c r="M4" s="28" t="s">
         <v>109</v>
       </c>
       <c r="N4" s="17" t="s">
@@ -7848,13 +7941,17 @@
       </c>
       <c r="P4" s="16">
         <f>IF(Q4&gt;R4,3,IF(Q4=R4,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>3</v>
+      </c>
+      <c r="R4" s="32">
+        <v>23</v>
+      </c>
       <c r="S4" s="16">
         <f>IF(R4&gt;Q4,3,IF(Q4=R4,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T4" s="17">
         <v>65</v>
@@ -7870,16 +7967,16 @@
       </c>
       <c r="Y4">
         <f>SUMIF(D$4:D$88,X4,E$4:E$88)+SUMIF(I$4:I$88,X4,H$4:H$88)+SUMIF(O$4:O$88,X4,P$4:P$88)+SUMIF(T$4:T$88,X4,S$4:S$88)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z4">
         <f>SUMIF(D$4:D$88,X4,F$4:F$88)+SUMIF(I$4:I$88,X4,G$4:G$88)+SUMIF(O$4:O$88,X4,Q$4:Q$88)+SUMIF(T$4:T$88,X4,R$4:R$88)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="B5" s="26"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="17" t="s">
         <v>13</v>
       </c>
@@ -7888,13 +7985,17 @@
       </c>
       <c r="E5" s="16">
         <f t="shared" ref="E5:E13" si="0">IF(F5&gt;G5,3,IF(F5=G5,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F5" s="16">
+        <v>0</v>
+      </c>
+      <c r="G5" s="16">
+        <v>10</v>
+      </c>
       <c r="H5" s="16">
         <f t="shared" ref="H5:H13" si="1">IF(G5&gt;F5,3,IF(F5=G5,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I5" s="17">
         <v>81</v>
@@ -7904,7 +8005,7 @@
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="13"/>
-      <c r="M5" s="26"/>
+      <c r="M5" s="28"/>
       <c r="N5" s="17" t="s">
         <v>15</v>
       </c>
@@ -7913,13 +8014,17 @@
       </c>
       <c r="P5" s="16">
         <f t="shared" ref="P5:P6" si="2">IF(Q5&gt;R5,3,IF(Q5=R5,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="16">
+        <v>6</v>
+      </c>
+      <c r="R5" s="32">
+        <v>25</v>
+      </c>
       <c r="S5" s="16">
         <f t="shared" ref="S5:S10" si="3">IF(R5&gt;Q5,3,IF(Q5=R5,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T5" s="17">
         <v>91</v>
@@ -7935,16 +8040,16 @@
       </c>
       <c r="Y5">
         <f t="shared" ref="Y5:Y43" si="4">SUMIF(D$4:D$88,X5,E$4:E$88)+SUMIF(I$4:I$88,X5,H$4:H$88)+SUMIF(O$4:O$88,X5,P$4:P$88)+SUMIF(T$4:T$88,X5,S$4:S$88)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z5">
         <f t="shared" ref="Z5:Z43" si="5">SUMIF(D$4:D$88,X5,F$4:F$88)+SUMIF(I$4:I$88,X5,G$4:G$88)+SUMIF(O$4:O$88,X5,Q$4:Q$88)+SUMIF(T$4:T$88,X5,R$4:R$88)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
-      <c r="B6" s="26"/>
+      <c r="B6" s="28"/>
       <c r="C6" s="17" t="s">
         <v>14</v>
       </c>
@@ -7953,13 +8058,17 @@
       </c>
       <c r="E6" s="16">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F6" s="16">
+        <v>5</v>
+      </c>
+      <c r="G6" s="16">
+        <v>3</v>
+      </c>
       <c r="H6" s="16">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" s="17">
         <v>61</v>
@@ -7969,7 +8078,7 @@
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="13"/>
-      <c r="M6" s="26"/>
+      <c r="M6" s="28"/>
       <c r="N6" s="17" t="s">
         <v>17</v>
       </c>
@@ -7980,8 +8089,12 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
+      <c r="Q6" s="16">
+        <v>0</v>
+      </c>
+      <c r="R6" s="32">
+        <v>0</v>
+      </c>
       <c r="S6" s="16">
         <f t="shared" si="3"/>
         <v>1</v>
@@ -8000,16 +8113,16 @@
       </c>
       <c r="Y6">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="B7" s="26"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="17" t="s">
         <v>14</v>
       </c>
@@ -8018,13 +8131,17 @@
       </c>
       <c r="E7" s="16">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F7" s="16">
+        <v>35</v>
+      </c>
+      <c r="G7" s="16">
+        <v>0</v>
+      </c>
       <c r="H7" s="16">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" s="17">
         <v>25</v>
@@ -8034,7 +8151,7 @@
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="13"/>
-      <c r="M7" s="26"/>
+      <c r="M7" s="28"/>
       <c r="N7" s="17" t="s">
         <v>5</v>
       </c>
@@ -8045,8 +8162,12 @@
         <f>IF(Q7&gt;R7,3,IF(Q7=R7,1,0))</f>
         <v>1</v>
       </c>
-      <c r="Q7" s="16"/>
-      <c r="R7" s="16"/>
+      <c r="Q7" s="16">
+        <v>0</v>
+      </c>
+      <c r="R7" s="32">
+        <v>0</v>
+      </c>
       <c r="S7" s="16">
         <f>IF(R7&gt;Q7,3,IF(Q7=R7,1,0))</f>
         <v>1</v>
@@ -8065,16 +8186,16 @@
       </c>
       <c r="Y7">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
-      <c r="B8" s="27"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="21" t="s">
         <v>20</v>
       </c>
@@ -8083,13 +8204,17 @@
       </c>
       <c r="E8" s="25">
         <f>IF(F8&gt;G8,3,IF(F8=G8,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F8" s="20"/>
-      <c r="G8" s="20"/>
+        <v>3</v>
+      </c>
+      <c r="F8" s="20">
+        <v>21</v>
+      </c>
+      <c r="G8" s="20">
+        <v>20</v>
+      </c>
       <c r="H8" s="25">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="21">
         <v>58</v>
@@ -8099,7 +8224,7 @@
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="13"/>
-      <c r="M8" s="27"/>
+      <c r="M8" s="29"/>
       <c r="N8" s="21" t="s">
         <v>14</v>
       </c>
@@ -8108,13 +8233,17 @@
       </c>
       <c r="P8" s="25">
         <f>IF(Q8&gt;R8,3,IF(Q8=R8,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>6</v>
+      </c>
+      <c r="R8" s="33">
+        <v>30</v>
+      </c>
       <c r="S8" s="25">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T8" s="21">
         <v>72</v>
@@ -8130,16 +8259,16 @@
       </c>
       <c r="Y8">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="30" t="s">
         <v>110</v>
       </c>
       <c r="C9" s="19" t="s">
@@ -8150,13 +8279,17 @@
       </c>
       <c r="E9" s="15">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="15">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15">
+        <v>10</v>
+      </c>
       <c r="H9" s="15">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I9" s="19">
         <v>85</v>
@@ -8166,7 +8299,7 @@
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="13"/>
-      <c r="M9" s="28" t="s">
+      <c r="M9" s="30" t="s">
         <v>110</v>
       </c>
       <c r="N9" s="19" t="s">
@@ -8177,13 +8310,17 @@
       </c>
       <c r="P9" s="15">
         <f t="shared" ref="P9:P13" si="6">IF(Q9&gt;R9,3,IF(Q9=R9,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q9" s="15"/>
-      <c r="R9" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="15">
+        <v>3</v>
+      </c>
+      <c r="R9" s="34">
+        <v>35</v>
+      </c>
       <c r="S9" s="15">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T9" s="19">
         <v>64</v>
@@ -8199,15 +8336,15 @@
       </c>
       <c r="Y9">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z9">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B10" s="29"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="17" t="s">
         <v>14</v>
       </c>
@@ -8216,13 +8353,17 @@
       </c>
       <c r="E10" s="16">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F10" s="16">
+        <v>18</v>
+      </c>
+      <c r="G10" s="16">
+        <v>1</v>
+      </c>
       <c r="H10" s="16">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I10" s="17">
         <v>70</v>
@@ -8232,7 +8373,7 @@
       </c>
       <c r="K10" s="7"/>
       <c r="L10" s="13"/>
-      <c r="M10" s="29"/>
+      <c r="M10" s="31"/>
       <c r="N10" s="17" t="s">
         <v>17</v>
       </c>
@@ -8241,13 +8382,17 @@
       </c>
       <c r="P10" s="16">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>0</v>
+      </c>
+      <c r="R10" s="32">
+        <v>10</v>
+      </c>
       <c r="S10" s="16">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T10" s="17">
         <v>37</v>
@@ -8263,15 +8408,15 @@
       </c>
       <c r="Y10">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z10">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B11" s="29"/>
+      <c r="B11" s="31"/>
       <c r="C11" s="17" t="s">
         <v>15</v>
       </c>
@@ -8280,13 +8425,17 @@
       </c>
       <c r="E11" s="16">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F11" s="16"/>
-      <c r="G11" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="16">
+        <v>0</v>
+      </c>
+      <c r="G11" s="16">
+        <v>23</v>
+      </c>
       <c r="H11" s="16">
         <f>IF(G11&gt;F11,3,IF(F11=G11,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="17">
         <v>30</v>
@@ -8296,7 +8445,7 @@
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="13"/>
-      <c r="M11" s="29"/>
+      <c r="M11" s="31"/>
       <c r="N11" s="17" t="s">
         <v>13</v>
       </c>
@@ -8305,13 +8454,17 @@
       </c>
       <c r="P11" s="16">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>24</v>
+      </c>
+      <c r="R11" s="32">
+        <v>31</v>
+      </c>
       <c r="S11" s="16">
         <f>IF(R11&gt;Q11,3,IF(Q11=R11,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T11" s="17">
         <v>73</v>
@@ -8327,7 +8480,7 @@
       </c>
       <c r="Y11">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z11">
         <f t="shared" si="5"/>
@@ -8335,7 +8488,7 @@
       </c>
     </row>
     <row r="12" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B12" s="29"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="17" t="s">
         <v>17</v>
       </c>
@@ -8344,13 +8497,17 @@
       </c>
       <c r="E12" s="16">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F12" s="16">
+        <v>15</v>
+      </c>
+      <c r="G12" s="16">
+        <v>12</v>
+      </c>
       <c r="H12" s="16">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I12" s="17">
         <v>28</v>
@@ -8360,7 +8517,7 @@
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="13"/>
-      <c r="M12" s="29"/>
+      <c r="M12" s="31"/>
       <c r="N12" s="17" t="s">
         <v>14</v>
       </c>
@@ -8369,13 +8526,17 @@
       </c>
       <c r="P12" s="16">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>1</v>
+      </c>
+      <c r="R12" s="32">
+        <v>13</v>
+      </c>
       <c r="S12" s="16">
         <f t="shared" ref="S12:S13" si="7">IF(R12&gt;Q12,3,IF(Q12=R12,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T12" s="17">
         <v>19</v>
@@ -8391,15 +8552,15 @@
       </c>
       <c r="Y12">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B13" s="29"/>
+      <c r="B13" s="31"/>
       <c r="C13" s="17" t="s">
         <v>5</v>
       </c>
@@ -8408,13 +8569,17 @@
       </c>
       <c r="E13" s="16">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="F13" s="16"/>
-      <c r="G13" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="16">
+        <v>0</v>
+      </c>
+      <c r="G13" s="16">
+        <v>21</v>
+      </c>
       <c r="H13" s="16">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I13" s="17">
         <v>89</v>
@@ -8424,7 +8589,7 @@
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="13"/>
-      <c r="M13" s="29"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="17" t="s">
         <v>15</v>
       </c>
@@ -8433,13 +8598,17 @@
       </c>
       <c r="P13" s="16">
         <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q13" s="16">
+        <v>8</v>
+      </c>
+      <c r="R13" s="32">
+        <v>5</v>
+      </c>
       <c r="S13" s="16">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" s="17">
         <v>67</v>
@@ -8455,11 +8624,11 @@
       </c>
       <c r="Y13">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
@@ -8492,11 +8661,11 @@
       </c>
       <c r="Y14">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z14">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
@@ -8529,7 +8698,7 @@
       </c>
       <c r="Y15">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z15">
         <f t="shared" si="5"/>
@@ -8537,28 +8706,28 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="27" x14ac:dyDescent="0.35">
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="30"/>
-      <c r="M16" s="30"/>
-      <c r="N16" s="30"/>
-      <c r="O16" s="30"/>
-      <c r="P16" s="30"/>
-      <c r="Q16" s="30"/>
-      <c r="R16" s="30"/>
-      <c r="S16" s="30"/>
-      <c r="T16" s="30"/>
-      <c r="U16" s="30"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="Q16" s="26"/>
+      <c r="R16" s="26"/>
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="26"/>
       <c r="V16" s="5"/>
       <c r="W16" t="s">
         <v>20</v>
@@ -8576,30 +8745,30 @@
       </c>
     </row>
     <row r="17" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+      <c r="J17" s="27"/>
       <c r="K17" s="8"/>
       <c r="L17" s="9"/>
-      <c r="M17" s="31" t="s">
+      <c r="M17" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="31"/>
-      <c r="Q17" s="31"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
+      <c r="N17" s="27"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="27"/>
+      <c r="Q17" s="27"/>
+      <c r="R17" s="27"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="27"/>
+      <c r="U17" s="27"/>
       <c r="V17" s="10"/>
       <c r="W17" t="s">
         <v>20</v>
@@ -8609,11 +8778,11 @@
       </c>
       <c r="Y17">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z17">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
@@ -8683,16 +8852,16 @@
       </c>
       <c r="Y18">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z18">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="28" t="s">
         <v>111</v>
       </c>
       <c r="C19" s="17" t="s">
@@ -8719,7 +8888,7 @@
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="13"/>
-      <c r="M19" s="26" t="s">
+      <c r="M19" s="28" t="s">
         <v>111</v>
       </c>
       <c r="N19" s="17" t="s">
@@ -8752,16 +8921,16 @@
       </c>
       <c r="Y19">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
-      <c r="B20" s="26"/>
+      <c r="B20" s="28"/>
       <c r="C20" s="17" t="s">
         <v>14</v>
       </c>
@@ -8786,7 +8955,7 @@
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="13"/>
-      <c r="M20" s="26"/>
+      <c r="M20" s="28"/>
       <c r="N20" s="17" t="s">
         <v>13</v>
       </c>
@@ -8821,12 +8990,12 @@
       </c>
       <c r="Z20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
-      <c r="B21" s="26"/>
+      <c r="B21" s="28"/>
       <c r="C21" s="17" t="s">
         <v>4</v>
       </c>
@@ -8851,7 +9020,7 @@
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="13"/>
-      <c r="M21" s="26"/>
+      <c r="M21" s="28"/>
       <c r="N21" s="17" t="s">
         <v>17</v>
       </c>
@@ -8882,16 +9051,16 @@
       </c>
       <c r="Y21">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z21">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
-      <c r="B22" s="26"/>
+      <c r="B22" s="28"/>
       <c r="C22" s="17" t="s">
         <v>13</v>
       </c>
@@ -8916,7 +9085,7 @@
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="13"/>
-      <c r="M22" s="26"/>
+      <c r="M22" s="28"/>
       <c r="N22" s="17" t="s">
         <v>5</v>
       </c>
@@ -8956,7 +9125,7 @@
     </row>
     <row r="23" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="27"/>
+      <c r="B23" s="29"/>
       <c r="C23" s="21" t="s">
         <v>17</v>
       </c>
@@ -8981,7 +9150,7 @@
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="13"/>
-      <c r="M23" s="27"/>
+      <c r="M23" s="29"/>
       <c r="N23" s="21" t="s">
         <v>4</v>
       </c>
@@ -9012,7 +9181,7 @@
       </c>
       <c r="Y23">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z23">
         <f t="shared" si="5"/>
@@ -9021,7 +9190,7 @@
     </row>
     <row r="24" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="30" t="s">
         <v>112</v>
       </c>
       <c r="C24" s="19" t="s">
@@ -9048,7 +9217,7 @@
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="13"/>
-      <c r="M24" s="28" t="s">
+      <c r="M24" s="30" t="s">
         <v>112</v>
       </c>
       <c r="N24" s="19" t="s">
@@ -9081,15 +9250,15 @@
       </c>
       <c r="Y24">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z24">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B25" s="29"/>
+      <c r="B25" s="31"/>
       <c r="C25" s="17" t="s">
         <v>4</v>
       </c>
@@ -9114,7 +9283,7 @@
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="13"/>
-      <c r="M25" s="29"/>
+      <c r="M25" s="31"/>
       <c r="N25" s="17" t="s">
         <v>15</v>
       </c>
@@ -9149,11 +9318,11 @@
       </c>
       <c r="Z25">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B26" s="29"/>
+      <c r="B26" s="31"/>
       <c r="C26" s="17" t="s">
         <v>13</v>
       </c>
@@ -9178,7 +9347,7 @@
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="13"/>
-      <c r="M26" s="29"/>
+      <c r="M26" s="31"/>
       <c r="N26" s="17" t="s">
         <v>5</v>
       </c>
@@ -9209,15 +9378,15 @@
       </c>
       <c r="Y26">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z26">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B27" s="29"/>
+      <c r="B27" s="31"/>
       <c r="C27" s="17" t="s">
         <v>15</v>
       </c>
@@ -9242,7 +9411,7 @@
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="13"/>
-      <c r="M27" s="29"/>
+      <c r="M27" s="31"/>
       <c r="N27" s="17" t="s">
         <v>13</v>
       </c>
@@ -9273,15 +9442,15 @@
       </c>
       <c r="Y27">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z27">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B28" s="29"/>
+      <c r="B28" s="31"/>
       <c r="C28" s="17" t="s">
         <v>5</v>
       </c>
@@ -9306,7 +9475,7 @@
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="13"/>
-      <c r="M28" s="29"/>
+      <c r="M28" s="31"/>
       <c r="N28" s="17" t="s">
         <v>13</v>
       </c>
@@ -9337,11 +9506,11 @@
       </c>
       <c r="Y28">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z28">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
@@ -9374,11 +9543,11 @@
       </c>
       <c r="Y29">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z29">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
@@ -9411,36 +9580,36 @@
       </c>
       <c r="Y30">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z30">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="27" x14ac:dyDescent="0.35">
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
-      <c r="E31" s="30"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="30"/>
-      <c r="H31" s="30"/>
-      <c r="I31" s="30"/>
-      <c r="J31" s="30"/>
-      <c r="K31" s="30"/>
-      <c r="L31" s="30"/>
-      <c r="M31" s="30"/>
-      <c r="N31" s="30"/>
-      <c r="O31" s="30"/>
-      <c r="P31" s="30"/>
-      <c r="Q31" s="30"/>
-      <c r="R31" s="30"/>
-      <c r="S31" s="30"/>
-      <c r="T31" s="30"/>
-      <c r="U31" s="30"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="26"/>
+      <c r="S31" s="26"/>
+      <c r="T31" s="26"/>
+      <c r="U31" s="26"/>
       <c r="V31" s="5"/>
       <c r="W31" t="s">
         <v>4</v>
@@ -9450,38 +9619,38 @@
       </c>
       <c r="Y31">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z31">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="27"/>
+      <c r="J32" s="27"/>
       <c r="K32" s="8"/>
       <c r="L32" s="9"/>
-      <c r="M32" s="31" t="s">
+      <c r="M32" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="31"/>
-      <c r="Q32" s="31"/>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
+      <c r="N32" s="27"/>
+      <c r="O32" s="27"/>
+      <c r="P32" s="27"/>
+      <c r="Q32" s="27"/>
+      <c r="R32" s="27"/>
+      <c r="S32" s="27"/>
+      <c r="T32" s="27"/>
+      <c r="U32" s="27"/>
       <c r="V32" s="10"/>
       <c r="W32" t="s">
         <v>4</v>
@@ -9491,11 +9660,11 @@
       </c>
       <c r="Y32">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z32">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
@@ -9565,16 +9734,16 @@
       </c>
       <c r="Y33">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z33">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="28" t="s">
         <v>116</v>
       </c>
       <c r="C34" s="17" t="s">
@@ -9601,7 +9770,7 @@
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="13"/>
-      <c r="M34" s="26" t="s">
+      <c r="M34" s="28" t="s">
         <v>116</v>
       </c>
       <c r="N34" s="17" t="s">
@@ -9634,7 +9803,7 @@
       </c>
       <c r="Y34">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z34">
         <f t="shared" si="5"/>
@@ -9643,7 +9812,7 @@
     </row>
     <row r="35" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
-      <c r="B35" s="26"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="17" t="s">
         <v>5</v>
       </c>
@@ -9668,7 +9837,7 @@
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="13"/>
-      <c r="M35" s="26"/>
+      <c r="M35" s="28"/>
       <c r="N35" s="17" t="s">
         <v>14</v>
       </c>
@@ -9708,7 +9877,7 @@
     </row>
     <row r="36" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
-      <c r="B36" s="26"/>
+      <c r="B36" s="28"/>
       <c r="C36" s="17" t="s">
         <v>15</v>
       </c>
@@ -9733,7 +9902,7 @@
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="13"/>
-      <c r="M36" s="26"/>
+      <c r="M36" s="28"/>
       <c r="N36" s="17" t="s">
         <v>4</v>
       </c>
@@ -9764,7 +9933,7 @@
       </c>
       <c r="Y36">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z36">
         <f t="shared" si="5"/>
@@ -9773,7 +9942,7 @@
     </row>
     <row r="37" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
-      <c r="B37" s="26"/>
+      <c r="B37" s="28"/>
       <c r="C37" s="17" t="s">
         <v>14</v>
       </c>
@@ -9798,7 +9967,7 @@
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="13"/>
-      <c r="M37" s="26"/>
+      <c r="M37" s="28"/>
       <c r="N37" s="17" t="s">
         <v>20</v>
       </c>
@@ -9829,16 +9998,16 @@
       </c>
       <c r="Y37">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z37">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
-      <c r="B38" s="27"/>
+      <c r="B38" s="29"/>
       <c r="C38" s="21" t="s">
         <v>4</v>
       </c>
@@ -9863,7 +10032,7 @@
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="13"/>
-      <c r="M38" s="27"/>
+      <c r="M38" s="29"/>
       <c r="N38" s="21" t="s">
         <v>13</v>
       </c>
@@ -9894,16 +10063,16 @@
       </c>
       <c r="Y38">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z38">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="22" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
-      <c r="B39" s="28" t="s">
+      <c r="B39" s="30" t="s">
         <v>117</v>
       </c>
       <c r="C39" s="19" t="s">
@@ -9930,7 +10099,7 @@
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="13"/>
-      <c r="M39" s="28" t="s">
+      <c r="M39" s="30" t="s">
         <v>117</v>
       </c>
       <c r="N39" s="19" t="s">
@@ -9963,15 +10132,15 @@
       </c>
       <c r="Y39">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z39">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B40" s="29"/>
+      <c r="B40" s="31"/>
       <c r="C40" s="17" t="s">
         <v>15</v>
       </c>
@@ -9996,7 +10165,7 @@
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="13"/>
-      <c r="M40" s="29"/>
+      <c r="M40" s="31"/>
       <c r="N40" s="17" t="s">
         <v>4</v>
       </c>
@@ -10035,7 +10204,7 @@
       </c>
     </row>
     <row r="41" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B41" s="29"/>
+      <c r="B41" s="31"/>
       <c r="C41" s="17" t="s">
         <v>14</v>
       </c>
@@ -10060,7 +10229,7 @@
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="13"/>
-      <c r="M41" s="29"/>
+      <c r="M41" s="31"/>
       <c r="N41" s="17" t="s">
         <v>5</v>
       </c>
@@ -10091,15 +10260,15 @@
       </c>
       <c r="Y41">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z41">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B42" s="29"/>
+      <c r="B42" s="31"/>
       <c r="C42" s="17" t="s">
         <v>4</v>
       </c>
@@ -10124,7 +10293,7 @@
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="13"/>
-      <c r="M42" s="29"/>
+      <c r="M42" s="31"/>
       <c r="N42" s="17" t="s">
         <v>15</v>
       </c>
@@ -10155,7 +10324,7 @@
       </c>
       <c r="Y42">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z42">
         <f t="shared" si="5"/>
@@ -10163,7 +10332,7 @@
       </c>
     </row>
     <row r="43" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B43" s="29"/>
+      <c r="B43" s="31"/>
       <c r="C43" s="17" t="s">
         <v>5</v>
       </c>
@@ -10188,7 +10357,7 @@
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="13"/>
-      <c r="M43" s="29"/>
+      <c r="M43" s="31"/>
       <c r="N43" s="17" t="s">
         <v>14</v>
       </c>
@@ -10219,11 +10388,11 @@
       </c>
       <c r="Y43">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z43">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
@@ -10273,55 +10442,55 @@
       <c r="V45" s="5"/>
     </row>
     <row r="46" spans="1:26" ht="27" x14ac:dyDescent="0.35">
-      <c r="B46" s="30" t="s">
+      <c r="B46" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="26"/>
+      <c r="K46" s="26"/>
+      <c r="L46" s="26"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="26"/>
+      <c r="O46" s="26"/>
+      <c r="P46" s="26"/>
+      <c r="Q46" s="26"/>
+      <c r="R46" s="26"/>
+      <c r="S46" s="26"/>
+      <c r="T46" s="26"/>
+      <c r="U46" s="26"/>
       <c r="V46" s="5"/>
     </row>
     <row r="47" spans="1:26" ht="22" x14ac:dyDescent="0.2">
-      <c r="B47" s="31" t="s">
+      <c r="B47" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C47" s="31"/>
-      <c r="D47" s="31"/>
-      <c r="E47" s="31"/>
-      <c r="F47" s="31"/>
-      <c r="G47" s="31"/>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="27"/>
       <c r="K47" s="8"/>
       <c r="L47" s="9"/>
-      <c r="M47" s="31" t="s">
+      <c r="M47" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="N47" s="31"/>
-      <c r="O47" s="31"/>
-      <c r="P47" s="31"/>
-      <c r="Q47" s="31"/>
-      <c r="R47" s="31"/>
-      <c r="S47" s="31"/>
-      <c r="T47" s="31"/>
-      <c r="U47" s="31"/>
+      <c r="N47" s="27"/>
+      <c r="O47" s="27"/>
+      <c r="P47" s="27"/>
+      <c r="Q47" s="27"/>
+      <c r="R47" s="27"/>
+      <c r="S47" s="27"/>
+      <c r="T47" s="27"/>
+      <c r="U47" s="27"/>
       <c r="V47" s="10"/>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.2">
@@ -10385,7 +10554,7 @@
     </row>
     <row r="49" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="28" t="s">
         <v>118</v>
       </c>
       <c r="C49" s="17" t="s">
@@ -10412,7 +10581,7 @@
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="13"/>
-      <c r="M49" s="26" t="s">
+      <c r="M49" s="28" t="s">
         <v>118</v>
       </c>
       <c r="N49" s="17" t="s">
@@ -10440,7 +10609,7 @@
     </row>
     <row r="50" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
-      <c r="B50" s="26"/>
+      <c r="B50" s="28"/>
       <c r="C50" s="17" t="s">
         <v>5</v>
       </c>
@@ -10465,7 +10634,7 @@
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="13"/>
-      <c r="M50" s="26"/>
+      <c r="M50" s="28"/>
       <c r="N50" s="17" t="s">
         <v>20</v>
       </c>
@@ -10491,7 +10660,7 @@
     </row>
     <row r="51" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
-      <c r="B51" s="26"/>
+      <c r="B51" s="28"/>
       <c r="C51" s="17" t="s">
         <v>13</v>
       </c>
@@ -10516,7 +10685,7 @@
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="13"/>
-      <c r="M51" s="26"/>
+      <c r="M51" s="28"/>
       <c r="N51" s="17" t="s">
         <v>17</v>
       </c>
@@ -10542,7 +10711,7 @@
     </row>
     <row r="52" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
-      <c r="B52" s="26"/>
+      <c r="B52" s="28"/>
       <c r="C52" s="17" t="s">
         <v>20</v>
       </c>
@@ -10567,7 +10736,7 @@
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="13"/>
-      <c r="M52" s="26"/>
+      <c r="M52" s="28"/>
       <c r="N52" s="17" t="s">
         <v>5</v>
       </c>
@@ -10593,7 +10762,7 @@
     </row>
     <row r="53" spans="1:22" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
-      <c r="B53" s="27"/>
+      <c r="B53" s="29"/>
       <c r="C53" s="21" t="s">
         <v>14</v>
       </c>
@@ -10618,7 +10787,7 @@
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="13"/>
-      <c r="M53" s="27"/>
+      <c r="M53" s="29"/>
       <c r="N53" s="21" t="s">
         <v>13</v>
       </c>
@@ -10644,7 +10813,7 @@
     </row>
     <row r="54" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
-      <c r="B54" s="28" t="s">
+      <c r="B54" s="30" t="s">
         <v>119</v>
       </c>
       <c r="C54" s="19" t="s">
@@ -10671,7 +10840,7 @@
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="13"/>
-      <c r="M54" s="28" t="s">
+      <c r="M54" s="30" t="s">
         <v>119</v>
       </c>
       <c r="N54" s="19" t="s">
@@ -10699,7 +10868,7 @@
     </row>
     <row r="55" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
-      <c r="B55" s="29"/>
+      <c r="B55" s="31"/>
       <c r="C55" s="17" t="s">
         <v>13</v>
       </c>
@@ -10724,7 +10893,7 @@
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="13"/>
-      <c r="M55" s="29"/>
+      <c r="M55" s="31"/>
       <c r="N55" s="17" t="s">
         <v>17</v>
       </c>
@@ -10749,7 +10918,7 @@
       </c>
     </row>
     <row r="56" spans="1:22" ht="22" x14ac:dyDescent="0.2">
-      <c r="B56" s="29"/>
+      <c r="B56" s="31"/>
       <c r="C56" s="17" t="s">
         <v>20</v>
       </c>
@@ -10774,7 +10943,7 @@
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="13"/>
-      <c r="M56" s="29"/>
+      <c r="M56" s="31"/>
       <c r="N56" s="17" t="s">
         <v>15</v>
       </c>
@@ -10799,7 +10968,7 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="22" x14ac:dyDescent="0.2">
-      <c r="B57" s="29"/>
+      <c r="B57" s="31"/>
       <c r="C57" s="17" t="s">
         <v>17</v>
       </c>
@@ -10824,7 +10993,7 @@
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="13"/>
-      <c r="M57" s="29"/>
+      <c r="M57" s="31"/>
       <c r="N57" s="17" t="s">
         <v>13</v>
       </c>
@@ -10849,7 +11018,7 @@
       </c>
     </row>
     <row r="58" spans="1:22" ht="22" x14ac:dyDescent="0.2">
-      <c r="B58" s="29"/>
+      <c r="B58" s="31"/>
       <c r="C58" s="17" t="s">
         <v>15</v>
       </c>
@@ -10874,7 +11043,7 @@
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="13"/>
-      <c r="M58" s="29"/>
+      <c r="M58" s="31"/>
       <c r="N58" s="17" t="s">
         <v>20</v>
       </c>
@@ -10945,55 +11114,55 @@
       <c r="V60" s="5"/>
     </row>
     <row r="61" spans="1:22" ht="27" x14ac:dyDescent="0.35">
-      <c r="B61" s="30" t="s">
+      <c r="B61" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="30"/>
-      <c r="P61" s="30"/>
-      <c r="Q61" s="30"/>
-      <c r="R61" s="30"/>
-      <c r="S61" s="30"/>
-      <c r="T61" s="30"/>
-      <c r="U61" s="30"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="26"/>
+      <c r="I61" s="26"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="26"/>
+      <c r="L61" s="26"/>
+      <c r="M61" s="26"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="26"/>
+      <c r="Q61" s="26"/>
+      <c r="R61" s="26"/>
+      <c r="S61" s="26"/>
+      <c r="T61" s="26"/>
+      <c r="U61" s="26"/>
       <c r="V61" s="5"/>
     </row>
     <row r="62" spans="1:22" ht="22" x14ac:dyDescent="0.2">
-      <c r="B62" s="31" t="s">
+      <c r="B62" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C62" s="31"/>
-      <c r="D62" s="31"/>
-      <c r="E62" s="31"/>
-      <c r="F62" s="31"/>
-      <c r="G62" s="31"/>
-      <c r="H62" s="31"/>
-      <c r="I62" s="31"/>
-      <c r="J62" s="31"/>
+      <c r="C62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="27"/>
+      <c r="H62" s="27"/>
+      <c r="I62" s="27"/>
+      <c r="J62" s="27"/>
       <c r="K62" s="8"/>
       <c r="L62" s="9"/>
-      <c r="M62" s="31" t="s">
+      <c r="M62" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="N62" s="31"/>
-      <c r="O62" s="31"/>
-      <c r="P62" s="31"/>
-      <c r="Q62" s="31"/>
-      <c r="R62" s="31"/>
-      <c r="S62" s="31"/>
-      <c r="T62" s="31"/>
-      <c r="U62" s="31"/>
+      <c r="N62" s="27"/>
+      <c r="O62" s="27"/>
+      <c r="P62" s="27"/>
+      <c r="Q62" s="27"/>
+      <c r="R62" s="27"/>
+      <c r="S62" s="27"/>
+      <c r="T62" s="27"/>
+      <c r="U62" s="27"/>
       <c r="V62" s="10"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.2">
@@ -11057,7 +11226,7 @@
     </row>
     <row r="64" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
-      <c r="B64" s="26" t="s">
+      <c r="B64" s="28" t="s">
         <v>113</v>
       </c>
       <c r="C64" s="17" t="s">
@@ -11084,7 +11253,7 @@
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="13"/>
-      <c r="M64" s="26" t="s">
+      <c r="M64" s="28" t="s">
         <v>113</v>
       </c>
       <c r="N64" s="17" t="s">
@@ -11112,7 +11281,7 @@
     </row>
     <row r="65" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
-      <c r="B65" s="26"/>
+      <c r="B65" s="28"/>
       <c r="C65" s="17" t="s">
         <v>4</v>
       </c>
@@ -11137,7 +11306,7 @@
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="13"/>
-      <c r="M65" s="26"/>
+      <c r="M65" s="28"/>
       <c r="N65" s="17" t="s">
         <v>15</v>
       </c>
@@ -11163,7 +11332,7 @@
     </row>
     <row r="66" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
-      <c r="B66" s="26"/>
+      <c r="B66" s="28"/>
       <c r="C66" s="17" t="s">
         <v>20</v>
       </c>
@@ -11188,7 +11357,7 @@
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="13"/>
-      <c r="M66" s="26"/>
+      <c r="M66" s="28"/>
       <c r="N66" s="17" t="s">
         <v>13</v>
       </c>
@@ -11214,7 +11383,7 @@
     </row>
     <row r="67" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
-      <c r="B67" s="26"/>
+      <c r="B67" s="28"/>
       <c r="C67" s="17" t="s">
         <v>15</v>
       </c>
@@ -11239,7 +11408,7 @@
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="13"/>
-      <c r="M67" s="26"/>
+      <c r="M67" s="28"/>
       <c r="N67" s="17" t="s">
         <v>4</v>
       </c>
@@ -11265,7 +11434,7 @@
     </row>
     <row r="68" spans="1:22" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
-      <c r="B68" s="27"/>
+      <c r="B68" s="29"/>
       <c r="C68" s="21" t="s">
         <v>13</v>
       </c>
@@ -11290,7 +11459,7 @@
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="13"/>
-      <c r="M68" s="27"/>
+      <c r="M68" s="29"/>
       <c r="N68" s="21" t="s">
         <v>20</v>
       </c>
@@ -11316,7 +11485,7 @@
     </row>
     <row r="69" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
-      <c r="B69" s="28" t="s">
+      <c r="B69" s="30" t="s">
         <v>120</v>
       </c>
       <c r="C69" s="19" t="s">
@@ -11343,7 +11512,7 @@
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="13"/>
-      <c r="M69" s="28" t="s">
+      <c r="M69" s="30" t="s">
         <v>120</v>
       </c>
       <c r="N69" s="19" t="s">
@@ -11371,7 +11540,7 @@
     </row>
     <row r="70" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
-      <c r="B70" s="29"/>
+      <c r="B70" s="31"/>
       <c r="C70" s="17" t="s">
         <v>20</v>
       </c>
@@ -11396,7 +11565,7 @@
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="13"/>
-      <c r="M70" s="29"/>
+      <c r="M70" s="31"/>
       <c r="N70" s="17" t="s">
         <v>13</v>
       </c>
@@ -11421,7 +11590,7 @@
       </c>
     </row>
     <row r="71" spans="1:22" ht="22" x14ac:dyDescent="0.2">
-      <c r="B71" s="29"/>
+      <c r="B71" s="31"/>
       <c r="C71" s="17" t="s">
         <v>15</v>
       </c>
@@ -11446,7 +11615,7 @@
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="13"/>
-      <c r="M71" s="29"/>
+      <c r="M71" s="31"/>
       <c r="N71" s="17" t="s">
         <v>4</v>
       </c>
@@ -11471,7 +11640,7 @@
       </c>
     </row>
     <row r="72" spans="1:22" ht="22" x14ac:dyDescent="0.2">
-      <c r="B72" s="29"/>
+      <c r="B72" s="31"/>
       <c r="C72" s="17" t="s">
         <v>17</v>
       </c>
@@ -11496,7 +11665,7 @@
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="13"/>
-      <c r="M72" s="29"/>
+      <c r="M72" s="31"/>
       <c r="N72" s="17" t="s">
         <v>20</v>
       </c>
@@ -11521,7 +11690,7 @@
       </c>
     </row>
     <row r="73" spans="1:22" ht="22" x14ac:dyDescent="0.2">
-      <c r="B73" s="29"/>
+      <c r="B73" s="31"/>
       <c r="C73" s="17" t="s">
         <v>5</v>
       </c>
@@ -11546,7 +11715,7 @@
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="13"/>
-      <c r="M73" s="29"/>
+      <c r="M73" s="31"/>
       <c r="N73" s="17" t="s">
         <v>15</v>
       </c>
@@ -11617,55 +11786,55 @@
       <c r="V75" s="5"/>
     </row>
     <row r="76" spans="1:22" ht="27" x14ac:dyDescent="0.35">
-      <c r="B76" s="30" t="s">
+      <c r="B76" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C76" s="30"/>
-      <c r="D76" s="30"/>
-      <c r="E76" s="30"/>
-      <c r="F76" s="30"/>
-      <c r="G76" s="30"/>
-      <c r="H76" s="30"/>
-      <c r="I76" s="30"/>
-      <c r="J76" s="30"/>
-      <c r="K76" s="30"/>
-      <c r="L76" s="30"/>
-      <c r="M76" s="30"/>
-      <c r="N76" s="30"/>
-      <c r="O76" s="30"/>
-      <c r="P76" s="30"/>
-      <c r="Q76" s="30"/>
-      <c r="R76" s="30"/>
-      <c r="S76" s="30"/>
-      <c r="T76" s="30"/>
-      <c r="U76" s="30"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="26"/>
+      <c r="N76" s="26"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="26"/>
+      <c r="Q76" s="26"/>
+      <c r="R76" s="26"/>
+      <c r="S76" s="26"/>
+      <c r="T76" s="26"/>
+      <c r="U76" s="26"/>
       <c r="V76" s="5"/>
     </row>
     <row r="77" spans="1:22" ht="22" x14ac:dyDescent="0.2">
-      <c r="B77" s="31" t="s">
+      <c r="B77" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="C77" s="31"/>
-      <c r="D77" s="31"/>
-      <c r="E77" s="31"/>
-      <c r="F77" s="31"/>
-      <c r="G77" s="31"/>
-      <c r="H77" s="31"/>
-      <c r="I77" s="31"/>
-      <c r="J77" s="31"/>
+      <c r="C77" s="27"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="27"/>
+      <c r="F77" s="27"/>
+      <c r="G77" s="27"/>
+      <c r="H77" s="27"/>
+      <c r="I77" s="27"/>
+      <c r="J77" s="27"/>
       <c r="K77" s="8"/>
       <c r="L77" s="9"/>
-      <c r="M77" s="31" t="s">
+      <c r="M77" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="N77" s="31"/>
-      <c r="O77" s="31"/>
-      <c r="P77" s="31"/>
-      <c r="Q77" s="31"/>
-      <c r="R77" s="31"/>
-      <c r="S77" s="31"/>
-      <c r="T77" s="31"/>
-      <c r="U77" s="31"/>
+      <c r="N77" s="27"/>
+      <c r="O77" s="27"/>
+      <c r="P77" s="27"/>
+      <c r="Q77" s="27"/>
+      <c r="R77" s="27"/>
+      <c r="S77" s="27"/>
+      <c r="T77" s="27"/>
+      <c r="U77" s="27"/>
       <c r="V77" s="10"/>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.2">
@@ -11729,7 +11898,7 @@
     </row>
     <row r="79" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
-      <c r="B79" s="26" t="s">
+      <c r="B79" s="28" t="s">
         <v>115</v>
       </c>
       <c r="C79" s="17" t="s">
@@ -11756,7 +11925,7 @@
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="13"/>
-      <c r="M79" s="26" t="s">
+      <c r="M79" s="28" t="s">
         <v>115</v>
       </c>
       <c r="N79" s="17" t="s">
@@ -11784,7 +11953,7 @@
     </row>
     <row r="80" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
-      <c r="B80" s="26"/>
+      <c r="B80" s="28"/>
       <c r="C80" s="17" t="s">
         <v>14</v>
       </c>
@@ -11809,7 +11978,7 @@
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="13"/>
-      <c r="M80" s="26"/>
+      <c r="M80" s="28"/>
       <c r="N80" s="17" t="s">
         <v>4</v>
       </c>
@@ -11835,7 +12004,7 @@
     </row>
     <row r="81" spans="1:22" ht="22" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
-      <c r="B81" s="26"/>
+      <c r="B81" s="28"/>
       <c r="C81" s="17" t="s">
         <v>20</v>
       </c>
@@ -11860,7 +12029,7 @@
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="13"/>
-      <c r="M81" s="26"/>
+      <c r="M81" s="28"/>
       <c r="N81" s="17" t="s">
         <v>17</v>
       </c>
@@ -11886,7 +12055,7 @@
     </row>
     <row r="82" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
-      <c r="B82" s="26"/>
+      <c r="B82" s="28"/>
       <c r="C82" s="17" t="s">
         <v>4</v>
       </c>
@@ -11911,7 +12080,7 @@
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="13"/>
-      <c r="M82" s="26"/>
+      <c r="M82" s="28"/>
       <c r="N82" s="17" t="s">
         <v>14</v>
       </c>
@@ -11937,7 +12106,7 @@
     </row>
     <row r="83" spans="1:22" ht="23" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
-      <c r="B83" s="27"/>
+      <c r="B83" s="29"/>
       <c r="C83" s="21" t="s">
         <v>17</v>
       </c>
@@ -11962,7 +12131,7 @@
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="13"/>
-      <c r="M83" s="27"/>
+      <c r="M83" s="29"/>
       <c r="N83" s="21" t="s">
         <v>20</v>
       </c>
@@ -11988,7 +12157,7 @@
     </row>
     <row r="84" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
-      <c r="B84" s="28" t="s">
+      <c r="B84" s="30" t="s">
         <v>114</v>
       </c>
       <c r="C84" s="19" t="s">
@@ -12015,7 +12184,7 @@
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="13"/>
-      <c r="M84" s="28" t="s">
+      <c r="M84" s="30" t="s">
         <v>114</v>
       </c>
       <c r="N84" s="19" t="s">
@@ -12043,7 +12212,7 @@
     </row>
     <row r="85" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
-      <c r="B85" s="29"/>
+      <c r="B85" s="31"/>
       <c r="C85" s="17" t="s">
         <v>20</v>
       </c>
@@ -12068,7 +12237,7 @@
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="13"/>
-      <c r="M85" s="29"/>
+      <c r="M85" s="31"/>
       <c r="N85" s="17" t="s">
         <v>17</v>
       </c>
@@ -12094,7 +12263,7 @@
     </row>
     <row r="86" spans="1:22" ht="22" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
-      <c r="B86" s="29"/>
+      <c r="B86" s="31"/>
       <c r="C86" s="17" t="s">
         <v>4</v>
       </c>
@@ -12119,7 +12288,7 @@
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="13"/>
-      <c r="M86" s="29"/>
+      <c r="M86" s="31"/>
       <c r="N86" s="17" t="s">
         <v>13</v>
       </c>
@@ -12144,7 +12313,7 @@
       </c>
     </row>
     <row r="87" spans="1:22" ht="22" x14ac:dyDescent="0.2">
-      <c r="B87" s="29"/>
+      <c r="B87" s="31"/>
       <c r="C87" s="17" t="s">
         <v>17</v>
       </c>
@@ -12169,7 +12338,7 @@
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="13"/>
-      <c r="M87" s="29"/>
+      <c r="M87" s="31"/>
       <c r="N87" s="17" t="s">
         <v>4</v>
       </c>
@@ -12194,7 +12363,7 @@
       </c>
     </row>
     <row r="88" spans="1:22" ht="22" x14ac:dyDescent="0.2">
-      <c r="B88" s="29"/>
+      <c r="B88" s="31"/>
       <c r="C88" s="17" t="s">
         <v>14</v>
       </c>
@@ -12219,7 +12388,7 @@
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="13"/>
-      <c r="M88" s="29"/>
+      <c r="M88" s="31"/>
       <c r="N88" s="17" t="s">
         <v>4</v>
       </c>
@@ -12504,6 +12673,32 @@
     </row>
   </sheetData>
   <mergeCells count="42">
+    <mergeCell ref="B79:B83"/>
+    <mergeCell ref="M79:M83"/>
+    <mergeCell ref="B84:B88"/>
+    <mergeCell ref="M84:M88"/>
+    <mergeCell ref="B69:B73"/>
+    <mergeCell ref="M69:M73"/>
+    <mergeCell ref="B76:U76"/>
+    <mergeCell ref="B77:J77"/>
+    <mergeCell ref="M77:U77"/>
+    <mergeCell ref="B61:U61"/>
+    <mergeCell ref="B62:J62"/>
+    <mergeCell ref="M62:U62"/>
+    <mergeCell ref="B64:B68"/>
+    <mergeCell ref="M64:M68"/>
+    <mergeCell ref="B47:J47"/>
+    <mergeCell ref="M47:U47"/>
+    <mergeCell ref="B49:B53"/>
+    <mergeCell ref="M49:M53"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="M54:M58"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="M32:U32"/>
+    <mergeCell ref="B34:B38"/>
+    <mergeCell ref="M34:M38"/>
+    <mergeCell ref="B39:B43"/>
+    <mergeCell ref="M39:M43"/>
     <mergeCell ref="B46:U46"/>
     <mergeCell ref="B1:U1"/>
     <mergeCell ref="B2:J2"/>
@@ -12520,32 +12715,6 @@
     <mergeCell ref="B24:B28"/>
     <mergeCell ref="M24:M28"/>
     <mergeCell ref="B31:U31"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="M32:U32"/>
-    <mergeCell ref="B34:B38"/>
-    <mergeCell ref="M34:M38"/>
-    <mergeCell ref="B39:B43"/>
-    <mergeCell ref="M39:M43"/>
-    <mergeCell ref="B47:J47"/>
-    <mergeCell ref="M47:U47"/>
-    <mergeCell ref="B49:B53"/>
-    <mergeCell ref="M49:M53"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="M54:M58"/>
-    <mergeCell ref="B61:U61"/>
-    <mergeCell ref="B62:J62"/>
-    <mergeCell ref="M62:U62"/>
-    <mergeCell ref="B64:B68"/>
-    <mergeCell ref="M64:M68"/>
-    <mergeCell ref="B79:B83"/>
-    <mergeCell ref="M79:M83"/>
-    <mergeCell ref="B84:B88"/>
-    <mergeCell ref="M84:M88"/>
-    <mergeCell ref="B69:B73"/>
-    <mergeCell ref="M69:M73"/>
-    <mergeCell ref="B76:U76"/>
-    <mergeCell ref="B77:J77"/>
-    <mergeCell ref="M77:U77"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
@@ -12583,153 +12752,153 @@
         <v>2c</v>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
-        <v>2c</v>
+        <v>2g</v>
       </c>
       <c r="B3">
-        <v>4</v>
+        <v>64</v>
       </c>
       <c r="C3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
-        <v>2c</v>
+        <v>2b</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>73</v>
       </c>
       <c r="C4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
-        <v>2c</v>
+        <v>2g</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="C5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
-        <v>2c</v>
+        <v>2f</v>
       </c>
       <c r="B6">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
-        <v>2c</v>
+        <v>2d</v>
       </c>
       <c r="B7">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
-        <v>2e</v>
+        <v>2g</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="C8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B9">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <v>2e</v>
+        <v>2f</v>
       </c>
       <c r="B10">
+        <v>89</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
         <v>21</v>
-      </c>
-      <c r="C10">
-        <v>6</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
-        <v>2e</v>
+        <v>2c</v>
       </c>
       <c r="B11">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <v>2e</v>
+        <v>2a</v>
       </c>
       <c r="B12">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="C12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -12737,13 +12906,13 @@
         <v>2e</v>
       </c>
       <c r="B13">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -12751,69 +12920,69 @@
         <v>2d</v>
       </c>
       <c r="B14">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
-        <v>2d</v>
+        <v>2b</v>
       </c>
       <c r="B15">
-        <v>28</v>
+        <v>81</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <v>2d</v>
+        <v>2f</v>
       </c>
       <c r="B16">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
-        <v>2d</v>
+        <v>2e</v>
       </c>
       <c r="B17">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
-        <v>2d</v>
+        <v>2c</v>
       </c>
       <c r="B18">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -12821,13 +12990,13 @@
         <v>2d</v>
       </c>
       <c r="B19">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -12835,21 +13004,21 @@
         <v>2a</v>
       </c>
       <c r="B20">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C20">
         <v>6</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
-        <v>2a</v>
+        <v>2d</v>
       </c>
       <c r="B21">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C21">
         <v>6</v>
@@ -12863,7 +13032,7 @@
         <v>2a</v>
       </c>
       <c r="B22">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C22">
         <v>6</v>
@@ -12874,10 +13043,10 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <v>2a</v>
+        <v>2b</v>
       </c>
       <c r="B23">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C23">
         <v>6</v>
@@ -12888,10 +13057,10 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <v>2a</v>
+        <v>2f</v>
       </c>
       <c r="B24">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C24">
         <v>6</v>
@@ -12902,73 +13071,73 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
-        <v>2g</v>
+        <v>2f</v>
       </c>
       <c r="B25">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="E25" s="12"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <v>2g</v>
+        <v>2a</v>
       </c>
       <c r="B26">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <v>2g</v>
+        <v>2d</v>
       </c>
       <c r="B27">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="C27">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <v>2g</v>
+        <v>2c</v>
       </c>
       <c r="B28">
-        <v>67</v>
+        <v>2</v>
       </c>
       <c r="C28">
+        <v>5</v>
+      </c>
+      <c r="D28">
         <v>6</v>
-      </c>
-      <c r="D28">
-        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <v>2g</v>
+        <v>2e</v>
       </c>
       <c r="B29">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="D29">
         <v>6</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -12976,95 +13145,95 @@
         <v>2g</v>
       </c>
       <c r="B30">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E30" s="12"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
-        <v>2b</v>
+        <v>2c</v>
       </c>
       <c r="B31">
-        <v>73</v>
+        <v>7</v>
       </c>
       <c r="C31">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <v>2b</v>
+        <v>2e</v>
       </c>
       <c r="B32">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <v>2b</v>
+        <v>2g</v>
       </c>
       <c r="B33">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <v>2b</v>
+        <v>2c</v>
       </c>
       <c r="B34">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
-        <v>2b</v>
+        <v>2g</v>
       </c>
       <c r="B35">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <v>2f</v>
+        <v>2e</v>
       </c>
       <c r="B36">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -13072,13 +13241,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <v>2f</v>
+        <v>2e</v>
       </c>
       <c r="B37">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -13086,13 +13255,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <v>2f</v>
+        <v>2a</v>
       </c>
       <c r="B38">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -13100,13 +13269,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
-        <v>2f</v>
+        <v>2b</v>
       </c>
       <c r="B39">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -13114,13 +13283,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
-        <v>2f</v>
+        <v>2b</v>
       </c>
       <c r="B40">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -13131,10 +13300,10 @@
         <v>2f</v>
       </c>
       <c r="B41">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C41">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -13610,6 +13779,38 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
+    <f8e6109263404e4da1831cd151bd9fd5 xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </f8e6109263404e4da1831cd151bd9fd5>
+    <kd8ebdb17ae1461db4d8c38e130fcffb xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </kd8ebdb17ae1461db4d8c38e130fcffb>
+    <AnzeigeStartseite xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001FDB85367C20A4499C08F4CA4D5990E0" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="3dd10242c9d5248a8f685c250a5fc978">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4af33632-ae06-419a-9cde-c132ea01998a" xmlns:ns3="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c3e60e7f399f82dd53caaf2d567bcde1" ns2:_="" ns3:_="">
     <xsd:import namespace="4af33632-ae06-419a-9cde-c132ea01998a"/>
@@ -13856,39 +14057,40 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
-    <f8e6109263404e4da1831cd151bd9fd5 xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </f8e6109263404e4da1831cd151bd9fd5>
-    <kd8ebdb17ae1461db4d8c38e130fcffb xmlns="4af33632-ae06-419a-9cde-c132ea01998a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </kd8ebdb17ae1461db4d8c38e130fcffb>
-    <AnzeigeStartseite xmlns="4af33632-ae06-419a-9cde-c132ea01998a" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33E82EA-34B8-478E-90E7-7586E722C072}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="4af33632-ae06-419a-9cde-c132ea01998a"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<SharedContentType xmlns="Microsoft.SharePoint.Taxonomy.ContentTypeSync" SourceId="2be96a66-639a-49bd-ae5f-911ec7d6c2fc" ContentTypeId="0x0101" PreviousValue="false"/>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{067E30AD-6895-4D50-B36C-27DC78AA4545}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13905,37 +14107,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64A7263C-2DE4-4511-A0DE-FB7A876B2661}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33E82EA-34B8-478E-90E7-7586E722C072}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1bcd6380-bda3-48d2-8fbc-3eb2b8842e9c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4af33632-ae06-419a-9cde-c132ea01998a"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FB4EAF91-C187-460F-9E0E-B856FB5E1932}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="Microsoft.SharePoint.Taxonomy.ContentTypeSync"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/KWI-RoboChallenge_Rangliste.xlsx
+++ b/KWI-RoboChallenge_Rangliste.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB1E81F-7047-0446-9593-7144F1390565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316E161E-6BAE-5442-A452-2D126D9D975A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Linienfolger-Resultate" sheetId="15" r:id="rId1"/>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z4">
         <f t="shared" ref="Z4:Z43" si="0">SUMIF(D$4:D$88,Y4,F$4:F$88)+SUMIF(I$4:I$88,Y4,G$4:G$88)+SUMIF(O$4:O$88,Y4,Q$4:Q$88)+SUMIF(T$4:T$88,Y4,R$4:R$88)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AA4">
         <f>SUMIF(D$4:D$88,Y4,E$4:E$88)+SUMIF(I$4:I$88,Y4,H$4:H$88)+SUMIF(O$4:O$88,Y4,P$4:P$88)+SUMIF(T$4:T$88,Y4,S$4:S$88)</f>
@@ -2446,7 +2446,7 @@
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AA5">
         <f t="shared" ref="AA5:AA43" si="5">SUMIF(D$4:D$88,Y5,E$4:E$88)+SUMIF(I$4:I$88,Y5,H$4:H$88)+SUMIF(O$4:O$88,Y5,P$4:P$88)+SUMIF(T$4:T$88,Y5,S$4:S$88)</f>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="Z7">
         <f>SUMIF(D$4:D$88,Y7,F$4:F$88)+SUMIF(I$4:I$88,Y7,G$4:G$88)+SUMIF(O$4:O$88,Y7,Q$4:Q$88)+SUMIF(T$4:T$88,Y7,R$4:R$88)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA7">
         <f t="shared" si="5"/>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Z8">
         <f>SUMIF(D$4:D$88,Y8,F$4:F$88)+SUMIF(I$4:I$88,Y8,G$4:G$88)+SUMIF(O$4:O$88,Y8,Q$4:Q$88)+SUMIF(T$4:T$88,Y8,R$4:R$88)</f>
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AA8">
         <f t="shared" si="5"/>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AA9">
         <f t="shared" si="5"/>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="Z10">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA10">
         <f t="shared" si="5"/>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z11">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AA11">
         <f t="shared" si="5"/>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z12">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AA12">
         <f t="shared" si="5"/>
@@ -3034,11 +3034,11 @@
       </c>
       <c r="Z13">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AA13">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="Z14">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AA14">
         <f t="shared" si="5"/>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="Z15">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AA15">
         <f t="shared" si="5"/>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="Z16">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AA16">
         <f t="shared" si="5"/>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="Z17">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA17">
         <f t="shared" si="5"/>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z18">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA18">
         <f t="shared" si="5"/>
@@ -3284,12 +3284,16 @@
       <c r="D19" s="17">
         <v>59</v>
       </c>
-      <c r="E19" s="16" t="str">
+      <c r="E19" s="16">
         <f>IF(F19 &gt; G19, 1, "")</f>
-        <v/>
-      </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F19" s="16">
+        <v>7</v>
+      </c>
+      <c r="G19" s="16">
+        <v>3</v>
+      </c>
       <c r="H19" s="16" t="str">
         <f>IF(G19 &gt; F19, 1, "")</f>
         <v/>
@@ -3311,12 +3315,16 @@
       <c r="O19" s="17">
         <v>83</v>
       </c>
-      <c r="P19" s="16" t="str">
+      <c r="P19" s="16">
         <f>IF(Q19 &gt; R19, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>8</v>
+      </c>
+      <c r="R19" s="16">
+        <v>2</v>
+      </c>
       <c r="S19" s="16" t="str">
         <f>IF(R19 &gt; Q19, 1, "")</f>
         <v/>
@@ -3335,7 +3343,7 @@
       </c>
       <c r="Z19">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA19">
         <f t="shared" si="5"/>
@@ -3351,12 +3359,16 @@
       <c r="D20" s="17">
         <v>75</v>
       </c>
-      <c r="E20" s="16" t="str">
+      <c r="E20" s="16">
         <f>IF(F20 &gt; G20, 1, "")</f>
-        <v/>
-      </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F20" s="16">
+        <v>8</v>
+      </c>
+      <c r="G20" s="16">
+        <v>2</v>
+      </c>
       <c r="H20" s="16" t="str">
         <f t="shared" ref="H20:H28" si="6">IF(G20 &gt; F20, 1, "")</f>
         <v/>
@@ -3376,12 +3388,16 @@
       <c r="O20" s="17">
         <v>55</v>
       </c>
-      <c r="P20" s="16" t="str">
+      <c r="P20" s="16">
         <f t="shared" ref="P20:P28" si="7">IF(Q20 &gt; R20, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q20" s="16">
+        <v>10</v>
+      </c>
+      <c r="R20" s="16">
+        <v>0</v>
+      </c>
       <c r="S20" s="16" t="str">
         <f t="shared" ref="S20:S28" si="8">IF(R20 &gt; Q20, 1, "")</f>
         <v/>
@@ -3400,7 +3416,7 @@
       </c>
       <c r="Z20">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AA20">
         <f t="shared" si="5"/>
@@ -3420,11 +3436,15 @@
         <f t="shared" ref="E21:E28" si="9">IF(F21 &gt; G21, 1, "")</f>
         <v/>
       </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16" t="str">
+      <c r="F21" s="16">
+        <v>4</v>
+      </c>
+      <c r="G21" s="16">
+        <v>6</v>
+      </c>
+      <c r="H21" s="16">
         <f t="shared" si="6"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I21" s="17">
         <v>68</v>
@@ -3441,12 +3461,16 @@
       <c r="O21" s="17">
         <v>74</v>
       </c>
-      <c r="P21" s="16" t="str">
+      <c r="P21" s="16">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q21" s="16">
+        <v>7</v>
+      </c>
+      <c r="R21" s="16">
+        <v>3</v>
+      </c>
       <c r="S21" s="16" t="str">
         <f>IF(R21 &gt; Q21, 1, "")</f>
         <v/>
@@ -3465,7 +3489,7 @@
       </c>
       <c r="Z21">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AA21">
         <f t="shared" si="5"/>
@@ -3481,12 +3505,16 @@
       <c r="D22" s="17">
         <v>93</v>
       </c>
-      <c r="E22" s="16" t="str">
+      <c r="E22" s="16">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F22" s="16">
+        <v>6</v>
+      </c>
+      <c r="G22" s="16">
+        <v>4</v>
+      </c>
       <c r="H22" s="16" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3510,8 +3538,12 @@
         <f>IF(Q22 &gt; R22, 1, "")</f>
         <v/>
       </c>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
+      <c r="Q22" s="16">
+        <v>5</v>
+      </c>
+      <c r="R22" s="16">
+        <v>5</v>
+      </c>
       <c r="S22" s="16" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -3530,11 +3562,11 @@
       </c>
       <c r="Z22">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AA22">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
@@ -3546,12 +3578,16 @@
       <c r="D23" s="21">
         <v>57</v>
       </c>
-      <c r="E23" s="25" t="str">
+      <c r="E23" s="25">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="F23" s="20">
+        <v>6</v>
+      </c>
+      <c r="G23" s="20">
+        <v>4</v>
+      </c>
       <c r="H23" s="20" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3571,12 +3607,16 @@
       <c r="O23" s="21">
         <v>84</v>
       </c>
-      <c r="P23" s="25" t="str">
+      <c r="P23" s="25">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="Q23" s="20">
+        <v>7</v>
+      </c>
+      <c r="R23" s="20">
+        <v>3</v>
+      </c>
       <c r="S23" s="20" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -3595,11 +3635,11 @@
       </c>
       <c r="Z23">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AA23">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3613,12 +3653,16 @@
       <c r="D24" s="19">
         <v>82</v>
       </c>
-      <c r="E24" s="15" t="str">
+      <c r="E24" s="15">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="F24" s="15">
+        <v>6</v>
+      </c>
+      <c r="G24" s="15">
+        <v>4</v>
+      </c>
       <c r="H24" s="15" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3640,12 +3684,16 @@
       <c r="O24" s="19">
         <v>51</v>
       </c>
-      <c r="P24" s="15" t="str">
+      <c r="P24" s="15">
         <f>IF(Q24 &gt; R24, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="Q24" s="15">
+        <v>6</v>
+      </c>
+      <c r="R24" s="15">
+        <v>4</v>
+      </c>
       <c r="S24" s="15" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -3664,11 +3712,11 @@
       </c>
       <c r="Z24">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AA24">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3680,12 +3728,16 @@
       <c r="D25" s="17">
         <v>18</v>
       </c>
-      <c r="E25" s="16" t="str">
+      <c r="E25" s="16">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F25" s="16">
+        <v>8</v>
+      </c>
+      <c r="G25" s="16">
+        <v>2</v>
+      </c>
       <c r="H25" s="16" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3705,12 +3757,16 @@
       <c r="O25" s="17">
         <v>80</v>
       </c>
-      <c r="P25" s="16" t="str">
+      <c r="P25" s="16">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q25" s="16">
+        <v>8</v>
+      </c>
+      <c r="R25" s="16">
+        <v>2</v>
+      </c>
       <c r="S25" s="16" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -3729,11 +3785,11 @@
       </c>
       <c r="Z25">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AA25">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3745,12 +3801,16 @@
       <c r="D26" s="17">
         <v>86</v>
       </c>
-      <c r="E26" s="16" t="str">
+      <c r="E26" s="16">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F26" s="16">
+        <v>8</v>
+      </c>
+      <c r="G26" s="16">
+        <v>2</v>
+      </c>
       <c r="H26" s="16" t="str">
         <f>IF(G26 &gt; F26, 1, "")</f>
         <v/>
@@ -3774,8 +3834,12 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
+      <c r="Q26" s="16">
+        <v>5</v>
+      </c>
+      <c r="R26" s="16">
+        <v>5</v>
+      </c>
       <c r="S26" s="16" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -3794,11 +3858,11 @@
       </c>
       <c r="Z26">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AA26">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3810,12 +3874,16 @@
       <c r="D27" s="17">
         <v>53</v>
       </c>
-      <c r="E27" s="16" t="str">
+      <c r="E27" s="16">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F27" s="16">
+        <v>6</v>
+      </c>
+      <c r="G27" s="16">
+        <v>4</v>
+      </c>
       <c r="H27" s="16" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3839,11 +3907,15 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16" t="str">
+      <c r="Q27" s="16">
+        <v>3</v>
+      </c>
+      <c r="R27" s="16">
+        <v>7</v>
+      </c>
+      <c r="S27" s="16">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T27" s="17">
         <v>94</v>
@@ -3859,7 +3931,7 @@
       </c>
       <c r="Z27">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AA27">
         <f t="shared" si="5"/>
@@ -3875,12 +3947,16 @@
       <c r="D28" s="17">
         <v>77</v>
       </c>
-      <c r="E28" s="16" t="str">
+      <c r="E28" s="16">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F28" s="16">
+        <v>6</v>
+      </c>
+      <c r="G28" s="16">
+        <v>4</v>
+      </c>
       <c r="H28" s="16" t="str">
         <f t="shared" si="6"/>
         <v/>
@@ -3904,8 +3980,12 @@
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
+      <c r="Q28" s="16">
+        <v>5</v>
+      </c>
+      <c r="R28" s="16">
+        <v>5</v>
+      </c>
       <c r="S28" s="16" t="str">
         <f t="shared" si="8"/>
         <v/>
@@ -3924,7 +4004,7 @@
       </c>
       <c r="Z28">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA28">
         <f t="shared" si="5"/>
@@ -3962,7 +4042,7 @@
       </c>
       <c r="Z29">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AA29">
         <f t="shared" si="5"/>
@@ -4000,11 +4080,11 @@
       </c>
       <c r="Z30">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AA30">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="27" x14ac:dyDescent="0.35">
@@ -4040,7 +4120,7 @@
       </c>
       <c r="Z31">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AA31">
         <f t="shared" si="5"/>
@@ -4082,7 +4162,7 @@
       </c>
       <c r="Z32">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AA32">
         <f t="shared" si="5"/>
@@ -4156,11 +4236,11 @@
       </c>
       <c r="Z33">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AA33">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4225,11 +4305,11 @@
       </c>
       <c r="Z34">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AA34">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4290,11 +4370,11 @@
       </c>
       <c r="Z35">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AA35">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -4355,11 +4435,11 @@
       </c>
       <c r="Z36">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="AA36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4420,11 +4500,11 @@
       </c>
       <c r="Z37">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AA37">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
@@ -4485,11 +4565,11 @@
       </c>
       <c r="Z38">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AA38">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4554,11 +4634,11 @@
       </c>
       <c r="Z39">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AA39">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4619,11 +4699,11 @@
       </c>
       <c r="Z40">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AA40">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4684,7 +4764,7 @@
       </c>
       <c r="Z41">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AA41">
         <f t="shared" si="5"/>
@@ -4749,11 +4829,11 @@
       </c>
       <c r="Z42">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AA42">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4814,11 +4894,11 @@
       </c>
       <c r="Z43">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AA43">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
@@ -7197,44 +7277,44 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
-        <v>2d</v>
+        <v>2b</v>
       </c>
       <c r="B2">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="str">
-        <v>2d</v>
+        <v>2f</v>
       </c>
       <c r="B3">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
-        <v>2b</v>
+        <v>2f</v>
       </c>
       <c r="B4">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -7242,52 +7322,52 @@
         <v>2f</v>
       </c>
       <c r="B5">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
-        <v>2f</v>
+        <v>2b</v>
       </c>
       <c r="B6">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
-        <v>2e</v>
+        <v>2f</v>
       </c>
       <c r="B7">
-        <v>20</v>
+        <v>94</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
-        <v>2a</v>
+        <v>2d</v>
       </c>
       <c r="B8">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -7295,69 +7375,69 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
-        <v>2g</v>
+        <v>2a</v>
       </c>
       <c r="B9">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <v>2g</v>
+        <v>2b</v>
       </c>
       <c r="B10">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
-        <v>2b</v>
+        <v>2f</v>
       </c>
       <c r="B11">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="C11">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <v>2b</v>
+        <v>2a</v>
       </c>
       <c r="B12">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <v>2f</v>
+        <v>2a</v>
       </c>
       <c r="B13">
-        <v>86</v>
+        <v>55</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -7365,13 +7445,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <v>2f</v>
+        <v>2g</v>
       </c>
       <c r="B14">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="C14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -7379,13 +7459,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
-        <v>2f</v>
+        <v>2e</v>
       </c>
       <c r="B15">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -7393,13 +7473,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <v>2e</v>
+        <v>2g</v>
       </c>
       <c r="B16">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7407,13 +7487,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
-        <v>2d</v>
+        <v>2b</v>
       </c>
       <c r="B17">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="C17">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -7421,13 +7501,13 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
-        <v>2a</v>
+        <v>2e</v>
       </c>
       <c r="B18">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="C18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -7435,13 +7515,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
-        <v>2g</v>
+        <v>2e</v>
       </c>
       <c r="B19">
-        <v>71</v>
+        <v>22</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7449,83 +7529,83 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
-        <v>2c</v>
+        <v>2d</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C20">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
-        <v>2c</v>
+        <v>2a</v>
       </c>
       <c r="B21">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <v>2d</v>
+        <v>2b</v>
       </c>
       <c r="B22">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <v>2d</v>
+        <v>2a</v>
       </c>
       <c r="B23">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <v>2c</v>
+        <v>2g</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>63</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
-        <v>2e</v>
+        <v>2c</v>
       </c>
       <c r="B25">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -7533,13 +7613,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <v>2b</v>
+        <v>2c</v>
       </c>
       <c r="B26">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -7547,13 +7627,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <v>2f</v>
+        <v>2d</v>
       </c>
       <c r="B27">
-        <v>92</v>
+        <v>35</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -7561,13 +7641,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <v>2c</v>
+        <v>2f</v>
       </c>
       <c r="B28">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -7575,41 +7655,41 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <v>2c</v>
+        <v>2d</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <v>2e</v>
+        <v>2g</v>
       </c>
       <c r="B30">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
-        <v>2e</v>
+        <v>2c</v>
       </c>
       <c r="B31">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="C31">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -7617,13 +7697,13 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <v>2a</v>
+        <v>2e</v>
       </c>
       <c r="B32">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C32">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -7631,13 +7711,13 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <v>2a</v>
+        <v>2g</v>
       </c>
       <c r="B33">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -7645,13 +7725,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <v>2g</v>
+        <v>2c</v>
       </c>
       <c r="B34">
-        <v>66</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -7659,13 +7739,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
-        <v>2g</v>
+        <v>2e</v>
       </c>
       <c r="B35">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -7673,13 +7753,13 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <v>2b</v>
+        <v>2d</v>
       </c>
       <c r="B36">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -7687,13 +7767,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <v>2e</v>
+        <v>2c</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7701,13 +7781,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <v>2d</v>
+        <v>2e</v>
       </c>
       <c r="B38">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C38">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -7715,13 +7795,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
-        <v>2a</v>
+        <v>2g</v>
       </c>
       <c r="B39">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -7729,13 +7809,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
-        <v>2g</v>
+        <v>2d</v>
       </c>
       <c r="B40">
-        <v>68</v>
+        <v>26</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -7967,11 +8047,11 @@
       </c>
       <c r="Y4">
         <f>SUMIF(D$4:D$88,X4,E$4:E$88)+SUMIF(I$4:I$88,X4,H$4:H$88)+SUMIF(O$4:O$88,X4,P$4:P$88)+SUMIF(T$4:T$88,X4,S$4:S$88)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z4">
         <f>SUMIF(D$4:D$88,X4,F$4:F$88)+SUMIF(I$4:I$88,X4,G$4:G$88)+SUMIF(O$4:O$88,X4,Q$4:Q$88)+SUMIF(T$4:T$88,X4,R$4:R$88)</f>
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8040,7 +8120,7 @@
       </c>
       <c r="Y5">
         <f t="shared" ref="Y5:Y43" si="4">SUMIF(D$4:D$88,X5,E$4:E$88)+SUMIF(I$4:I$88,X5,H$4:H$88)+SUMIF(O$4:O$88,X5,P$4:P$88)+SUMIF(T$4:T$88,X5,S$4:S$88)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z5">
         <f t="shared" ref="Z5:Z43" si="5">SUMIF(D$4:D$88,X5,F$4:F$88)+SUMIF(I$4:I$88,X5,G$4:G$88)+SUMIF(O$4:O$88,X5,Q$4:Q$88)+SUMIF(T$4:T$88,X5,R$4:R$88)</f>
@@ -8113,11 +8193,11 @@
       </c>
       <c r="Y6">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z6">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8259,7 +8339,7 @@
       </c>
       <c r="Y8">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <f t="shared" si="5"/>
@@ -8336,11 +8416,11 @@
       </c>
       <c r="Y9">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z9">
         <f t="shared" si="5"/>
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8408,7 +8488,7 @@
       </c>
       <c r="Y10">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z10">
         <f t="shared" si="5"/>
@@ -8480,11 +8560,11 @@
       </c>
       <c r="Y11">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8556,7 +8636,7 @@
       </c>
       <c r="Z12">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8628,7 +8708,7 @@
       </c>
       <c r="Z13">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
@@ -8661,11 +8741,11 @@
       </c>
       <c r="Y14">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z14">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
@@ -8698,11 +8778,11 @@
       </c>
       <c r="Y15">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z15">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="27" x14ac:dyDescent="0.35">
@@ -8737,11 +8817,11 @@
       </c>
       <c r="Y16">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z16">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8778,11 +8858,11 @@
       </c>
       <c r="Y17">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z17">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
@@ -8852,11 +8932,11 @@
       </c>
       <c r="Y18">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z18">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -8872,13 +8952,17 @@
       </c>
       <c r="E19" s="16">
         <f>IF(F19&gt;G19,3,IF(F19=G19,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F19" s="16">
+        <v>15</v>
+      </c>
+      <c r="G19" s="16">
+        <v>20</v>
+      </c>
       <c r="H19" s="16">
         <f>IF(G19&gt;F19,3,IF(F19=G19,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I19" s="17">
         <v>58</v>
@@ -8899,13 +8983,17 @@
       </c>
       <c r="P19" s="16">
         <f>IF(Q19&gt;R19,3,IF(Q19=R19,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q19" s="16"/>
-      <c r="R19" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>30</v>
+      </c>
+      <c r="R19" s="16">
+        <v>8</v>
+      </c>
       <c r="S19" s="16">
         <f>IF(R19&gt;Q19,3,IF(Q19=R19,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" s="18">
         <v>34</v>
@@ -8921,7 +9009,7 @@
       </c>
       <c r="Y19">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z19">
         <f t="shared" si="5"/>
@@ -8941,8 +9029,12 @@
         <f t="shared" ref="E20:E21" si="8">IF(F20&gt;G20,3,IF(F20=G20,1,0))</f>
         <v>1</v>
       </c>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
+      <c r="F20" s="16">
+        <v>0</v>
+      </c>
+      <c r="G20" s="16">
+        <v>0</v>
+      </c>
       <c r="H20" s="16">
         <f t="shared" ref="H20:H25" si="9">IF(G20&gt;F20,3,IF(F20=G20,1,0))</f>
         <v>1</v>
@@ -8964,13 +9056,17 @@
       </c>
       <c r="P20" s="16">
         <f t="shared" ref="P20:P21" si="10">IF(Q20&gt;R20,3,IF(Q20=R20,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q20" s="16"/>
-      <c r="R20" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q20" s="16">
+        <v>24</v>
+      </c>
+      <c r="R20" s="16">
+        <v>12</v>
+      </c>
       <c r="S20" s="16">
         <f t="shared" ref="S20:S21" si="11">IF(R20&gt;Q20,3,IF(Q20=R20,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" s="17">
         <v>16</v>
@@ -8986,11 +9082,11 @@
       </c>
       <c r="Y20">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z20">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -9004,13 +9100,17 @@
       </c>
       <c r="E21" s="16">
         <f t="shared" si="8"/>
-        <v>1</v>
-      </c>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F21" s="16">
+        <v>14</v>
+      </c>
+      <c r="G21" s="16">
+        <v>10</v>
+      </c>
       <c r="H21" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
         <v>27</v>
@@ -9029,13 +9129,17 @@
       </c>
       <c r="P21" s="16">
         <f t="shared" si="10"/>
-        <v>1</v>
-      </c>
-      <c r="Q21" s="16"/>
-      <c r="R21" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q21" s="16">
+        <v>1</v>
+      </c>
+      <c r="R21" s="16">
+        <v>9</v>
+      </c>
       <c r="S21" s="16">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T21" s="17">
         <v>24</v>
@@ -9069,13 +9173,17 @@
       </c>
       <c r="E22" s="16">
         <f>IF(F22&gt;G22,3,IF(F22=G22,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F22" s="16">
+        <v>18</v>
+      </c>
+      <c r="G22" s="16">
+        <v>30</v>
+      </c>
       <c r="H22" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" s="17">
         <v>12</v>
@@ -9094,13 +9202,17 @@
       </c>
       <c r="P22" s="16">
         <f>IF(Q22&gt;R22,3,IF(Q22=R22,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q22" s="16"/>
-      <c r="R22" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="16">
+        <v>4</v>
+      </c>
+      <c r="R22" s="16">
+        <v>12</v>
+      </c>
       <c r="S22" s="16">
         <f>IF(R22&gt;Q22,3,IF(Q22=R22,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T22" s="17">
         <v>2</v>
@@ -9116,11 +9228,11 @@
       </c>
       <c r="Y22">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z22">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
@@ -9134,13 +9246,17 @@
       </c>
       <c r="E23" s="25">
         <f>IF(F23&gt;G23,3,IF(F23=G23,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
+        <v>3</v>
+      </c>
+      <c r="F23" s="20">
+        <v>8</v>
+      </c>
+      <c r="G23" s="20">
+        <v>0</v>
+      </c>
       <c r="H23" s="25">
         <f>IF(G23&gt;F23,3,IF(F23=G23,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="21">
         <v>14</v>
@@ -9159,13 +9275,17 @@
       </c>
       <c r="P23" s="25">
         <f>IF(Q23&gt;R23,3,IF(Q23=R23,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q23" s="20"/>
-      <c r="R23" s="20"/>
+        <v>0</v>
+      </c>
+      <c r="Q23" s="20">
+        <v>3</v>
+      </c>
+      <c r="R23" s="20">
+        <v>15</v>
+      </c>
       <c r="S23" s="25">
         <f t="shared" ref="S23:S25" si="12">IF(R23&gt;Q23,3,IF(Q23=R23,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T23" s="21">
         <v>28</v>
@@ -9185,7 +9305,7 @@
       </c>
       <c r="Z23">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9201,13 +9321,17 @@
       </c>
       <c r="E24" s="15">
         <f t="shared" ref="E24:E28" si="13">IF(F24&gt;G24,3,IF(F24=G24,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
+        <v>3</v>
+      </c>
+      <c r="F24" s="15">
+        <v>22</v>
+      </c>
+      <c r="G24" s="15">
+        <v>15</v>
+      </c>
       <c r="H24" s="15">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24" s="19">
         <v>5</v>
@@ -9230,8 +9354,12 @@
         <f t="shared" ref="P24:P28" si="14">IF(Q24&gt;R24,3,IF(Q24=R24,1,0))</f>
         <v>1</v>
       </c>
-      <c r="Q24" s="15"/>
-      <c r="R24" s="15"/>
+      <c r="Q24" s="15">
+        <v>0</v>
+      </c>
+      <c r="R24" s="15">
+        <v>0</v>
+      </c>
       <c r="S24" s="15">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -9254,7 +9382,7 @@
       </c>
       <c r="Z24">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9267,13 +9395,17 @@
       </c>
       <c r="E25" s="16">
         <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F25" s="16">
+        <v>33</v>
+      </c>
+      <c r="G25" s="16">
+        <v>0</v>
+      </c>
       <c r="H25" s="16">
         <f t="shared" si="9"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" s="17">
         <v>33</v>
@@ -9294,8 +9426,12 @@
         <f t="shared" si="14"/>
         <v>1</v>
       </c>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
+      <c r="Q25" s="16">
+        <v>5</v>
+      </c>
+      <c r="R25" s="16">
+        <v>5</v>
+      </c>
       <c r="S25" s="16">
         <f t="shared" si="12"/>
         <v>1</v>
@@ -9314,11 +9450,11 @@
       </c>
       <c r="Y25">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z25">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9333,8 +9469,12 @@
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
+      <c r="F26" s="16">
+        <v>0</v>
+      </c>
+      <c r="G26" s="16">
+        <v>0</v>
+      </c>
       <c r="H26" s="16">
         <f>IF(G26&gt;F26,3,IF(F26=G26,1,0))</f>
         <v>1</v>
@@ -9356,13 +9496,17 @@
       </c>
       <c r="P26" s="16">
         <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q26" s="16">
+        <v>3</v>
+      </c>
+      <c r="R26" s="16">
+        <v>0</v>
+      </c>
       <c r="S26" s="16">
         <f>IF(R26&gt;Q26,3,IF(Q26=R26,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" s="17">
         <v>9</v>
@@ -9378,11 +9522,11 @@
       </c>
       <c r="Y26">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9397,8 +9541,12 @@
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
+      <c r="F27" s="16">
+        <v>25</v>
+      </c>
+      <c r="G27" s="16">
+        <v>25</v>
+      </c>
       <c r="H27" s="16">
         <f t="shared" ref="H27:H28" si="15">IF(G27&gt;F27,3,IF(F27=G27,1,0))</f>
         <v>1</v>
@@ -9420,13 +9568,17 @@
       </c>
       <c r="P27" s="16">
         <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q27" s="16">
+        <v>1</v>
+      </c>
+      <c r="R27" s="16">
+        <v>0</v>
+      </c>
       <c r="S27" s="16">
         <f t="shared" ref="S27:S28" si="16">IF(R27&gt;Q27,3,IF(Q27=R27,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" s="17">
         <v>61</v>
@@ -9442,7 +9594,7 @@
       </c>
       <c r="Y27">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z27">
         <f t="shared" si="5"/>
@@ -9459,13 +9611,17 @@
       </c>
       <c r="E28" s="16">
         <f t="shared" si="13"/>
-        <v>1</v>
-      </c>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F28" s="16">
+        <v>30</v>
+      </c>
+      <c r="G28" s="16">
+        <v>0</v>
+      </c>
       <c r="H28" s="16">
         <f t="shared" si="15"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" s="17">
         <v>4</v>
@@ -9484,13 +9640,17 @@
       </c>
       <c r="P28" s="16">
         <f t="shared" si="14"/>
-        <v>1</v>
-      </c>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q28" s="16">
+        <v>20</v>
+      </c>
+      <c r="R28" s="16">
+        <v>21</v>
+      </c>
       <c r="S28" s="16">
         <f t="shared" si="16"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T28" s="17">
         <v>30</v>
@@ -9506,11 +9666,11 @@
       </c>
       <c r="Y28">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z28">
         <f t="shared" si="5"/>
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
@@ -9543,11 +9703,11 @@
       </c>
       <c r="Y29">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z29">
         <f t="shared" si="5"/>
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
@@ -9580,11 +9740,11 @@
       </c>
       <c r="Y30">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z30">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="27" x14ac:dyDescent="0.35">
@@ -9660,11 +9820,11 @@
       </c>
       <c r="Y32">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z32">
         <f t="shared" si="5"/>
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
@@ -9734,11 +9894,11 @@
       </c>
       <c r="Y33">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z33">
         <f t="shared" si="5"/>
-        <v>31</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9803,11 +9963,11 @@
       </c>
       <c r="Y34">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z34">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9868,11 +10028,11 @@
       </c>
       <c r="Y35">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z35">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9998,11 +10158,11 @@
       </c>
       <c r="Y37">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z37">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
@@ -10063,11 +10223,11 @@
       </c>
       <c r="Y38">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z38">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10260,11 +10420,11 @@
       </c>
       <c r="Y41">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z41">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>48</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10324,11 +10484,11 @@
       </c>
       <c r="Y42">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z42">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10388,11 +10548,11 @@
       </c>
       <c r="Y43">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z43">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
@@ -12755,10 +12915,10 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -12769,206 +12929,206 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D3">
-        <v>35</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
-        <v>2b</v>
+        <v>2g</v>
       </c>
       <c r="B4">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
-        <v>2g</v>
+        <v>2b</v>
       </c>
       <c r="B5">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
-        <v>2f</v>
+        <v>2d</v>
       </c>
       <c r="B6">
-        <v>91</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
-        <v>2d</v>
+        <v>2b</v>
       </c>
       <c r="B7">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
-        <v>2g</v>
+        <v>2e</v>
       </c>
       <c r="B8">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="C8">
         <v>8</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
-        <v>2d</v>
+        <v>2a</v>
       </c>
       <c r="B9">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C9">
         <v>8</v>
       </c>
       <c r="D9">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <v>2f</v>
+        <v>2e</v>
       </c>
       <c r="B10">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="C10">
         <v>8</v>
       </c>
       <c r="D10">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
-        <v>2c</v>
+        <v>2d</v>
       </c>
       <c r="B11">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>8</v>
       </c>
       <c r="D11">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <v>2a</v>
+        <v>2f</v>
       </c>
       <c r="B12">
-        <v>54</v>
+        <v>85</v>
       </c>
       <c r="C12">
         <v>8</v>
       </c>
       <c r="D12">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <v>2e</v>
+        <v>2a</v>
       </c>
       <c r="B13">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="C13">
         <v>8</v>
       </c>
       <c r="D13">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <v>2d</v>
+        <v>2f</v>
       </c>
       <c r="B14">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="C14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
-        <v>2b</v>
+        <v>2f</v>
       </c>
       <c r="B15">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <v>2f</v>
+        <v>2a</v>
       </c>
       <c r="B16">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
-        <v>2e</v>
+        <v>2f</v>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -12976,13 +13136,13 @@
         <v>2c</v>
       </c>
       <c r="B18">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -12990,27 +13150,27 @@
         <v>2d</v>
       </c>
       <c r="B19">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
-        <v>2a</v>
+        <v>2g</v>
       </c>
       <c r="B20">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -13018,183 +13178,183 @@
         <v>2d</v>
       </c>
       <c r="B21">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <v>2a</v>
+        <v>2g</v>
       </c>
       <c r="B22">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <v>2b</v>
+        <v>2c</v>
       </c>
       <c r="B23">
-        <v>78</v>
+        <v>2</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <v>2f</v>
+        <v>2e</v>
       </c>
       <c r="B24">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
-        <v>2f</v>
+        <v>2c</v>
       </c>
       <c r="B25">
-        <v>88</v>
+        <v>9</v>
       </c>
       <c r="C25">
+        <v>7</v>
+      </c>
+      <c r="D25">
         <v>5</v>
-      </c>
-      <c r="D25">
-        <v>24</v>
       </c>
       <c r="E25" s="12"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <v>2a</v>
+        <v>2b</v>
       </c>
       <c r="B26">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D26">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <v>2d</v>
+        <v>2f</v>
       </c>
       <c r="B27">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="C27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D27">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <v>2c</v>
+        <v>2f</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>87</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <v>2e</v>
+        <v>2a</v>
       </c>
       <c r="B29">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>5</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <v>2g</v>
+        <v>2d</v>
       </c>
       <c r="B30">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="C30">
         <v>5</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E30" s="12"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
-        <v>2c</v>
+        <v>2a</v>
       </c>
       <c r="B31">
-        <v>7</v>
+        <v>56</v>
       </c>
       <c r="C31">
         <v>5</v>
       </c>
       <c r="D31">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B32">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C32">
         <v>5</v>
       </c>
       <c r="D32">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <v>2g</v>
+        <v>2b</v>
       </c>
       <c r="B33">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C33">
         <v>5</v>
       </c>
       <c r="D33">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
@@ -13202,13 +13362,13 @@
         <v>2c</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C34">
         <v>5</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -13227,10 +13387,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <v>2e</v>
+        <v>2b</v>
       </c>
       <c r="B36">
-        <v>16</v>
+        <v>79</v>
       </c>
       <c r="C36">
         <v>5</v>
@@ -13247,66 +13407,66 @@
         <v>25</v>
       </c>
       <c r="C37">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <v>2a</v>
+        <v>2e</v>
       </c>
       <c r="B38">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C38">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
-        <v>2b</v>
+        <v>2e</v>
       </c>
       <c r="B39">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="C39">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
-        <v>2b</v>
+        <v>2g</v>
       </c>
       <c r="B40">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
-        <v>2f</v>
+        <v>2c</v>
       </c>
       <c r="B41">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="C41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/KWI-RoboChallenge_Rangliste.xlsx
+++ b/KWI-RoboChallenge_Rangliste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{316E161E-6BAE-5442-A452-2D126D9D975A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E664C4AC-28B8-DF49-825B-17426CFDD3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z4">
         <f t="shared" ref="Z4:Z43" si="0">SUMIF(D$4:D$88,Y4,F$4:F$88)+SUMIF(I$4:I$88,Y4,G$4:G$88)+SUMIF(O$4:O$88,Y4,Q$4:Q$88)+SUMIF(T$4:T$88,Y4,R$4:R$88)</f>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AA4">
         <f>SUMIF(D$4:D$88,Y4,E$4:E$88)+SUMIF(I$4:I$88,Y4,H$4:H$88)+SUMIF(O$4:O$88,Y4,P$4:P$88)+SUMIF(T$4:T$88,Y4,S$4:S$88)</f>
@@ -2446,11 +2446,11 @@
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AA5">
         <f t="shared" ref="AA5:AA43" si="5">SUMIF(D$4:D$88,Y5,E$4:E$88)+SUMIF(I$4:I$88,Y5,H$4:H$88)+SUMIF(O$4:O$88,Y5,P$4:P$88)+SUMIF(T$4:T$88,Y5,S$4:S$88)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -2592,11 +2592,11 @@
       </c>
       <c r="Z7">
         <f>SUMIF(D$4:D$88,Y7,F$4:F$88)+SUMIF(I$4:I$88,Y7,G$4:G$88)+SUMIF(O$4:O$88,Y7,Q$4:Q$88)+SUMIF(T$4:T$88,Y7,R$4:R$88)</f>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AA7">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Z8">
         <f>SUMIF(D$4:D$88,Y8,F$4:F$88)+SUMIF(I$4:I$88,Y8,G$4:G$88)+SUMIF(O$4:O$88,Y8,Q$4:Q$88)+SUMIF(T$4:T$88,Y8,R$4:R$88)</f>
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AA8">
         <f t="shared" si="5"/>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AA9">
         <f t="shared" si="5"/>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="Z10">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA10">
         <f t="shared" si="5"/>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z11">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AA11">
         <f t="shared" si="5"/>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z12">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA12">
         <f t="shared" si="5"/>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="Z13">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AA13">
         <f t="shared" si="5"/>
@@ -3072,11 +3072,11 @@
       </c>
       <c r="Z14">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AA14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="Z15">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <f t="shared" si="5"/>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="Z16">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AA16">
         <f t="shared" si="5"/>
@@ -3192,11 +3192,11 @@
       </c>
       <c r="Z17">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AA17">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z18">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AA18">
         <f t="shared" si="5"/>
@@ -3343,11 +3343,11 @@
       </c>
       <c r="Z19">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AA19">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="Z21">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA21">
         <f t="shared" si="5"/>
@@ -3562,11 +3562,11 @@
       </c>
       <c r="Z22">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA22">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
@@ -3635,11 +3635,11 @@
       </c>
       <c r="Z23">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="AA23">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="Z24">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AA24">
         <f t="shared" si="5"/>
@@ -3785,11 +3785,11 @@
       </c>
       <c r="Z25">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AA25">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="Z26">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA26">
         <f t="shared" si="5"/>
@@ -3931,7 +3931,7 @@
       </c>
       <c r="Z27">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AA27">
         <f t="shared" si="5"/>
@@ -4004,11 +4004,11 @@
       </c>
       <c r="Z28">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AA28">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="Z29">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA29">
         <f t="shared" si="5"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="Z30">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AA30">
         <f t="shared" si="5"/>
@@ -4120,11 +4120,11 @@
       </c>
       <c r="Z31">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="AA31">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="Z32">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AA32">
         <f t="shared" si="5"/>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="Z33">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA33">
         <f t="shared" si="5"/>
@@ -4258,11 +4258,15 @@
         <f>IF(F34 &gt; G34, 1, "")</f>
         <v/>
       </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16" t="str">
+      <c r="F34" s="16">
+        <v>3</v>
+      </c>
+      <c r="G34" s="16">
+        <v>7</v>
+      </c>
+      <c r="H34" s="16">
         <f>IF(G34 &gt; F34, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I34" s="17">
         <v>29</v>
@@ -4281,12 +4285,16 @@
       <c r="O34" s="17">
         <v>8</v>
       </c>
-      <c r="P34" s="16" t="str">
+      <c r="P34" s="16">
         <f>IF(Q34 &gt; R34, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q34" s="16">
+        <v>6</v>
+      </c>
+      <c r="R34" s="16">
+        <v>4</v>
+      </c>
       <c r="S34" s="16" t="str">
         <f>IF(R34 &gt; Q34, 1, "")</f>
         <v/>
@@ -4321,12 +4329,16 @@
       <c r="D35" s="17">
         <v>77</v>
       </c>
-      <c r="E35" s="16" t="str">
+      <c r="E35" s="16">
         <f>IF(F35 &gt; G35, 1, "")</f>
-        <v/>
-      </c>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F35" s="16">
+        <v>8</v>
+      </c>
+      <c r="G35" s="16">
+        <v>2</v>
+      </c>
       <c r="H35" s="16" t="str">
         <f t="shared" ref="H35:H43" si="10">IF(G35 &gt; F35, 1, "")</f>
         <v/>
@@ -4346,12 +4358,16 @@
       <c r="O35" s="17">
         <v>63</v>
       </c>
-      <c r="P35" s="16" t="str">
+      <c r="P35" s="16">
         <f>IF(Q35 &gt; R35, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q35" s="16">
+        <v>6</v>
+      </c>
+      <c r="R35" s="16">
+        <v>4</v>
+      </c>
       <c r="S35" s="16" t="str">
         <f t="shared" ref="S35:S40" si="11">IF(R35 &gt; Q35, 1, "")</f>
         <v/>
@@ -4370,11 +4386,11 @@
       </c>
       <c r="Z35">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AA35">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -4390,11 +4406,15 @@
         <f t="shared" ref="E36:E43" si="12">IF(F36 &gt; G36, 1, "")</f>
         <v/>
       </c>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16" t="str">
+      <c r="F36" s="16">
+        <v>4</v>
+      </c>
+      <c r="G36" s="16">
+        <v>6</v>
+      </c>
+      <c r="H36" s="16">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I36" s="17">
         <v>84</v>
@@ -4411,12 +4431,16 @@
       <c r="O36" s="18">
         <v>53</v>
       </c>
-      <c r="P36" s="16" t="str">
+      <c r="P36" s="16">
         <f t="shared" ref="P36:P43" si="13">IF(Q36 &gt; R36, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q36" s="16">
+        <v>10</v>
+      </c>
+      <c r="R36" s="16">
+        <v>0</v>
+      </c>
       <c r="S36" s="16" t="str">
         <f t="shared" si="11"/>
         <v/>
@@ -4435,11 +4459,11 @@
       </c>
       <c r="Z36">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AA36">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4451,12 +4475,16 @@
       <c r="D37" s="17">
         <v>69</v>
       </c>
-      <c r="E37" s="16" t="str">
+      <c r="E37" s="16">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F37" s="16">
+        <v>6</v>
+      </c>
+      <c r="G37" s="16">
+        <v>4</v>
+      </c>
       <c r="H37" s="16" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -4480,11 +4508,15 @@
         <f>IF(Q37 &gt; R37, 1, "")</f>
         <v/>
       </c>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="16"/>
-      <c r="S37" s="16" t="str">
+      <c r="Q37" s="16">
+        <v>0</v>
+      </c>
+      <c r="R37" s="16">
+        <v>10</v>
+      </c>
+      <c r="S37" s="16">
         <f t="shared" si="11"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T37" s="17">
         <v>22</v>
@@ -4500,7 +4532,7 @@
       </c>
       <c r="Z37">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AA37">
         <f t="shared" si="5"/>
@@ -4516,12 +4548,16 @@
       <c r="D38" s="21">
         <v>51</v>
       </c>
-      <c r="E38" s="25" t="str">
+      <c r="E38" s="25">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="F38" s="20">
+        <v>6</v>
+      </c>
+      <c r="G38" s="20">
+        <v>4</v>
+      </c>
       <c r="H38" s="20" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -4545,11 +4581,15 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
-      <c r="S38" s="20" t="str">
+      <c r="Q38" s="20">
+        <v>0</v>
+      </c>
+      <c r="R38" s="20">
+        <v>10</v>
+      </c>
+      <c r="S38" s="20">
         <f>IF(R38 &gt; Q38, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T38" s="21">
         <v>86</v>
@@ -4565,11 +4605,11 @@
       </c>
       <c r="Z38">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AA38">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4583,12 +4623,16 @@
       <c r="D39" s="19">
         <v>80</v>
       </c>
-      <c r="E39" s="15" t="str">
+      <c r="E39" s="15">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="F39" s="15">
+        <v>7</v>
+      </c>
+      <c r="G39" s="15">
+        <v>3</v>
+      </c>
       <c r="H39" s="15" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -4614,8 +4658,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q39" s="15"/>
-      <c r="R39" s="15"/>
+      <c r="Q39" s="15">
+        <v>5</v>
+      </c>
+      <c r="R39" s="15">
+        <v>5</v>
+      </c>
       <c r="S39" s="15" t="str">
         <f t="shared" si="11"/>
         <v/>
@@ -4634,11 +4682,11 @@
       </c>
       <c r="Z39">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AA39">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4654,11 +4702,15 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16" t="str">
+      <c r="F40" s="16">
+        <v>4</v>
+      </c>
+      <c r="G40" s="16">
+        <v>6</v>
+      </c>
+      <c r="H40" s="16">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I40" s="17">
         <v>94</v>
@@ -4675,12 +4727,16 @@
       <c r="O40" s="17">
         <v>57</v>
       </c>
-      <c r="P40" s="16" t="str">
+      <c r="P40" s="16">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q40" s="16">
+        <v>7</v>
+      </c>
+      <c r="R40" s="16">
+        <v>3</v>
+      </c>
       <c r="S40" s="16" t="str">
         <f t="shared" si="11"/>
         <v/>
@@ -4699,11 +4755,11 @@
       </c>
       <c r="Z40">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="AA40">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4719,8 +4775,12 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
+      <c r="F41" s="16">
+        <v>5</v>
+      </c>
+      <c r="G41" s="16">
+        <v>5</v>
+      </c>
       <c r="H41" s="16" t="str">
         <f>IF(G41 &gt; F41, 1, "")</f>
         <v/>
@@ -4744,8 +4804,12 @@
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="Q41" s="16"/>
-      <c r="R41" s="16"/>
+      <c r="Q41" s="16">
+        <v>5</v>
+      </c>
+      <c r="R41" s="16">
+        <v>5</v>
+      </c>
       <c r="S41" s="16" t="str">
         <f>IF(R41 &gt; Q41, 1, "")</f>
         <v/>
@@ -4764,7 +4828,7 @@
       </c>
       <c r="Z41">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AA41">
         <f t="shared" si="5"/>
@@ -4784,11 +4848,15 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
-      <c r="H42" s="16" t="str">
+      <c r="F42" s="16">
+        <v>3</v>
+      </c>
+      <c r="G42" s="16">
+        <v>7</v>
+      </c>
+      <c r="H42" s="16">
         <f t="shared" si="10"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I42" s="17">
         <v>32</v>
@@ -4805,12 +4873,16 @@
       <c r="O42" s="17">
         <v>3</v>
       </c>
-      <c r="P42" s="16" t="str">
+      <c r="P42" s="16">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q42" s="16">
+        <v>6</v>
+      </c>
+      <c r="R42" s="16">
+        <v>4</v>
+      </c>
       <c r="S42" s="16" t="str">
         <f t="shared" ref="S42:S43" si="14">IF(R42 &gt; Q42, 1, "")</f>
         <v/>
@@ -4829,7 +4901,7 @@
       </c>
       <c r="Z42">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA42">
         <f t="shared" si="5"/>
@@ -4849,8 +4921,12 @@
         <f t="shared" si="12"/>
         <v/>
       </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
+      <c r="F43" s="16">
+        <v>5</v>
+      </c>
+      <c r="G43" s="16">
+        <v>5</v>
+      </c>
       <c r="H43" s="16" t="str">
         <f t="shared" si="10"/>
         <v/>
@@ -4870,12 +4946,16 @@
       <c r="O43" s="17">
         <v>83</v>
       </c>
-      <c r="P43" s="16" t="str">
+      <c r="P43" s="16">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="Q43" s="16"/>
-      <c r="R43" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q43" s="16">
+        <v>9</v>
+      </c>
+      <c r="R43" s="16">
+        <v>1</v>
+      </c>
       <c r="S43" s="16" t="str">
         <f t="shared" si="14"/>
         <v/>
@@ -4894,11 +4974,11 @@
       </c>
       <c r="Z43">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AA43">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
@@ -7277,16 +7357,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
-        <v>2b</v>
+        <v>2f</v>
       </c>
       <c r="B2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C2">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -7294,27 +7374,27 @@
         <v>2f</v>
       </c>
       <c r="B3">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C3">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
-        <v>2f</v>
+        <v>2b</v>
       </c>
       <c r="B4">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C4">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
@@ -7322,24 +7402,24 @@
         <v>2f</v>
       </c>
       <c r="B5">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
-        <v>2b</v>
+        <v>2d</v>
       </c>
       <c r="B6">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="C6">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -7353,24 +7433,24 @@
         <v>94</v>
       </c>
       <c r="C7">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
-        <v>2d</v>
+        <v>2e</v>
       </c>
       <c r="B8">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C8">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -7381,35 +7461,35 @@
         <v>51</v>
       </c>
       <c r="C9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <v>2b</v>
+        <v>2a</v>
       </c>
       <c r="B10">
-        <v>77</v>
+        <v>57</v>
       </c>
       <c r="C10">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
-        <v>2f</v>
+        <v>2a</v>
       </c>
       <c r="B11">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C11">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D11">
         <v>2</v>
@@ -7417,13 +7497,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <v>2a</v>
+        <v>2b</v>
       </c>
       <c r="B12">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C12">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -7431,55 +7511,55 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <v>2a</v>
+        <v>2b</v>
       </c>
       <c r="B13">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="C13">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <v>2g</v>
+        <v>2f</v>
       </c>
       <c r="B14">
-        <v>62</v>
+        <v>93</v>
       </c>
       <c r="C14">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
-        <v>2e</v>
+        <v>2b</v>
       </c>
       <c r="B15">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="C15">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <v>2g</v>
+        <v>2e</v>
       </c>
       <c r="B16">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="C16">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7487,13 +7567,13 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
-        <v>2b</v>
+        <v>2g</v>
       </c>
       <c r="B17">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D17">
         <v>1</v>
@@ -7501,16 +7581,16 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
-        <v>2e</v>
+        <v>2g</v>
       </c>
       <c r="B18">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="C18">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
@@ -7518,10 +7598,10 @@
         <v>2e</v>
       </c>
       <c r="B19">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -7529,13 +7609,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
-        <v>2d</v>
+        <v>2a</v>
       </c>
       <c r="B20">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -7543,13 +7623,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
-        <v>2a</v>
+        <v>2b</v>
       </c>
       <c r="B21">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7557,13 +7637,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <v>2b</v>
+        <v>2c</v>
       </c>
       <c r="B22">
-        <v>82</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -7571,13 +7651,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <v>2a</v>
+        <v>2d</v>
       </c>
       <c r="B23">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -7585,13 +7665,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <v>2g</v>
+        <v>2d</v>
       </c>
       <c r="B24">
-        <v>63</v>
+        <v>36</v>
       </c>
       <c r="C24">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -7599,55 +7679,55 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
-        <v>2c</v>
+        <v>2a</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>59</v>
       </c>
       <c r="C25">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <v>2c</v>
+        <v>2g</v>
       </c>
       <c r="B26">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <v>2d</v>
+        <v>2g</v>
       </c>
       <c r="B27">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <v>2f</v>
+        <v>2c</v>
       </c>
       <c r="B28">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="C28">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -7655,30 +7735,30 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <v>2d</v>
+        <v>2c</v>
       </c>
       <c r="B29">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <v>2g</v>
+        <v>2f</v>
       </c>
       <c r="B30">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -7686,38 +7766,38 @@
         <v>2c</v>
       </c>
       <c r="B31">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C31">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <v>2e</v>
+        <v>2g</v>
       </c>
       <c r="B32">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="C32">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <v>2g</v>
+        <v>2e</v>
       </c>
       <c r="B33">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -7725,13 +7805,13 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <v>2c</v>
+        <v>2g</v>
       </c>
       <c r="B34">
-        <v>10</v>
+        <v>66</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -7739,27 +7819,27 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B35">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C35">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <v>2d</v>
+        <v>2c</v>
       </c>
       <c r="B36">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C36">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -7767,13 +7847,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <v>2c</v>
+        <v>2e</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C37">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7781,13 +7861,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B38">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C38">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -7795,13 +7875,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
-        <v>2g</v>
+        <v>2d</v>
       </c>
       <c r="B39">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="C39">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -7809,13 +7889,13 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
-        <v>2d</v>
+        <v>2e</v>
       </c>
       <c r="B40">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C40">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -8047,11 +8127,11 @@
       </c>
       <c r="Y4">
         <f>SUMIF(D$4:D$88,X4,E$4:E$88)+SUMIF(I$4:I$88,X4,H$4:H$88)+SUMIF(O$4:O$88,X4,P$4:P$88)+SUMIF(T$4:T$88,X4,S$4:S$88)</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <f>SUMIF(D$4:D$88,X4,F$4:F$88)+SUMIF(I$4:I$88,X4,G$4:G$88)+SUMIF(O$4:O$88,X4,Q$4:Q$88)+SUMIF(T$4:T$88,X4,R$4:R$88)</f>
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8120,7 +8200,7 @@
       </c>
       <c r="Y5">
         <f t="shared" ref="Y5:Y43" si="4">SUMIF(D$4:D$88,X5,E$4:E$88)+SUMIF(I$4:I$88,X5,H$4:H$88)+SUMIF(O$4:O$88,X5,P$4:P$88)+SUMIF(T$4:T$88,X5,S$4:S$88)</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z5">
         <f t="shared" ref="Z5:Z43" si="5">SUMIF(D$4:D$88,X5,F$4:F$88)+SUMIF(I$4:I$88,X5,G$4:G$88)+SUMIF(O$4:O$88,X5,Q$4:Q$88)+SUMIF(T$4:T$88,X5,R$4:R$88)</f>
@@ -8193,11 +8273,11 @@
       </c>
       <c r="Y6">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z6">
         <f t="shared" si="5"/>
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8266,11 +8346,11 @@
       </c>
       <c r="Y7">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z7">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
@@ -8343,7 +8423,7 @@
       </c>
       <c r="Z8">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8416,11 +8496,11 @@
       </c>
       <c r="Y9">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z9">
         <f t="shared" si="5"/>
-        <v>65</v>
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8488,11 +8568,11 @@
       </c>
       <c r="Y10">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z10">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8560,11 +8640,11 @@
       </c>
       <c r="Y11">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8704,11 +8784,11 @@
       </c>
       <c r="Y13">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Z13">
         <f t="shared" si="5"/>
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
@@ -8741,11 +8821,11 @@
       </c>
       <c r="Y14">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
@@ -8778,11 +8858,11 @@
       </c>
       <c r="Y15">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z15">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="27" x14ac:dyDescent="0.35">
@@ -8817,11 +8897,11 @@
       </c>
       <c r="Y16">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z16">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8858,11 +8938,11 @@
       </c>
       <c r="Y17">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z17">
         <f t="shared" si="5"/>
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
@@ -8932,7 +9012,7 @@
       </c>
       <c r="Y18">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z18">
         <f t="shared" si="5"/>
@@ -9009,7 +9089,7 @@
       </c>
       <c r="Y19">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <f t="shared" si="5"/>
@@ -9082,7 +9162,7 @@
       </c>
       <c r="Y20">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z20">
         <f t="shared" si="5"/>
@@ -9155,7 +9235,7 @@
       </c>
       <c r="Y21">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z21">
         <f t="shared" si="5"/>
@@ -9228,11 +9308,11 @@
       </c>
       <c r="Y22">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
@@ -9301,11 +9381,11 @@
       </c>
       <c r="Y23">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z23">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9378,11 +9458,11 @@
       </c>
       <c r="Y24">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <f t="shared" si="5"/>
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9450,11 +9530,11 @@
       </c>
       <c r="Y25">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z25">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9522,11 +9602,11 @@
       </c>
       <c r="Y26">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z26">
         <f t="shared" si="5"/>
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9594,11 +9674,11 @@
       </c>
       <c r="Y27">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z27">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9666,11 +9746,11 @@
       </c>
       <c r="Y28">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z28">
         <f t="shared" si="5"/>
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
@@ -9703,11 +9783,11 @@
       </c>
       <c r="Y29">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z29">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
@@ -9740,11 +9820,11 @@
       </c>
       <c r="Y30">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z30">
         <f t="shared" si="5"/>
-        <v>19</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="27" x14ac:dyDescent="0.35">
@@ -9779,11 +9859,11 @@
       </c>
       <c r="Y31">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z31">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9820,11 +9900,11 @@
       </c>
       <c r="Y32">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z32">
         <f t="shared" si="5"/>
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
@@ -9894,11 +9974,11 @@
       </c>
       <c r="Y33">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z33">
         <f t="shared" si="5"/>
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9914,13 +9994,17 @@
       </c>
       <c r="E34" s="16">
         <f>IF(F34&gt;G34,3,IF(F34=G34,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="16">
+        <v>13</v>
+      </c>
+      <c r="G34" s="16">
+        <v>15</v>
+      </c>
       <c r="H34" s="16">
         <f>IF(G34&gt;F34,3,IF(F34=G34,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I34" s="17">
         <v>52</v>
@@ -9941,13 +10025,17 @@
       </c>
       <c r="P34" s="16">
         <f>IF(Q34&gt;R34,3,IF(Q34=R34,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q34" s="16">
+        <v>30</v>
+      </c>
+      <c r="R34" s="16">
+        <v>0</v>
+      </c>
       <c r="S34" s="16">
         <f>IF(R34&gt;Q34,3,IF(Q34=R34,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34" s="17">
         <v>90</v>
@@ -9963,11 +10051,11 @@
       </c>
       <c r="Y34">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z34">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9981,13 +10069,17 @@
       </c>
       <c r="E35" s="16">
         <f t="shared" ref="E35:E36" si="17">IF(F35&gt;G35,3,IF(F35=G35,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F35" s="16"/>
-      <c r="G35" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="16">
+        <v>11</v>
+      </c>
+      <c r="G35" s="16">
+        <v>15</v>
+      </c>
       <c r="H35" s="16">
         <f t="shared" ref="H35:H37" si="18">IF(G35&gt;F35,3,IF(F35=G35,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I35" s="17">
         <v>27</v>
@@ -10008,8 +10100,12 @@
         <f t="shared" ref="P35:P36" si="19">IF(Q35&gt;R35,3,IF(Q35=R35,1,0))</f>
         <v>1</v>
       </c>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
+      <c r="Q35" s="16">
+        <v>1</v>
+      </c>
+      <c r="R35" s="16">
+        <v>1</v>
+      </c>
       <c r="S35" s="16">
         <f t="shared" ref="S35:S36" si="20">IF(R35&gt;Q35,3,IF(Q35=R35,1,0))</f>
         <v>1</v>
@@ -10028,11 +10124,11 @@
       </c>
       <c r="Y35">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z35">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10046,13 +10142,17 @@
       </c>
       <c r="E36" s="16">
         <f t="shared" si="17"/>
-        <v>1</v>
-      </c>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F36" s="16">
+        <v>21</v>
+      </c>
+      <c r="G36" s="16">
+        <v>19</v>
+      </c>
       <c r="H36" s="16">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I36" s="17">
         <v>89</v>
@@ -10071,13 +10171,17 @@
       </c>
       <c r="P36" s="16">
         <f t="shared" si="19"/>
-        <v>1</v>
-      </c>
-      <c r="Q36" s="16"/>
-      <c r="R36" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q36" s="16">
+        <v>21</v>
+      </c>
+      <c r="R36" s="16">
+        <v>6</v>
+      </c>
       <c r="S36" s="16">
         <f t="shared" si="20"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36" s="17">
         <v>54</v>
@@ -10093,7 +10197,7 @@
       </c>
       <c r="Y36">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z36">
         <f t="shared" si="5"/>
@@ -10111,13 +10215,17 @@
       </c>
       <c r="E37" s="16">
         <f>IF(F37&gt;G37,3,IF(F37=G37,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F37" s="16">
+        <v>33</v>
+      </c>
+      <c r="G37" s="16">
+        <v>0</v>
+      </c>
       <c r="H37" s="16">
         <f t="shared" si="18"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" s="17">
         <v>33</v>
@@ -10136,13 +10244,17 @@
       </c>
       <c r="P37" s="16">
         <f>IF(Q37&gt;R37,3,IF(Q37=R37,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q37" s="16"/>
-      <c r="R37" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q37" s="16">
+        <v>0</v>
+      </c>
+      <c r="R37" s="16">
+        <v>4</v>
+      </c>
       <c r="S37" s="16">
         <f>IF(R37&gt;Q37,3,IF(Q37=R37,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T37" s="17">
         <v>76</v>
@@ -10158,11 +10270,11 @@
       </c>
       <c r="Y37">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z37">
         <f t="shared" si="5"/>
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
@@ -10176,13 +10288,17 @@
       </c>
       <c r="E38" s="25">
         <f>IF(F38&gt;G38,3,IF(F38=G38,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
+        <v>3</v>
+      </c>
+      <c r="F38" s="20">
+        <v>20</v>
+      </c>
+      <c r="G38" s="20">
+        <v>16</v>
+      </c>
       <c r="H38" s="25">
         <f>IF(G38&gt;F38,3,IF(F38=G38,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I38" s="21">
         <v>56</v>
@@ -10203,8 +10319,12 @@
         <f>IF(Q38&gt;R38,3,IF(Q38=R38,1,0))</f>
         <v>1</v>
       </c>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
+      <c r="Q38" s="20">
+        <v>0</v>
+      </c>
+      <c r="R38" s="20">
+        <v>0</v>
+      </c>
       <c r="S38" s="25">
         <f t="shared" ref="S38:S40" si="21">IF(R38&gt;Q38,3,IF(Q38=R38,1,0))</f>
         <v>1</v>
@@ -10223,11 +10343,11 @@
       </c>
       <c r="Y38">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z38">
         <f t="shared" si="5"/>
-        <v>39</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10243,13 +10363,17 @@
       </c>
       <c r="E39" s="15">
         <f t="shared" ref="E39:E43" si="22">IF(F39&gt;G39,3,IF(F39=G39,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
+        <v>3</v>
+      </c>
+      <c r="F39" s="15">
+        <v>2</v>
+      </c>
+      <c r="G39" s="15">
+        <v>0</v>
+      </c>
       <c r="H39" s="15">
         <f t="shared" ref="H39:H40" si="23">IF(G39&gt;F39,3,IF(F39=G39,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I39" s="19">
         <v>79</v>
@@ -10270,13 +10394,17 @@
       </c>
       <c r="P39" s="15">
         <f t="shared" ref="P39:P43" si="24">IF(Q39&gt;R39,3,IF(Q39=R39,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q39" s="15"/>
-      <c r="R39" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="Q39" s="15">
+        <v>0</v>
+      </c>
+      <c r="R39" s="15">
+        <v>23</v>
+      </c>
       <c r="S39" s="15">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T39" s="19">
         <v>67</v>
@@ -10292,11 +10420,11 @@
       </c>
       <c r="Y39">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z39">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10309,13 +10437,17 @@
       </c>
       <c r="E40" s="16">
         <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F40" s="16">
+        <v>21</v>
+      </c>
+      <c r="G40" s="16">
+        <v>20</v>
+      </c>
       <c r="H40" s="16">
         <f t="shared" si="23"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I40" s="17">
         <v>85</v>
@@ -10334,13 +10466,17 @@
       </c>
       <c r="P40" s="16">
         <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q40" s="16">
+        <v>12</v>
+      </c>
+      <c r="R40" s="16">
+        <v>3</v>
+      </c>
       <c r="S40" s="16">
         <f t="shared" si="21"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40" s="17">
         <v>50</v>
@@ -10373,13 +10509,17 @@
       </c>
       <c r="E41" s="16">
         <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="16">
+        <v>3</v>
+      </c>
+      <c r="G41" s="16">
+        <v>12</v>
+      </c>
       <c r="H41" s="16">
         <f>IF(G41&gt;F41,3,IF(F41=G41,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" s="17">
         <v>16</v>
@@ -10398,13 +10538,17 @@
       </c>
       <c r="P41" s="16">
         <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="Q41" s="16"/>
-      <c r="R41" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q41" s="16">
+        <v>15</v>
+      </c>
+      <c r="R41" s="16">
+        <v>0</v>
+      </c>
       <c r="S41" s="16">
         <f>IF(R41&gt;Q41,3,IF(Q41=R41,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41" s="17">
         <v>34</v>
@@ -10424,7 +10568,7 @@
       </c>
       <c r="Z41">
         <f t="shared" si="5"/>
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10437,13 +10581,17 @@
       </c>
       <c r="E42" s="16">
         <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="F42" s="16"/>
-      <c r="G42" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="16">
+        <v>6</v>
+      </c>
+      <c r="G42" s="16">
+        <v>20</v>
+      </c>
       <c r="H42" s="16">
         <f t="shared" ref="H42:H43" si="25">IF(G42&gt;F42,3,IF(F42=G42,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I42" s="17">
         <v>58</v>
@@ -10462,13 +10610,17 @@
       </c>
       <c r="P42" s="16">
         <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q42" s="16">
+        <v>9</v>
+      </c>
+      <c r="R42" s="16">
+        <v>16</v>
+      </c>
       <c r="S42" s="16">
         <f t="shared" ref="S42:S43" si="26">IF(R42&gt;Q42,3,IF(Q42=R42,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T42" s="17">
         <v>7</v>
@@ -10484,7 +10636,7 @@
       </c>
       <c r="Y42">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z42">
         <f t="shared" si="5"/>
@@ -10501,13 +10653,17 @@
       </c>
       <c r="E43" s="16">
         <f t="shared" si="22"/>
-        <v>1</v>
-      </c>
-      <c r="F43" s="16"/>
-      <c r="G43" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F43" s="16">
+        <v>5</v>
+      </c>
+      <c r="G43" s="16">
+        <v>0</v>
+      </c>
       <c r="H43" s="16">
         <f t="shared" si="25"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I43" s="17">
         <v>37</v>
@@ -10526,13 +10682,17 @@
       </c>
       <c r="P43" s="16">
         <f t="shared" si="24"/>
-        <v>1</v>
-      </c>
-      <c r="Q43" s="16"/>
-      <c r="R43" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q43" s="16">
+        <v>20</v>
+      </c>
+      <c r="R43" s="16">
+        <v>19</v>
+      </c>
       <c r="S43" s="16">
         <f t="shared" si="26"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43" s="17">
         <v>91</v>
@@ -10548,11 +10708,11 @@
       </c>
       <c r="Y43">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z43">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
@@ -12915,10 +13075,10 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2">
-        <v>65</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -12929,10 +13089,10 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -12943,10 +13103,10 @@
         <v>72</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -12957,242 +13117,242 @@
         <v>73</v>
       </c>
       <c r="C5">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D5">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
-        <v>2d</v>
+        <v>2e</v>
       </c>
       <c r="B6">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6">
-        <v>44</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
-        <v>2b</v>
+        <v>2a</v>
       </c>
       <c r="B7">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
-        <v>2e</v>
+        <v>2c</v>
       </c>
       <c r="B8">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
-        <v>2a</v>
+        <v>2g</v>
       </c>
       <c r="B9">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B10">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
-        <v>2d</v>
+        <v>2b</v>
       </c>
       <c r="B11">
-        <v>37</v>
+        <v>81</v>
       </c>
       <c r="C11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <v>2f</v>
+        <v>2g</v>
       </c>
       <c r="B12">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="C12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <v>2a</v>
+        <v>2d</v>
       </c>
       <c r="B13">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13">
-        <v>8</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <v>2f</v>
+        <v>2b</v>
       </c>
       <c r="B14">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
         <v>7</v>
-      </c>
-      <c r="D14">
-        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
-        <v>2f</v>
+        <v>2e</v>
       </c>
       <c r="B15">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15">
-        <v>45</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <v>2a</v>
+        <v>2f</v>
       </c>
       <c r="B16">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="C16">
         <v>7</v>
       </c>
       <c r="D16">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
-        <v>2f</v>
+        <v>2a</v>
       </c>
       <c r="B17">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="C17">
         <v>7</v>
       </c>
       <c r="D17">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
-        <v>2c</v>
+        <v>2f</v>
       </c>
       <c r="B18">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="C18">
         <v>7</v>
       </c>
       <c r="D18">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
-        <v>2d</v>
+        <v>2a</v>
       </c>
       <c r="B19">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C19">
         <v>7</v>
       </c>
       <c r="D19">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
-        <v>2g</v>
+        <v>2d</v>
       </c>
       <c r="B20">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="C20">
         <v>7</v>
       </c>
       <c r="D20">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
-        <v>2d</v>
+        <v>2c</v>
       </c>
       <c r="B21">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="C21">
         <v>7</v>
       </c>
       <c r="D21">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <v>2g</v>
+        <v>2b</v>
       </c>
       <c r="B22">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C22">
         <v>7</v>
@@ -13203,30 +13363,30 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <v>2c</v>
+        <v>2a</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="C23">
         <v>7</v>
       </c>
       <c r="D23">
-        <v>18</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B24">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C24">
         <v>7</v>
       </c>
       <c r="D24">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -13240,22 +13400,22 @@
         <v>7</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E25" s="12"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <v>2b</v>
+        <v>2f</v>
       </c>
       <c r="B26">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="C26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -13263,182 +13423,182 @@
         <v>2f</v>
       </c>
       <c r="B27">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <v>2f</v>
+        <v>2e</v>
       </c>
       <c r="B28">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <v>2a</v>
+        <v>2e</v>
       </c>
       <c r="B29">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D29">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <v>2d</v>
+        <v>2e</v>
       </c>
       <c r="B30">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E30" s="12"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
-        <v>2a</v>
+        <v>2e</v>
       </c>
       <c r="B31">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <v>2d</v>
+        <v>2c</v>
       </c>
       <c r="B32">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <v>2b</v>
+        <v>2d</v>
       </c>
       <c r="B33">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <v>2c</v>
+        <v>2f</v>
       </c>
       <c r="B34">
-        <v>7</v>
+        <v>90</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
-        <v>2g</v>
+        <v>2f</v>
       </c>
       <c r="B35">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <v>2b</v>
+        <v>2a</v>
       </c>
       <c r="B36">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B37">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C37">
         <v>4</v>
       </c>
       <c r="D37">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <v>2e</v>
+        <v>2g</v>
       </c>
       <c r="B38">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C38">
         <v>4</v>
       </c>
       <c r="D38">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
-        <v>2e</v>
+        <v>2b</v>
       </c>
       <c r="B39">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="C39">
         <v>4</v>
       </c>
       <c r="D39">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -13449,10 +13609,10 @@
         <v>61</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -13463,7 +13623,7 @@
         <v>4</v>
       </c>
       <c r="C41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D41">
         <v>1</v>

--- a/KWI-RoboChallenge_Rangliste.xlsx
+++ b/KWI-RoboChallenge_Rangliste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E664C4AC-28B8-DF49-825B-17426CFDD3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D511F1E5-198E-E54B-90DE-BA30DF94A1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2373,11 +2373,11 @@
       </c>
       <c r="Z4">
         <f t="shared" ref="Z4:Z43" si="0">SUMIF(D$4:D$88,Y4,F$4:F$88)+SUMIF(I$4:I$88,Y4,G$4:G$88)+SUMIF(O$4:O$88,Y4,Q$4:Q$88)+SUMIF(T$4:T$88,Y4,R$4:R$88)</f>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA4">
         <f>SUMIF(D$4:D$88,Y4,E$4:E$88)+SUMIF(I$4:I$88,Y4,H$4:H$88)+SUMIF(O$4:O$88,Y4,P$4:P$88)+SUMIF(T$4:T$88,Y4,S$4:S$88)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA5">
         <f t="shared" ref="AA5:AA43" si="5">SUMIF(D$4:D$88,Y5,E$4:E$88)+SUMIF(I$4:I$88,Y5,H$4:H$88)+SUMIF(O$4:O$88,Y5,P$4:P$88)+SUMIF(T$4:T$88,Y5,S$4:S$88)</f>
@@ -2592,11 +2592,11 @@
       </c>
       <c r="Z7">
         <f>SUMIF(D$4:D$88,Y7,F$4:F$88)+SUMIF(I$4:I$88,Y7,G$4:G$88)+SUMIF(O$4:O$88,Y7,Q$4:Q$88)+SUMIF(T$4:T$88,Y7,R$4:R$88)</f>
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AA7">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="Z8">
         <f>SUMIF(D$4:D$88,Y8,F$4:F$88)+SUMIF(I$4:I$88,Y8,G$4:G$88)+SUMIF(O$4:O$88,Y8,Q$4:Q$88)+SUMIF(T$4:T$88,Y8,R$4:R$88)</f>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AA8">
         <f t="shared" si="5"/>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA9">
         <f t="shared" si="5"/>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="Z10">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AA10">
         <f t="shared" si="5"/>
@@ -2888,7 +2888,7 @@
       </c>
       <c r="Z11">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AA11">
         <f t="shared" si="5"/>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z12">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AA12">
         <f t="shared" si="5"/>
@@ -3034,11 +3034,11 @@
       </c>
       <c r="Z13">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="AA13">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="Z14">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AA14">
         <f t="shared" si="5"/>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="Z15">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AA15">
         <f t="shared" si="5"/>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="Z16">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AA16">
         <f t="shared" si="5"/>
@@ -3192,11 +3192,11 @@
       </c>
       <c r="Z17">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AA17">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z18">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA18">
         <f t="shared" si="5"/>
@@ -3343,11 +3343,11 @@
       </c>
       <c r="Z19">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AA19">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="Z20">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AA20">
         <f t="shared" si="5"/>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="Z21">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA21">
         <f t="shared" si="5"/>
@@ -3562,11 +3562,11 @@
       </c>
       <c r="Z22">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="AA22">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="Z23">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AA23">
         <f t="shared" si="5"/>
@@ -3712,11 +3712,11 @@
       </c>
       <c r="Z24">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AA24">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3785,11 +3785,11 @@
       </c>
       <c r="Z25">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AA25">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="Z26">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AA26">
         <f t="shared" si="5"/>
@@ -3931,11 +3931,11 @@
       </c>
       <c r="Z27">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="AA27">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="Z28">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AA28">
         <f t="shared" si="5"/>
@@ -4042,11 +4042,11 @@
       </c>
       <c r="Z29">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AA29">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="Z30">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AA30">
         <f t="shared" si="5"/>
@@ -4120,11 +4120,11 @@
       </c>
       <c r="Z31">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AA31">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="Z32">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA32">
         <f t="shared" si="5"/>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="Z33">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AA33">
         <f t="shared" si="5"/>
@@ -4313,11 +4313,11 @@
       </c>
       <c r="Z34">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AA34">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="Z35">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AA35">
         <f t="shared" si="5"/>
@@ -4459,11 +4459,11 @@
       </c>
       <c r="Z36">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AA36">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="Z37">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AA37">
         <f t="shared" si="5"/>
@@ -4605,7 +4605,7 @@
       </c>
       <c r="Z38">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA38">
         <f t="shared" si="5"/>
@@ -4682,11 +4682,11 @@
       </c>
       <c r="Z39">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="AA39">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z40">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA40">
         <f t="shared" si="5"/>
@@ -4828,11 +4828,11 @@
       </c>
       <c r="Z41">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA41">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4901,11 +4901,11 @@
       </c>
       <c r="Z42">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AA42">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4974,11 +4974,11 @@
       </c>
       <c r="Z43">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="AA43">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
@@ -5158,8 +5158,12 @@
         <f>IF(F49 &gt; G49, 1, "")</f>
         <v/>
       </c>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
+      <c r="F49" s="16">
+        <v>5</v>
+      </c>
+      <c r="G49" s="16">
+        <v>5</v>
+      </c>
       <c r="H49" s="16" t="str">
         <f>IF(G49 &gt; F49, 1, "")</f>
         <v/>
@@ -5185,8 +5189,12 @@
         <f>IF(Q49 &gt; R49, 1, "")</f>
         <v/>
       </c>
-      <c r="Q49" s="16"/>
-      <c r="R49" s="16"/>
+      <c r="Q49" s="16">
+        <v>5</v>
+      </c>
+      <c r="R49" s="16">
+        <v>5</v>
+      </c>
       <c r="S49" s="16" t="str">
         <f>IF(R49 &gt; Q49, 1, "")</f>
         <v/>
@@ -5211,11 +5219,15 @@
         <f>IF(F50 &gt; G50, 1, "")</f>
         <v/>
       </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
-      <c r="H50" s="16" t="str">
+      <c r="F50" s="16">
+        <v>2</v>
+      </c>
+      <c r="G50" s="16">
+        <v>8</v>
+      </c>
+      <c r="H50" s="16">
         <f t="shared" ref="H50:H58" si="15">IF(G50 &gt; F50, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I50" s="17">
         <v>94</v>
@@ -5232,12 +5244,16 @@
       <c r="O50" s="19">
         <v>84</v>
       </c>
-      <c r="P50" s="16" t="str">
+      <c r="P50" s="16">
         <f>IF(Q50 &gt; R50, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q50" s="16">
+        <v>7</v>
+      </c>
+      <c r="R50" s="16">
+        <v>3</v>
+      </c>
       <c r="S50" s="16" t="str">
         <f t="shared" ref="S50:S55" si="16">IF(R50 &gt; Q50, 1, "")</f>
         <v/>
@@ -5262,8 +5278,12 @@
         <f t="shared" ref="E51:E58" si="17">IF(F51 &gt; G51, 1, "")</f>
         <v/>
       </c>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
+      <c r="F51" s="16">
+        <v>5</v>
+      </c>
+      <c r="G51" s="16">
+        <v>5</v>
+      </c>
       <c r="H51" s="16" t="str">
         <f t="shared" si="15"/>
         <v/>
@@ -5283,12 +5303,16 @@
       <c r="O51" s="18">
         <v>51</v>
       </c>
-      <c r="P51" s="16" t="str">
+      <c r="P51" s="16">
         <f t="shared" ref="P51:P58" si="18">IF(Q51 &gt; R51, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q51" s="16">
+        <v>8</v>
+      </c>
+      <c r="R51" s="16">
+        <v>2</v>
+      </c>
       <c r="S51" s="16" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5313,11 +5337,15 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
-      <c r="H52" s="16" t="str">
+      <c r="F52" s="16">
+        <v>4</v>
+      </c>
+      <c r="G52" s="16">
+        <v>6</v>
+      </c>
+      <c r="H52" s="16">
         <f t="shared" si="15"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I52" s="17">
         <v>8</v>
@@ -5334,12 +5362,16 @@
       <c r="O52" s="17">
         <v>80</v>
       </c>
-      <c r="P52" s="16" t="str">
+      <c r="P52" s="16">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="Q52" s="16"/>
-      <c r="R52" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q52" s="16">
+        <v>8</v>
+      </c>
+      <c r="R52" s="16">
+        <v>2</v>
+      </c>
       <c r="S52" s="16" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5360,12 +5392,16 @@
       <c r="D53" s="21">
         <v>55</v>
       </c>
-      <c r="E53" s="25" t="str">
+      <c r="E53" s="25">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="F53" s="20">
+        <v>6</v>
+      </c>
+      <c r="G53" s="20">
+        <v>4</v>
+      </c>
       <c r="H53" s="20" t="str">
         <f t="shared" si="15"/>
         <v/>
@@ -5389,11 +5425,15 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="Q53" s="20"/>
-      <c r="R53" s="20"/>
-      <c r="S53" s="20" t="str">
+      <c r="Q53" s="20">
+        <v>0</v>
+      </c>
+      <c r="R53" s="20">
+        <v>10</v>
+      </c>
+      <c r="S53" s="20">
         <f t="shared" si="16"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T53" s="21">
         <v>66</v>
@@ -5417,11 +5457,15 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
-      <c r="H54" s="15" t="str">
+      <c r="F54" s="15">
+        <v>4</v>
+      </c>
+      <c r="G54" s="15">
+        <v>6</v>
+      </c>
+      <c r="H54" s="15">
         <f t="shared" si="15"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I54" s="19">
         <v>92</v>
@@ -5444,11 +5488,15 @@
         <f>IF(Q54 &gt; R54, 1, "")</f>
         <v/>
       </c>
-      <c r="Q54" s="15"/>
-      <c r="R54" s="15"/>
-      <c r="S54" s="15" t="str">
+      <c r="Q54" s="15">
+        <v>3</v>
+      </c>
+      <c r="R54" s="15">
+        <v>7</v>
+      </c>
+      <c r="S54" s="15">
         <f t="shared" si="16"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T54" s="19">
         <v>62</v>
@@ -5466,12 +5514,16 @@
       <c r="D55" s="17">
         <v>1</v>
       </c>
-      <c r="E55" s="16" t="str">
+      <c r="E55" s="16">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F55" s="16">
+        <v>6</v>
+      </c>
+      <c r="G55" s="16">
+        <v>4</v>
+      </c>
       <c r="H55" s="16" t="str">
         <f t="shared" si="15"/>
         <v/>
@@ -5491,12 +5543,16 @@
       <c r="O55" s="17">
         <v>57</v>
       </c>
-      <c r="P55" s="16" t="str">
+      <c r="P55" s="16">
         <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="Q55" s="16"/>
-      <c r="R55" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q55" s="16">
+        <v>7</v>
+      </c>
+      <c r="R55" s="16">
+        <v>3</v>
+      </c>
       <c r="S55" s="16" t="str">
         <f t="shared" si="16"/>
         <v/>
@@ -5517,12 +5573,16 @@
       <c r="D56" s="17">
         <v>29</v>
       </c>
-      <c r="E56" s="16" t="str">
+      <c r="E56" s="16">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F56" s="16">
+        <v>6</v>
+      </c>
+      <c r="G56" s="16">
+        <v>4</v>
+      </c>
       <c r="H56" s="16" t="str">
         <f>IF(G56 &gt; F56, 1, "")</f>
         <v/>
@@ -5546,11 +5606,15 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="Q56" s="16"/>
-      <c r="R56" s="16"/>
-      <c r="S56" s="16" t="str">
+      <c r="Q56" s="16">
+        <v>2</v>
+      </c>
+      <c r="R56" s="16">
+        <v>8</v>
+      </c>
+      <c r="S56" s="16">
         <f>IF(R56 &gt; Q56, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T56" s="17">
         <v>93</v>
@@ -5572,11 +5636,15 @@
         <f t="shared" si="17"/>
         <v/>
       </c>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16" t="str">
+      <c r="F57" s="16">
+        <v>4</v>
+      </c>
+      <c r="G57" s="16">
+        <v>6</v>
+      </c>
+      <c r="H57" s="16">
         <f t="shared" si="15"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I57" s="17">
         <v>18</v>
@@ -5597,11 +5665,15 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="Q57" s="16"/>
-      <c r="R57" s="16"/>
-      <c r="S57" s="16" t="str">
+      <c r="Q57" s="16">
+        <v>4</v>
+      </c>
+      <c r="R57" s="16">
+        <v>6</v>
+      </c>
+      <c r="S57" s="16">
         <f>IF(R57 &gt; Q57, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T57" s="17">
         <v>32</v>
@@ -5619,12 +5691,16 @@
       <c r="D58" s="17">
         <v>75</v>
       </c>
-      <c r="E58" s="16" t="str">
+      <c r="E58" s="16">
         <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F58" s="16">
+        <v>8</v>
+      </c>
+      <c r="G58" s="16">
+        <v>2</v>
+      </c>
       <c r="H58" s="16" t="str">
         <f t="shared" si="15"/>
         <v/>
@@ -5648,11 +5724,15 @@
         <f t="shared" si="18"/>
         <v/>
       </c>
-      <c r="Q58" s="16"/>
-      <c r="R58" s="16"/>
-      <c r="S58" s="16" t="str">
+      <c r="Q58" s="16">
+        <v>3</v>
+      </c>
+      <c r="R58" s="16">
+        <v>7</v>
+      </c>
+      <c r="S58" s="16">
         <f t="shared" ref="S58" si="19">IF(R58 &gt; Q58, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T58" s="17">
         <v>69</v>
@@ -7360,13 +7440,13 @@
         <v>2f</v>
       </c>
       <c r="B2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -7374,38 +7454,38 @@
         <v>2f</v>
       </c>
       <c r="B3">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
-        <v>2b</v>
+        <v>2a</v>
       </c>
       <c r="B4">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C4">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
-        <v>2f</v>
+        <v>2d</v>
       </c>
       <c r="B5">
-        <v>84</v>
+        <v>32</v>
       </c>
       <c r="C5">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -7413,16 +7493,16 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
-        <v>2d</v>
+        <v>2f</v>
       </c>
       <c r="B6">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="C6">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
@@ -7430,10 +7510,10 @@
         <v>2f</v>
       </c>
       <c r="B7">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -7441,27 +7521,27 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
-        <v>2e</v>
+        <v>2a</v>
       </c>
       <c r="B8">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
-        <v>2a</v>
+        <v>2b</v>
       </c>
       <c r="B9">
-        <v>51</v>
+        <v>80</v>
       </c>
       <c r="C9">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -7469,13 +7549,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <v>2a</v>
+        <v>2f</v>
       </c>
       <c r="B10">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="C10">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>3</v>
@@ -7483,16 +7563,16 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
-        <v>2a</v>
+        <v>2b</v>
       </c>
       <c r="B11">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C11">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
@@ -7500,24 +7580,24 @@
         <v>2b</v>
       </c>
       <c r="B12">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D12">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <v>2b</v>
+        <v>2e</v>
       </c>
       <c r="B13">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="C13">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -7525,13 +7605,13 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <v>2f</v>
+        <v>2a</v>
       </c>
       <c r="B14">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -7539,13 +7619,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
-        <v>2b</v>
+        <v>2e</v>
       </c>
       <c r="B15">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="C15">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -7553,13 +7633,13 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <v>2e</v>
+        <v>2g</v>
       </c>
       <c r="B16">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C16">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -7567,27 +7647,27 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
-        <v>2g</v>
+        <v>2a</v>
       </c>
       <c r="B17">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="C17">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
-        <v>2g</v>
+        <v>2b</v>
       </c>
       <c r="B18">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C18">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -7595,41 +7675,41 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B19">
+        <v>29</v>
+      </c>
+      <c r="C19">
         <v>20</v>
       </c>
-      <c r="C19">
-        <v>15</v>
-      </c>
       <c r="D19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
-        <v>2a</v>
+        <v>2g</v>
       </c>
       <c r="B20">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
-        <v>2b</v>
+        <v>2e</v>
       </c>
       <c r="B21">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C21">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -7637,13 +7717,13 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <v>2c</v>
+        <v>2g</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>71</v>
       </c>
       <c r="C22">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -7651,27 +7731,27 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <v>2d</v>
+        <v>2g</v>
       </c>
       <c r="B23">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="C23">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <v>2d</v>
+        <v>2c</v>
       </c>
       <c r="B24">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="C24">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -7679,13 +7759,13 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
-        <v>2a</v>
+        <v>2c</v>
       </c>
       <c r="B25">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -7693,13 +7773,13 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <v>2g</v>
+        <v>2d</v>
       </c>
       <c r="B26">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="C26">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -7707,13 +7787,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <v>2g</v>
+        <v>2f</v>
       </c>
       <c r="B27">
-        <v>68</v>
+        <v>92</v>
       </c>
       <c r="C27">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -7724,41 +7804,41 @@
         <v>2c</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C28">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <v>2c</v>
+        <v>2g</v>
       </c>
       <c r="B29">
-        <v>11</v>
+        <v>63</v>
       </c>
       <c r="C29">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <v>2f</v>
+        <v>2g</v>
       </c>
       <c r="B30">
-        <v>92</v>
+        <v>68</v>
       </c>
       <c r="C30">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -7766,24 +7846,24 @@
         <v>2c</v>
       </c>
       <c r="B31">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <v>2g</v>
+        <v>2a</v>
       </c>
       <c r="B32">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C32">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D32">
         <v>1</v>
@@ -7791,27 +7871,27 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <v>2e</v>
+        <v>2b</v>
       </c>
       <c r="B33">
+        <v>82</v>
+      </c>
+      <c r="C33">
         <v>17</v>
       </c>
-      <c r="C33">
-        <v>12</v>
-      </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <v>2g</v>
+        <v>2e</v>
       </c>
       <c r="B34">
-        <v>66</v>
+        <v>17</v>
       </c>
       <c r="C34">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -7819,41 +7899,41 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="str">
-        <v>2d</v>
+        <v>2c</v>
       </c>
       <c r="B35">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C35">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <v>2c</v>
+        <v>2d</v>
       </c>
       <c r="B36">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C36">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B37">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C37">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7861,13 +7941,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <v>2d</v>
+        <v>2e</v>
       </c>
       <c r="B38">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C38">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -7881,7 +7961,7 @@
         <v>35</v>
       </c>
       <c r="C39">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -7895,7 +7975,7 @@
         <v>23</v>
       </c>
       <c r="C40">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -8127,11 +8207,11 @@
       </c>
       <c r="Y4">
         <f>SUMIF(D$4:D$88,X4,E$4:E$88)+SUMIF(I$4:I$88,X4,H$4:H$88)+SUMIF(O$4:O$88,X4,P$4:P$88)+SUMIF(T$4:T$88,X4,S$4:S$88)</f>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z4">
         <f>SUMIF(D$4:D$88,X4,F$4:F$88)+SUMIF(I$4:I$88,X4,G$4:G$88)+SUMIF(O$4:O$88,X4,Q$4:Q$88)+SUMIF(T$4:T$88,X4,R$4:R$88)</f>
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8200,7 +8280,7 @@
       </c>
       <c r="Y5">
         <f t="shared" ref="Y5:Y43" si="4">SUMIF(D$4:D$88,X5,E$4:E$88)+SUMIF(I$4:I$88,X5,H$4:H$88)+SUMIF(O$4:O$88,X5,P$4:P$88)+SUMIF(T$4:T$88,X5,S$4:S$88)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z5">
         <f t="shared" ref="Z5:Z43" si="5">SUMIF(D$4:D$88,X5,F$4:F$88)+SUMIF(I$4:I$88,X5,G$4:G$88)+SUMIF(O$4:O$88,X5,Q$4:Q$88)+SUMIF(T$4:T$88,X5,R$4:R$88)</f>
@@ -8273,11 +8353,11 @@
       </c>
       <c r="Y6">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z6">
         <f t="shared" si="5"/>
-        <v>53</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8346,11 +8426,11 @@
       </c>
       <c r="Y7">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z7">
         <f t="shared" si="5"/>
-        <v>19</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
@@ -8419,11 +8499,11 @@
       </c>
       <c r="Y8">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z8">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8496,11 +8576,11 @@
       </c>
       <c r="Y9">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z9">
         <f t="shared" si="5"/>
-        <v>98</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8568,11 +8648,11 @@
       </c>
       <c r="Y10">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z10">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8640,11 +8720,11 @@
       </c>
       <c r="Y11">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z11">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8712,11 +8792,11 @@
       </c>
       <c r="Y12">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <f t="shared" si="5"/>
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8784,11 +8864,11 @@
       </c>
       <c r="Y13">
         <f t="shared" si="4"/>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="Z13">
         <f t="shared" si="5"/>
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
@@ -8821,11 +8901,11 @@
       </c>
       <c r="Y14">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z14">
         <f t="shared" si="5"/>
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
@@ -8858,11 +8938,11 @@
       </c>
       <c r="Y15">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z15">
         <f t="shared" si="5"/>
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="27" x14ac:dyDescent="0.35">
@@ -8897,11 +8977,11 @@
       </c>
       <c r="Y16">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z16">
         <f t="shared" si="5"/>
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8938,11 +9018,11 @@
       </c>
       <c r="Y17">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <f t="shared" si="5"/>
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
@@ -9012,11 +9092,11 @@
       </c>
       <c r="Y18">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z18">
         <f t="shared" si="5"/>
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -9089,11 +9169,11 @@
       </c>
       <c r="Y19">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Z19">
         <f t="shared" si="5"/>
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9162,11 +9242,11 @@
       </c>
       <c r="Y20">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z20">
         <f t="shared" si="5"/>
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -9235,11 +9315,11 @@
       </c>
       <c r="Y21">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z21">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9308,7 +9388,7 @@
       </c>
       <c r="Y22">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z22">
         <f t="shared" si="5"/>
@@ -9381,11 +9461,11 @@
       </c>
       <c r="Y23">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z23">
         <f t="shared" si="5"/>
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9458,11 +9538,11 @@
       </c>
       <c r="Y24">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z24">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9530,11 +9610,11 @@
       </c>
       <c r="Y25">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z25">
         <f t="shared" si="5"/>
-        <v>27</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9602,11 +9682,11 @@
       </c>
       <c r="Y26">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z26">
         <f t="shared" si="5"/>
-        <v>60</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9674,11 +9754,11 @@
       </c>
       <c r="Y27">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z27">
         <f t="shared" si="5"/>
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9746,11 +9826,11 @@
       </c>
       <c r="Y28">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z28">
         <f t="shared" si="5"/>
-        <v>85</v>
+        <v>115</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
@@ -9783,11 +9863,11 @@
       </c>
       <c r="Y29">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z29">
         <f t="shared" si="5"/>
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
@@ -9820,7 +9900,7 @@
       </c>
       <c r="Y30">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z30">
         <f t="shared" si="5"/>
@@ -9859,11 +9939,11 @@
       </c>
       <c r="Y31">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z31">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9900,11 +9980,11 @@
       </c>
       <c r="Y32">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z32">
         <f t="shared" si="5"/>
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
@@ -9974,11 +10054,11 @@
       </c>
       <c r="Y33">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Z33">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10051,11 +10131,11 @@
       </c>
       <c r="Y34">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z34">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10124,7 +10204,7 @@
       </c>
       <c r="Y35">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z35">
         <f t="shared" si="5"/>
@@ -10197,11 +10277,11 @@
       </c>
       <c r="Y36">
         <f t="shared" si="4"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Z36">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10270,11 +10350,11 @@
       </c>
       <c r="Y37">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z37">
         <f t="shared" si="5"/>
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
@@ -10343,11 +10423,11 @@
       </c>
       <c r="Y38">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z38">
         <f t="shared" si="5"/>
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10420,11 +10500,11 @@
       </c>
       <c r="Y39">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z39">
         <f t="shared" si="5"/>
-        <v>30</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10492,7 +10572,7 @@
       </c>
       <c r="Y40">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z40">
         <f t="shared" si="5"/>
@@ -10564,7 +10644,7 @@
       </c>
       <c r="Y41">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z41">
         <f t="shared" si="5"/>
@@ -10636,7 +10716,7 @@
       </c>
       <c r="Y42">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z42">
         <f t="shared" si="5"/>
@@ -10708,7 +10788,7 @@
       </c>
       <c r="Y43">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z43">
         <f t="shared" si="5"/>
@@ -10885,13 +10965,17 @@
       </c>
       <c r="E49" s="16">
         <f>IF(F49&gt;G49,3,IF(F49=G49,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F49" s="16">
+        <v>3</v>
+      </c>
+      <c r="G49" s="16">
+        <v>0</v>
+      </c>
       <c r="H49" s="16">
         <f>IF(G49&gt;F49,3,IF(F49=G49,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="17">
         <v>50</v>
@@ -10911,14 +10995,16 @@
         <v>91</v>
       </c>
       <c r="P49" s="16">
-        <f>IF(Q49&gt;R49,3,IF(Q49=R49,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q49" s="16"/>
-      <c r="R49" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q49" s="16">
+        <v>0</v>
+      </c>
+      <c r="R49" s="16">
+        <v>0</v>
+      </c>
       <c r="S49" s="16">
-        <f>IF(R49&gt;Q49,3,IF(Q49=R49,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T49" s="17">
         <v>67</v>
@@ -10938,13 +11024,17 @@
       </c>
       <c r="E50" s="16">
         <f t="shared" ref="E50:E51" si="27">IF(F50&gt;G50,3,IF(F50=G50,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F50" s="16"/>
-      <c r="G50" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F50" s="16">
+        <v>6</v>
+      </c>
+      <c r="G50" s="16">
+        <v>9</v>
+      </c>
       <c r="H50" s="16">
         <f t="shared" ref="H50:H52" si="28">IF(G50&gt;F50,3,IF(F50=G50,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I50" s="17">
         <v>24</v>
@@ -10963,13 +11053,17 @@
       </c>
       <c r="P50" s="16">
         <f t="shared" ref="P50:P51" si="29">IF(Q50&gt;R50,3,IF(Q50=R50,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q50" s="16">
+        <v>4</v>
+      </c>
+      <c r="R50" s="16">
+        <v>0</v>
+      </c>
       <c r="S50" s="16">
         <f t="shared" ref="S50:S51" si="30">IF(R50&gt;Q50,3,IF(Q50=R50,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50" s="17">
         <v>87</v>
@@ -10989,13 +11083,17 @@
       </c>
       <c r="E51" s="16">
         <f t="shared" si="27"/>
-        <v>1</v>
-      </c>
-      <c r="F51" s="16"/>
-      <c r="G51" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F51" s="16">
+        <v>0</v>
+      </c>
+      <c r="G51" s="16">
+        <v>10</v>
+      </c>
       <c r="H51" s="16">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I51" s="17">
         <v>65</v>
@@ -11014,13 +11112,17 @@
       </c>
       <c r="P51" s="16">
         <f t="shared" si="29"/>
-        <v>1</v>
-      </c>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q51" s="16">
+        <v>20</v>
+      </c>
+      <c r="R51" s="16">
+        <v>0</v>
+      </c>
       <c r="S51" s="16">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51" s="17">
         <v>4</v>
@@ -11040,13 +11142,17 @@
       </c>
       <c r="E52" s="16">
         <f>IF(F52&gt;G52,3,IF(F52=G52,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F52" s="16"/>
-      <c r="G52" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F52" s="16">
+        <v>23</v>
+      </c>
+      <c r="G52" s="16">
+        <v>15</v>
+      </c>
       <c r="H52" s="16">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I52" s="17">
         <v>5</v>
@@ -11065,13 +11171,17 @@
       </c>
       <c r="P52" s="16">
         <f>IF(Q52&gt;R52,3,IF(Q52=R52,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q52" s="16"/>
-      <c r="R52" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q52" s="16">
+        <v>10</v>
+      </c>
+      <c r="R52" s="16">
+        <v>20</v>
+      </c>
       <c r="S52" s="16">
         <f>IF(R52&gt;Q52,3,IF(Q52=R52,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T52" s="17">
         <v>25</v>
@@ -11091,13 +11201,17 @@
       </c>
       <c r="E53" s="25">
         <f>IF(F53&gt;G53,3,IF(F53=G53,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
+        <v>3</v>
+      </c>
+      <c r="F53" s="20">
+        <v>30</v>
+      </c>
+      <c r="G53" s="20">
+        <v>25</v>
+      </c>
       <c r="H53" s="25">
         <f>IF(G53&gt;F53,3,IF(F53=G53,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I53" s="21">
         <v>56</v>
@@ -11116,13 +11230,17 @@
       </c>
       <c r="P53" s="25">
         <f>IF(Q53&gt;R53,3,IF(Q53=R53,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q53" s="20"/>
-      <c r="R53" s="20"/>
+        <v>0</v>
+      </c>
+      <c r="Q53" s="20">
+        <v>7</v>
+      </c>
+      <c r="R53" s="20">
+        <v>8</v>
+      </c>
       <c r="S53" s="25">
         <f t="shared" ref="S53:S55" si="31">IF(R53&gt;Q53,3,IF(Q53=R53,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T53" s="21">
         <v>72</v>
@@ -11144,13 +11262,17 @@
       </c>
       <c r="E54" s="15">
         <f t="shared" ref="E54:E58" si="32">IF(F54&gt;G54,3,IF(F54=G54,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F54" s="15"/>
-      <c r="G54" s="15"/>
+        <v>3</v>
+      </c>
+      <c r="F54" s="15">
+        <v>25</v>
+      </c>
+      <c r="G54" s="15">
+        <v>19</v>
+      </c>
       <c r="H54" s="15">
         <f t="shared" ref="H54:H55" si="33">IF(G54&gt;F54,3,IF(F54=G54,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I54" s="19">
         <v>21</v>
@@ -11171,13 +11293,17 @@
       </c>
       <c r="P54" s="15">
         <f t="shared" ref="P54:P58" si="34">IF(Q54&gt;R54,3,IF(Q54=R54,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q54" s="15"/>
-      <c r="R54" s="15"/>
+        <v>3</v>
+      </c>
+      <c r="Q54" s="15">
+        <v>22</v>
+      </c>
+      <c r="R54" s="15">
+        <v>14</v>
+      </c>
       <c r="S54" s="15">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54" s="19">
         <v>61</v>
@@ -11197,13 +11323,17 @@
       </c>
       <c r="E55" s="16">
         <f t="shared" si="32"/>
-        <v>1</v>
-      </c>
-      <c r="F55" s="16"/>
-      <c r="G55" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="16">
+        <v>16</v>
+      </c>
+      <c r="G55" s="16">
+        <v>30</v>
+      </c>
       <c r="H55" s="16">
         <f t="shared" si="33"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I55" s="17">
         <v>64</v>
@@ -11222,13 +11352,17 @@
       </c>
       <c r="P55" s="16">
         <f t="shared" si="34"/>
-        <v>1</v>
-      </c>
-      <c r="Q55" s="16"/>
-      <c r="R55" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q55" s="16">
+        <v>7</v>
+      </c>
+      <c r="R55" s="16">
+        <v>16</v>
+      </c>
       <c r="S55" s="16">
         <f t="shared" si="31"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T55" s="17">
         <v>7</v>
@@ -11247,13 +11381,17 @@
       </c>
       <c r="E56" s="16">
         <f t="shared" si="32"/>
-        <v>1</v>
-      </c>
-      <c r="F56" s="16"/>
-      <c r="G56" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="16">
+        <v>11</v>
+      </c>
+      <c r="G56" s="16">
+        <v>20</v>
+      </c>
       <c r="H56" s="16">
         <f>IF(G56&gt;F56,3,IF(F56=G56,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I56" s="17">
         <v>14</v>
@@ -11272,13 +11410,17 @@
       </c>
       <c r="P56" s="16">
         <f t="shared" si="34"/>
-        <v>1</v>
-      </c>
-      <c r="Q56" s="16"/>
-      <c r="R56" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q56" s="16">
+        <v>20</v>
+      </c>
+      <c r="R56" s="16">
+        <v>15</v>
+      </c>
       <c r="S56" s="16">
         <f>IF(R56&gt;Q56,3,IF(Q56=R56,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" s="17">
         <v>81</v>
@@ -11297,13 +11439,17 @@
       </c>
       <c r="E57" s="16">
         <f t="shared" si="32"/>
-        <v>1</v>
-      </c>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F57" s="16">
+        <v>23</v>
+      </c>
+      <c r="G57" s="16">
+        <v>15</v>
+      </c>
       <c r="H57" s="16">
         <f t="shared" ref="H57:H58" si="35">IF(G57&gt;F57,3,IF(F57=G57,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I57" s="17">
         <v>2</v>
@@ -11322,13 +11468,17 @@
       </c>
       <c r="P57" s="16">
         <f t="shared" si="34"/>
-        <v>1</v>
-      </c>
-      <c r="Q57" s="16"/>
-      <c r="R57" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q57" s="16">
+        <v>0</v>
+      </c>
+      <c r="R57" s="16">
+        <v>6</v>
+      </c>
       <c r="S57" s="16">
         <f t="shared" ref="S57:S58" si="36">IF(R57&gt;Q57,3,IF(Q57=R57,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T57" s="17">
         <v>33</v>
@@ -11347,13 +11497,17 @@
       </c>
       <c r="E58" s="16">
         <f t="shared" si="32"/>
-        <v>1</v>
-      </c>
-      <c r="F58" s="16"/>
-      <c r="G58" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F58" s="16">
+        <v>3</v>
+      </c>
+      <c r="G58" s="16">
+        <v>0</v>
+      </c>
       <c r="H58" s="16">
         <f t="shared" si="35"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I58" s="17">
         <v>78</v>
@@ -11372,13 +11526,17 @@
       </c>
       <c r="P58" s="16">
         <f t="shared" si="34"/>
-        <v>1</v>
-      </c>
-      <c r="Q58" s="16"/>
-      <c r="R58" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q58" s="16">
+        <v>16</v>
+      </c>
+      <c r="R58" s="16">
+        <v>1</v>
+      </c>
       <c r="S58" s="16">
         <f t="shared" si="36"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58" s="17">
         <v>70</v>
@@ -13075,10 +13233,10 @@
         <v>12</v>
       </c>
       <c r="C2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D2">
-        <v>98</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -13089,38 +13247,38 @@
         <v>64</v>
       </c>
       <c r="C3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D3">
-        <v>85</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
-        <v>2g</v>
+        <v>2b</v>
       </c>
       <c r="B4">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D4">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
-        <v>2b</v>
+        <v>2g</v>
       </c>
       <c r="B5">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C5">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5">
-        <v>66</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -13131,10 +13289,10 @@
         <v>19</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D6">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -13145,24 +13303,24 @@
         <v>58</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>60</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
-        <v>2c</v>
+        <v>2d</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8">
-        <v>53</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -13173,150 +13331,150 @@
         <v>65</v>
       </c>
       <c r="C9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D9">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <v>2d</v>
+        <v>2g</v>
       </c>
       <c r="B10">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="C10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D10">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
-        <v>2b</v>
+        <v>2a</v>
       </c>
       <c r="B11">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="C11">
         <v>9</v>
       </c>
       <c r="D11">
-        <v>43</v>
+        <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <v>2g</v>
+        <v>2d</v>
       </c>
       <c r="B12">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>9</v>
       </c>
       <c r="D12">
-        <v>42</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <v>2d</v>
+        <v>2c</v>
       </c>
       <c r="B13">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C13">
         <v>9</v>
       </c>
       <c r="D13">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <v>2b</v>
+        <v>2d</v>
       </c>
       <c r="B14">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>9</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
-        <v>2e</v>
+        <v>2c</v>
       </c>
       <c r="B15">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <v>2f</v>
+        <v>2c</v>
       </c>
       <c r="B16">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
-        <v>2a</v>
+        <v>2e</v>
       </c>
       <c r="B17">
-        <v>52</v>
+        <v>25</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17">
-        <v>40</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
-        <v>2f</v>
+        <v>2b</v>
       </c>
       <c r="B18">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
-        <v>2a</v>
+        <v>2e</v>
       </c>
       <c r="B19">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -13324,83 +13482,83 @@
         <v>2d</v>
       </c>
       <c r="B20">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
-        <v>2c</v>
+        <v>2e</v>
       </c>
       <c r="B21">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D21">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <v>2b</v>
+        <v>2e</v>
       </c>
       <c r="B22">
-        <v>78</v>
+        <v>16</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <v>2a</v>
+        <v>2d</v>
       </c>
       <c r="B23">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <v>2d</v>
+        <v>2b</v>
       </c>
       <c r="B24">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
-        <v>2c</v>
+        <v>2e</v>
       </c>
       <c r="B25">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C25">
         <v>7</v>
       </c>
       <c r="D25">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="E25" s="12"/>
     </row>
@@ -13409,13 +13567,13 @@
         <v>2f</v>
       </c>
       <c r="B26">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C26">
         <v>6</v>
       </c>
       <c r="D26">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -13423,112 +13581,112 @@
         <v>2f</v>
       </c>
       <c r="B27">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C27">
         <v>6</v>
       </c>
       <c r="D27">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <v>2e</v>
+        <v>2a</v>
       </c>
       <c r="B28">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
       <c r="D28">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B29">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C29">
         <v>6</v>
       </c>
       <c r="D29">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <v>2e</v>
+        <v>2b</v>
       </c>
       <c r="B30">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="C30">
         <v>6</v>
       </c>
       <c r="D30">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E30" s="12"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
-        <v>2e</v>
+        <v>2a</v>
       </c>
       <c r="B31">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C31">
         <v>6</v>
       </c>
       <c r="D31">
-        <v>24</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <v>2c</v>
+        <v>2f</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>89</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>21</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <v>2d</v>
+        <v>2f</v>
       </c>
       <c r="B33">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="C33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <v>2f</v>
+        <v>2c</v>
       </c>
       <c r="B34">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -13536,41 +13694,41 @@
         <v>2f</v>
       </c>
       <c r="B35">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C35">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <v>2a</v>
+        <v>2f</v>
       </c>
       <c r="B36">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C36">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D36">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <v>2d</v>
+        <v>2a</v>
       </c>
       <c r="B37">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="C37">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D37">
-        <v>18</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -13581,10 +13739,10 @@
         <v>70</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -13595,10 +13753,10 @@
         <v>79</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -13609,10 +13767,10 @@
         <v>61</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>16</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -13623,7 +13781,7 @@
         <v>4</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D41">
         <v>1</v>

--- a/KWI-RoboChallenge_Rangliste.xlsx
+++ b/KWI-RoboChallenge_Rangliste.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/camillagretsch/KWI-RoboChallenge/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D511F1E5-198E-E54B-90DE-BA30DF94A1DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E2F4FC-B120-4A47-9AFD-274314EEF3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2373,11 +2373,11 @@
       </c>
       <c r="Z4">
         <f t="shared" ref="Z4:Z43" si="0">SUMIF(D$4:D$88,Y4,F$4:F$88)+SUMIF(I$4:I$88,Y4,G$4:G$88)+SUMIF(O$4:O$88,Y4,Q$4:Q$88)+SUMIF(T$4:T$88,Y4,R$4:R$88)</f>
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="AA4">
         <f>SUMIF(D$4:D$88,Y4,E$4:E$88)+SUMIF(I$4:I$88,Y4,H$4:H$88)+SUMIF(O$4:O$88,Y4,P$4:P$88)+SUMIF(T$4:T$88,Y4,S$4:S$88)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -2446,11 +2446,11 @@
       </c>
       <c r="Z5">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="AA5">
         <f t="shared" ref="AA5:AA43" si="5">SUMIF(D$4:D$88,Y5,E$4:E$88)+SUMIF(I$4:I$88,Y5,H$4:H$88)+SUMIF(O$4:O$88,Y5,P$4:P$88)+SUMIF(T$4:T$88,Y5,S$4:S$88)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -2592,11 +2592,11 @@
       </c>
       <c r="Z7">
         <f>SUMIF(D$4:D$88,Y7,F$4:F$88)+SUMIF(I$4:I$88,Y7,G$4:G$88)+SUMIF(O$4:O$88,Y7,Q$4:Q$88)+SUMIF(T$4:T$88,Y7,R$4:R$88)</f>
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="AA7">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
@@ -2665,11 +2665,11 @@
       </c>
       <c r="Z8">
         <f>SUMIF(D$4:D$88,Y8,F$4:F$88)+SUMIF(I$4:I$88,Y8,G$4:G$88)+SUMIF(O$4:O$88,Y8,Q$4:Q$88)+SUMIF(T$4:T$88,Y8,R$4:R$88)</f>
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="AA8">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="Z9">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="AA9">
         <f t="shared" si="5"/>
@@ -2815,11 +2815,11 @@
       </c>
       <c r="Z10">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AA10">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z12">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="AA12">
         <f t="shared" si="5"/>
@@ -3034,11 +3034,11 @@
       </c>
       <c r="Z13">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AA13">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
@@ -3072,11 +3072,11 @@
       </c>
       <c r="Z14">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AA14">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
@@ -3110,7 +3110,7 @@
       </c>
       <c r="Z15">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AA15">
         <f t="shared" si="5"/>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="Z16">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AA16">
         <f t="shared" si="5"/>
@@ -3192,11 +3192,11 @@
       </c>
       <c r="Z17">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="AA17">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.2">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z18">
         <f t="shared" si="0"/>
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AA18">
         <f t="shared" si="5"/>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="Z19">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="AA19">
         <f t="shared" si="5"/>
@@ -3416,11 +3416,11 @@
       </c>
       <c r="Z20">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="AA20">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -3489,11 +3489,11 @@
       </c>
       <c r="Z21">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="AA21">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3562,11 +3562,11 @@
       </c>
       <c r="Z22">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="AA22">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="Z23">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AA23">
         <f t="shared" si="5"/>
@@ -3712,7 +3712,7 @@
       </c>
       <c r="Z24">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AA24">
         <f t="shared" si="5"/>
@@ -3785,11 +3785,11 @@
       </c>
       <c r="Z25">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="AA25">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3858,11 +3858,11 @@
       </c>
       <c r="Z26">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AA26">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -3931,11 +3931,11 @@
       </c>
       <c r="Z27">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AA27">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4004,11 +4004,11 @@
       </c>
       <c r="Z28">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="AA28">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.2">
@@ -4042,11 +4042,11 @@
       </c>
       <c r="Z29">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="AA29">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.2">
@@ -4080,7 +4080,7 @@
       </c>
       <c r="Z30">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AA30">
         <f t="shared" si="5"/>
@@ -4120,11 +4120,11 @@
       </c>
       <c r="Z31">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AA31">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="Z32">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AA32">
         <f t="shared" si="5"/>
@@ -4236,11 +4236,11 @@
       </c>
       <c r="Z33">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AA33">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4313,11 +4313,11 @@
       </c>
       <c r="Z34">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AA34">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4386,11 +4386,11 @@
       </c>
       <c r="Z35">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="AA35">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -4459,11 +4459,11 @@
       </c>
       <c r="Z36">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="AA36">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4509,14 +4509,14 @@
         <v/>
       </c>
       <c r="Q37" s="16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R37" s="16">
-        <v>10</v>
-      </c>
-      <c r="S37" s="16">
+        <v>5</v>
+      </c>
+      <c r="S37" s="16" t="str">
         <f t="shared" si="11"/>
-        <v>1</v>
+        <v/>
       </c>
       <c r="T37" s="17">
         <v>22</v>
@@ -4532,11 +4532,11 @@
       </c>
       <c r="Z37">
         <f t="shared" si="0"/>
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AA37">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:27" ht="24" thickBot="1" x14ac:dyDescent="0.25">
@@ -4605,11 +4605,11 @@
       </c>
       <c r="Z38">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="AA38">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4682,11 +4682,11 @@
       </c>
       <c r="Z39">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="AA39">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4755,11 +4755,11 @@
       </c>
       <c r="Z40">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AA40">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4828,11 +4828,11 @@
       </c>
       <c r="Z41">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="AA41">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:27" ht="22" x14ac:dyDescent="0.2">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="Z42">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="AA42">
         <f t="shared" si="5"/>
@@ -4974,11 +4974,11 @@
       </c>
       <c r="Z43">
         <f t="shared" si="0"/>
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="AA43">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.2">
@@ -5914,12 +5914,16 @@
       <c r="D64" s="17">
         <v>59</v>
       </c>
-      <c r="E64" s="16" t="str">
+      <c r="E64" s="16">
         <f>IF(F64 &gt; G64, 1, "")</f>
-        <v/>
-      </c>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F64" s="16">
+        <v>6</v>
+      </c>
+      <c r="G64" s="16">
+        <v>4</v>
+      </c>
       <c r="H64" s="16" t="str">
         <f>IF(G64 &gt; F64, 1, "")</f>
         <v/>
@@ -5941,12 +5945,16 @@
       <c r="O64" s="17">
         <v>35</v>
       </c>
-      <c r="P64" s="16" t="str">
+      <c r="P64" s="16">
         <f>IF(Q64 &gt; R64, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q64" s="16"/>
-      <c r="R64" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q64" s="16">
+        <v>6</v>
+      </c>
+      <c r="R64" s="16">
+        <v>4</v>
+      </c>
       <c r="S64" s="16" t="str">
         <f>IF(R64 &gt; Q64, 1, "")</f>
         <v/>
@@ -5967,12 +5975,16 @@
       <c r="D65" s="17">
         <v>74</v>
       </c>
-      <c r="E65" s="16" t="str">
+      <c r="E65" s="16">
         <f>IF(F65 &gt; G65, 1, "")</f>
-        <v/>
-      </c>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F65" s="16">
+        <v>10</v>
+      </c>
+      <c r="G65" s="16">
+        <v>0</v>
+      </c>
       <c r="H65" s="16" t="str">
         <f t="shared" ref="H65:H73" si="20">IF(G65 &gt; F65, 1, "")</f>
         <v/>
@@ -5992,12 +6004,16 @@
       <c r="O65" s="17">
         <v>83</v>
       </c>
-      <c r="P65" s="16" t="str">
+      <c r="P65" s="16">
         <f>IF(Q65 &gt; R65, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q65" s="16"/>
-      <c r="R65" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q65" s="16">
+        <v>10</v>
+      </c>
+      <c r="R65" s="16">
+        <v>0</v>
+      </c>
       <c r="S65" s="16" t="str">
         <f t="shared" ref="S65:S66" si="21">IF(R65 &gt; Q65, 1, "")</f>
         <v/>
@@ -6022,8 +6038,12 @@
         <f>IF(F66 &gt; G66, 1, "")</f>
         <v/>
       </c>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
+      <c r="F66" s="16">
+        <v>5</v>
+      </c>
+      <c r="G66" s="16">
+        <v>5</v>
+      </c>
       <c r="H66" s="16" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -6043,12 +6063,16 @@
       <c r="O66" s="18">
         <v>57</v>
       </c>
-      <c r="P66" s="16" t="str">
+      <c r="P66" s="16">
         <f>IF(Q66 &gt; R66, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q66" s="16"/>
-      <c r="R66" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q66" s="16">
+        <v>6</v>
+      </c>
+      <c r="R66" s="16">
+        <v>4</v>
+      </c>
       <c r="S66" s="16" t="str">
         <f t="shared" si="21"/>
         <v/>
@@ -6073,8 +6097,12 @@
         <f t="shared" ref="E67:E73" si="22">IF(F67 &gt; G67, 1, "")</f>
         <v/>
       </c>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
+      <c r="F67" s="16">
+        <v>5</v>
+      </c>
+      <c r="G67" s="16">
+        <v>5</v>
+      </c>
       <c r="H67" s="16" t="str">
         <f>IF(G67 &gt; F67, 1, "")</f>
         <v/>
@@ -6094,12 +6122,16 @@
       <c r="O67" s="17">
         <v>77</v>
       </c>
-      <c r="P67" s="16" t="str">
+      <c r="P67" s="16">
         <f t="shared" ref="P67:P73" si="23">IF(Q67 &gt; R67, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q67" s="16"/>
-      <c r="R67" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q67" s="16">
+        <v>7</v>
+      </c>
+      <c r="R67" s="16">
+        <v>3</v>
+      </c>
       <c r="S67" s="16" t="str">
         <f>IF(R67 &gt; Q67, 1, "")</f>
         <v/>
@@ -6124,8 +6156,12 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
+      <c r="F68" s="20">
+        <v>5</v>
+      </c>
+      <c r="G68" s="20">
+        <v>5</v>
+      </c>
       <c r="H68" s="20" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -6145,12 +6181,16 @@
       <c r="O68" s="21">
         <v>36</v>
       </c>
-      <c r="P68" s="25" t="str">
+      <c r="P68" s="25">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="Q68" s="20"/>
-      <c r="R68" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="Q68" s="20">
+        <v>10</v>
+      </c>
+      <c r="R68" s="20">
+        <v>0</v>
+      </c>
       <c r="S68" s="20" t="str">
         <f t="shared" ref="S68:S70" si="24">IF(R68 &gt; Q68, 1, "")</f>
         <v/>
@@ -6173,12 +6213,16 @@
       <c r="D69" s="19">
         <v>75</v>
       </c>
-      <c r="E69" s="15" t="str">
+      <c r="E69" s="15">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="F69" s="15">
+        <v>9</v>
+      </c>
+      <c r="G69" s="15">
+        <v>1</v>
+      </c>
       <c r="H69" s="15" t="str">
         <f t="shared" si="20"/>
         <v/>
@@ -6200,12 +6244,16 @@
       <c r="O69" s="19">
         <v>86</v>
       </c>
-      <c r="P69" s="15" t="str">
+      <c r="P69" s="15">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="Q69" s="15"/>
-      <c r="R69" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="Q69" s="15">
+        <v>6</v>
+      </c>
+      <c r="R69" s="15">
+        <v>4</v>
+      </c>
       <c r="S69" s="15" t="str">
         <f t="shared" si="24"/>
         <v/>
@@ -6230,11 +6278,15 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
-      <c r="H70" s="16" t="str">
+      <c r="F70" s="16">
+        <v>3</v>
+      </c>
+      <c r="G70" s="16">
+        <v>7</v>
+      </c>
+      <c r="H70" s="16">
         <f t="shared" si="20"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I70" s="17">
         <v>22</v>
@@ -6255,11 +6307,15 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q70" s="16"/>
-      <c r="R70" s="16"/>
-      <c r="S70" s="16" t="str">
+      <c r="Q70" s="16">
+        <v>4</v>
+      </c>
+      <c r="R70" s="16">
+        <v>6</v>
+      </c>
+      <c r="S70" s="16">
         <f t="shared" si="24"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T70" s="17">
         <v>62</v>
@@ -6277,12 +6333,16 @@
       <c r="D71" s="17">
         <v>84</v>
       </c>
-      <c r="E71" s="16" t="str">
+      <c r="E71" s="16">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F71" s="16">
+        <v>6</v>
+      </c>
+      <c r="G71" s="16">
+        <v>4</v>
+      </c>
       <c r="H71" s="16" t="str">
         <f>IF(G71 &gt; F71, 1, "")</f>
         <v/>
@@ -6302,12 +6362,16 @@
       <c r="O71" s="17">
         <v>82</v>
       </c>
-      <c r="P71" s="16" t="str">
+      <c r="P71" s="16">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="Q71" s="16"/>
-      <c r="R71" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q71" s="16">
+        <v>7</v>
+      </c>
+      <c r="R71" s="16">
+        <v>3</v>
+      </c>
       <c r="S71" s="16" t="str">
         <f>IF(R71 &gt; Q71, 1, "")</f>
         <v/>
@@ -6332,11 +6396,15 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16"/>
-      <c r="H72" s="16" t="str">
+      <c r="F72" s="16">
+        <v>3</v>
+      </c>
+      <c r="G72" s="16">
+        <v>7</v>
+      </c>
+      <c r="H72" s="16">
         <f t="shared" si="20"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I72" s="17">
         <v>69</v>
@@ -6357,8 +6425,12 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q72" s="16"/>
-      <c r="R72" s="16"/>
+      <c r="Q72" s="16">
+        <v>5</v>
+      </c>
+      <c r="R72" s="16">
+        <v>5</v>
+      </c>
       <c r="S72" s="16" t="str">
         <f t="shared" ref="S72:S73" si="25">IF(R72 &gt; Q72, 1, "")</f>
         <v/>
@@ -6383,11 +6455,15 @@
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16"/>
-      <c r="H73" s="16" t="str">
+      <c r="F73" s="16">
+        <v>4</v>
+      </c>
+      <c r="G73" s="16">
+        <v>6</v>
+      </c>
+      <c r="H73" s="16">
         <f t="shared" si="20"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I73" s="17">
         <v>8</v>
@@ -6408,11 +6484,15 @@
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="Q73" s="16"/>
-      <c r="R73" s="16"/>
-      <c r="S73" s="16" t="str">
+      <c r="Q73" s="16">
+        <v>3</v>
+      </c>
+      <c r="R73" s="16">
+        <v>7</v>
+      </c>
+      <c r="S73" s="16">
         <f t="shared" si="25"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T73" s="17">
         <v>18</v>
@@ -6598,11 +6678,15 @@
         <f>IF(F79 &gt; G79, 1, "")</f>
         <v/>
       </c>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
-      <c r="H79" s="16" t="str">
+      <c r="F79" s="16">
+        <v>3</v>
+      </c>
+      <c r="G79" s="16">
+        <v>7</v>
+      </c>
+      <c r="H79" s="16">
         <f>IF(G79 &gt; F79, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I79" s="17">
         <v>92</v>
@@ -6621,12 +6705,16 @@
       <c r="O79" s="17">
         <v>3</v>
       </c>
-      <c r="P79" s="16" t="str">
+      <c r="P79" s="16">
         <f>IF(Q79 &gt; R79, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q79" s="16"/>
-      <c r="R79" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q79" s="16">
+        <v>10</v>
+      </c>
+      <c r="R79" s="16">
+        <v>0</v>
+      </c>
       <c r="S79" s="16" t="str">
         <f>IF(R79 &gt; Q79, 1, "")</f>
         <v/>
@@ -6647,12 +6735,16 @@
       <c r="D80" s="17">
         <v>74</v>
       </c>
-      <c r="E80" s="16" t="str">
+      <c r="E80" s="16">
         <f>IF(F80 &gt; G80, 1, "")</f>
-        <v/>
-      </c>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F80" s="16">
+        <v>7</v>
+      </c>
+      <c r="G80" s="16">
+        <v>3</v>
+      </c>
       <c r="H80" s="16" t="str">
         <f t="shared" ref="H80:H88" si="26">IF(G80 &gt; F80, 1, "")</f>
         <v/>
@@ -6676,11 +6768,15 @@
         <f>IF(Q80 &gt; R80, 1, "")</f>
         <v/>
       </c>
-      <c r="Q80" s="16"/>
-      <c r="R80" s="16"/>
-      <c r="S80" s="16" t="str">
+      <c r="Q80" s="16">
+        <v>4</v>
+      </c>
+      <c r="R80" s="16">
+        <v>6</v>
+      </c>
+      <c r="S80" s="16">
         <f t="shared" ref="S80:S81" si="27">IF(R80 &gt; Q80, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T80" s="17">
         <v>94</v>
@@ -6698,12 +6794,16 @@
       <c r="D81" s="18">
         <v>10</v>
       </c>
-      <c r="E81" s="16" t="str">
+      <c r="E81" s="16">
         <f>IF(F81 &gt; G81, 1, "")</f>
-        <v/>
-      </c>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F81" s="16">
+        <v>10</v>
+      </c>
+      <c r="G81" s="16">
+        <v>0</v>
+      </c>
       <c r="H81" s="16" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -6723,12 +6823,16 @@
       <c r="O81" s="18">
         <v>51</v>
       </c>
-      <c r="P81" s="16" t="str">
+      <c r="P81" s="16">
         <f>IF(Q81 &gt; R81, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q81" s="16"/>
-      <c r="R81" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q81" s="16">
+        <v>6</v>
+      </c>
+      <c r="R81" s="16">
+        <v>4</v>
+      </c>
       <c r="S81" s="16" t="str">
         <f t="shared" si="27"/>
         <v/>
@@ -6749,12 +6853,16 @@
       <c r="D82" s="17">
         <v>29</v>
       </c>
-      <c r="E82" s="16" t="str">
+      <c r="E82" s="16">
         <f t="shared" ref="E82:E88" si="28">IF(F82 &gt; G82, 1, "")</f>
-        <v/>
-      </c>
-      <c r="F82" s="16"/>
-      <c r="G82" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="F82" s="16">
+        <v>10</v>
+      </c>
+      <c r="G82" s="16">
+        <v>0</v>
+      </c>
       <c r="H82" s="16" t="str">
         <f>IF(G82 &gt; F82, 1, "")</f>
         <v/>
@@ -6774,12 +6882,16 @@
       <c r="O82" s="17">
         <v>80</v>
       </c>
-      <c r="P82" s="16" t="str">
+      <c r="P82" s="16">
         <f t="shared" ref="P82:P88" si="29">IF(Q82 &gt; R82, 1, "")</f>
-        <v/>
-      </c>
-      <c r="Q82" s="16"/>
-      <c r="R82" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q82" s="16">
+        <v>9</v>
+      </c>
+      <c r="R82" s="16">
+        <v>1</v>
+      </c>
       <c r="S82" s="16" t="str">
         <f>IF(R82 &gt; Q82, 1, "")</f>
         <v/>
@@ -6804,11 +6916,15 @@
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="F83" s="20"/>
-      <c r="G83" s="20"/>
-      <c r="H83" s="20" t="str">
+      <c r="F83" s="20">
+        <v>3</v>
+      </c>
+      <c r="G83" s="20">
+        <v>7</v>
+      </c>
+      <c r="H83" s="20">
         <f t="shared" si="26"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I83" s="21">
         <v>86</v>
@@ -6825,12 +6941,16 @@
       <c r="O83" s="21">
         <v>1</v>
       </c>
-      <c r="P83" s="25" t="str">
+      <c r="P83" s="25">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="Q83" s="20"/>
-      <c r="R83" s="20"/>
+        <v>1</v>
+      </c>
+      <c r="Q83" s="20">
+        <v>6</v>
+      </c>
+      <c r="R83" s="20">
+        <v>4</v>
+      </c>
       <c r="S83" s="20" t="str">
         <f t="shared" ref="S83:S85" si="30">IF(R83 &gt; Q83, 1, "")</f>
         <v/>
@@ -6853,12 +6973,16 @@
       <c r="D84" s="19">
         <v>75</v>
       </c>
-      <c r="E84" s="15" t="str">
+      <c r="E84" s="15">
         <f t="shared" si="28"/>
-        <v/>
-      </c>
-      <c r="F84" s="15"/>
-      <c r="G84" s="15"/>
+        <v>1</v>
+      </c>
+      <c r="F84" s="15">
+        <v>6</v>
+      </c>
+      <c r="G84" s="15">
+        <v>4</v>
+      </c>
       <c r="H84" s="15" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -6884,11 +7008,15 @@
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="Q84" s="15"/>
-      <c r="R84" s="15"/>
-      <c r="S84" s="15" t="str">
+      <c r="Q84" s="15">
+        <v>4</v>
+      </c>
+      <c r="R84" s="15">
+        <v>6</v>
+      </c>
+      <c r="S84" s="15">
         <f t="shared" si="30"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T84" s="19">
         <v>63</v>
@@ -6910,11 +7038,15 @@
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="F85" s="16"/>
-      <c r="G85" s="16"/>
-      <c r="H85" s="16" t="str">
+      <c r="F85" s="16">
+        <v>4</v>
+      </c>
+      <c r="G85" s="16">
+        <v>6</v>
+      </c>
+      <c r="H85" s="16">
         <f t="shared" si="26"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I85" s="17">
         <v>22</v>
@@ -6935,11 +7067,15 @@
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="Q85" s="16"/>
-      <c r="R85" s="16"/>
-      <c r="S85" s="16" t="str">
+      <c r="Q85" s="16">
+        <v>4</v>
+      </c>
+      <c r="R85" s="16">
+        <v>6</v>
+      </c>
+      <c r="S85" s="16">
         <f t="shared" si="30"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T85" s="17">
         <v>83</v>
@@ -6961,11 +7097,15 @@
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="16"/>
-      <c r="H86" s="16" t="str">
+      <c r="F86" s="16">
+        <v>2</v>
+      </c>
+      <c r="G86" s="16">
+        <v>8</v>
+      </c>
+      <c r="H86" s="16">
         <f>IF(G86 &gt; F86, 1, "")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I86" s="17">
         <v>18</v>
@@ -6982,12 +7122,16 @@
       <c r="O86" s="17">
         <v>77</v>
       </c>
-      <c r="P86" s="16" t="str">
+      <c r="P86" s="16">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="Q86" s="16"/>
-      <c r="R86" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q86" s="16">
+        <v>7</v>
+      </c>
+      <c r="R86" s="16">
+        <v>3</v>
+      </c>
       <c r="S86" s="16" t="str">
         <f>IF(R86 &gt; Q86, 1, "")</f>
         <v/>
@@ -7012,8 +7156,12 @@
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="F87" s="16"/>
-      <c r="G87" s="16"/>
+      <c r="F87" s="16">
+        <v>5</v>
+      </c>
+      <c r="G87" s="16">
+        <v>5</v>
+      </c>
       <c r="H87" s="16" t="str">
         <f t="shared" si="26"/>
         <v/>
@@ -7033,12 +7181,16 @@
       <c r="O87" s="17">
         <v>8</v>
       </c>
-      <c r="P87" s="16" t="str">
+      <c r="P87" s="16">
         <f t="shared" si="29"/>
-        <v/>
-      </c>
-      <c r="Q87" s="16"/>
-      <c r="R87" s="16"/>
+        <v>1</v>
+      </c>
+      <c r="Q87" s="16">
+        <v>6</v>
+      </c>
+      <c r="R87" s="16">
+        <v>4</v>
+      </c>
       <c r="S87" s="16" t="str">
         <f t="shared" ref="S87:S88" si="31">IF(R87 &gt; Q87, 1, "")</f>
         <v/>
@@ -7063,11 +7215,15 @@
         <f t="shared" si="28"/>
         <v/>
       </c>
-      <c r="F88" s="16"/>
-      <c r="G88" s="16"/>
-      <c r="H88" s="16" t="str">
+      <c r="F88" s="16">
+        <v>2</v>
+      </c>
+      <c r="G88" s="16">
+        <v>8</v>
+      </c>
+      <c r="H88" s="16">
         <f t="shared" si="26"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="I88" s="17">
         <v>66</v>
@@ -7088,11 +7244,15 @@
         <f t="shared" si="29"/>
         <v/>
       </c>
-      <c r="Q88" s="16"/>
-      <c r="R88" s="16"/>
-      <c r="S88" s="16" t="str">
+      <c r="Q88" s="16">
+        <v>3</v>
+      </c>
+      <c r="R88" s="16">
+        <v>7</v>
+      </c>
+      <c r="S88" s="16">
         <f t="shared" si="31"/>
-        <v/>
+        <v>1</v>
       </c>
       <c r="T88" s="17">
         <v>20</v>
@@ -7437,16 +7597,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
-        <v>2f</v>
+        <v>2b</v>
       </c>
       <c r="B2">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C2">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
@@ -7454,41 +7614,41 @@
         <v>2f</v>
       </c>
       <c r="B3">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C3">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
-        <v>2a</v>
+        <v>2f</v>
       </c>
       <c r="B4">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="C4">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
-        <v>2d</v>
+        <v>2b</v>
       </c>
       <c r="B5">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="C5">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
@@ -7496,38 +7656,38 @@
         <v>2f</v>
       </c>
       <c r="B6">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C6">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="str">
-        <v>2f</v>
+        <v>2b</v>
       </c>
       <c r="B7">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C7">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="str">
-        <v>2a</v>
+        <v>2b</v>
       </c>
       <c r="B8">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="C8">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D8">
         <v>4</v>
@@ -7535,16 +7695,16 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="str">
-        <v>2b</v>
+        <v>2a</v>
       </c>
       <c r="B9">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="C9">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
@@ -7552,80 +7712,80 @@
         <v>2f</v>
       </c>
       <c r="B10">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C10">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D10">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
-        <v>2b</v>
+        <v>2e</v>
       </c>
       <c r="B11">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="C11">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <v>2b</v>
+        <v>2a</v>
       </c>
       <c r="B12">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="C12">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D12">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B13">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C13">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="str">
-        <v>2a</v>
+        <v>2f</v>
       </c>
       <c r="B14">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="C14">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
-        <v>2e</v>
+        <v>2g</v>
       </c>
       <c r="B15">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="C15">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -7633,27 +7793,27 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <v>2g</v>
+        <v>2d</v>
       </c>
       <c r="B16">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="C16">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
-        <v>2a</v>
+        <v>2d</v>
       </c>
       <c r="B17">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C17">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -7661,27 +7821,27 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="str">
-        <v>2b</v>
+        <v>2e</v>
       </c>
       <c r="B18">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="C18">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="str">
-        <v>2d</v>
+        <v>2c</v>
       </c>
       <c r="B19">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C19">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -7689,13 +7849,13 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
-        <v>2g</v>
+        <v>2a</v>
       </c>
       <c r="B20">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C20">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -7703,125 +7863,125 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
-        <v>2e</v>
+        <v>2f</v>
       </c>
       <c r="B21">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="C21">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <v>2g</v>
+        <v>2c</v>
       </c>
       <c r="B22">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D22">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <v>2g</v>
+        <v>2c</v>
       </c>
       <c r="B23">
-        <v>69</v>
+        <v>10</v>
       </c>
       <c r="C23">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <v>2c</v>
+        <v>2g</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>69</v>
       </c>
       <c r="C24">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
-        <v>2c</v>
+        <v>2a</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="C25">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <v>2d</v>
+        <v>2g</v>
       </c>
       <c r="B26">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="C26">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <v>2f</v>
+        <v>2c</v>
       </c>
       <c r="B27">
-        <v>92</v>
+        <v>1</v>
       </c>
       <c r="C27">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <v>2c</v>
+        <v>2g</v>
       </c>
       <c r="B28">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="C28">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <v>2g</v>
+        <v>2e</v>
       </c>
       <c r="B29">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="C29">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D29">
         <v>2</v>
@@ -7832,10 +7992,10 @@
         <v>2g</v>
       </c>
       <c r="B30">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C30">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -7843,41 +8003,41 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
-        <v>2c</v>
+        <v>2a</v>
       </c>
       <c r="B31">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="C31">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <v>2a</v>
+        <v>2b</v>
       </c>
       <c r="B32">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="C32">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <v>2b</v>
+        <v>2g</v>
       </c>
       <c r="B33">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C33">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -7891,7 +8051,7 @@
         <v>17</v>
       </c>
       <c r="C34">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -7902,10 +8062,10 @@
         <v>2c</v>
       </c>
       <c r="B35">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C35">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -7916,10 +8076,10 @@
         <v>2d</v>
       </c>
       <c r="B36">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C36">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -7933,7 +8093,7 @@
         <v>26</v>
       </c>
       <c r="C37">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7941,27 +8101,27 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B38">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C38">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
-        <v>2d</v>
+        <v>2e</v>
       </c>
       <c r="B39">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C39">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -7972,10 +8132,10 @@
         <v>2e</v>
       </c>
       <c r="B40">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C40">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -8207,11 +8367,11 @@
       </c>
       <c r="Y4">
         <f>SUMIF(D$4:D$88,X4,E$4:E$88)+SUMIF(I$4:I$88,X4,H$4:H$88)+SUMIF(O$4:O$88,X4,P$4:P$88)+SUMIF(T$4:T$88,X4,S$4:S$88)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z4">
         <f>SUMIF(D$4:D$88,X4,F$4:F$88)+SUMIF(I$4:I$88,X4,G$4:G$88)+SUMIF(O$4:O$88,X4,Q$4:Q$88)+SUMIF(T$4:T$88,X4,R$4:R$88)</f>
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8280,11 +8440,11 @@
       </c>
       <c r="Y5">
         <f t="shared" ref="Y5:Y43" si="4">SUMIF(D$4:D$88,X5,E$4:E$88)+SUMIF(I$4:I$88,X5,H$4:H$88)+SUMIF(O$4:O$88,X5,P$4:P$88)+SUMIF(T$4:T$88,X5,S$4:S$88)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z5">
         <f t="shared" ref="Z5:Z43" si="5">SUMIF(D$4:D$88,X5,F$4:F$88)+SUMIF(I$4:I$88,X5,G$4:G$88)+SUMIF(O$4:O$88,X5,Q$4:Q$88)+SUMIF(T$4:T$88,X5,R$4:R$88)</f>
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8353,11 +8513,11 @@
       </c>
       <c r="Y6">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z6">
         <f t="shared" si="5"/>
-        <v>68</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8426,11 +8586,11 @@
       </c>
       <c r="Y7">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z7">
         <f t="shared" si="5"/>
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
@@ -8499,7 +8659,7 @@
       </c>
       <c r="Y8">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <f t="shared" si="5"/>
@@ -8576,11 +8736,11 @@
       </c>
       <c r="Y9">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z9">
         <f t="shared" si="5"/>
-        <v>128</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8648,11 +8808,11 @@
       </c>
       <c r="Y10">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="Z10">
         <f t="shared" si="5"/>
-        <v>44</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8720,11 +8880,11 @@
       </c>
       <c r="Y11">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <f t="shared" si="5"/>
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8792,11 +8952,11 @@
       </c>
       <c r="Y12">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Z12">
         <f t="shared" si="5"/>
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -8864,11 +9024,11 @@
       </c>
       <c r="Y13">
         <f t="shared" si="4"/>
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="Z13">
         <f t="shared" si="5"/>
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.2">
@@ -8901,11 +9061,11 @@
       </c>
       <c r="Y14">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z14">
         <f t="shared" si="5"/>
-        <v>33</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.2">
@@ -8938,11 +9098,11 @@
       </c>
       <c r="Y15">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z15">
         <f t="shared" si="5"/>
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="27" x14ac:dyDescent="0.35">
@@ -8977,11 +9137,11 @@
       </c>
       <c r="Y16">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z16">
         <f t="shared" si="5"/>
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9018,11 +9178,11 @@
       </c>
       <c r="Y17">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z17">
         <f t="shared" si="5"/>
-        <v>40</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.2">
@@ -9092,11 +9252,11 @@
       </c>
       <c r="Y18">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z18">
         <f t="shared" si="5"/>
-        <v>66</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:26" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -9169,11 +9329,11 @@
       </c>
       <c r="Y19">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z19">
         <f t="shared" si="5"/>
-        <v>27</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9242,11 +9402,11 @@
       </c>
       <c r="Y20">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z20">
         <f t="shared" si="5"/>
-        <v>22</v>
+        <v>53</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="22" customHeight="1" x14ac:dyDescent="0.2">
@@ -9315,11 +9475,11 @@
       </c>
       <c r="Y21">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z21">
         <f t="shared" si="5"/>
-        <v>26</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9388,11 +9548,11 @@
       </c>
       <c r="Y22">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z22">
         <f t="shared" si="5"/>
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
@@ -9461,11 +9621,11 @@
       </c>
       <c r="Y23">
         <f t="shared" si="4"/>
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Z23">
         <f t="shared" si="5"/>
-        <v>60</v>
+        <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9538,11 +9698,11 @@
       </c>
       <c r="Y24">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z24">
         <f t="shared" si="5"/>
-        <v>33</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9610,11 +9770,11 @@
       </c>
       <c r="Y25">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z25">
         <f t="shared" si="5"/>
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9682,11 +9842,11 @@
       </c>
       <c r="Y26">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z26">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9754,11 +9914,11 @@
       </c>
       <c r="Y27">
         <f t="shared" si="4"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Z27">
         <f t="shared" si="5"/>
-        <v>30</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9826,11 +9986,11 @@
       </c>
       <c r="Y28">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Z28">
         <f t="shared" si="5"/>
-        <v>115</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.2">
@@ -9863,11 +10023,11 @@
       </c>
       <c r="Y29">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Z29">
         <f t="shared" si="5"/>
-        <v>57</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.2">
@@ -9900,11 +10060,11 @@
       </c>
       <c r="Y30">
         <f t="shared" si="4"/>
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="Z30">
         <f t="shared" si="5"/>
-        <v>42</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:26" ht="27" x14ac:dyDescent="0.35">
@@ -9939,11 +10099,11 @@
       </c>
       <c r="Y31">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z31">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>39</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -9980,11 +10140,11 @@
       </c>
       <c r="Y32">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="Z32">
         <f t="shared" si="5"/>
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.2">
@@ -10054,11 +10214,11 @@
       </c>
       <c r="Y33">
         <f t="shared" si="4"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Z33">
         <f t="shared" si="5"/>
-        <v>91</v>
+        <v>146</v>
       </c>
     </row>
     <row r="34" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10131,11 +10291,11 @@
       </c>
       <c r="Y34">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z34">
         <f t="shared" si="5"/>
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10204,11 +10364,11 @@
       </c>
       <c r="Y35">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z35">
         <f t="shared" si="5"/>
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10277,11 +10437,11 @@
       </c>
       <c r="Y36">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z36">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10350,11 +10510,11 @@
       </c>
       <c r="Y37">
         <f t="shared" si="4"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z37">
         <f t="shared" si="5"/>
-        <v>58</v>
+        <v>103</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="23" thickBot="1" x14ac:dyDescent="0.25">
@@ -10423,11 +10583,11 @@
       </c>
       <c r="Y38">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z38">
         <f t="shared" si="5"/>
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10500,11 +10660,11 @@
       </c>
       <c r="Y39">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Z39">
         <f t="shared" si="5"/>
-        <v>37</v>
+        <v>102</v>
       </c>
     </row>
     <row r="40" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10572,7 +10732,7 @@
       </c>
       <c r="Y40">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z40">
         <f t="shared" si="5"/>
@@ -10644,7 +10804,7 @@
       </c>
       <c r="Y41">
         <f t="shared" si="4"/>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Z41">
         <f t="shared" si="5"/>
@@ -10716,11 +10876,11 @@
       </c>
       <c r="Y42">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z42">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:26" ht="22" x14ac:dyDescent="0.2">
@@ -10788,11 +10948,11 @@
       </c>
       <c r="Y43">
         <f t="shared" si="4"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z43">
         <f t="shared" si="5"/>
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.2">
@@ -11715,13 +11875,17 @@
       </c>
       <c r="E64" s="16">
         <f>IF(F64&gt;G64,3,IF(F64=G64,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F64" s="16"/>
-      <c r="G64" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F64" s="16">
+        <v>20</v>
+      </c>
+      <c r="G64" s="16">
+        <v>3</v>
+      </c>
       <c r="H64" s="16">
         <f>IF(G64&gt;F64,3,IF(F64=G64,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" s="17">
         <v>89</v>
@@ -11742,13 +11906,17 @@
       </c>
       <c r="P64" s="16">
         <f>IF(Q64&gt;R64,3,IF(Q64=R64,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q64" s="16"/>
-      <c r="R64" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q64" s="16">
+        <v>35</v>
+      </c>
+      <c r="R64" s="16">
+        <v>6</v>
+      </c>
       <c r="S64" s="16">
         <f>IF(R64&gt;Q64,3,IF(Q64=R64,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T64" s="17">
         <v>2</v>
@@ -11768,13 +11936,17 @@
       </c>
       <c r="E65" s="16">
         <f t="shared" ref="E65:E66" si="37">IF(F65&gt;G65,3,IF(F65=G65,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F65" s="16"/>
-      <c r="G65" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F65" s="16">
+        <v>26</v>
+      </c>
+      <c r="G65" s="16">
+        <v>25</v>
+      </c>
       <c r="H65" s="16">
         <f t="shared" ref="H65:H67" si="38">IF(G65&gt;F65,3,IF(F65=G65,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I65" s="17">
         <v>73</v>
@@ -11793,13 +11965,17 @@
       </c>
       <c r="P65" s="16">
         <f t="shared" ref="P65:P66" si="39">IF(Q65&gt;R65,3,IF(Q65=R65,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q65" s="16"/>
-      <c r="R65" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q65" s="16">
+        <v>9</v>
+      </c>
+      <c r="R65" s="16">
+        <v>11</v>
+      </c>
       <c r="S65" s="16">
         <f t="shared" ref="S65:S66" si="40">IF(R65&gt;Q65,3,IF(Q65=R65,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T65" s="17">
         <v>90</v>
@@ -11819,13 +11995,17 @@
       </c>
       <c r="E66" s="16">
         <f t="shared" si="37"/>
-        <v>1</v>
-      </c>
-      <c r="F66" s="16"/>
-      <c r="G66" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F66" s="16">
+        <v>5</v>
+      </c>
+      <c r="G66" s="16">
+        <v>11</v>
+      </c>
       <c r="H66" s="16">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I66" s="17">
         <v>7</v>
@@ -11844,13 +12024,17 @@
       </c>
       <c r="P66" s="16">
         <f t="shared" si="39"/>
-        <v>1</v>
-      </c>
-      <c r="Q66" s="16"/>
-      <c r="R66" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q66" s="16">
+        <v>0</v>
+      </c>
+      <c r="R66" s="16">
+        <v>3</v>
+      </c>
       <c r="S66" s="16">
         <f t="shared" si="40"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T66" s="17">
         <v>50</v>
@@ -11870,13 +12054,17 @@
       </c>
       <c r="E67" s="16">
         <f>IF(F67&gt;G67,3,IF(F67=G67,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F67" s="16"/>
-      <c r="G67" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F67" s="16">
+        <v>8</v>
+      </c>
+      <c r="G67" s="16">
+        <v>0</v>
+      </c>
       <c r="H67" s="16">
         <f t="shared" si="38"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" s="17">
         <v>5</v>
@@ -11895,13 +12083,17 @@
       </c>
       <c r="P67" s="16">
         <f>IF(Q67&gt;R67,3,IF(Q67=R67,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q67" s="16"/>
-      <c r="R67" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q67" s="16">
+        <v>20</v>
+      </c>
+      <c r="R67" s="16">
+        <v>1</v>
+      </c>
       <c r="S67" s="16">
         <f>IF(R67&gt;Q67,3,IF(Q67=R67,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T67" s="17">
         <v>76</v>
@@ -11921,13 +12113,17 @@
       </c>
       <c r="E68" s="25">
         <f>IF(F68&gt;G68,3,IF(F68=G68,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
+        <v>0</v>
+      </c>
+      <c r="F68" s="20">
+        <v>2</v>
+      </c>
+      <c r="G68" s="20">
+        <v>23</v>
+      </c>
       <c r="H68" s="25">
         <f>IF(G68&gt;F68,3,IF(F68=G68,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I68" s="21">
         <v>52</v>
@@ -11946,13 +12142,17 @@
       </c>
       <c r="P68" s="25">
         <f>IF(Q68&gt;R68,3,IF(Q68=R68,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q68" s="20"/>
-      <c r="R68" s="20"/>
+        <v>0</v>
+      </c>
+      <c r="Q68" s="20">
+        <v>18</v>
+      </c>
+      <c r="R68" s="20">
+        <v>26</v>
+      </c>
       <c r="S68" s="25">
         <f t="shared" ref="S68:S70" si="41">IF(R68&gt;Q68,3,IF(Q68=R68,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T68" s="21">
         <v>12</v>
@@ -11974,13 +12174,17 @@
       </c>
       <c r="E69" s="15">
         <f t="shared" ref="E69:E73" si="42">IF(F69&gt;G69,3,IF(F69=G69,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F69" s="15"/>
-      <c r="G69" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="F69" s="15">
+        <v>27</v>
+      </c>
+      <c r="G69" s="15">
+        <v>35</v>
+      </c>
       <c r="H69" s="15">
         <f t="shared" ref="H69:H70" si="43">IF(G69&gt;F69,3,IF(F69=G69,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I69" s="19">
         <v>64</v>
@@ -12001,13 +12205,17 @@
       </c>
       <c r="P69" s="15">
         <f t="shared" ref="P69:P73" si="44">IF(Q69&gt;R69,3,IF(Q69=R69,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q69" s="15"/>
-      <c r="R69" s="15"/>
+        <v>0</v>
+      </c>
+      <c r="Q69" s="15">
+        <v>2</v>
+      </c>
+      <c r="R69" s="15">
+        <v>5</v>
+      </c>
       <c r="S69" s="15">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T69" s="19">
         <v>72</v>
@@ -12027,13 +12235,17 @@
       </c>
       <c r="E70" s="16">
         <f t="shared" si="42"/>
-        <v>1</v>
-      </c>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F70" s="16">
+        <v>35</v>
+      </c>
+      <c r="G70" s="16">
+        <v>0</v>
+      </c>
       <c r="H70" s="16">
         <f t="shared" si="43"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I70" s="17">
         <v>4</v>
@@ -12052,13 +12264,17 @@
       </c>
       <c r="P70" s="16">
         <f t="shared" si="44"/>
-        <v>1</v>
-      </c>
-      <c r="Q70" s="16"/>
-      <c r="R70" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q70" s="16">
+        <v>35</v>
+      </c>
+      <c r="R70" s="16">
+        <v>6</v>
+      </c>
       <c r="S70" s="16">
         <f t="shared" si="41"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T70" s="17">
         <v>54</v>
@@ -12077,13 +12293,17 @@
       </c>
       <c r="E71" s="16">
         <f t="shared" si="42"/>
-        <v>1</v>
-      </c>
-      <c r="F71" s="16"/>
-      <c r="G71" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F71" s="16">
+        <v>9</v>
+      </c>
+      <c r="G71" s="16">
+        <v>13</v>
+      </c>
       <c r="H71" s="16">
         <f>IF(G71&gt;F71,3,IF(F71=G71,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I71" s="17">
         <v>34</v>
@@ -12102,13 +12322,17 @@
       </c>
       <c r="P71" s="16">
         <f t="shared" si="44"/>
-        <v>1</v>
-      </c>
-      <c r="Q71" s="16"/>
-      <c r="R71" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q71" s="16">
+        <v>24</v>
+      </c>
+      <c r="R71" s="16">
+        <v>0</v>
+      </c>
       <c r="S71" s="16">
         <f>IF(R71&gt;Q71,3,IF(Q71=R71,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T71" s="17">
         <v>78</v>
@@ -12127,13 +12351,17 @@
       </c>
       <c r="E72" s="16">
         <f t="shared" si="42"/>
-        <v>1</v>
-      </c>
-      <c r="F72" s="16"/>
-      <c r="G72" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F72" s="16">
+        <v>25</v>
+      </c>
+      <c r="G72" s="16">
+        <v>0</v>
+      </c>
       <c r="H72" s="16">
         <f t="shared" ref="H72:H73" si="45">IF(G72&gt;F72,3,IF(F72=G72,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I72" s="17">
         <v>88</v>
@@ -12152,13 +12380,17 @@
       </c>
       <c r="P72" s="16">
         <f t="shared" si="44"/>
-        <v>1</v>
-      </c>
-      <c r="Q72" s="16"/>
-      <c r="R72" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q72" s="16">
+        <v>3</v>
+      </c>
+      <c r="R72" s="16">
+        <v>11</v>
+      </c>
       <c r="S72" s="16">
         <f t="shared" ref="S72:S73" si="46">IF(R72&gt;Q72,3,IF(Q72=R72,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T72" s="17">
         <v>19</v>
@@ -12177,13 +12409,17 @@
       </c>
       <c r="E73" s="16">
         <f t="shared" si="42"/>
-        <v>1</v>
-      </c>
-      <c r="F73" s="16"/>
-      <c r="G73" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="16">
+        <v>3</v>
+      </c>
+      <c r="G73" s="16">
+        <v>35</v>
+      </c>
       <c r="H73" s="16">
         <f t="shared" si="45"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I73" s="17">
         <v>65</v>
@@ -12202,13 +12438,17 @@
       </c>
       <c r="P73" s="16">
         <f t="shared" si="44"/>
-        <v>1</v>
-      </c>
-      <c r="Q73" s="16"/>
-      <c r="R73" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q73" s="16">
+        <v>5</v>
+      </c>
+      <c r="R73" s="16">
+        <v>0</v>
+      </c>
       <c r="S73" s="16">
         <f t="shared" si="46"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T73" s="17">
         <v>9</v>
@@ -12387,13 +12627,17 @@
       </c>
       <c r="E79" s="16">
         <f>IF(F79&gt;G79,3,IF(F79=G79,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F79" s="16"/>
-      <c r="G79" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F79" s="16">
+        <v>30</v>
+      </c>
+      <c r="G79" s="16">
+        <v>1</v>
+      </c>
       <c r="H79" s="16">
         <f>IF(G79&gt;F79,3,IF(F79=G79,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" s="17">
         <v>79</v>
@@ -12414,13 +12658,17 @@
       </c>
       <c r="P79" s="16">
         <f>IF(Q79&gt;R79,3,IF(Q79=R79,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q79" s="16"/>
-      <c r="R79" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q79" s="16">
+        <v>9</v>
+      </c>
+      <c r="R79" s="16">
+        <v>20</v>
+      </c>
       <c r="S79" s="16">
         <f>IF(R79&gt;Q79,3,IF(Q79=R79,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T79" s="17">
         <v>14</v>
@@ -12440,13 +12688,17 @@
       </c>
       <c r="E80" s="16">
         <f t="shared" ref="E80:E81" si="47">IF(F80&gt;G80,3,IF(F80=G80,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F80" s="16"/>
-      <c r="G80" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F80" s="16">
+        <v>6</v>
+      </c>
+      <c r="G80" s="16">
+        <v>0</v>
+      </c>
       <c r="H80" s="16">
         <f t="shared" ref="H80:H82" si="48">IF(G80&gt;F80,3,IF(F80=G80,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" s="17">
         <v>87</v>
@@ -12465,13 +12717,17 @@
       </c>
       <c r="P80" s="16">
         <f t="shared" ref="P80:P81" si="49">IF(Q80&gt;R80,3,IF(Q80=R80,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q80" s="16"/>
-      <c r="R80" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q80" s="16">
+        <v>20</v>
+      </c>
+      <c r="R80" s="16">
+        <v>25</v>
+      </c>
       <c r="S80" s="16">
         <f t="shared" ref="S80:S81" si="50">IF(R80&gt;Q80,3,IF(Q80=R80,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T80" s="17">
         <v>19</v>
@@ -12493,8 +12749,12 @@
         <f t="shared" si="47"/>
         <v>1</v>
       </c>
-      <c r="F81" s="16"/>
-      <c r="G81" s="16"/>
+      <c r="F81" s="16">
+        <v>15</v>
+      </c>
+      <c r="G81" s="16">
+        <v>15</v>
+      </c>
       <c r="H81" s="16">
         <f t="shared" si="48"/>
         <v>1</v>
@@ -12516,13 +12776,17 @@
       </c>
       <c r="P81" s="16">
         <f t="shared" si="49"/>
-        <v>1</v>
-      </c>
-      <c r="Q81" s="16"/>
-      <c r="R81" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q81" s="16">
+        <v>13</v>
+      </c>
+      <c r="R81" s="16">
+        <v>9</v>
+      </c>
       <c r="S81" s="16">
         <f t="shared" si="50"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T81" s="17">
         <v>78</v>
@@ -12542,13 +12806,17 @@
       </c>
       <c r="E82" s="16">
         <f>IF(F82&gt;G82,3,IF(F82=G82,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F82" s="16"/>
-      <c r="G82" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F82" s="16">
+        <v>35</v>
+      </c>
+      <c r="G82" s="16">
+        <v>26</v>
+      </c>
       <c r="H82" s="16">
         <f t="shared" si="48"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I82" s="17">
         <v>12</v>
@@ -12567,13 +12835,17 @@
       </c>
       <c r="P82" s="16">
         <f>IF(Q82&gt;R82,3,IF(Q82=R82,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q82" s="16"/>
-      <c r="R82" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q82" s="16">
+        <v>16</v>
+      </c>
+      <c r="R82" s="16">
+        <v>0</v>
+      </c>
       <c r="S82" s="16">
         <f>IF(R82&gt;Q82,3,IF(Q82=R82,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T82" s="17">
         <v>88</v>
@@ -12593,13 +12865,17 @@
       </c>
       <c r="E83" s="25">
         <f>IF(F83&gt;G83,3,IF(F83=G83,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F83" s="20"/>
-      <c r="G83" s="20"/>
+        <v>0</v>
+      </c>
+      <c r="F83" s="20">
+        <v>3</v>
+      </c>
+      <c r="G83" s="20">
+        <v>30</v>
+      </c>
       <c r="H83" s="25">
         <f>IF(G83&gt;F83,3,IF(F83=G83,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I83" s="21">
         <v>73</v>
@@ -12618,13 +12894,17 @@
       </c>
       <c r="P83" s="25">
         <f>IF(Q83&gt;R83,3,IF(Q83=R83,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q83" s="20"/>
-      <c r="R83" s="20"/>
+        <v>3</v>
+      </c>
+      <c r="Q83" s="20">
+        <v>21</v>
+      </c>
+      <c r="R83" s="20">
+        <v>12</v>
+      </c>
       <c r="S83" s="25">
         <f t="shared" ref="S83:S85" si="51">IF(R83&gt;Q83,3,IF(Q83=R83,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T83" s="21">
         <v>24</v>
@@ -12646,13 +12926,17 @@
       </c>
       <c r="E84" s="15">
         <f t="shared" ref="E84:E88" si="52">IF(F84&gt;G84,3,IF(F84=G84,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F84" s="15"/>
-      <c r="G84" s="15"/>
+        <v>3</v>
+      </c>
+      <c r="F84" s="15">
+        <v>22</v>
+      </c>
+      <c r="G84" s="15">
+        <v>16</v>
+      </c>
       <c r="H84" s="15">
         <f t="shared" ref="H84:H85" si="53">IF(G84&gt;F84,3,IF(F84=G84,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" s="19">
         <v>90</v>
@@ -12672,14 +12956,16 @@
         <v>72</v>
       </c>
       <c r="P84" s="15">
-        <f t="shared" ref="P84:P88" si="54">IF(Q84&gt;R84,3,IF(Q84=R84,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="Q84" s="15"/>
-      <c r="R84" s="15"/>
+        <v>3</v>
+      </c>
+      <c r="Q84" s="15">
+        <v>1</v>
+      </c>
+      <c r="R84" s="15">
+        <v>5</v>
+      </c>
       <c r="S84" s="15">
-        <f t="shared" si="51"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T84" s="19">
         <v>91</v>
@@ -12699,13 +12985,17 @@
       </c>
       <c r="E85" s="16">
         <f>IF(F85&gt;G85,3,IF(F85=G85,1,0))</f>
-        <v>1</v>
-      </c>
-      <c r="F85" s="16"/>
-      <c r="G85" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F85" s="16">
+        <v>18</v>
+      </c>
+      <c r="G85" s="16">
+        <v>20</v>
+      </c>
       <c r="H85" s="16">
         <f t="shared" si="53"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I85" s="17">
         <v>25</v>
@@ -12723,14 +13013,18 @@
         <v>54</v>
       </c>
       <c r="P85" s="16">
-        <f t="shared" si="54"/>
-        <v>1</v>
-      </c>
-      <c r="Q85" s="16"/>
-      <c r="R85" s="16"/>
+        <f t="shared" ref="P84:P88" si="54">IF(Q85&gt;R85,3,IF(Q85=R85,1,0))</f>
+        <v>0</v>
+      </c>
+      <c r="Q85" s="16">
+        <v>16</v>
+      </c>
+      <c r="R85" s="16">
+        <v>18</v>
+      </c>
       <c r="S85" s="16">
         <f t="shared" si="51"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T85" s="17">
         <v>81</v>
@@ -12750,13 +13044,17 @@
       </c>
       <c r="E86" s="16">
         <f t="shared" si="52"/>
-        <v>1</v>
-      </c>
-      <c r="F86" s="16"/>
-      <c r="G86" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F86" s="16">
+        <v>10</v>
+      </c>
+      <c r="G86" s="16">
+        <v>7</v>
+      </c>
       <c r="H86" s="16">
         <f>IF(G86&gt;F86,3,IF(F86=G86,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" s="17">
         <v>28</v>
@@ -12775,13 +13073,17 @@
       </c>
       <c r="P86" s="16">
         <f t="shared" si="54"/>
-        <v>1</v>
-      </c>
-      <c r="Q86" s="16"/>
-      <c r="R86" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q86" s="16">
+        <v>16</v>
+      </c>
+      <c r="R86" s="16">
+        <v>0</v>
+      </c>
       <c r="S86" s="16">
         <f>IF(R86&gt;Q86,3,IF(Q86=R86,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T86" s="17">
         <v>9</v>
@@ -12800,13 +13102,17 @@
       </c>
       <c r="E87" s="16">
         <f t="shared" si="52"/>
-        <v>1</v>
-      </c>
-      <c r="F87" s="16"/>
-      <c r="G87" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="F87" s="16">
+        <v>11</v>
+      </c>
+      <c r="G87" s="16">
+        <v>0</v>
+      </c>
       <c r="H87" s="16">
         <f t="shared" ref="H87:H88" si="55">IF(G87&gt;F87,3,IF(F87=G87,1,0))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I87" s="17">
         <v>76</v>
@@ -12825,13 +13131,17 @@
       </c>
       <c r="P87" s="16">
         <f t="shared" si="54"/>
-        <v>1</v>
-      </c>
-      <c r="Q87" s="16"/>
-      <c r="R87" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="Q87" s="16">
+        <v>11</v>
+      </c>
+      <c r="R87" s="16">
+        <v>23</v>
+      </c>
       <c r="S87" s="16">
         <f t="shared" ref="S87:S88" si="56">IF(R87&gt;Q87,3,IF(Q87=R87,1,0))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T87" s="17">
         <v>30</v>
@@ -12850,13 +13160,17 @@
       </c>
       <c r="E88" s="16">
         <f t="shared" si="52"/>
-        <v>1</v>
-      </c>
-      <c r="F88" s="16"/>
-      <c r="G88" s="16"/>
+        <v>0</v>
+      </c>
+      <c r="F88" s="16">
+        <v>20</v>
+      </c>
+      <c r="G88" s="16">
+        <v>30</v>
+      </c>
       <c r="H88" s="16">
         <f t="shared" si="55"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I88" s="17">
         <v>85</v>
@@ -12875,13 +13189,17 @@
       </c>
       <c r="P88" s="16">
         <f t="shared" si="54"/>
-        <v>1</v>
-      </c>
-      <c r="Q88" s="16"/>
-      <c r="R88" s="16"/>
+        <v>3</v>
+      </c>
+      <c r="Q88" s="16">
+        <v>21</v>
+      </c>
+      <c r="R88" s="16">
+        <v>6</v>
+      </c>
       <c r="S88" s="16">
         <f t="shared" si="56"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T88" s="17">
         <v>16</v>
@@ -13227,16 +13545,16 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="str">
-        <v>2c</v>
+        <v>2g</v>
       </c>
       <c r="B2">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D2">
-        <v>128</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -13244,55 +13562,55 @@
         <v>2g</v>
       </c>
       <c r="B3">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3">
-        <v>115</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
-        <v>2b</v>
+        <v>2e</v>
       </c>
       <c r="B4">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="C4">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
-        <v>2g</v>
+        <v>2c</v>
       </c>
       <c r="B5">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5">
-        <v>83</v>
+        <v>180</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
-        <v>2e</v>
+        <v>2b</v>
       </c>
       <c r="B6">
-        <v>19</v>
+        <v>73</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6">
-        <v>79</v>
+        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -13303,10 +13621,10 @@
         <v>58</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D7">
-        <v>83</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -13317,10 +13635,10 @@
         <v>30</v>
       </c>
       <c r="C8">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D8">
-        <v>66</v>
+        <v>124</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -13328,69 +13646,69 @@
         <v>2g</v>
       </c>
       <c r="B9">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C9">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D9">
-        <v>57</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" t="str">
-        <v>2g</v>
+        <v>2a</v>
       </c>
       <c r="B10">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="C10">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D10">
-        <v>42</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" t="str">
-        <v>2a</v>
+        <v>2c</v>
       </c>
       <c r="B11">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D11">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" t="str">
-        <v>2d</v>
+        <v>2g</v>
       </c>
       <c r="B12">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="C12">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>48</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" t="str">
-        <v>2c</v>
+        <v>2e</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C13">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
@@ -13401,52 +13719,52 @@
         <v>37</v>
       </c>
       <c r="C14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>26</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" t="str">
-        <v>2c</v>
+        <v>2f</v>
       </c>
       <c r="B15">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" t="str">
-        <v>2c</v>
+        <v>2d</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="str">
-        <v>2e</v>
+        <v>2a</v>
       </c>
       <c r="B17">
+        <v>50</v>
+      </c>
+      <c r="C17">
+        <v>10</v>
+      </c>
+      <c r="D17">
         <v>25</v>
-      </c>
-      <c r="C17">
-        <v>8</v>
-      </c>
-      <c r="D17">
-        <v>65</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -13457,10 +13775,10 @@
         <v>81</v>
       </c>
       <c r="C18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18">
-        <v>58</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -13468,225 +13786,225 @@
         <v>2e</v>
       </c>
       <c r="B19">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19">
-        <v>44</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="str">
-        <v>2d</v>
+        <v>2e</v>
       </c>
       <c r="B20">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="str">
-        <v>2e</v>
+        <v>2d</v>
       </c>
       <c r="B21">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D21">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="str">
-        <v>2e</v>
+        <v>2c</v>
       </c>
       <c r="B22">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D22">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="str">
-        <v>2d</v>
+        <v>2f</v>
       </c>
       <c r="B23">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>27</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="str">
-        <v>2b</v>
+        <v>2c</v>
       </c>
       <c r="B24">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D24">
-        <v>17</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="str">
-        <v>2e</v>
+        <v>2g</v>
       </c>
       <c r="B25">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="C25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D25">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="E25" s="12"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="str">
-        <v>2f</v>
+        <v>2d</v>
       </c>
       <c r="B26">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="C26">
         <v>6</v>
       </c>
       <c r="D26">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="str">
-        <v>2f</v>
+        <v>2e</v>
       </c>
       <c r="B27">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="C27">
         <v>6</v>
       </c>
       <c r="D27">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="str">
-        <v>2a</v>
+        <v>2c</v>
       </c>
       <c r="B28">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>6</v>
       </c>
       <c r="D28">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="str">
-        <v>2d</v>
+        <v>2e</v>
       </c>
       <c r="B29">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C29">
         <v>6</v>
       </c>
       <c r="D29">
-        <v>22</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="str">
-        <v>2b</v>
+        <v>2d</v>
       </c>
       <c r="B30">
-        <v>78</v>
+        <v>33</v>
       </c>
       <c r="C30">
         <v>6</v>
       </c>
       <c r="D30">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E30" s="12"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="str">
-        <v>2a</v>
+        <v>2f</v>
       </c>
       <c r="B31">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C31">
         <v>6</v>
       </c>
       <c r="D31">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="str">
-        <v>2f</v>
+        <v>2b</v>
       </c>
       <c r="B32">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>74</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="str">
-        <v>2f</v>
+        <v>2a</v>
       </c>
       <c r="B33">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="C33">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D33">
-        <v>64</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="str">
-        <v>2c</v>
+        <v>2a</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>54</v>
       </c>
       <c r="C34">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D34">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
@@ -13694,97 +14012,97 @@
         <v>2f</v>
       </c>
       <c r="B35">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C35">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="str">
-        <v>2f</v>
+        <v>2g</v>
       </c>
       <c r="B36">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="str">
-        <v>2a</v>
+        <v>2b</v>
       </c>
       <c r="B37">
-        <v>56</v>
+        <v>78</v>
       </c>
       <c r="C37">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D37">
-        <v>52</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="str">
-        <v>2g</v>
+        <v>2f</v>
       </c>
       <c r="B38">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38">
-        <v>8</v>
+        <v>71</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="str">
-        <v>2b</v>
+        <v>2c</v>
       </c>
       <c r="B39">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="str">
-        <v>2g</v>
+        <v>2f</v>
       </c>
       <c r="B40">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="str">
-        <v>2c</v>
+        <v>2b</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="C41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
